--- a/data/transactions/أذونات الإضافة لشهر 3.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7868058F-C819-45A2-ABE4-7FB72E40C1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3313370A-44D2-4BE8-96D1-1216B10DD512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2504,7 +2504,7 @@
   <cols>
     <col min="1" max="1" width="6.5703125" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="50.7109375" customWidth="1"/>
     <col min="4" max="4" width="8.140625" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" customWidth="1"/>

--- a/data/transactions/أذونات الإضافة لشهر 3.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12EBFF4-61F9-4F86-8517-FB16C727E2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F422FE17-76FC-4789-8D5A-C2A8B176F78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="774">
   <si>
     <t>بورسعيد لصناعة المعادن</t>
   </si>
@@ -1218,9 +1218,6 @@
     <t>زجاج سيكوريت 8 مم مقاس  47 سم ×51.6 سم</t>
   </si>
   <si>
-    <t>جريش الدوليه للصناعات الزجاجيه</t>
-  </si>
-  <si>
     <t>11201096</t>
   </si>
   <si>
@@ -1299,9 +1296,6 @@
     <t>لوح 1.25 مم مصنفر 1×2 SST</t>
   </si>
   <si>
-    <t>768.101.75</t>
-  </si>
-  <si>
     <t>بستله 1/2 كيلو لميع</t>
   </si>
   <si>
@@ -1857,9 +1851,6 @@
     <t>نبل 1 بوصه SST</t>
   </si>
   <si>
-    <t>الرضوان للتجاره</t>
-  </si>
-  <si>
     <t>10401016</t>
   </si>
   <si>
@@ -1878,9 +1869,6 @@
     <t>24/2/2026</t>
   </si>
   <si>
-    <t>15/1/2026</t>
-  </si>
-  <si>
     <t>10204010</t>
   </si>
   <si>
@@ -2199,9 +2187,6 @@
     <t>10/2/2026</t>
   </si>
   <si>
-    <t>اسكيو للهندسه</t>
-  </si>
-  <si>
     <t>29/3/2026</t>
   </si>
   <si>
@@ -2365,6 +2350,15 @@
   </si>
   <si>
     <t>ماران اثا</t>
+  </si>
+  <si>
+    <t>اسكيمو للهندسه</t>
+  </si>
+  <si>
+    <t>جريش الدوليه للصناعات الزجاج</t>
+  </si>
+  <si>
+    <t>الرضوان</t>
   </si>
 </sst>
 </file>
@@ -2437,7 +2431,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2459,6 +2453,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2595,7 +2595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2654,28 +2654,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2698,6 +2680,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3008,7 +3031,7 @@
     </row>
     <row r="3" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4114,7 +4137,7 @@
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L33" s="7">
         <v>6194</v>
@@ -4153,7 +4176,7 @@
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L34" s="7">
         <v>6194</v>
@@ -4192,7 +4215,7 @@
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L35" s="7">
         <v>6194</v>
@@ -4231,7 +4254,7 @@
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L36" s="7">
         <v>6194</v>
@@ -4270,7 +4293,7 @@
       </c>
       <c r="J37" s="6"/>
       <c r="K37" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L37" s="7">
         <v>6194</v>
@@ -4309,7 +4332,7 @@
       </c>
       <c r="J38" s="6"/>
       <c r="K38" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L38" s="7">
         <v>6194</v>
@@ -4348,7 +4371,7 @@
       </c>
       <c r="J39" s="6"/>
       <c r="K39" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L39" s="7">
         <v>6194</v>
@@ -4387,7 +4410,7 @@
       </c>
       <c r="J40" s="6"/>
       <c r="K40" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L40" s="7">
         <v>6194</v>
@@ -4426,7 +4449,7 @@
       </c>
       <c r="J41" s="6"/>
       <c r="K41" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L41" s="7">
         <v>6194</v>
@@ -6744,7 +6767,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>215</v>
@@ -6783,7 +6806,7 @@
         <v>96</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>217</v>
@@ -6822,7 +6845,7 @@
         <v>97</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>218</v>
@@ -6861,7 +6884,7 @@
         <v>98</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>219</v>
@@ -6900,7 +6923,7 @@
         <v>99</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>220</v>
@@ -6939,7 +6962,7 @@
         <v>100</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>221</v>
@@ -6978,7 +7001,7 @@
         <v>101</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>222</v>
@@ -7017,7 +7040,7 @@
         <v>102</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>223</v>
@@ -7056,7 +7079,7 @@
         <v>103</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>224</v>
@@ -7095,7 +7118,7 @@
         <v>104</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>225</v>
@@ -7134,7 +7157,7 @@
         <v>105</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>247</v>
@@ -7173,7 +7196,7 @@
         <v>106</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>226</v>
@@ -7212,7 +7235,7 @@
         <v>107</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>227</v>
@@ -7251,7 +7274,7 @@
         <v>108</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>228</v>
@@ -7290,7 +7313,7 @@
         <v>109</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>229</v>
@@ -7329,7 +7352,7 @@
         <v>110</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>230</v>
@@ -7368,7 +7391,7 @@
         <v>111</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>231</v>
@@ -7407,7 +7430,7 @@
         <v>112</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>232</v>
@@ -7446,7 +7469,7 @@
         <v>113</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>233</v>
@@ -7485,7 +7508,7 @@
         <v>114</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>234</v>
@@ -7524,7 +7547,7 @@
         <v>115</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>235</v>
@@ -7563,7 +7586,7 @@
         <v>116</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>236</v>
@@ -7602,7 +7625,7 @@
         <v>117</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>237</v>
@@ -7641,7 +7664,7 @@
         <v>118</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>238</v>
@@ -7680,7 +7703,7 @@
         <v>119</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>239</v>
@@ -7719,7 +7742,7 @@
         <v>120</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>240</v>
@@ -7758,7 +7781,7 @@
         <v>121</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>241</v>
@@ -7797,7 +7820,7 @@
         <v>122</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>242</v>
@@ -7836,7 +7859,7 @@
         <v>123</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>243</v>
@@ -7875,7 +7898,7 @@
         <v>124</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>244</v>
@@ -7914,7 +7937,7 @@
         <v>125</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>245</v>
@@ -7953,7 +7976,7 @@
         <v>126</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>246</v>
@@ -7992,7 +8015,7 @@
         <v>127</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>248</v>
@@ -8031,7 +8054,7 @@
         <v>128</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>249</v>
@@ -8070,7 +8093,7 @@
         <v>129</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>250</v>
@@ -8109,7 +8132,7 @@
         <v>130</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>251</v>
@@ -8148,7 +8171,7 @@
         <v>131</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>252</v>
@@ -8187,7 +8210,7 @@
         <v>132</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>253</v>
@@ -8226,7 +8249,7 @@
         <v>133</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>254</v>
@@ -8265,7 +8288,7 @@
         <v>134</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>255</v>
@@ -8304,7 +8327,7 @@
         <v>135</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>256</v>
@@ -8345,7 +8368,7 @@
         <v>136</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C142" s="7" t="s">
         <v>257</v>
@@ -8384,7 +8407,7 @@
         <v>137</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C143" s="7" t="s">
         <v>250</v>
@@ -8682,7 +8705,7 @@
       </c>
       <c r="J150" s="6"/>
       <c r="K150" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L150" s="7">
         <v>6211</v>
@@ -8721,7 +8744,7 @@
       </c>
       <c r="J151" s="6"/>
       <c r="K151" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L151" s="7">
         <v>6211</v>
@@ -8760,7 +8783,7 @@
       </c>
       <c r="J152" s="6"/>
       <c r="K152" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L152" s="7">
         <v>6211</v>
@@ -8799,7 +8822,7 @@
       </c>
       <c r="J153" s="6"/>
       <c r="K153" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L153" s="7">
         <v>6211</v>
@@ -8838,7 +8861,7 @@
       </c>
       <c r="J154" s="6"/>
       <c r="K154" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L154" s="7">
         <v>6211</v>
@@ -8877,7 +8900,7 @@
       </c>
       <c r="J155" s="6"/>
       <c r="K155" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L155" s="7">
         <v>6211</v>
@@ -8916,7 +8939,7 @@
       </c>
       <c r="J156" s="6"/>
       <c r="K156" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L156" s="7">
         <v>6211</v>
@@ -8955,7 +8978,7 @@
       </c>
       <c r="J157" s="6"/>
       <c r="K157" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L157" s="7">
         <v>6211</v>
@@ -8994,7 +9017,7 @@
       </c>
       <c r="J158" s="6"/>
       <c r="K158" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L158" s="7">
         <v>6211</v>
@@ -9033,7 +9056,7 @@
       </c>
       <c r="J159" s="6"/>
       <c r="K159" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L159" s="7">
         <v>6211</v>
@@ -9072,7 +9095,7 @@
       </c>
       <c r="J160" s="6"/>
       <c r="K160" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L160" s="7">
         <v>6212</v>
@@ -9111,7 +9134,7 @@
       </c>
       <c r="J161" s="6"/>
       <c r="K161" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L161" s="7">
         <v>6213</v>
@@ -9150,7 +9173,7 @@
       </c>
       <c r="J162" s="6"/>
       <c r="K162" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L162" s="7">
         <v>6213</v>
@@ -9705,7 +9728,7 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="177" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="18">
         <v>171</v>
       </c>
@@ -9721,14 +9744,14 @@
       <c r="E177" s="21">
         <v>173</v>
       </c>
-      <c r="F177" s="22">
+      <c r="F177" s="33">
         <v>1443407.87</v>
       </c>
-      <c r="G177" s="23"/>
+      <c r="G177" s="34"/>
       <c r="H177" s="21">
         <v>59798</v>
       </c>
-      <c r="I177" s="24">
+      <c r="I177" s="22">
         <v>46237</v>
       </c>
       <c r="J177" s="21"/>
@@ -9738,11 +9761,11 @@
       <c r="L177" s="20">
         <v>6217</v>
       </c>
-      <c r="M177" s="24">
+      <c r="M177" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="178" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="18">
         <v>172</v>
       </c>
@@ -9758,12 +9781,12 @@
       <c r="E178" s="21">
         <v>247</v>
       </c>
-      <c r="F178" s="26"/>
-      <c r="G178" s="27"/>
+      <c r="F178" s="35"/>
+      <c r="G178" s="36"/>
       <c r="H178" s="21">
         <v>59798</v>
       </c>
-      <c r="I178" s="24">
+      <c r="I178" s="22">
         <v>46237</v>
       </c>
       <c r="J178" s="21"/>
@@ -9773,11 +9796,11 @@
       <c r="L178" s="20">
         <v>6217</v>
       </c>
-      <c r="M178" s="24">
+      <c r="M178" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="179" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="18">
         <v>173</v>
       </c>
@@ -9793,12 +9816,12 @@
       <c r="E179" s="21">
         <v>82</v>
       </c>
-      <c r="F179" s="26"/>
-      <c r="G179" s="27"/>
+      <c r="F179" s="35"/>
+      <c r="G179" s="36"/>
       <c r="H179" s="21">
         <v>59798</v>
       </c>
-      <c r="I179" s="24">
+      <c r="I179" s="22">
         <v>46237</v>
       </c>
       <c r="J179" s="21"/>
@@ -9808,11 +9831,11 @@
       <c r="L179" s="20">
         <v>6217</v>
       </c>
-      <c r="M179" s="24">
+      <c r="M179" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="180" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="18">
         <v>174</v>
       </c>
@@ -9828,12 +9851,12 @@
       <c r="E180" s="21">
         <v>125</v>
       </c>
-      <c r="F180" s="26"/>
-      <c r="G180" s="27"/>
+      <c r="F180" s="35"/>
+      <c r="G180" s="36"/>
       <c r="H180" s="21">
         <v>59798</v>
       </c>
-      <c r="I180" s="24">
+      <c r="I180" s="22">
         <v>46237</v>
       </c>
       <c r="J180" s="21"/>
@@ -9843,11 +9866,11 @@
       <c r="L180" s="20">
         <v>6217</v>
       </c>
-      <c r="M180" s="24">
+      <c r="M180" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="181" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="18">
         <v>175</v>
       </c>
@@ -9863,12 +9886,12 @@
       <c r="E181" s="21">
         <v>41</v>
       </c>
-      <c r="F181" s="26"/>
-      <c r="G181" s="27"/>
+      <c r="F181" s="35"/>
+      <c r="G181" s="36"/>
       <c r="H181" s="21">
         <v>59798</v>
       </c>
-      <c r="I181" s="24">
+      <c r="I181" s="22">
         <v>46237</v>
       </c>
       <c r="J181" s="21"/>
@@ -9878,11 +9901,11 @@
       <c r="L181" s="20">
         <v>6217</v>
       </c>
-      <c r="M181" s="24">
+      <c r="M181" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="182" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="18">
         <v>176</v>
       </c>
@@ -9898,12 +9921,12 @@
       <c r="E182" s="21">
         <v>29</v>
       </c>
-      <c r="F182" s="26"/>
-      <c r="G182" s="27"/>
+      <c r="F182" s="35"/>
+      <c r="G182" s="36"/>
       <c r="H182" s="21">
         <v>59798</v>
       </c>
-      <c r="I182" s="24">
+      <c r="I182" s="22">
         <v>46237</v>
       </c>
       <c r="J182" s="21"/>
@@ -9913,11 +9936,11 @@
       <c r="L182" s="20">
         <v>6217</v>
       </c>
-      <c r="M182" s="24">
+      <c r="M182" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="183" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="18">
         <v>177</v>
       </c>
@@ -9933,12 +9956,12 @@
       <c r="E183" s="21">
         <v>118</v>
       </c>
-      <c r="F183" s="26"/>
-      <c r="G183" s="27"/>
+      <c r="F183" s="35"/>
+      <c r="G183" s="36"/>
       <c r="H183" s="21">
         <v>59798</v>
       </c>
-      <c r="I183" s="24">
+      <c r="I183" s="22">
         <v>46237</v>
       </c>
       <c r="J183" s="21"/>
@@ -9948,11 +9971,11 @@
       <c r="L183" s="20">
         <v>6217</v>
       </c>
-      <c r="M183" s="24">
+      <c r="M183" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="184" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="18">
         <v>178</v>
       </c>
@@ -9968,12 +9991,12 @@
       <c r="E184" s="21">
         <v>44</v>
       </c>
-      <c r="F184" s="28"/>
-      <c r="G184" s="29"/>
+      <c r="F184" s="37"/>
+      <c r="G184" s="38"/>
       <c r="H184" s="21">
         <v>59798</v>
       </c>
-      <c r="I184" s="24">
+      <c r="I184" s="22">
         <v>46237</v>
       </c>
       <c r="J184" s="21"/>
@@ -9983,7 +10006,7 @@
       <c r="L184" s="20">
         <v>6217</v>
       </c>
-      <c r="M184" s="24">
+      <c r="M184" s="22">
         <v>46329</v>
       </c>
     </row>
@@ -10572,7 +10595,7 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="200" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="18">
         <v>194</v>
       </c>
@@ -10583,19 +10606,22 @@
         <v>368</v>
       </c>
       <c r="D200" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E200" s="21">
-        <v>29</v>
-      </c>
-      <c r="F200" s="22" t="s">
-        <v>420</v>
-      </c>
-      <c r="G200" s="23"/>
+        <v>695.99400000000003</v>
+      </c>
+      <c r="F200" s="39">
+        <v>142.98245600000001</v>
+      </c>
+      <c r="G200" s="40">
+        <f>F200*E200</f>
+        <v>99514.931481264008</v>
+      </c>
       <c r="H200" s="21">
         <v>59753</v>
       </c>
-      <c r="I200" s="24">
+      <c r="I200" s="22">
         <v>46328</v>
       </c>
       <c r="J200" s="21"/>
@@ -10605,11 +10631,11 @@
       <c r="L200" s="20">
         <v>6223</v>
       </c>
-      <c r="M200" s="24">
+      <c r="M200" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="201" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="18">
         <v>195</v>
       </c>
@@ -10620,17 +10646,22 @@
         <v>369</v>
       </c>
       <c r="D201" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E201" s="21">
-        <v>49</v>
-      </c>
-      <c r="F201" s="26"/>
-      <c r="G201" s="27"/>
+        <v>1175.991</v>
+      </c>
+      <c r="F201" s="39">
+        <v>142.98245600000001</v>
+      </c>
+      <c r="G201" s="40">
+        <f t="shared" ref="G201:G203" si="0">F201*E201</f>
+        <v>168146.08141389603</v>
+      </c>
       <c r="H201" s="21">
         <v>59753</v>
       </c>
-      <c r="I201" s="24">
+      <c r="I201" s="22">
         <v>46328</v>
       </c>
       <c r="J201" s="21"/>
@@ -10640,11 +10671,11 @@
       <c r="L201" s="20">
         <v>6223</v>
       </c>
-      <c r="M201" s="24">
+      <c r="M201" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="202" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="18">
         <v>196</v>
       </c>
@@ -10655,17 +10686,22 @@
         <v>370</v>
       </c>
       <c r="D202" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E202" s="21">
-        <v>45</v>
-      </c>
-      <c r="F202" s="26"/>
-      <c r="G202" s="27"/>
+        <v>1800</v>
+      </c>
+      <c r="F202" s="39">
+        <v>142.98245600000001</v>
+      </c>
+      <c r="G202" s="40">
+        <f t="shared" si="0"/>
+        <v>257368.42080000002</v>
+      </c>
       <c r="H202" s="21">
         <v>59753</v>
       </c>
-      <c r="I202" s="24">
+      <c r="I202" s="22">
         <v>46328</v>
       </c>
       <c r="J202" s="21"/>
@@ -10675,11 +10711,11 @@
       <c r="L202" s="20">
         <v>6223</v>
       </c>
-      <c r="M202" s="24">
+      <c r="M202" s="22">
         <v>46329</v>
       </c>
     </row>
-    <row r="203" spans="1:13" s="25" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="18">
         <v>197</v>
       </c>
@@ -10690,17 +10726,22 @@
         <v>371</v>
       </c>
       <c r="D203" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E203" s="21">
-        <v>125</v>
-      </c>
-      <c r="F203" s="28"/>
-      <c r="G203" s="29"/>
+        <v>2000</v>
+      </c>
+      <c r="F203" s="39">
+        <v>142.98245600000001</v>
+      </c>
+      <c r="G203" s="40">
+        <f t="shared" si="0"/>
+        <v>285964.91200000001</v>
+      </c>
       <c r="H203" s="21">
         <v>59753</v>
       </c>
-      <c r="I203" s="24">
+      <c r="I203" s="22">
         <v>46328</v>
       </c>
       <c r="J203" s="21"/>
@@ -10710,7 +10751,7 @@
       <c r="L203" s="20">
         <v>6223</v>
       </c>
-      <c r="M203" s="24">
+      <c r="M203" s="22">
         <v>46329</v>
       </c>
     </row>
@@ -10758,7 +10799,7 @@
         <v>199</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C205" s="14" t="s">
         <v>376</v>
@@ -10783,7 +10824,7 @@
       </c>
       <c r="J205" s="6"/>
       <c r="K205" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L205" s="7">
         <v>6226</v>
@@ -10797,7 +10838,7 @@
         <v>200</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C206" s="7" t="s">
         <v>377</v>
@@ -10822,7 +10863,7 @@
       </c>
       <c r="J206" s="6"/>
       <c r="K206" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L206" s="7">
         <v>6226</v>
@@ -10836,7 +10877,7 @@
         <v>201</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C207" s="7" t="s">
         <v>378</v>
@@ -10861,7 +10902,7 @@
       </c>
       <c r="J207" s="6"/>
       <c r="K207" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L207" s="7">
         <v>6226</v>
@@ -10875,7 +10916,7 @@
         <v>202</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C208" s="7" t="s">
         <v>379</v>
@@ -10900,7 +10941,7 @@
       </c>
       <c r="J208" s="6"/>
       <c r="K208" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L208" s="7">
         <v>6226</v>
@@ -10914,7 +10955,7 @@
         <v>203</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C209" s="7" t="s">
         <v>380</v>
@@ -10939,7 +10980,7 @@
       </c>
       <c r="J209" s="6"/>
       <c r="K209" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L209" s="7">
         <v>6226</v>
@@ -10953,7 +10994,7 @@
         <v>204</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C210" s="7" t="s">
         <v>381</v>
@@ -10978,7 +11019,7 @@
       </c>
       <c r="J210" s="6"/>
       <c r="K210" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L210" s="7">
         <v>6226</v>
@@ -10992,7 +11033,7 @@
         <v>205</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C211" s="7" t="s">
         <v>382</v>
@@ -11017,7 +11058,7 @@
       </c>
       <c r="J211" s="6"/>
       <c r="K211" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L211" s="7">
         <v>6226</v>
@@ -11031,7 +11072,7 @@
         <v>206</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C212" s="7" t="s">
         <v>383</v>
@@ -11056,7 +11097,7 @@
       </c>
       <c r="J212" s="6"/>
       <c r="K212" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L212" s="7">
         <v>6226</v>
@@ -11070,7 +11111,7 @@
         <v>207</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C213" s="7" t="s">
         <v>384</v>
@@ -11095,7 +11136,7 @@
       </c>
       <c r="J213" s="6"/>
       <c r="K213" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L213" s="7">
         <v>6226</v>
@@ -11109,7 +11150,7 @@
         <v>208</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C214" s="7" t="s">
         <v>385</v>
@@ -11134,7 +11175,7 @@
       </c>
       <c r="J214" s="6"/>
       <c r="K214" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L214" s="7">
         <v>6226</v>
@@ -11148,7 +11189,7 @@
         <v>209</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C215" s="7" t="s">
         <v>386</v>
@@ -11173,7 +11214,7 @@
       </c>
       <c r="J215" s="6"/>
       <c r="K215" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L215" s="7">
         <v>6226</v>
@@ -11187,7 +11228,7 @@
         <v>210</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C216" s="7" t="s">
         <v>387</v>
@@ -11212,7 +11253,7 @@
       </c>
       <c r="J216" s="6"/>
       <c r="K216" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L216" s="7">
         <v>6226</v>
@@ -11226,7 +11267,7 @@
         <v>211</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C217" s="7" t="s">
         <v>388</v>
@@ -11251,7 +11292,7 @@
       </c>
       <c r="J217" s="6"/>
       <c r="K217" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L217" s="7">
         <v>6226</v>
@@ -11265,7 +11306,7 @@
         <v>212</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C218" s="7" t="s">
         <v>389</v>
@@ -11290,7 +11331,7 @@
       </c>
       <c r="J218" s="6"/>
       <c r="K218" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L218" s="7">
         <v>6227</v>
@@ -11304,7 +11345,7 @@
         <v>213</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C219" s="7" t="s">
         <v>390</v>
@@ -11329,7 +11370,7 @@
       </c>
       <c r="J219" s="6"/>
       <c r="K219" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L219" s="7">
         <v>6227</v>
@@ -11343,7 +11384,7 @@
         <v>214</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C220" s="7" t="s">
         <v>391</v>
@@ -11368,7 +11409,7 @@
       </c>
       <c r="J220" s="6"/>
       <c r="K220" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L220" s="7">
         <v>6227</v>
@@ -11382,7 +11423,7 @@
         <v>215</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C221" s="7" t="s">
         <v>392</v>
@@ -11407,7 +11448,7 @@
       </c>
       <c r="J221" s="6"/>
       <c r="K221" s="7" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="L221" s="7">
         <v>6227</v>
@@ -11424,7 +11465,7 @@
         <v>208</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D222" s="7" t="s">
         <v>17</v>
@@ -11442,7 +11483,7 @@
         <v>1476</v>
       </c>
       <c r="I222" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J222" s="6"/>
       <c r="K222" s="7" t="s">
@@ -11463,7 +11504,7 @@
         <v>209</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D223" s="7" t="s">
         <v>17</v>
@@ -11481,7 +11522,7 @@
         <v>1476</v>
       </c>
       <c r="I223" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J223" s="6"/>
       <c r="K223" s="7" t="s">
@@ -11499,13 +11540,13 @@
         <v>218</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C224" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D224" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="D224" s="7" t="s">
-        <v>415</v>
       </c>
       <c r="E224" s="6">
         <v>5.5</v>
@@ -11520,11 +11561,11 @@
         <v>783</v>
       </c>
       <c r="I224" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J224" s="6"/>
       <c r="K224" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L224" s="7">
         <v>6229</v>
@@ -11533,83 +11574,83 @@
         <v>46359</v>
       </c>
     </row>
-    <row r="225" spans="1:13" s="37" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A225" s="30">
+    <row r="225" spans="1:13" s="31" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A225" s="24">
         <v>219</v>
       </c>
-      <c r="B225" s="31" t="s">
+      <c r="B225" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C225" s="32" t="s">
-        <v>418</v>
-      </c>
-      <c r="D225" s="32" t="s">
+      <c r="C225" s="26" t="s">
+        <v>417</v>
+      </c>
+      <c r="D225" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="E225" s="33">
+      <c r="E225" s="27">
         <v>400</v>
       </c>
-      <c r="F225" s="34">
+      <c r="F225" s="28">
         <v>129.15163999999999</v>
       </c>
-      <c r="G225" s="35">
+      <c r="G225" s="29">
         <f>F225*E225</f>
         <v>51660.655999999995</v>
       </c>
-      <c r="H225" s="33">
+      <c r="H225" s="27">
         <v>699</v>
       </c>
-      <c r="I225" s="36" t="s">
-        <v>413</v>
-      </c>
-      <c r="J225" s="33"/>
-      <c r="K225" s="32" t="s">
+      <c r="I225" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="J225" s="27"/>
+      <c r="K225" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="L225" s="32">
+      <c r="L225" s="26">
         <v>6230</v>
       </c>
-      <c r="M225" s="36">
+      <c r="M225" s="30">
         <v>46359</v>
       </c>
     </row>
-    <row r="226" spans="1:13" s="37" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A226" s="30">
+    <row r="226" spans="1:13" s="31" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A226" s="24">
         <v>220</v>
       </c>
-      <c r="B226" s="31" t="s">
+      <c r="B226" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C226" s="32" t="s">
-        <v>419</v>
-      </c>
-      <c r="D226" s="32" t="s">
+      <c r="C226" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="D226" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="E226" s="33">
+      <c r="E226" s="27">
         <v>200</v>
       </c>
-      <c r="F226" s="38">
+      <c r="F226" s="32">
         <v>129.15163999999999</v>
       </c>
-      <c r="G226" s="35">
+      <c r="G226" s="29">
         <f>F226*E226</f>
         <v>25830.327999999998</v>
       </c>
-      <c r="H226" s="33">
+      <c r="H226" s="27">
         <v>699</v>
       </c>
-      <c r="I226" s="36" t="s">
-        <v>413</v>
-      </c>
-      <c r="J226" s="33"/>
-      <c r="K226" s="32" t="s">
+      <c r="I226" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="J226" s="27"/>
+      <c r="K226" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="L226" s="32">
+      <c r="L226" s="26">
         <v>6230</v>
       </c>
-      <c r="M226" s="36">
+      <c r="M226" s="30">
         <v>46359</v>
       </c>
     </row>
@@ -11618,10 +11659,10 @@
         <v>221</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D227" s="7" t="s">
         <v>17</v>
@@ -11639,7 +11680,7 @@
         <v>13750</v>
       </c>
       <c r="I227" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J227" s="6"/>
       <c r="K227" s="7" t="s">
@@ -11657,10 +11698,10 @@
         <v>222</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D228" s="7" t="s">
         <v>17</v>
@@ -11678,7 +11719,7 @@
         <v>13750</v>
       </c>
       <c r="I228" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J228" s="6"/>
       <c r="K228" s="7" t="s">
@@ -11696,10 +11737,10 @@
         <v>223</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D229" s="7" t="s">
         <v>17</v>
@@ -11717,7 +11758,7 @@
         <v>13750</v>
       </c>
       <c r="I229" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J229" s="6"/>
       <c r="K229" s="7" t="s">
@@ -11735,10 +11776,10 @@
         <v>224</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D230" s="7" t="s">
         <v>17</v>
@@ -11756,11 +11797,11 @@
         <v>34</v>
       </c>
       <c r="I230" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J230" s="6"/>
       <c r="K230" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L230" s="7">
         <v>6232</v>
@@ -11774,10 +11815,10 @@
         <v>225</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D231" s="7" t="s">
         <v>75</v>
@@ -11795,11 +11836,11 @@
         <v>34</v>
       </c>
       <c r="I231" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J231" s="6"/>
       <c r="K231" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L231" s="7">
         <v>6232</v>
@@ -11813,10 +11854,10 @@
         <v>226</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D232" s="7" t="s">
         <v>17</v>
@@ -11834,11 +11875,11 @@
         <v>34</v>
       </c>
       <c r="I232" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J232" s="6"/>
       <c r="K232" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L232" s="7">
         <v>6232</v>
@@ -11852,10 +11893,10 @@
         <v>227</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D233" s="7" t="s">
         <v>75</v>
@@ -11873,11 +11914,11 @@
         <v>34</v>
       </c>
       <c r="I233" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J233" s="6"/>
       <c r="K233" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L233" s="7">
         <v>6232</v>
@@ -11891,10 +11932,10 @@
         <v>228</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D234" s="7" t="s">
         <v>17</v>
@@ -11912,11 +11953,11 @@
         <v>34</v>
       </c>
       <c r="I234" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J234" s="6"/>
       <c r="K234" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L234" s="7">
         <v>6232</v>
@@ -11930,10 +11971,10 @@
         <v>229</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D235" s="7" t="s">
         <v>17</v>
@@ -11951,11 +11992,11 @@
         <v>34</v>
       </c>
       <c r="I235" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J235" s="6"/>
       <c r="K235" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L235" s="7">
         <v>6232</v>
@@ -11969,10 +12010,10 @@
         <v>230</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D236" s="7" t="s">
         <v>17</v>
@@ -11990,11 +12031,11 @@
         <v>34</v>
       </c>
       <c r="I236" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J236" s="6"/>
       <c r="K236" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L236" s="7">
         <v>6232</v>
@@ -12008,10 +12049,10 @@
         <v>231</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D237" s="7" t="s">
         <v>17</v>
@@ -12029,11 +12070,11 @@
         <v>34</v>
       </c>
       <c r="I237" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J237" s="6"/>
       <c r="K237" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L237" s="7">
         <v>6232</v>
@@ -12047,10 +12088,10 @@
         <v>232</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D238" s="7" t="s">
         <v>17</v>
@@ -12068,11 +12109,11 @@
         <v>34</v>
       </c>
       <c r="I238" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J238" s="6"/>
       <c r="K238" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L238" s="7">
         <v>6232</v>
@@ -12086,10 +12127,10 @@
         <v>233</v>
       </c>
       <c r="B239" s="11" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D239" s="7" t="s">
         <v>17</v>
@@ -12107,11 +12148,11 @@
         <v>34</v>
       </c>
       <c r="I239" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J239" s="6"/>
       <c r="K239" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L239" s="7">
         <v>6232</v>
@@ -12125,10 +12166,10 @@
         <v>234</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D240" s="7" t="s">
         <v>17</v>
@@ -12146,11 +12187,11 @@
         <v>35</v>
       </c>
       <c r="I240" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J240" s="6"/>
       <c r="K240" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L240" s="7">
         <v>6233</v>
@@ -12164,10 +12205,10 @@
         <v>235</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D241" s="7" t="s">
         <v>17</v>
@@ -12185,11 +12226,11 @@
         <v>36</v>
       </c>
       <c r="I241" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J241" s="6"/>
       <c r="K241" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L241" s="7">
         <v>6234</v>
@@ -12206,7 +12247,7 @@
         <v>92</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D242" s="7" t="s">
         <v>17</v>
@@ -12224,11 +12265,11 @@
         <v>36</v>
       </c>
       <c r="I242" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J242" s="6"/>
       <c r="K242" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L242" s="7">
         <v>6234</v>
@@ -12242,10 +12283,10 @@
         <v>237</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D243" s="7" t="s">
         <v>17</v>
@@ -12263,11 +12304,11 @@
         <v>36</v>
       </c>
       <c r="I243" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J243" s="6"/>
       <c r="K243" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L243" s="7">
         <v>6234</v>
@@ -12281,10 +12322,10 @@
         <v>238</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D244" s="7" t="s">
         <v>17</v>
@@ -12302,11 +12343,11 @@
         <v>36</v>
       </c>
       <c r="I244" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J244" s="6"/>
       <c r="K244" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L244" s="7">
         <v>6234</v>
@@ -12320,10 +12361,10 @@
         <v>239</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D245" s="7" t="s">
         <v>17</v>
@@ -12341,7 +12382,7 @@
         <v>121</v>
       </c>
       <c r="I245" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J245" s="6"/>
       <c r="K245" s="7" t="s">
@@ -12362,7 +12403,7 @@
         <v>298</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D246" s="7" t="s">
         <v>17</v>
@@ -12380,7 +12421,7 @@
         <v>339</v>
       </c>
       <c r="I246" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J246" s="6"/>
       <c r="K246" s="7" t="s">
@@ -12401,7 +12442,7 @@
         <v>299</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D247" s="7" t="s">
         <v>17</v>
@@ -12419,7 +12460,7 @@
         <v>339</v>
       </c>
       <c r="I247" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J247" s="6"/>
       <c r="K247" s="7" t="s">
@@ -12437,10 +12478,10 @@
         <v>242</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D248" s="7" t="s">
         <v>17</v>
@@ -12458,7 +12499,7 @@
         <v>5166</v>
       </c>
       <c r="I248" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J248" s="6"/>
       <c r="K248" s="7" t="s">
@@ -12476,10 +12517,10 @@
         <v>243</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D249" s="7" t="s">
         <v>17</v>
@@ -12497,7 +12538,7 @@
         <v>5166</v>
       </c>
       <c r="I249" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J249" s="6"/>
       <c r="K249" s="7" t="s">
@@ -12515,10 +12556,10 @@
         <v>244</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D250" s="7" t="s">
         <v>17</v>
@@ -12536,7 +12577,7 @@
         <v>5166</v>
       </c>
       <c r="I250" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J250" s="6"/>
       <c r="K250" s="7" t="s">
@@ -12549,277 +12590,277 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="251" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A251" s="1">
+    <row r="251" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A251" s="41">
         <v>245</v>
       </c>
-      <c r="B251" s="9" t="s">
+      <c r="B251" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="C251" s="43" t="s">
+        <v>466</v>
+      </c>
+      <c r="D251" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E251" s="44">
+        <v>100</v>
+      </c>
+      <c r="F251" s="43">
+        <v>204.75</v>
+      </c>
+      <c r="G251" s="43">
+        <v>20475</v>
+      </c>
+      <c r="H251" s="44">
+        <v>83</v>
+      </c>
+      <c r="I251" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="J251" s="44"/>
+      <c r="K251" s="43" t="s">
+        <v>770</v>
+      </c>
+      <c r="L251" s="43">
+        <v>6238</v>
+      </c>
+      <c r="M251" s="45">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A252" s="41">
+        <v>246</v>
+      </c>
+      <c r="B252" s="42" t="s">
+        <v>473</v>
+      </c>
+      <c r="C252" s="43" t="s">
+        <v>467</v>
+      </c>
+      <c r="D252" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E252" s="44">
+        <v>2</v>
+      </c>
+      <c r="F252" s="43">
+        <v>526.5</v>
+      </c>
+      <c r="G252" s="43">
+        <v>1053</v>
+      </c>
+      <c r="H252" s="44">
+        <v>83</v>
+      </c>
+      <c r="I252" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="J252" s="44"/>
+      <c r="K252" s="43" t="s">
+        <v>770</v>
+      </c>
+      <c r="L252" s="43">
+        <v>6238</v>
+      </c>
+      <c r="M252" s="45">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A253" s="41">
+        <v>247</v>
+      </c>
+      <c r="B253" s="42" t="s">
         <v>474</v>
       </c>
-      <c r="C251" s="7" t="s">
+      <c r="C253" s="43" t="s">
         <v>468</v>
       </c>
-      <c r="D251" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E251" s="6">
-        <v>100</v>
-      </c>
-      <c r="F251" s="7">
-        <v>204.75</v>
-      </c>
-      <c r="G251" s="7">
-        <v>20475</v>
-      </c>
-      <c r="H251" s="6">
+      <c r="D253" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E253" s="44">
+        <v>25</v>
+      </c>
+      <c r="F253" s="43">
+        <v>58.5</v>
+      </c>
+      <c r="G253" s="43">
+        <v>1462.5</v>
+      </c>
+      <c r="H253" s="44">
         <v>83</v>
       </c>
-      <c r="I251" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="J251" s="6"/>
-      <c r="K251" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="L251" s="7">
+      <c r="I253" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="J253" s="44"/>
+      <c r="K253" s="43" t="s">
+        <v>770</v>
+      </c>
+      <c r="L253" s="43">
         <v>6238</v>
       </c>
-      <c r="M251" s="8">
-        <v>46357</v>
-      </c>
-    </row>
-    <row r="252" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A252" s="1">
-        <v>246</v>
-      </c>
-      <c r="B252" s="9" t="s">
+      <c r="M253" s="45">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A254" s="41">
+        <v>248</v>
+      </c>
+      <c r="B254" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C254" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="D254" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E254" s="44">
+        <v>1</v>
+      </c>
+      <c r="F254" s="43">
+        <v>3100.5</v>
+      </c>
+      <c r="G254" s="43">
+        <v>3100.5</v>
+      </c>
+      <c r="H254" s="44">
+        <v>83</v>
+      </c>
+      <c r="I254" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="J254" s="44"/>
+      <c r="K254" s="43" t="s">
+        <v>770</v>
+      </c>
+      <c r="L254" s="43">
+        <v>6238</v>
+      </c>
+      <c r="M254" s="45">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A255" s="41">
+        <v>249</v>
+      </c>
+      <c r="B255" s="42" t="s">
         <v>475</v>
       </c>
-      <c r="C252" s="7" t="s">
+      <c r="C255" s="43" t="s">
         <v>469</v>
       </c>
-      <c r="D252" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E252" s="6">
-        <v>2</v>
-      </c>
-      <c r="F252" s="7">
-        <v>526.5</v>
-      </c>
-      <c r="G252" s="7">
-        <v>1053</v>
-      </c>
-      <c r="H252" s="6">
+      <c r="D255" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E255" s="44">
+        <v>1</v>
+      </c>
+      <c r="F255" s="43">
+        <v>3393</v>
+      </c>
+      <c r="G255" s="43">
+        <v>3393</v>
+      </c>
+      <c r="H255" s="44">
         <v>83</v>
       </c>
-      <c r="I252" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="J252" s="6"/>
-      <c r="K252" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="L252" s="7">
+      <c r="I255" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="J255" s="44"/>
+      <c r="K255" s="43" t="s">
+        <v>770</v>
+      </c>
+      <c r="L255" s="43">
         <v>6238</v>
       </c>
-      <c r="M252" s="8">
-        <v>46357</v>
-      </c>
-    </row>
-    <row r="253" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="1">
-        <v>247</v>
-      </c>
-      <c r="B253" s="9" t="s">
+      <c r="M255" s="45">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A256" s="41">
+        <v>250</v>
+      </c>
+      <c r="B256" s="47" t="s">
         <v>476</v>
       </c>
-      <c r="C253" s="7" t="s">
+      <c r="C256" s="43" t="s">
         <v>470</v>
       </c>
-      <c r="D253" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E253" s="6">
-        <v>25</v>
-      </c>
-      <c r="F253" s="7">
-        <v>58.5</v>
-      </c>
-      <c r="G253" s="7">
-        <v>1462.5</v>
-      </c>
-      <c r="H253" s="6">
+      <c r="D256" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E256" s="44">
+        <v>1</v>
+      </c>
+      <c r="F256" s="43">
+        <v>152.1</v>
+      </c>
+      <c r="G256" s="43">
+        <v>152.1</v>
+      </c>
+      <c r="H256" s="44">
         <v>83</v>
       </c>
-      <c r="I253" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="J253" s="6"/>
-      <c r="K253" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="L253" s="7">
+      <c r="I256" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="J256" s="44"/>
+      <c r="K256" s="43" t="s">
+        <v>770</v>
+      </c>
+      <c r="L256" s="43">
         <v>6238</v>
       </c>
-      <c r="M253" s="8">
-        <v>46357</v>
-      </c>
-    </row>
-    <row r="254" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A254" s="1">
-        <v>248</v>
-      </c>
-      <c r="B254" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C254" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D254" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E254" s="6">
+      <c r="M256" s="45">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A257" s="41">
+        <v>251</v>
+      </c>
+      <c r="B257" s="47" t="s">
+        <v>477</v>
+      </c>
+      <c r="C257" s="43" t="s">
+        <v>471</v>
+      </c>
+      <c r="D257" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E257" s="44">
         <v>1</v>
       </c>
-      <c r="F254" s="7">
-        <v>3100.5</v>
-      </c>
-      <c r="G254" s="7">
-        <v>3100.5</v>
-      </c>
-      <c r="H254" s="6">
+      <c r="F257" s="43">
+        <v>157.94999999999999</v>
+      </c>
+      <c r="G257" s="43">
+        <v>157.94999999999999</v>
+      </c>
+      <c r="H257" s="44">
         <v>83</v>
       </c>
-      <c r="I254" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="J254" s="6"/>
-      <c r="K254" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="L254" s="7">
+      <c r="I257" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="J257" s="44"/>
+      <c r="K257" s="43" t="s">
+        <v>770</v>
+      </c>
+      <c r="L257" s="43">
         <v>6238</v>
       </c>
-      <c r="M254" s="8">
-        <v>46357</v>
-      </c>
-    </row>
-    <row r="255" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A255" s="1">
-        <v>249</v>
-      </c>
-      <c r="B255" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="C255" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="D255" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E255" s="6">
-        <v>1</v>
-      </c>
-      <c r="F255" s="7">
-        <v>3393</v>
-      </c>
-      <c r="G255" s="7">
-        <v>3393</v>
-      </c>
-      <c r="H255" s="6">
-        <v>83</v>
-      </c>
-      <c r="I255" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="J255" s="6"/>
-      <c r="K255" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="L255" s="7">
-        <v>6238</v>
-      </c>
-      <c r="M255" s="8">
-        <v>46357</v>
-      </c>
-    </row>
-    <row r="256" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A256" s="1">
-        <v>250</v>
-      </c>
-      <c r="B256" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="C256" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="D256" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E256" s="6">
-        <v>1</v>
-      </c>
-      <c r="F256" s="7">
-        <v>152.1</v>
-      </c>
-      <c r="G256" s="7">
-        <v>152.1</v>
-      </c>
-      <c r="H256" s="6">
-        <v>83</v>
-      </c>
-      <c r="I256" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="J256" s="6"/>
-      <c r="K256" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="L256" s="7">
-        <v>6238</v>
-      </c>
-      <c r="M256" s="8">
-        <v>46357</v>
-      </c>
-    </row>
-    <row r="257" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A257" s="1">
-        <v>251</v>
-      </c>
-      <c r="B257" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="C257" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="D257" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E257" s="6">
-        <v>1</v>
-      </c>
-      <c r="F257" s="7">
-        <v>157.94999999999999</v>
-      </c>
-      <c r="G257" s="7">
-        <v>157.94999999999999</v>
-      </c>
-      <c r="H257" s="6">
-        <v>83</v>
-      </c>
-      <c r="I257" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="J257" s="6"/>
-      <c r="K257" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="L257" s="7">
-        <v>6238</v>
-      </c>
-      <c r="M257" s="8">
-        <v>46357</v>
+      <c r="M257" s="45">
+        <v>46359</v>
       </c>
     </row>
     <row r="258" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -12827,10 +12868,10 @@
         <v>252</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D258" s="7" t="s">
         <v>17</v>
@@ -12848,11 +12889,11 @@
         <v>39</v>
       </c>
       <c r="I258" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J258" s="6"/>
       <c r="K258" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L258" s="7">
         <v>6239</v>
@@ -12866,10 +12907,10 @@
         <v>253</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D259" s="7" t="s">
         <v>17</v>
@@ -12887,11 +12928,11 @@
         <v>39</v>
       </c>
       <c r="I259" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J259" s="6"/>
       <c r="K259" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L259" s="7">
         <v>6239</v>
@@ -12908,7 +12949,7 @@
         <v>92</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D260" s="7" t="s">
         <v>17</v>
@@ -12926,11 +12967,11 @@
         <v>39</v>
       </c>
       <c r="I260" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J260" s="6"/>
       <c r="K260" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L260" s="7">
         <v>6239</v>
@@ -12944,10 +12985,10 @@
         <v>255</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D261" s="7" t="s">
         <v>17</v>
@@ -12965,11 +13006,11 @@
         <v>39</v>
       </c>
       <c r="I261" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J261" s="6"/>
       <c r="K261" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L261" s="7">
         <v>6239</v>
@@ -12983,10 +13024,10 @@
         <v>256</v>
       </c>
       <c r="B262" s="15" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D262" s="7" t="s">
         <v>17</v>
@@ -13004,7 +13045,7 @@
         <v>2437</v>
       </c>
       <c r="I262" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J262" s="6"/>
       <c r="K262" s="7" t="s">
@@ -13022,10 +13063,10 @@
         <v>257</v>
       </c>
       <c r="B263" s="15" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D263" s="7" t="s">
         <v>17</v>
@@ -13043,7 +13084,7 @@
         <v>2437</v>
       </c>
       <c r="I263" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J263" s="6"/>
       <c r="K263" s="7" t="s">
@@ -13061,10 +13102,10 @@
         <v>258</v>
       </c>
       <c r="B264" s="11" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D264" s="7" t="s">
         <v>75</v>
@@ -13082,7 +13123,7 @@
         <v>2437</v>
       </c>
       <c r="I264" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J264" s="6"/>
       <c r="K264" s="7" t="s">
@@ -13100,10 +13141,10 @@
         <v>259</v>
       </c>
       <c r="B265" s="11" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D265" s="7" t="s">
         <v>17</v>
@@ -13121,7 +13162,7 @@
         <v>2437</v>
       </c>
       <c r="I265" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J265" s="6"/>
       <c r="K265" s="7" t="s">
@@ -13139,10 +13180,10 @@
         <v>260</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D266" s="7" t="s">
         <v>17</v>
@@ -13160,7 +13201,7 @@
         <v>2437</v>
       </c>
       <c r="I266" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J266" s="6"/>
       <c r="K266" s="7" t="s">
@@ -13178,10 +13219,10 @@
         <v>261</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D267" s="7" t="s">
         <v>17</v>
@@ -13199,7 +13240,7 @@
         <v>2437</v>
       </c>
       <c r="I267" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J267" s="6"/>
       <c r="K267" s="7" t="s">
@@ -13217,10 +13258,10 @@
         <v>262</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D268" s="7" t="s">
         <v>17</v>
@@ -13238,7 +13279,7 @@
         <v>2437</v>
       </c>
       <c r="I268" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J268" s="6"/>
       <c r="K268" s="7" t="s">
@@ -13256,10 +13297,10 @@
         <v>263</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D269" s="7" t="s">
         <v>17</v>
@@ -13277,7 +13318,7 @@
         <v>2437</v>
       </c>
       <c r="I269" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J269" s="6"/>
       <c r="K269" s="7" t="s">
@@ -13295,10 +13336,10 @@
         <v>264</v>
       </c>
       <c r="B270" s="11" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D270" s="7" t="s">
         <v>17</v>
@@ -13316,7 +13357,7 @@
         <v>2437</v>
       </c>
       <c r="I270" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J270" s="6"/>
       <c r="K270" s="7" t="s">
@@ -13334,10 +13375,10 @@
         <v>265</v>
       </c>
       <c r="B271" s="11" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D271" s="7" t="s">
         <v>17</v>
@@ -13355,7 +13396,7 @@
         <v>2437</v>
       </c>
       <c r="I271" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J271" s="6"/>
       <c r="K271" s="7" t="s">
@@ -13373,10 +13414,10 @@
         <v>266</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D272" s="7" t="s">
         <v>17</v>
@@ -13394,7 +13435,7 @@
         <v>2437</v>
       </c>
       <c r="I272" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J272" s="6"/>
       <c r="K272" s="7" t="s">
@@ -13412,10 +13453,10 @@
         <v>267</v>
       </c>
       <c r="B273" s="11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D273" s="7" t="s">
         <v>17</v>
@@ -13433,7 +13474,7 @@
         <v>2437</v>
       </c>
       <c r="I273" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J273" s="6"/>
       <c r="K273" s="7" t="s">
@@ -13451,10 +13492,10 @@
         <v>268</v>
       </c>
       <c r="B274" s="11" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D274" s="7" t="s">
         <v>17</v>
@@ -13472,7 +13513,7 @@
         <v>2437</v>
       </c>
       <c r="I274" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J274" s="6"/>
       <c r="K274" s="7" t="s">
@@ -13490,10 +13531,10 @@
         <v>269</v>
       </c>
       <c r="B275" s="15" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D275" s="7" t="s">
         <v>17</v>
@@ -13511,7 +13552,7 @@
         <v>2437</v>
       </c>
       <c r="I275" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J275" s="6"/>
       <c r="K275" s="7" t="s">
@@ -13529,10 +13570,10 @@
         <v>270</v>
       </c>
       <c r="B276" s="11" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D276" s="7" t="s">
         <v>17</v>
@@ -13550,7 +13591,7 @@
         <v>2437</v>
       </c>
       <c r="I276" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J276" s="6"/>
       <c r="K276" s="7" t="s">
@@ -13568,10 +13609,10 @@
         <v>271</v>
       </c>
       <c r="B277" s="12" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D277" s="7" t="s">
         <v>17</v>
@@ -13589,7 +13630,7 @@
         <v>2437</v>
       </c>
       <c r="I277" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J277" s="6"/>
       <c r="K277" s="7" t="s">
@@ -13607,10 +13648,10 @@
         <v>272</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D278" s="7" t="s">
         <v>17</v>
@@ -13628,7 +13669,7 @@
         <v>2437</v>
       </c>
       <c r="I278" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J278" s="6"/>
       <c r="K278" s="7" t="s">
@@ -13646,10 +13687,10 @@
         <v>273</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D279" s="7" t="s">
         <v>17</v>
@@ -13667,7 +13708,7 @@
         <v>2437</v>
       </c>
       <c r="I279" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J279" s="6"/>
       <c r="K279" s="7" t="s">
@@ -13685,10 +13726,10 @@
         <v>274</v>
       </c>
       <c r="B280" s="15" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D280" s="7" t="s">
         <v>17</v>
@@ -13706,7 +13747,7 @@
         <v>2437</v>
       </c>
       <c r="I280" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J280" s="6"/>
       <c r="K280" s="7" t="s">
@@ -13724,10 +13765,10 @@
         <v>275</v>
       </c>
       <c r="B281" s="15" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D281" s="7" t="s">
         <v>17</v>
@@ -13745,7 +13786,7 @@
         <v>2437</v>
       </c>
       <c r="I281" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J281" s="6"/>
       <c r="K281" s="7" t="s">
@@ -13763,10 +13804,10 @@
         <v>276</v>
       </c>
       <c r="B282" s="15" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D282" s="7" t="s">
         <v>17</v>
@@ -13784,7 +13825,7 @@
         <v>2437</v>
       </c>
       <c r="I282" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J282" s="6"/>
       <c r="K282" s="7" t="s">
@@ -13802,10 +13843,10 @@
         <v>277</v>
       </c>
       <c r="B283" s="11" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D283" s="7" t="s">
         <v>17</v>
@@ -13823,7 +13864,7 @@
         <v>2437</v>
       </c>
       <c r="I283" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J283" s="6"/>
       <c r="K283" s="7" t="s">
@@ -13841,10 +13882,10 @@
         <v>278</v>
       </c>
       <c r="B284" s="15" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D284" s="7" t="s">
         <v>17</v>
@@ -13862,7 +13903,7 @@
         <v>2437</v>
       </c>
       <c r="I284" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J284" s="6"/>
       <c r="K284" s="7" t="s">
@@ -13880,10 +13921,10 @@
         <v>279</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D285" s="7" t="s">
         <v>17</v>
@@ -13901,7 +13942,7 @@
         <v>2437</v>
       </c>
       <c r="I285" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J285" s="6"/>
       <c r="K285" s="7" t="s">
@@ -13919,10 +13960,10 @@
         <v>280</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D286" s="7" t="s">
         <v>17</v>
@@ -13940,7 +13981,7 @@
         <v>2437</v>
       </c>
       <c r="I286" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J286" s="6"/>
       <c r="K286" s="7" t="s">
@@ -13958,10 +13999,10 @@
         <v>281</v>
       </c>
       <c r="B287" s="15" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D287" s="7" t="s">
         <v>17</v>
@@ -13979,7 +14020,7 @@
         <v>2437</v>
       </c>
       <c r="I287" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J287" s="6"/>
       <c r="K287" s="7" t="s">
@@ -13997,10 +14038,10 @@
         <v>282</v>
       </c>
       <c r="B288" s="15" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D288" s="7" t="s">
         <v>17</v>
@@ -14018,7 +14059,7 @@
         <v>2437</v>
       </c>
       <c r="I288" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J288" s="6"/>
       <c r="K288" s="7" t="s">
@@ -14036,10 +14077,10 @@
         <v>283</v>
       </c>
       <c r="B289" s="15" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D289" s="7" t="s">
         <v>17</v>
@@ -14057,7 +14098,7 @@
         <v>2437</v>
       </c>
       <c r="I289" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J289" s="6"/>
       <c r="K289" s="7" t="s">
@@ -14075,10 +14116,10 @@
         <v>284</v>
       </c>
       <c r="B290" s="15" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D290" s="7" t="s">
         <v>17</v>
@@ -14096,7 +14137,7 @@
         <v>2437</v>
       </c>
       <c r="I290" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J290" s="6"/>
       <c r="K290" s="7" t="s">
@@ -14114,10 +14155,10 @@
         <v>285</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D291" s="7" t="s">
         <v>17</v>
@@ -14135,7 +14176,7 @@
         <v>2437</v>
       </c>
       <c r="I291" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J291" s="6"/>
       <c r="K291" s="7" t="s">
@@ -14153,10 +14194,10 @@
         <v>286</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D292" s="7" t="s">
         <v>17</v>
@@ -14174,7 +14215,7 @@
         <v>2437</v>
       </c>
       <c r="I292" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J292" s="6"/>
       <c r="K292" s="7" t="s">
@@ -14192,10 +14233,10 @@
         <v>287</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D293" s="7" t="s">
         <v>17</v>
@@ -14213,7 +14254,7 @@
         <v>2437</v>
       </c>
       <c r="I293" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J293" s="6"/>
       <c r="K293" s="7" t="s">
@@ -14231,10 +14272,10 @@
         <v>288</v>
       </c>
       <c r="B294" s="9" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D294" s="7" t="s">
         <v>17</v>
@@ -14252,7 +14293,7 @@
         <v>2437</v>
       </c>
       <c r="I294" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J294" s="6"/>
       <c r="K294" s="7" t="s">
@@ -14270,10 +14311,10 @@
         <v>289</v>
       </c>
       <c r="B295" s="9" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D295" s="7" t="s">
         <v>17</v>
@@ -14291,7 +14332,7 @@
         <v>1480</v>
       </c>
       <c r="I295" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J295" s="6"/>
       <c r="K295" s="7" t="s">
@@ -14309,10 +14350,10 @@
         <v>290</v>
       </c>
       <c r="B296" s="9" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D296" s="7" t="s">
         <v>17</v>
@@ -14330,7 +14371,7 @@
         <v>1480</v>
       </c>
       <c r="I296" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J296" s="6"/>
       <c r="K296" s="7" t="s">
@@ -14348,10 +14389,10 @@
         <v>291</v>
       </c>
       <c r="B297" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D297" s="7" t="s">
         <v>75</v>
@@ -14369,11 +14410,11 @@
         <v>809</v>
       </c>
       <c r="I297" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J297" s="6"/>
       <c r="K297" s="7" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="L297" s="7">
         <v>6244</v>
@@ -14387,10 +14428,10 @@
         <v>292</v>
       </c>
       <c r="B298" s="9" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D298" s="7" t="s">
         <v>75</v>
@@ -14408,11 +14449,11 @@
         <v>809</v>
       </c>
       <c r="I298" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J298" s="6"/>
       <c r="K298" s="7" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="L298" s="7">
         <v>6244</v>
@@ -14426,10 +14467,10 @@
         <v>293</v>
       </c>
       <c r="B299" s="9" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D299" s="7" t="s">
         <v>17</v>
@@ -14447,11 +14488,11 @@
         <v>34382</v>
       </c>
       <c r="I299" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J299" s="6"/>
       <c r="K299" s="7" t="s">
-        <v>606</v>
+        <v>773</v>
       </c>
       <c r="L299" s="7">
         <v>6245</v>
@@ -14465,10 +14506,10 @@
         <v>294</v>
       </c>
       <c r="B300" s="9" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D300" s="7" t="s">
         <v>17</v>
@@ -14486,11 +14527,11 @@
         <v>34382</v>
       </c>
       <c r="I300" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J300" s="6"/>
       <c r="K300" s="7" t="s">
-        <v>606</v>
+        <v>773</v>
       </c>
       <c r="L300" s="7">
         <v>6245</v>
@@ -14504,10 +14545,10 @@
         <v>295</v>
       </c>
       <c r="B301" s="9" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D301" s="7" t="s">
         <v>17</v>
@@ -14525,11 +14566,11 @@
         <v>34382</v>
       </c>
       <c r="I301" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J301" s="6"/>
       <c r="K301" s="7" t="s">
-        <v>606</v>
+        <v>773</v>
       </c>
       <c r="L301" s="7">
         <v>6245</v>
@@ -14543,10 +14584,10 @@
         <v>296</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D302" s="7" t="s">
         <v>17</v>
@@ -14564,7 +14605,7 @@
         <v>394</v>
       </c>
       <c r="I302" s="8" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J302" s="6"/>
       <c r="K302" s="7" t="s">
@@ -14574,7 +14615,7 @@
         <v>6246</v>
       </c>
       <c r="M302" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="303" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14582,10 +14623,10 @@
         <v>297</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D303" s="7" t="s">
         <v>17</v>
@@ -14603,7 +14644,7 @@
         <v>394</v>
       </c>
       <c r="I303" s="8" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J303" s="6"/>
       <c r="K303" s="7" t="s">
@@ -14613,7 +14654,7 @@
         <v>6246</v>
       </c>
       <c r="M303" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="304" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14621,10 +14662,10 @@
         <v>298</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="D304" s="7" t="s">
         <v>17</v>
@@ -14642,17 +14683,17 @@
         <v>42</v>
       </c>
       <c r="I304" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="J304" s="6"/>
       <c r="K304" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L304" s="7">
         <v>6247</v>
       </c>
       <c r="M304" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="305" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14660,10 +14701,10 @@
         <v>299</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="D305" s="7" t="s">
         <v>17</v>
@@ -14681,17 +14722,17 @@
         <v>42</v>
       </c>
       <c r="I305" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="J305" s="6"/>
       <c r="K305" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L305" s="7">
         <v>6247</v>
       </c>
       <c r="M305" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="306" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14699,10 +14740,10 @@
         <v>300</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D306" s="7" t="s">
         <v>17</v>
@@ -14720,17 +14761,17 @@
         <v>42</v>
       </c>
       <c r="I306" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="J306" s="6"/>
       <c r="K306" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L306" s="7">
         <v>6247</v>
       </c>
       <c r="M306" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="307" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14738,10 +14779,10 @@
         <v>301</v>
       </c>
       <c r="B307" s="9" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="D307" s="7" t="s">
         <v>17</v>
@@ -14759,17 +14800,17 @@
         <v>42</v>
       </c>
       <c r="I307" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="J307" s="6"/>
       <c r="K307" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L307" s="7">
         <v>6247</v>
       </c>
       <c r="M307" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="308" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14777,10 +14818,10 @@
         <v>302</v>
       </c>
       <c r="B308" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="D308" s="7" t="s">
         <v>17</v>
@@ -14798,17 +14839,17 @@
         <v>42</v>
       </c>
       <c r="I308" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="J308" s="6"/>
       <c r="K308" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L308" s="7">
         <v>6247</v>
       </c>
       <c r="M308" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="309" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14816,10 +14857,10 @@
         <v>303</v>
       </c>
       <c r="B309" s="9" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D309" s="7" t="s">
         <v>17</v>
@@ -14837,17 +14878,17 @@
         <v>42</v>
       </c>
       <c r="I309" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="J309" s="6"/>
       <c r="K309" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L309" s="7">
         <v>6247</v>
       </c>
       <c r="M309" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="310" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14855,10 +14896,10 @@
         <v>304</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="D310" s="7" t="s">
         <v>17</v>
@@ -14876,17 +14917,17 @@
         <v>42</v>
       </c>
       <c r="I310" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="J310" s="6"/>
       <c r="K310" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L310" s="7">
         <v>6247</v>
       </c>
       <c r="M310" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="311" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14915,17 +14956,17 @@
         <v>42</v>
       </c>
       <c r="I311" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="J311" s="6"/>
       <c r="K311" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L311" s="7">
         <v>6247</v>
       </c>
       <c r="M311" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14933,10 +14974,10 @@
         <v>306</v>
       </c>
       <c r="B312" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D312" s="7" t="s">
         <v>17</v>
@@ -14954,17 +14995,17 @@
         <v>42</v>
       </c>
       <c r="I312" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="J312" s="6"/>
       <c r="K312" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="L312" s="7">
         <v>6247</v>
       </c>
       <c r="M312" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15003,7 +15044,7 @@
         <v>6248</v>
       </c>
       <c r="M313" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="314" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15011,10 +15052,10 @@
         <v>308</v>
       </c>
       <c r="B314" s="16" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C314" s="17" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D314" s="6" t="s">
         <v>17</v>
@@ -15032,7 +15073,7 @@
         <v>89598</v>
       </c>
       <c r="I314" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J314" s="6"/>
       <c r="K314" s="7" t="s">
@@ -15042,7 +15083,7 @@
         <v>6250</v>
       </c>
       <c r="M314" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="315" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15050,10 +15091,10 @@
         <v>309</v>
       </c>
       <c r="B315" s="16" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C315" s="17" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D315" s="6" t="s">
         <v>17</v>
@@ -15071,7 +15112,7 @@
         <v>89598</v>
       </c>
       <c r="I315" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J315" s="6"/>
       <c r="K315" s="7" t="s">
@@ -15081,7 +15122,7 @@
         <v>6250</v>
       </c>
       <c r="M315" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="316" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15089,10 +15130,10 @@
         <v>310</v>
       </c>
       <c r="B316" s="16" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C316" s="17" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D316" s="6" t="s">
         <v>17</v>
@@ -15110,7 +15151,7 @@
         <v>89598</v>
       </c>
       <c r="I316" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J316" s="6"/>
       <c r="K316" s="7" t="s">
@@ -15120,7 +15161,7 @@
         <v>6250</v>
       </c>
       <c r="M316" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="317" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15128,10 +15169,10 @@
         <v>311</v>
       </c>
       <c r="B317" s="16" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C317" s="17" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D317" s="6" t="s">
         <v>17</v>
@@ -15149,7 +15190,7 @@
         <v>89598</v>
       </c>
       <c r="I317" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J317" s="6"/>
       <c r="K317" s="7" t="s">
@@ -15159,7 +15200,7 @@
         <v>6250</v>
       </c>
       <c r="M317" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="318" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15167,10 +15208,10 @@
         <v>312</v>
       </c>
       <c r="B318" s="16" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C318" s="17" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D318" s="6" t="s">
         <v>17</v>
@@ -15188,7 +15229,7 @@
         <v>89598</v>
       </c>
       <c r="I318" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J318" s="6"/>
       <c r="K318" s="7" t="s">
@@ -15198,7 +15239,7 @@
         <v>6250</v>
       </c>
       <c r="M318" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="319" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15206,10 +15247,10 @@
         <v>313</v>
       </c>
       <c r="B319" s="16" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C319" s="17" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D319" s="6" t="s">
         <v>17</v>
@@ -15227,7 +15268,7 @@
         <v>89598</v>
       </c>
       <c r="I319" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J319" s="6"/>
       <c r="K319" s="7" t="s">
@@ -15237,7 +15278,7 @@
         <v>6250</v>
       </c>
       <c r="M319" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="320" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15245,10 +15286,10 @@
         <v>314</v>
       </c>
       <c r="B320" s="16" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C320" s="17" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D320" s="6" t="s">
         <v>17</v>
@@ -15266,7 +15307,7 @@
         <v>89598</v>
       </c>
       <c r="I320" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J320" s="6"/>
       <c r="K320" s="7" t="s">
@@ -15276,7 +15317,7 @@
         <v>6250</v>
       </c>
       <c r="M320" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="321" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15284,10 +15325,10 @@
         <v>315</v>
       </c>
       <c r="B321" s="16" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C321" s="17" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D321" s="6" t="s">
         <v>17</v>
@@ -15305,7 +15346,7 @@
         <v>89598</v>
       </c>
       <c r="I321" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J321" s="6"/>
       <c r="K321" s="7" t="s">
@@ -15315,7 +15356,7 @@
         <v>6250</v>
       </c>
       <c r="M321" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="322" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15323,10 +15364,10 @@
         <v>316</v>
       </c>
       <c r="B322" s="11" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D322" s="6" t="s">
         <v>17</v>
@@ -15344,17 +15385,17 @@
         <v>420</v>
       </c>
       <c r="I322" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J322" s="6"/>
       <c r="K322" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L322" s="7">
         <v>6252</v>
       </c>
       <c r="M322" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="323" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15362,10 +15403,10 @@
         <v>317</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C323" s="7" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D323" s="6" t="s">
         <v>17</v>
@@ -15383,17 +15424,17 @@
         <v>420</v>
       </c>
       <c r="I323" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J323" s="6"/>
       <c r="K323" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L323" s="7">
         <v>6252</v>
       </c>
       <c r="M323" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="324" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15401,10 +15442,10 @@
         <v>318</v>
       </c>
       <c r="B324" s="11" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D324" s="6" t="s">
         <v>17</v>
@@ -15422,17 +15463,17 @@
         <v>420</v>
       </c>
       <c r="I324" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J324" s="6"/>
       <c r="K324" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L324" s="7">
         <v>6252</v>
       </c>
       <c r="M324" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="325" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15440,10 +15481,10 @@
         <v>319</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C325" s="7" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D325" s="6" t="s">
         <v>17</v>
@@ -15461,17 +15502,17 @@
         <v>420</v>
       </c>
       <c r="I325" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J325" s="6"/>
       <c r="K325" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L325" s="7">
         <v>6252</v>
       </c>
       <c r="M325" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="326" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15479,10 +15520,10 @@
         <v>320</v>
       </c>
       <c r="B326" s="11" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C326" s="7" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="D326" s="6" t="s">
         <v>17</v>
@@ -15500,17 +15541,17 @@
         <v>420</v>
       </c>
       <c r="I326" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J326" s="6"/>
       <c r="K326" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L326" s="7">
         <v>6252</v>
       </c>
       <c r="M326" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="327" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15518,10 +15559,10 @@
         <v>321</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C327" s="7" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D327" s="6" t="s">
         <v>17</v>
@@ -15539,17 +15580,17 @@
         <v>420</v>
       </c>
       <c r="I327" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J327" s="6"/>
       <c r="K327" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L327" s="7">
         <v>6252</v>
       </c>
       <c r="M327" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="328" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15557,10 +15598,10 @@
         <v>322</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="C328" s="7" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D328" s="6" t="s">
         <v>17</v>
@@ -15578,17 +15619,17 @@
         <v>420</v>
       </c>
       <c r="I328" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J328" s="6"/>
       <c r="K328" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L328" s="7">
         <v>6252</v>
       </c>
       <c r="M328" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="329" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15596,10 +15637,10 @@
         <v>323</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="C329" s="7" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D329" s="6" t="s">
         <v>17</v>
@@ -15617,17 +15658,17 @@
         <v>420</v>
       </c>
       <c r="I329" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J329" s="6"/>
       <c r="K329" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L329" s="7">
         <v>6252</v>
       </c>
       <c r="M329" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="330" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15635,10 +15676,10 @@
         <v>324</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C330" s="7" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>17</v>
@@ -15656,17 +15697,17 @@
         <v>420</v>
       </c>
       <c r="I330" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J330" s="6"/>
       <c r="K330" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L330" s="7">
         <v>6252</v>
       </c>
       <c r="M330" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="331" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15677,7 +15718,7 @@
         <v>298</v>
       </c>
       <c r="C331" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D331" s="6" t="s">
         <v>17</v>
@@ -15695,17 +15736,17 @@
         <v>420</v>
       </c>
       <c r="I331" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J331" s="6"/>
       <c r="K331" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L331" s="7">
         <v>6252</v>
       </c>
       <c r="M331" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="332" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15713,10 +15754,10 @@
         <v>326</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="D332" s="6" t="s">
         <v>17</v>
@@ -15734,17 +15775,17 @@
         <v>420</v>
       </c>
       <c r="I332" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J332" s="6"/>
       <c r="K332" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L332" s="7">
         <v>6252</v>
       </c>
       <c r="M332" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="333" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15752,10 +15793,10 @@
         <v>327</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C333" s="7" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D333" s="6" t="s">
         <v>17</v>
@@ -15773,17 +15814,17 @@
         <v>420</v>
       </c>
       <c r="I333" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J333" s="6"/>
       <c r="K333" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L333" s="7">
         <v>6252</v>
       </c>
       <c r="M333" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="334" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15791,10 +15832,10 @@
         <v>328</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C334" s="7" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D334" s="6" t="s">
         <v>17</v>
@@ -15812,17 +15853,17 @@
         <v>420</v>
       </c>
       <c r="I334" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J334" s="6"/>
       <c r="K334" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L334" s="7">
         <v>6253</v>
       </c>
       <c r="M334" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="335" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15830,10 +15871,10 @@
         <v>329</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="D335" s="6" t="s">
         <v>17</v>
@@ -15851,17 +15892,17 @@
         <v>420</v>
       </c>
       <c r="I335" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J335" s="6"/>
       <c r="K335" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L335" s="7">
         <v>6253</v>
       </c>
       <c r="M335" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="336" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15869,10 +15910,10 @@
         <v>330</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C336" s="7" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D336" s="6" t="s">
         <v>17</v>
@@ -15890,17 +15931,17 @@
         <v>420</v>
       </c>
       <c r="I336" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J336" s="6"/>
       <c r="K336" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L336" s="7">
         <v>6253</v>
       </c>
       <c r="M336" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="337" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15908,10 +15949,10 @@
         <v>331</v>
       </c>
       <c r="B337" s="11" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C337" s="7" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="D337" s="6" t="s">
         <v>17</v>
@@ -15929,17 +15970,17 @@
         <v>420</v>
       </c>
       <c r="I337" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J337" s="6"/>
       <c r="K337" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L337" s="7">
         <v>6253</v>
       </c>
       <c r="M337" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="338" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15947,10 +15988,10 @@
         <v>332</v>
       </c>
       <c r="B338" s="11" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="C338" s="7" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="D338" s="6" t="s">
         <v>17</v>
@@ -15968,17 +16009,17 @@
         <v>420</v>
       </c>
       <c r="I338" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J338" s="6"/>
       <c r="K338" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L338" s="7">
         <v>6253</v>
       </c>
       <c r="M338" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="339" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15986,10 +16027,10 @@
         <v>333</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="C339" s="7" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D339" s="6" t="s">
         <v>17</v>
@@ -16007,17 +16048,17 @@
         <v>420</v>
       </c>
       <c r="I339" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J339" s="6"/>
       <c r="K339" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L339" s="7">
         <v>6253</v>
       </c>
       <c r="M339" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="340" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16025,10 +16066,10 @@
         <v>334</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="C340" s="7" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D340" s="6" t="s">
         <v>52</v>
@@ -16046,17 +16087,17 @@
         <v>420</v>
       </c>
       <c r="I340" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J340" s="6"/>
       <c r="K340" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L340" s="7">
         <v>6253</v>
       </c>
       <c r="M340" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="341" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16064,10 +16105,10 @@
         <v>335</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="C341" s="7" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D341" s="6" t="s">
         <v>17</v>
@@ -16085,17 +16126,17 @@
         <v>420</v>
       </c>
       <c r="I341" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J341" s="6"/>
       <c r="K341" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L341" s="7">
         <v>6253</v>
       </c>
       <c r="M341" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="342" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16103,10 +16144,10 @@
         <v>336</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="C342" s="7" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D342" s="6" t="s">
         <v>17</v>
@@ -16124,17 +16165,17 @@
         <v>420</v>
       </c>
       <c r="I342" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J342" s="6"/>
       <c r="K342" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L342" s="7">
         <v>6253</v>
       </c>
       <c r="M342" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="343" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16142,10 +16183,10 @@
         <v>338</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C343" s="7" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="D343" s="6" t="s">
         <v>17</v>
@@ -16163,17 +16204,17 @@
         <v>420</v>
       </c>
       <c r="I343" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J343" s="6"/>
       <c r="K343" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L343" s="7">
         <v>6253</v>
       </c>
       <c r="M343" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="344" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16181,10 +16222,10 @@
         <v>339</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C344" s="7" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D344" s="6" t="s">
         <v>17</v>
@@ -16202,17 +16243,17 @@
         <v>420</v>
       </c>
       <c r="I344" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J344" s="6"/>
       <c r="K344" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L344" s="7">
         <v>6254</v>
       </c>
       <c r="M344" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="345" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16220,10 +16261,10 @@
         <v>340</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C345" s="7" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D345" s="6" t="s">
         <v>17</v>
@@ -16241,17 +16282,17 @@
         <v>420</v>
       </c>
       <c r="I345" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J345" s="6"/>
       <c r="K345" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L345" s="7">
         <v>6254</v>
       </c>
       <c r="M345" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="346" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16259,10 +16300,10 @@
         <v>341</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C346" s="7" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="D346" s="6" t="s">
         <v>17</v>
@@ -16280,17 +16321,17 @@
         <v>420</v>
       </c>
       <c r="I346" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J346" s="6"/>
       <c r="K346" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L346" s="7">
         <v>6254</v>
       </c>
       <c r="M346" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="347" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16298,10 +16339,10 @@
         <v>342</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C347" s="7" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D347" s="6" t="s">
         <v>17</v>
@@ -16319,17 +16360,17 @@
         <v>420</v>
       </c>
       <c r="I347" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J347" s="6"/>
       <c r="K347" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L347" s="7">
         <v>6254</v>
       </c>
       <c r="M347" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="348" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16337,10 +16378,10 @@
         <v>343</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="C348" s="7" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="D348" s="6" t="s">
         <v>17</v>
@@ -16358,17 +16399,17 @@
         <v>420</v>
       </c>
       <c r="I348" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J348" s="6"/>
       <c r="K348" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L348" s="7">
         <v>6254</v>
       </c>
       <c r="M348" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="349" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16376,10 +16417,10 @@
         <v>344</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D349" s="6" t="s">
         <v>17</v>
@@ -16397,17 +16438,17 @@
         <v>420</v>
       </c>
       <c r="I349" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J349" s="6"/>
       <c r="K349" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L349" s="7">
         <v>6254</v>
       </c>
       <c r="M349" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="350" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16415,10 +16456,10 @@
         <v>346</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C350" s="7" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="D350" s="6" t="s">
         <v>17</v>
@@ -16436,17 +16477,17 @@
         <v>420</v>
       </c>
       <c r="I350" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J350" s="6"/>
       <c r="K350" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L350" s="7">
         <v>6254</v>
       </c>
       <c r="M350" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="351" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16454,10 +16495,10 @@
         <v>347</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C351" s="7" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D351" s="6" t="s">
         <v>17</v>
@@ -16475,17 +16516,17 @@
         <v>420</v>
       </c>
       <c r="I351" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J351" s="6"/>
       <c r="K351" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L351" s="7">
         <v>6254</v>
       </c>
       <c r="M351" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="352" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16493,10 +16534,10 @@
         <v>348</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="C352" s="7" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="D352" s="6" t="s">
         <v>17</v>
@@ -16514,17 +16555,17 @@
         <v>420</v>
       </c>
       <c r="I352" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J352" s="6"/>
       <c r="K352" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L352" s="7">
         <v>6254</v>
       </c>
       <c r="M352" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="353" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16532,10 +16573,10 @@
         <v>349</v>
       </c>
       <c r="B353" s="11" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C353" s="7" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D353" s="6" t="s">
         <v>17</v>
@@ -16553,17 +16594,17 @@
         <v>420</v>
       </c>
       <c r="I353" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J353" s="6"/>
       <c r="K353" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L353" s="7">
         <v>6254</v>
       </c>
       <c r="M353" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="354" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16571,10 +16612,10 @@
         <v>350</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C354" s="7" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D354" s="6" t="s">
         <v>17</v>
@@ -16592,17 +16633,17 @@
         <v>420</v>
       </c>
       <c r="I354" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J354" s="6"/>
       <c r="K354" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L354" s="7">
         <v>6255</v>
       </c>
       <c r="M354" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="355" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16610,10 +16651,10 @@
         <v>351</v>
       </c>
       <c r="B355" s="11" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="C355" s="7" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="D355" s="6" t="s">
         <v>17</v>
@@ -16631,17 +16672,17 @@
         <v>420</v>
       </c>
       <c r="I355" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J355" s="6"/>
       <c r="K355" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L355" s="7">
         <v>6255</v>
       </c>
       <c r="M355" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="356" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16649,10 +16690,10 @@
         <v>352</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C356" s="7" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D356" s="6" t="s">
         <v>17</v>
@@ -16670,17 +16711,17 @@
         <v>420</v>
       </c>
       <c r="I356" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J356" s="6"/>
       <c r="K356" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L356" s="7">
         <v>6255</v>
       </c>
       <c r="M356" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="357" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16688,13 +16729,13 @@
         <v>353</v>
       </c>
       <c r="B357" s="11" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C357" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="D357" s="6" t="s">
         <v>686</v>
-      </c>
-      <c r="D357" s="6" t="s">
-        <v>690</v>
       </c>
       <c r="E357" s="6">
         <v>3</v>
@@ -16709,17 +16750,17 @@
         <v>420</v>
       </c>
       <c r="I357" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J357" s="6"/>
       <c r="K357" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L357" s="7">
         <v>6255</v>
       </c>
       <c r="M357" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="358" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16727,10 +16768,10 @@
         <v>354</v>
       </c>
       <c r="B358" s="11" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C358" s="7" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D358" s="6" t="s">
         <v>17</v>
@@ -16748,17 +16789,17 @@
         <v>420</v>
       </c>
       <c r="I358" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J358" s="6"/>
       <c r="K358" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L358" s="7">
         <v>6255</v>
       </c>
       <c r="M358" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="359" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16766,10 +16807,10 @@
         <v>355</v>
       </c>
       <c r="B359" s="11" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="C359" s="7" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="D359" s="6" t="s">
         <v>17</v>
@@ -16787,17 +16828,17 @@
         <v>420</v>
       </c>
       <c r="I359" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J359" s="6"/>
       <c r="K359" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L359" s="7">
         <v>6255</v>
       </c>
       <c r="M359" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="360" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16805,10 +16846,10 @@
         <v>356</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C360" s="7" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="D360" s="6" t="s">
         <v>17</v>
@@ -16826,17 +16867,17 @@
         <v>420</v>
       </c>
       <c r="I360" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J360" s="6"/>
       <c r="K360" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L360" s="7">
         <v>6255</v>
       </c>
       <c r="M360" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="361" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16847,7 +16888,7 @@
         <v>340</v>
       </c>
       <c r="C361" s="7" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D361" s="6" t="s">
         <v>17</v>
@@ -16865,17 +16906,17 @@
         <v>420</v>
       </c>
       <c r="I361" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J361" s="6"/>
       <c r="K361" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L361" s="7">
         <v>6255</v>
       </c>
       <c r="M361" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="362" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16883,10 +16924,10 @@
         <v>358</v>
       </c>
       <c r="B362" s="11" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C362" s="7" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="D362" s="6" t="s">
         <v>17</v>
@@ -16904,17 +16945,17 @@
         <v>419</v>
       </c>
       <c r="I362" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J362" s="6"/>
       <c r="K362" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L362" s="7">
         <v>6256</v>
       </c>
       <c r="M362" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="363" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16922,10 +16963,10 @@
         <v>359</v>
       </c>
       <c r="B363" s="11" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C363" s="7" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D363" s="6" t="s">
         <v>17</v>
@@ -16943,17 +16984,17 @@
         <v>419</v>
       </c>
       <c r="I363" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J363" s="6"/>
       <c r="K363" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L363" s="7">
         <v>6256</v>
       </c>
       <c r="M363" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="364" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16961,13 +17002,13 @@
         <v>360</v>
       </c>
       <c r="B364" s="11" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C364" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="D364" s="6" t="s">
         <v>686</v>
-      </c>
-      <c r="D364" s="6" t="s">
-        <v>690</v>
       </c>
       <c r="E364" s="6">
         <v>3</v>
@@ -16982,17 +17023,17 @@
         <v>419</v>
       </c>
       <c r="I364" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J364" s="6"/>
       <c r="K364" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L364" s="7">
         <v>6256</v>
       </c>
       <c r="M364" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="365" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17000,10 +17041,10 @@
         <v>361</v>
       </c>
       <c r="B365" s="11" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C365" s="7" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D365" s="6" t="s">
         <v>17</v>
@@ -17021,17 +17062,17 @@
         <v>419</v>
       </c>
       <c r="I365" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J365" s="6"/>
       <c r="K365" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L365" s="7">
         <v>6256</v>
       </c>
       <c r="M365" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="366" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17039,10 +17080,10 @@
         <v>362</v>
       </c>
       <c r="B366" s="11" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C366" s="7" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D366" s="6" t="s">
         <v>17</v>
@@ -17060,17 +17101,17 @@
         <v>419</v>
       </c>
       <c r="I366" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J366" s="6"/>
       <c r="K366" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L366" s="7">
         <v>6256</v>
       </c>
       <c r="M366" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="367" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17078,13 +17119,13 @@
         <v>365</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="C367" s="7" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D367" s="6" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="E367" s="6">
         <v>25</v>
@@ -17099,17 +17140,17 @@
         <v>419</v>
       </c>
       <c r="I367" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J367" s="6"/>
       <c r="K367" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L367" s="7">
         <v>6256</v>
       </c>
       <c r="M367" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="368" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17117,10 +17158,10 @@
         <v>366</v>
       </c>
       <c r="B368" s="9" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C368" s="7" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D368" s="6" t="s">
         <v>17</v>
@@ -17138,17 +17179,17 @@
         <v>419</v>
       </c>
       <c r="I368" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J368" s="6"/>
       <c r="K368" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L368" s="7">
         <v>6256</v>
       </c>
       <c r="M368" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="369" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17156,13 +17197,13 @@
         <v>367</v>
       </c>
       <c r="B369" s="11" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C369" s="7" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D369" s="6" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="E369" s="6">
         <v>11</v>
@@ -17177,17 +17218,17 @@
         <v>419</v>
       </c>
       <c r="I369" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J369" s="6"/>
       <c r="K369" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L369" s="7">
         <v>6256</v>
       </c>
       <c r="M369" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="370" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17195,10 +17236,10 @@
         <v>368</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C370" s="7" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D370" s="6" t="s">
         <v>17</v>
@@ -17216,17 +17257,17 @@
         <v>419</v>
       </c>
       <c r="I370" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J370" s="6"/>
       <c r="K370" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L370" s="7">
         <v>6256</v>
       </c>
       <c r="M370" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="371" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17234,10 +17275,10 @@
         <v>369</v>
       </c>
       <c r="B371" s="11" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="C371" s="7" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D371" s="6" t="s">
         <v>17</v>
@@ -17255,17 +17296,17 @@
         <v>419</v>
       </c>
       <c r="I371" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J371" s="6"/>
       <c r="K371" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L371" s="7">
         <v>6256</v>
       </c>
       <c r="M371" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="372" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17273,10 +17314,10 @@
         <v>370</v>
       </c>
       <c r="B372" s="11" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="C372" s="7" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D372" s="6" t="s">
         <v>17</v>
@@ -17294,17 +17335,17 @@
         <v>419</v>
       </c>
       <c r="I372" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J372" s="6"/>
       <c r="K372" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L372" s="7">
         <v>6257</v>
       </c>
       <c r="M372" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="373" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17312,10 +17353,10 @@
         <v>371</v>
       </c>
       <c r="B373" s="11" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C373" s="7" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D373" s="6" t="s">
         <v>17</v>
@@ -17333,17 +17374,17 @@
         <v>419</v>
       </c>
       <c r="I373" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J373" s="6"/>
       <c r="K373" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L373" s="7">
         <v>6257</v>
       </c>
       <c r="M373" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="374" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17351,10 +17392,10 @@
         <v>372</v>
       </c>
       <c r="B374" s="11" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C374" s="7" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="D374" s="6" t="s">
         <v>17</v>
@@ -17372,17 +17413,17 @@
         <v>419</v>
       </c>
       <c r="I374" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J374" s="6"/>
       <c r="K374" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L374" s="7">
         <v>6257</v>
       </c>
       <c r="M374" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="375" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17390,10 +17431,10 @@
         <v>373</v>
       </c>
       <c r="B375" s="11" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C375" s="7" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D375" s="6" t="s">
         <v>17</v>
@@ -17411,17 +17452,17 @@
         <v>419</v>
       </c>
       <c r="I375" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J375" s="6"/>
       <c r="K375" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L375" s="7">
         <v>6257</v>
       </c>
       <c r="M375" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="376" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17429,10 +17470,10 @@
         <v>374</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="C376" s="7" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="D376" s="6" t="s">
         <v>17</v>
@@ -17450,17 +17491,17 @@
         <v>419</v>
       </c>
       <c r="I376" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J376" s="6"/>
       <c r="K376" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L376" s="7">
         <v>6257</v>
       </c>
       <c r="M376" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="377" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17468,10 +17509,10 @@
         <v>375</v>
       </c>
       <c r="B377" s="11" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="C377" s="7" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D377" s="6" t="s">
         <v>17</v>
@@ -17489,17 +17530,17 @@
         <v>419</v>
       </c>
       <c r="I377" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J377" s="6"/>
       <c r="K377" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L377" s="7">
         <v>6257</v>
       </c>
       <c r="M377" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="378" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17507,10 +17548,10 @@
         <v>376</v>
       </c>
       <c r="B378" s="9" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C378" s="7" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D378" s="6" t="s">
         <v>17</v>
@@ -17528,17 +17569,17 @@
         <v>419</v>
       </c>
       <c r="I378" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J378" s="6"/>
       <c r="K378" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L378" s="7">
         <v>6257</v>
       </c>
       <c r="M378" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="379" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17546,10 +17587,10 @@
         <v>377</v>
       </c>
       <c r="B379" s="11" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="C379" s="7" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D379" s="6" t="s">
         <v>17</v>
@@ -17567,17 +17608,17 @@
         <v>419</v>
       </c>
       <c r="I379" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J379" s="6"/>
       <c r="K379" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L379" s="7">
         <v>6257</v>
       </c>
       <c r="M379" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="380" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17588,7 +17629,7 @@
         <v>340</v>
       </c>
       <c r="C380" s="7" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D380" s="6" t="s">
         <v>17</v>
@@ -17606,17 +17647,17 @@
         <v>419</v>
       </c>
       <c r="I380" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J380" s="6"/>
       <c r="K380" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L380" s="7">
         <v>6257</v>
       </c>
       <c r="M380" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="381" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17624,10 +17665,10 @@
         <v>379</v>
       </c>
       <c r="B381" s="9" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="C381" s="7" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D381" s="6" t="s">
         <v>17</v>
@@ -17645,17 +17686,17 @@
         <v>419</v>
       </c>
       <c r="I381" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J381" s="6"/>
       <c r="K381" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L381" s="7">
         <v>6257</v>
       </c>
       <c r="M381" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="382" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17666,7 +17707,7 @@
         <v>299</v>
       </c>
       <c r="C382" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D382" s="6" t="s">
         <v>17</v>
@@ -17684,17 +17725,17 @@
         <v>419</v>
       </c>
       <c r="I382" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J382" s="6"/>
       <c r="K382" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L382" s="7">
         <v>6257</v>
       </c>
       <c r="M382" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="383" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17702,10 +17743,10 @@
         <v>381</v>
       </c>
       <c r="B383" s="9" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C383" s="7" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="D383" s="6" t="s">
         <v>17</v>
@@ -17723,17 +17764,17 @@
         <v>419</v>
       </c>
       <c r="I383" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J383" s="6"/>
       <c r="K383" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L383" s="7">
         <v>6257</v>
       </c>
       <c r="M383" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="384" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17741,10 +17782,10 @@
         <v>382</v>
       </c>
       <c r="B384" s="9" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C384" s="7" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D384" s="6" t="s">
         <v>17</v>
@@ -17762,17 +17803,17 @@
         <v>419</v>
       </c>
       <c r="I384" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J384" s="6"/>
       <c r="K384" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L384" s="7">
         <v>6257</v>
       </c>
       <c r="M384" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="385" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17780,10 +17821,10 @@
         <v>383</v>
       </c>
       <c r="B385" s="9" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C385" s="7" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D385" s="6" t="s">
         <v>17</v>
@@ -17801,17 +17842,17 @@
         <v>419</v>
       </c>
       <c r="I385" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J385" s="6"/>
       <c r="K385" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L385" s="7">
         <v>6257</v>
       </c>
       <c r="M385" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="386" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17819,10 +17860,10 @@
         <v>384</v>
       </c>
       <c r="B386" s="11" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="C386" s="7" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D386" s="6" t="s">
         <v>17</v>
@@ -17840,17 +17881,17 @@
         <v>419</v>
       </c>
       <c r="I386" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J386" s="6"/>
       <c r="K386" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L386" s="7">
         <v>6257</v>
       </c>
       <c r="M386" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="387" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17858,10 +17899,10 @@
         <v>385</v>
       </c>
       <c r="B387" s="11" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C387" s="7" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D387" s="6" t="s">
         <v>17</v>
@@ -17879,17 +17920,17 @@
         <v>419</v>
       </c>
       <c r="I387" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J387" s="6"/>
       <c r="K387" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L387" s="7">
         <v>6257</v>
       </c>
       <c r="M387" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="388" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17897,10 +17938,10 @@
         <v>386</v>
       </c>
       <c r="B388" s="11" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="C388" s="7" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="D388" s="6" t="s">
         <v>17</v>
@@ -17918,17 +17959,17 @@
         <v>419</v>
       </c>
       <c r="I388" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J388" s="6"/>
       <c r="K388" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L388" s="7">
         <v>6257</v>
       </c>
       <c r="M388" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="389" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17936,10 +17977,10 @@
         <v>387</v>
       </c>
       <c r="B389" s="9" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C389" s="7" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="D389" s="6" t="s">
         <v>17</v>
@@ -17957,17 +17998,17 @@
         <v>419</v>
       </c>
       <c r="I389" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J389" s="6"/>
       <c r="K389" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L389" s="7">
         <v>6257</v>
       </c>
       <c r="M389" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="390" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17975,10 +18016,10 @@
         <v>388</v>
       </c>
       <c r="B390" s="11" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C390" s="7" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D390" s="6" t="s">
         <v>17</v>
@@ -17996,17 +18037,17 @@
         <v>419</v>
       </c>
       <c r="I390" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J390" s="6"/>
       <c r="K390" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L390" s="7">
         <v>6257</v>
       </c>
       <c r="M390" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="391" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18014,10 +18055,10 @@
         <v>389</v>
       </c>
       <c r="B391" s="9" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="C391" s="7" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="D391" s="6" t="s">
         <v>17</v>
@@ -18035,17 +18076,17 @@
         <v>419</v>
       </c>
       <c r="I391" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J391" s="6"/>
       <c r="K391" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L391" s="7">
         <v>6257</v>
       </c>
       <c r="M391" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="392" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18053,10 +18094,10 @@
         <v>390</v>
       </c>
       <c r="B392" s="9" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C392" s="7" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D392" s="6" t="s">
         <v>17</v>
@@ -18074,17 +18115,17 @@
         <v>419</v>
       </c>
       <c r="I392" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J392" s="6"/>
       <c r="K392" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L392" s="7">
         <v>6257</v>
       </c>
       <c r="M392" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="393" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18092,10 +18133,10 @@
         <v>391</v>
       </c>
       <c r="B393" s="9" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C393" s="7" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D393" s="6" t="s">
         <v>17</v>
@@ -18113,17 +18154,17 @@
         <v>419</v>
       </c>
       <c r="I393" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J393" s="6"/>
       <c r="K393" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L393" s="7">
         <v>6257</v>
       </c>
       <c r="M393" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="394" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18131,10 +18172,10 @@
         <v>392</v>
       </c>
       <c r="B394" s="9" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="C394" s="7" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="D394" s="6" t="s">
         <v>17</v>
@@ -18152,17 +18193,17 @@
         <v>419</v>
       </c>
       <c r="I394" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J394" s="6"/>
       <c r="K394" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L394" s="7">
         <v>6259</v>
       </c>
       <c r="M394" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="395" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18170,10 +18211,10 @@
         <v>393</v>
       </c>
       <c r="B395" s="9" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C395" s="7" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="D395" s="6" t="s">
         <v>17</v>
@@ -18191,17 +18232,17 @@
         <v>419</v>
       </c>
       <c r="I395" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J395" s="6"/>
       <c r="K395" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L395" s="7">
         <v>6259</v>
       </c>
       <c r="M395" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="396" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18209,10 +18250,10 @@
         <v>394</v>
       </c>
       <c r="B396" s="9" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C396" s="7" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="D396" s="6" t="s">
         <v>17</v>
@@ -18230,17 +18271,17 @@
         <v>419</v>
       </c>
       <c r="I396" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J396" s="6"/>
       <c r="K396" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L396" s="7">
         <v>6259</v>
       </c>
       <c r="M396" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="397" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18248,10 +18289,10 @@
         <v>395</v>
       </c>
       <c r="B397" s="11" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="C397" s="7" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="D397" s="6" t="s">
         <v>17</v>
@@ -18269,17 +18310,17 @@
         <v>419</v>
       </c>
       <c r="I397" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J397" s="6"/>
       <c r="K397" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L397" s="7">
         <v>6259</v>
       </c>
       <c r="M397" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="398" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18287,10 +18328,10 @@
         <v>396</v>
       </c>
       <c r="B398" s="9" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C398" s="7" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D398" s="6" t="s">
         <v>17</v>
@@ -18308,17 +18349,17 @@
         <v>419</v>
       </c>
       <c r="I398" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J398" s="6"/>
       <c r="K398" s="7" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="L398" s="7">
         <v>6259</v>
       </c>
       <c r="M398" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="399" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18326,10 +18367,10 @@
         <v>397</v>
       </c>
       <c r="B399" s="15" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C399" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D399" s="6" t="s">
         <v>17</v>
@@ -18347,7 +18388,7 @@
         <v>2443</v>
       </c>
       <c r="I399" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J399" s="6"/>
       <c r="K399" s="7" t="s">
@@ -18357,7 +18398,7 @@
         <v>6260</v>
       </c>
       <c r="M399" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="400" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18365,10 +18406,10 @@
         <v>398</v>
       </c>
       <c r="B400" s="11" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C400" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D400" s="6" t="s">
         <v>17</v>
@@ -18386,7 +18427,7 @@
         <v>2443</v>
       </c>
       <c r="I400" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J400" s="6"/>
       <c r="K400" s="7" t="s">
@@ -18396,7 +18437,7 @@
         <v>6260</v>
       </c>
       <c r="M400" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="401" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18425,7 +18466,7 @@
         <v>2443</v>
       </c>
       <c r="I401" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J401" s="6"/>
       <c r="K401" s="7" t="s">
@@ -18435,7 +18476,7 @@
         <v>6260</v>
       </c>
       <c r="M401" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="402" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18443,10 +18484,10 @@
         <v>400</v>
       </c>
       <c r="B402" s="11" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C402" s="7" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="D402" s="6" t="s">
         <v>17</v>
@@ -18464,7 +18505,7 @@
         <v>2443</v>
       </c>
       <c r="I402" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J402" s="6"/>
       <c r="K402" s="7" t="s">
@@ -18474,7 +18515,7 @@
         <v>6260</v>
       </c>
       <c r="M402" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="403" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18482,10 +18523,10 @@
         <v>401</v>
       </c>
       <c r="B403" s="11" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C403" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D403" s="6" t="s">
         <v>17</v>
@@ -18503,7 +18544,7 @@
         <v>2443</v>
       </c>
       <c r="I403" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J403" s="6"/>
       <c r="K403" s="7" t="s">
@@ -18513,7 +18554,7 @@
         <v>6260</v>
       </c>
       <c r="M403" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="404" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18521,10 +18562,10 @@
         <v>402</v>
       </c>
       <c r="B404" s="11" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C404" s="7" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D404" s="6" t="s">
         <v>17</v>
@@ -18542,7 +18583,7 @@
         <v>2443</v>
       </c>
       <c r="I404" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J404" s="6"/>
       <c r="K404" s="7" t="s">
@@ -18552,7 +18593,7 @@
         <v>6260</v>
       </c>
       <c r="M404" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="405" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18560,10 +18601,10 @@
         <v>403</v>
       </c>
       <c r="B405" s="11" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C405" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D405" s="6" t="s">
         <v>17</v>
@@ -18581,7 +18622,7 @@
         <v>2443</v>
       </c>
       <c r="I405" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J405" s="6"/>
       <c r="K405" s="7" t="s">
@@ -18591,7 +18632,7 @@
         <v>6260</v>
       </c>
       <c r="M405" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="406" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18599,10 +18640,10 @@
         <v>404</v>
       </c>
       <c r="B406" s="15" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C406" s="7" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="D406" s="6" t="s">
         <v>17</v>
@@ -18620,7 +18661,7 @@
         <v>2443</v>
       </c>
       <c r="I406" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J406" s="6"/>
       <c r="K406" s="7" t="s">
@@ -18630,7 +18671,7 @@
         <v>6260</v>
       </c>
       <c r="M406" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="407" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18638,10 +18679,10 @@
         <v>405</v>
       </c>
       <c r="B407" s="11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C407" s="7" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="D407" s="6" t="s">
         <v>17</v>
@@ -18659,7 +18700,7 @@
         <v>2443</v>
       </c>
       <c r="I407" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J407" s="6"/>
       <c r="K407" s="7" t="s">
@@ -18669,7 +18710,7 @@
         <v>6260</v>
       </c>
       <c r="M407" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="408" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18677,10 +18718,10 @@
         <v>406</v>
       </c>
       <c r="B408" s="9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C408" s="7" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D408" s="6" t="s">
         <v>17</v>
@@ -18698,7 +18739,7 @@
         <v>2443</v>
       </c>
       <c r="I408" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J408" s="6"/>
       <c r="K408" s="7" t="s">
@@ -18708,7 +18749,7 @@
         <v>6260</v>
       </c>
       <c r="M408" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="409" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18716,10 +18757,10 @@
         <v>407</v>
       </c>
       <c r="B409" s="15" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="C409" s="7" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D409" s="6" t="s">
         <v>17</v>
@@ -18737,7 +18778,7 @@
         <v>2443</v>
       </c>
       <c r="I409" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J409" s="6"/>
       <c r="K409" s="7" t="s">
@@ -18747,7 +18788,7 @@
         <v>6260</v>
       </c>
       <c r="M409" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="410" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18755,10 +18796,10 @@
         <v>408</v>
       </c>
       <c r="B410" s="15" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C410" s="7" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D410" s="6" t="s">
         <v>17</v>
@@ -18776,7 +18817,7 @@
         <v>2443</v>
       </c>
       <c r="I410" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J410" s="6"/>
       <c r="K410" s="7" t="s">
@@ -18786,7 +18827,7 @@
         <v>6260</v>
       </c>
       <c r="M410" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="411" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18794,10 +18835,10 @@
         <v>409</v>
       </c>
       <c r="B411" s="15" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C411" s="7" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="D411" s="6" t="s">
         <v>17</v>
@@ -18815,7 +18856,7 @@
         <v>2443</v>
       </c>
       <c r="I411" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J411" s="6"/>
       <c r="K411" s="7" t="s">
@@ -18825,7 +18866,7 @@
         <v>6261</v>
       </c>
       <c r="M411" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="412" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18833,10 +18874,10 @@
         <v>410</v>
       </c>
       <c r="B412" s="15" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C412" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D412" s="6" t="s">
         <v>17</v>
@@ -18854,7 +18895,7 @@
         <v>2443</v>
       </c>
       <c r="I412" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J412" s="6"/>
       <c r="K412" s="7" t="s">
@@ -18864,7 +18905,7 @@
         <v>6261</v>
       </c>
       <c r="M412" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="413" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18872,10 +18913,10 @@
         <v>411</v>
       </c>
       <c r="B413" s="15" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="C413" s="7" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D413" s="6" t="s">
         <v>17</v>
@@ -18893,7 +18934,7 @@
         <v>2443</v>
       </c>
       <c r="I413" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J413" s="6"/>
       <c r="K413" s="7" t="s">
@@ -18903,7 +18944,7 @@
         <v>6261</v>
       </c>
       <c r="M413" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="414" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18911,10 +18952,10 @@
         <v>412</v>
       </c>
       <c r="B414" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C414" s="7" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="D414" s="6" t="s">
         <v>17</v>
@@ -18932,7 +18973,7 @@
         <v>2443</v>
       </c>
       <c r="I414" s="8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J414" s="6"/>
       <c r="K414" s="7" t="s">
@@ -18942,7 +18983,7 @@
         <v>6261</v>
       </c>
       <c r="M414" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="415" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18950,10 +18991,10 @@
         <v>413</v>
       </c>
       <c r="B415" s="9" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C415" s="7" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D415" s="6" t="s">
         <v>17</v>
@@ -18971,17 +19012,17 @@
         <v>26</v>
       </c>
       <c r="I415" s="8" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="J415" s="6"/>
       <c r="K415" s="7" t="s">
-        <v>720</v>
+        <v>771</v>
       </c>
       <c r="L415" s="7">
         <v>6263</v>
       </c>
       <c r="M415" s="8" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="416" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18989,10 +19030,10 @@
         <v>414</v>
       </c>
       <c r="B416" s="9" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="C416" s="7" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="D416" s="6" t="s">
         <v>17</v>
@@ -19010,17 +19051,17 @@
         <v>26</v>
       </c>
       <c r="I416" s="8" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="J416" s="6"/>
       <c r="K416" s="7" t="s">
-        <v>720</v>
+        <v>771</v>
       </c>
       <c r="L416" s="7">
         <v>6263</v>
       </c>
       <c r="M416" s="8" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="417" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19028,10 +19069,10 @@
         <v>416</v>
       </c>
       <c r="B417" s="11" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="C417" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D417" s="6" t="s">
         <v>17</v>
@@ -19049,17 +19090,17 @@
         <v>26</v>
       </c>
       <c r="I417" s="8" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="J417" s="6"/>
       <c r="K417" s="7" t="s">
-        <v>720</v>
+        <v>771</v>
       </c>
       <c r="L417" s="7">
         <v>6263</v>
       </c>
       <c r="M417" s="8" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="418" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19067,10 +19108,10 @@
         <v>417</v>
       </c>
       <c r="B418" s="11" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C418" s="7" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="D418" s="6" t="s">
         <v>17</v>
@@ -19088,17 +19129,17 @@
         <v>26</v>
       </c>
       <c r="I418" s="8" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="J418" s="6"/>
       <c r="K418" s="7" t="s">
-        <v>720</v>
+        <v>771</v>
       </c>
       <c r="L418" s="7">
         <v>6263</v>
       </c>
       <c r="M418" s="8" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="419" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19106,10 +19147,10 @@
         <v>418</v>
       </c>
       <c r="B419" s="9" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="C419" s="7" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="D419" s="6" t="s">
         <v>17</v>
@@ -19127,24 +19168,23 @@
         <v>26</v>
       </c>
       <c r="I419" s="8" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="J419" s="6"/>
       <c r="K419" s="7" t="s">
-        <v>720</v>
+        <v>771</v>
       </c>
       <c r="L419" s="7">
         <v>6263</v>
       </c>
       <c r="M419" s="8" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="420" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="F177:G184"/>
-    <mergeCell ref="F200:G203"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/data/transactions/أذونات الإضافة لشهر 3.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F422FE17-76FC-4789-8D5A-C2A8B176F78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2919998B-695B-424F-98C5-82759DDC1C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1281,9 +1281,6 @@
     <t xml:space="preserve">خشب فلندي 3/4 ×4 طول 600 سم عدد 395 مكعب </t>
   </si>
   <si>
-    <t>متر 2</t>
-  </si>
-  <si>
     <t>اخشاب النعام</t>
   </si>
   <si>
@@ -2359,6 +2356,9 @@
   </si>
   <si>
     <t>الرضوان</t>
+  </si>
+  <si>
+    <t>متر 3</t>
   </si>
 </sst>
 </file>
@@ -2682,24 +2682,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2721,6 +2703,24 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3031,7 +3031,7 @@
     </row>
     <row r="3" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L33" s="7">
         <v>6194</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L34" s="7">
         <v>6194</v>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L35" s="7">
         <v>6194</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L36" s="7">
         <v>6194</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="J37" s="6"/>
       <c r="K37" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L37" s="7">
         <v>6194</v>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="J38" s="6"/>
       <c r="K38" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L38" s="7">
         <v>6194</v>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="J39" s="6"/>
       <c r="K39" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L39" s="7">
         <v>6194</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="J40" s="6"/>
       <c r="K40" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L40" s="7">
         <v>6194</v>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="J41" s="6"/>
       <c r="K41" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L41" s="7">
         <v>6194</v>
@@ -6767,7 +6767,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>215</v>
@@ -6806,7 +6806,7 @@
         <v>96</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>217</v>
@@ -6845,7 +6845,7 @@
         <v>97</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>218</v>
@@ -6884,7 +6884,7 @@
         <v>98</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>219</v>
@@ -6923,7 +6923,7 @@
         <v>99</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>220</v>
@@ -6962,7 +6962,7 @@
         <v>100</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>221</v>
@@ -7001,7 +7001,7 @@
         <v>101</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>222</v>
@@ -7040,7 +7040,7 @@
         <v>102</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>223</v>
@@ -7079,7 +7079,7 @@
         <v>103</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>224</v>
@@ -7118,7 +7118,7 @@
         <v>104</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>225</v>
@@ -7157,7 +7157,7 @@
         <v>105</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>247</v>
@@ -7196,7 +7196,7 @@
         <v>106</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>226</v>
@@ -7235,7 +7235,7 @@
         <v>107</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>227</v>
@@ -7274,7 +7274,7 @@
         <v>108</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>228</v>
@@ -7313,7 +7313,7 @@
         <v>109</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>229</v>
@@ -7352,7 +7352,7 @@
         <v>110</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>230</v>
@@ -7391,7 +7391,7 @@
         <v>111</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>231</v>
@@ -7430,7 +7430,7 @@
         <v>112</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>232</v>
@@ -7469,7 +7469,7 @@
         <v>113</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>233</v>
@@ -7508,7 +7508,7 @@
         <v>114</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>234</v>
@@ -7547,7 +7547,7 @@
         <v>115</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>235</v>
@@ -7586,7 +7586,7 @@
         <v>116</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>236</v>
@@ -7625,7 +7625,7 @@
         <v>117</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>237</v>
@@ -7664,7 +7664,7 @@
         <v>118</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>238</v>
@@ -7703,7 +7703,7 @@
         <v>119</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>239</v>
@@ -7742,7 +7742,7 @@
         <v>120</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>240</v>
@@ -7781,7 +7781,7 @@
         <v>121</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>241</v>
@@ -7820,7 +7820,7 @@
         <v>122</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>242</v>
@@ -7859,7 +7859,7 @@
         <v>123</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>243</v>
@@ -7898,7 +7898,7 @@
         <v>124</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>244</v>
@@ -7937,7 +7937,7 @@
         <v>125</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>245</v>
@@ -7976,7 +7976,7 @@
         <v>126</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>246</v>
@@ -8015,7 +8015,7 @@
         <v>127</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>248</v>
@@ -8054,7 +8054,7 @@
         <v>128</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>249</v>
@@ -8093,7 +8093,7 @@
         <v>129</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>250</v>
@@ -8132,7 +8132,7 @@
         <v>130</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>251</v>
@@ -8171,7 +8171,7 @@
         <v>131</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>252</v>
@@ -8210,7 +8210,7 @@
         <v>132</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>253</v>
@@ -8249,7 +8249,7 @@
         <v>133</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>254</v>
@@ -8288,7 +8288,7 @@
         <v>134</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>255</v>
@@ -8327,7 +8327,7 @@
         <v>135</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>256</v>
@@ -8368,7 +8368,7 @@
         <v>136</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C142" s="7" t="s">
         <v>257</v>
@@ -8407,7 +8407,7 @@
         <v>137</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C143" s="7" t="s">
         <v>250</v>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="J150" s="6"/>
       <c r="K150" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L150" s="7">
         <v>6211</v>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="J151" s="6"/>
       <c r="K151" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L151" s="7">
         <v>6211</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="J152" s="6"/>
       <c r="K152" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L152" s="7">
         <v>6211</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="J153" s="6"/>
       <c r="K153" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L153" s="7">
         <v>6211</v>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="J154" s="6"/>
       <c r="K154" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L154" s="7">
         <v>6211</v>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="J155" s="6"/>
       <c r="K155" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L155" s="7">
         <v>6211</v>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="J156" s="6"/>
       <c r="K156" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L156" s="7">
         <v>6211</v>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="J157" s="6"/>
       <c r="K157" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L157" s="7">
         <v>6211</v>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="J158" s="6"/>
       <c r="K158" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L158" s="7">
         <v>6211</v>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="J159" s="6"/>
       <c r="K159" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L159" s="7">
         <v>6211</v>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="J160" s="6"/>
       <c r="K160" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L160" s="7">
         <v>6212</v>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="J161" s="6"/>
       <c r="K161" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L161" s="7">
         <v>6213</v>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="J162" s="6"/>
       <c r="K162" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L162" s="7">
         <v>6213</v>
@@ -9744,10 +9744,10 @@
       <c r="E177" s="21">
         <v>173</v>
       </c>
-      <c r="F177" s="33">
+      <c r="F177" s="42">
         <v>1443407.87</v>
       </c>
-      <c r="G177" s="34"/>
+      <c r="G177" s="43"/>
       <c r="H177" s="21">
         <v>59798</v>
       </c>
@@ -9781,8 +9781,8 @@
       <c r="E178" s="21">
         <v>247</v>
       </c>
-      <c r="F178" s="35"/>
-      <c r="G178" s="36"/>
+      <c r="F178" s="44"/>
+      <c r="G178" s="45"/>
       <c r="H178" s="21">
         <v>59798</v>
       </c>
@@ -9816,8 +9816,8 @@
       <c r="E179" s="21">
         <v>82</v>
       </c>
-      <c r="F179" s="35"/>
-      <c r="G179" s="36"/>
+      <c r="F179" s="44"/>
+      <c r="G179" s="45"/>
       <c r="H179" s="21">
         <v>59798</v>
       </c>
@@ -9851,8 +9851,8 @@
       <c r="E180" s="21">
         <v>125</v>
       </c>
-      <c r="F180" s="35"/>
-      <c r="G180" s="36"/>
+      <c r="F180" s="44"/>
+      <c r="G180" s="45"/>
       <c r="H180" s="21">
         <v>59798</v>
       </c>
@@ -9886,8 +9886,8 @@
       <c r="E181" s="21">
         <v>41</v>
       </c>
-      <c r="F181" s="35"/>
-      <c r="G181" s="36"/>
+      <c r="F181" s="44"/>
+      <c r="G181" s="45"/>
       <c r="H181" s="21">
         <v>59798</v>
       </c>
@@ -9921,8 +9921,8 @@
       <c r="E182" s="21">
         <v>29</v>
       </c>
-      <c r="F182" s="35"/>
-      <c r="G182" s="36"/>
+      <c r="F182" s="44"/>
+      <c r="G182" s="45"/>
       <c r="H182" s="21">
         <v>59798</v>
       </c>
@@ -9956,8 +9956,8 @@
       <c r="E183" s="21">
         <v>118</v>
       </c>
-      <c r="F183" s="35"/>
-      <c r="G183" s="36"/>
+      <c r="F183" s="44"/>
+      <c r="G183" s="45"/>
       <c r="H183" s="21">
         <v>59798</v>
       </c>
@@ -9991,8 +9991,8 @@
       <c r="E184" s="21">
         <v>44</v>
       </c>
-      <c r="F184" s="37"/>
-      <c r="G184" s="38"/>
+      <c r="F184" s="46"/>
+      <c r="G184" s="47"/>
       <c r="H184" s="21">
         <v>59798</v>
       </c>
@@ -10611,10 +10611,10 @@
       <c r="E200" s="21">
         <v>695.99400000000003</v>
       </c>
-      <c r="F200" s="39">
+      <c r="F200" s="33">
         <v>142.98245600000001</v>
       </c>
-      <c r="G200" s="40">
+      <c r="G200" s="34">
         <f>F200*E200</f>
         <v>99514.931481264008</v>
       </c>
@@ -10651,10 +10651,10 @@
       <c r="E201" s="21">
         <v>1175.991</v>
       </c>
-      <c r="F201" s="39">
+      <c r="F201" s="33">
         <v>142.98245600000001</v>
       </c>
-      <c r="G201" s="40">
+      <c r="G201" s="34">
         <f t="shared" ref="G201:G203" si="0">F201*E201</f>
         <v>168146.08141389603</v>
       </c>
@@ -10691,10 +10691,10 @@
       <c r="E202" s="21">
         <v>1800</v>
       </c>
-      <c r="F202" s="39">
+      <c r="F202" s="33">
         <v>142.98245600000001</v>
       </c>
-      <c r="G202" s="40">
+      <c r="G202" s="34">
         <f t="shared" si="0"/>
         <v>257368.42080000002</v>
       </c>
@@ -10731,10 +10731,10 @@
       <c r="E203" s="21">
         <v>2000</v>
       </c>
-      <c r="F203" s="39">
+      <c r="F203" s="33">
         <v>142.98245600000001</v>
       </c>
-      <c r="G203" s="40">
+      <c r="G203" s="34">
         <f t="shared" si="0"/>
         <v>285964.91200000001</v>
       </c>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="J205" s="6"/>
       <c r="K205" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L205" s="7">
         <v>6226</v>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="J206" s="6"/>
       <c r="K206" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L206" s="7">
         <v>6226</v>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="J207" s="6"/>
       <c r="K207" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L207" s="7">
         <v>6226</v>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="J208" s="6"/>
       <c r="K208" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L208" s="7">
         <v>6226</v>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="J209" s="6"/>
       <c r="K209" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L209" s="7">
         <v>6226</v>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="J210" s="6"/>
       <c r="K210" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L210" s="7">
         <v>6226</v>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="J211" s="6"/>
       <c r="K211" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L211" s="7">
         <v>6226</v>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="J212" s="6"/>
       <c r="K212" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L212" s="7">
         <v>6226</v>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="J213" s="6"/>
       <c r="K213" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L213" s="7">
         <v>6226</v>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="J214" s="6"/>
       <c r="K214" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L214" s="7">
         <v>6226</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="J215" s="6"/>
       <c r="K215" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L215" s="7">
         <v>6226</v>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="J216" s="6"/>
       <c r="K216" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L216" s="7">
         <v>6226</v>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="J217" s="6"/>
       <c r="K217" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L217" s="7">
         <v>6226</v>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="J218" s="6"/>
       <c r="K218" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L218" s="7">
         <v>6227</v>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="J219" s="6"/>
       <c r="K219" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L219" s="7">
         <v>6227</v>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="J220" s="6"/>
       <c r="K220" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L220" s="7">
         <v>6227</v>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="J221" s="6"/>
       <c r="K221" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L221" s="7">
         <v>6227</v>
@@ -11540,13 +11540,13 @@
         <v>218</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C224" s="7" t="s">
         <v>413</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>414</v>
+        <v>773</v>
       </c>
       <c r="E224" s="6">
         <v>5.5</v>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="J224" s="6"/>
       <c r="K224" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L224" s="7">
         <v>6229</v>
@@ -11582,7 +11582,7 @@
         <v>40</v>
       </c>
       <c r="C225" s="26" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D225" s="26" t="s">
         <v>75</v>
@@ -11622,7 +11622,7 @@
         <v>43</v>
       </c>
       <c r="C226" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D226" s="26" t="s">
         <v>75</v>
@@ -11659,10 +11659,10 @@
         <v>221</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D227" s="7" t="s">
         <v>17</v>
@@ -11680,7 +11680,7 @@
         <v>13750</v>
       </c>
       <c r="I227" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J227" s="6"/>
       <c r="K227" s="7" t="s">
@@ -11698,10 +11698,10 @@
         <v>222</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D228" s="7" t="s">
         <v>17</v>
@@ -11719,7 +11719,7 @@
         <v>13750</v>
       </c>
       <c r="I228" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J228" s="6"/>
       <c r="K228" s="7" t="s">
@@ -11737,10 +11737,10 @@
         <v>223</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D229" s="7" t="s">
         <v>17</v>
@@ -11758,7 +11758,7 @@
         <v>13750</v>
       </c>
       <c r="I229" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J229" s="6"/>
       <c r="K229" s="7" t="s">
@@ -11776,10 +11776,10 @@
         <v>224</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D230" s="7" t="s">
         <v>17</v>
@@ -11797,11 +11797,11 @@
         <v>34</v>
       </c>
       <c r="I230" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J230" s="6"/>
       <c r="K230" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L230" s="7">
         <v>6232</v>
@@ -11815,10 +11815,10 @@
         <v>225</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D231" s="7" t="s">
         <v>75</v>
@@ -11836,11 +11836,11 @@
         <v>34</v>
       </c>
       <c r="I231" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J231" s="6"/>
       <c r="K231" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L231" s="7">
         <v>6232</v>
@@ -11854,10 +11854,10 @@
         <v>226</v>
       </c>
       <c r="B232" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C232" s="7" t="s">
         <v>437</v>
-      </c>
-      <c r="C232" s="7" t="s">
-        <v>438</v>
       </c>
       <c r="D232" s="7" t="s">
         <v>17</v>
@@ -11875,11 +11875,11 @@
         <v>34</v>
       </c>
       <c r="I232" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J232" s="6"/>
       <c r="K232" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L232" s="7">
         <v>6232</v>
@@ -11893,10 +11893,10 @@
         <v>227</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D233" s="7" t="s">
         <v>75</v>
@@ -11914,11 +11914,11 @@
         <v>34</v>
       </c>
       <c r="I233" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J233" s="6"/>
       <c r="K233" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L233" s="7">
         <v>6232</v>
@@ -11932,10 +11932,10 @@
         <v>228</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D234" s="7" t="s">
         <v>17</v>
@@ -11953,11 +11953,11 @@
         <v>34</v>
       </c>
       <c r="I234" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J234" s="6"/>
       <c r="K234" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L234" s="7">
         <v>6232</v>
@@ -11971,10 +11971,10 @@
         <v>229</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D235" s="7" t="s">
         <v>17</v>
@@ -11992,11 +11992,11 @@
         <v>34</v>
       </c>
       <c r="I235" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J235" s="6"/>
       <c r="K235" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L235" s="7">
         <v>6232</v>
@@ -12010,10 +12010,10 @@
         <v>230</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D236" s="7" t="s">
         <v>17</v>
@@ -12031,11 +12031,11 @@
         <v>34</v>
       </c>
       <c r="I236" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J236" s="6"/>
       <c r="K236" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L236" s="7">
         <v>6232</v>
@@ -12049,10 +12049,10 @@
         <v>231</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D237" s="7" t="s">
         <v>17</v>
@@ -12070,11 +12070,11 @@
         <v>34</v>
       </c>
       <c r="I237" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J237" s="6"/>
       <c r="K237" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L237" s="7">
         <v>6232</v>
@@ -12088,10 +12088,10 @@
         <v>232</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D238" s="7" t="s">
         <v>17</v>
@@ -12109,11 +12109,11 @@
         <v>34</v>
       </c>
       <c r="I238" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J238" s="6"/>
       <c r="K238" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L238" s="7">
         <v>6232</v>
@@ -12127,10 +12127,10 @@
         <v>233</v>
       </c>
       <c r="B239" s="11" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D239" s="7" t="s">
         <v>17</v>
@@ -12148,11 +12148,11 @@
         <v>34</v>
       </c>
       <c r="I239" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J239" s="6"/>
       <c r="K239" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L239" s="7">
         <v>6232</v>
@@ -12166,10 +12166,10 @@
         <v>234</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D240" s="7" t="s">
         <v>17</v>
@@ -12187,11 +12187,11 @@
         <v>35</v>
       </c>
       <c r="I240" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J240" s="6"/>
       <c r="K240" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L240" s="7">
         <v>6233</v>
@@ -12205,10 +12205,10 @@
         <v>235</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D241" s="7" t="s">
         <v>17</v>
@@ -12226,11 +12226,11 @@
         <v>36</v>
       </c>
       <c r="I241" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J241" s="6"/>
       <c r="K241" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L241" s="7">
         <v>6234</v>
@@ -12247,7 +12247,7 @@
         <v>92</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D242" s="7" t="s">
         <v>17</v>
@@ -12265,11 +12265,11 @@
         <v>36</v>
       </c>
       <c r="I242" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J242" s="6"/>
       <c r="K242" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L242" s="7">
         <v>6234</v>
@@ -12283,10 +12283,10 @@
         <v>237</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D243" s="7" t="s">
         <v>17</v>
@@ -12304,11 +12304,11 @@
         <v>36</v>
       </c>
       <c r="I243" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J243" s="6"/>
       <c r="K243" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L243" s="7">
         <v>6234</v>
@@ -12322,10 +12322,10 @@
         <v>238</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D244" s="7" t="s">
         <v>17</v>
@@ -12343,11 +12343,11 @@
         <v>36</v>
       </c>
       <c r="I244" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J244" s="6"/>
       <c r="K244" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L244" s="7">
         <v>6234</v>
@@ -12361,10 +12361,10 @@
         <v>239</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D245" s="7" t="s">
         <v>17</v>
@@ -12382,7 +12382,7 @@
         <v>121</v>
       </c>
       <c r="I245" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J245" s="6"/>
       <c r="K245" s="7" t="s">
@@ -12403,7 +12403,7 @@
         <v>298</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D246" s="7" t="s">
         <v>17</v>
@@ -12421,7 +12421,7 @@
         <v>339</v>
       </c>
       <c r="I246" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J246" s="6"/>
       <c r="K246" s="7" t="s">
@@ -12442,7 +12442,7 @@
         <v>299</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D247" s="7" t="s">
         <v>17</v>
@@ -12460,7 +12460,7 @@
         <v>339</v>
       </c>
       <c r="I247" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J247" s="6"/>
       <c r="K247" s="7" t="s">
@@ -12478,10 +12478,10 @@
         <v>242</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D248" s="7" t="s">
         <v>17</v>
@@ -12499,7 +12499,7 @@
         <v>5166</v>
       </c>
       <c r="I248" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J248" s="6"/>
       <c r="K248" s="7" t="s">
@@ -12517,10 +12517,10 @@
         <v>243</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D249" s="7" t="s">
         <v>17</v>
@@ -12538,7 +12538,7 @@
         <v>5166</v>
       </c>
       <c r="I249" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J249" s="6"/>
       <c r="K249" s="7" t="s">
@@ -12556,10 +12556,10 @@
         <v>244</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D250" s="7" t="s">
         <v>17</v>
@@ -12577,7 +12577,7 @@
         <v>5166</v>
       </c>
       <c r="I250" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J250" s="6"/>
       <c r="K250" s="7" t="s">
@@ -12590,276 +12590,276 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="251" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A251" s="41">
+    <row r="251" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A251" s="35">
         <v>245</v>
       </c>
-      <c r="B251" s="42" t="s">
+      <c r="B251" s="36" t="s">
+        <v>471</v>
+      </c>
+      <c r="C251" s="37" t="s">
+        <v>465</v>
+      </c>
+      <c r="D251" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E251" s="38">
+        <v>100</v>
+      </c>
+      <c r="F251" s="37">
+        <v>204.75</v>
+      </c>
+      <c r="G251" s="37">
+        <v>20475</v>
+      </c>
+      <c r="H251" s="38">
+        <v>83</v>
+      </c>
+      <c r="I251" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="J251" s="38"/>
+      <c r="K251" s="37" t="s">
+        <v>769</v>
+      </c>
+      <c r="L251" s="37">
+        <v>6238</v>
+      </c>
+      <c r="M251" s="39">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A252" s="35">
+        <v>246</v>
+      </c>
+      <c r="B252" s="36" t="s">
         <v>472</v>
       </c>
-      <c r="C251" s="43" t="s">
+      <c r="C252" s="37" t="s">
         <v>466</v>
       </c>
-      <c r="D251" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E251" s="44">
-        <v>100</v>
-      </c>
-      <c r="F251" s="43">
-        <v>204.75</v>
-      </c>
-      <c r="G251" s="43">
-        <v>20475</v>
-      </c>
-      <c r="H251" s="44">
+      <c r="D252" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E252" s="38">
+        <v>2</v>
+      </c>
+      <c r="F252" s="37">
+        <v>526.5</v>
+      </c>
+      <c r="G252" s="37">
+        <v>1053</v>
+      </c>
+      <c r="H252" s="38">
         <v>83</v>
       </c>
-      <c r="I251" s="45" t="s">
-        <v>459</v>
-      </c>
-      <c r="J251" s="44"/>
-      <c r="K251" s="43" t="s">
-        <v>770</v>
-      </c>
-      <c r="L251" s="43">
+      <c r="I252" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="J252" s="38"/>
+      <c r="K252" s="37" t="s">
+        <v>769</v>
+      </c>
+      <c r="L252" s="37">
         <v>6238</v>
       </c>
-      <c r="M251" s="45">
+      <c r="M252" s="39">
         <v>46359</v>
       </c>
     </row>
-    <row r="252" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A252" s="41">
-        <v>246</v>
-      </c>
-      <c r="B252" s="42" t="s">
+    <row r="253" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A253" s="35">
+        <v>247</v>
+      </c>
+      <c r="B253" s="36" t="s">
         <v>473</v>
       </c>
-      <c r="C252" s="43" t="s">
+      <c r="C253" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D252" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E252" s="44">
-        <v>2</v>
-      </c>
-      <c r="F252" s="43">
-        <v>526.5</v>
-      </c>
-      <c r="G252" s="43">
-        <v>1053</v>
-      </c>
-      <c r="H252" s="44">
+      <c r="D253" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E253" s="38">
+        <v>25</v>
+      </c>
+      <c r="F253" s="37">
+        <v>58.5</v>
+      </c>
+      <c r="G253" s="37">
+        <v>1462.5</v>
+      </c>
+      <c r="H253" s="38">
         <v>83</v>
       </c>
-      <c r="I252" s="45" t="s">
-        <v>459</v>
-      </c>
-      <c r="J252" s="44"/>
-      <c r="K252" s="43" t="s">
-        <v>770</v>
-      </c>
-      <c r="L252" s="43">
+      <c r="I253" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="J253" s="38"/>
+      <c r="K253" s="37" t="s">
+        <v>769</v>
+      </c>
+      <c r="L253" s="37">
         <v>6238</v>
       </c>
-      <c r="M252" s="45">
+      <c r="M253" s="39">
         <v>46359</v>
       </c>
     </row>
-    <row r="253" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="41">
-        <v>247</v>
-      </c>
-      <c r="B253" s="42" t="s">
+    <row r="254" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A254" s="35">
+        <v>248</v>
+      </c>
+      <c r="B254" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="C254" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D254" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E254" s="38">
+        <v>1</v>
+      </c>
+      <c r="F254" s="37">
+        <v>3100.5</v>
+      </c>
+      <c r="G254" s="37">
+        <v>3100.5</v>
+      </c>
+      <c r="H254" s="38">
+        <v>83</v>
+      </c>
+      <c r="I254" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="J254" s="38"/>
+      <c r="K254" s="37" t="s">
+        <v>769</v>
+      </c>
+      <c r="L254" s="37">
+        <v>6238</v>
+      </c>
+      <c r="M254" s="39">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A255" s="35">
+        <v>249</v>
+      </c>
+      <c r="B255" s="36" t="s">
         <v>474</v>
       </c>
-      <c r="C253" s="43" t="s">
+      <c r="C255" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="D253" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E253" s="44">
-        <v>25</v>
-      </c>
-      <c r="F253" s="43">
-        <v>58.5</v>
-      </c>
-      <c r="G253" s="43">
-        <v>1462.5</v>
-      </c>
-      <c r="H253" s="44">
+      <c r="D255" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E255" s="38">
+        <v>1</v>
+      </c>
+      <c r="F255" s="37">
+        <v>3393</v>
+      </c>
+      <c r="G255" s="37">
+        <v>3393</v>
+      </c>
+      <c r="H255" s="38">
         <v>83</v>
       </c>
-      <c r="I253" s="45" t="s">
-        <v>459</v>
-      </c>
-      <c r="J253" s="44"/>
-      <c r="K253" s="43" t="s">
-        <v>770</v>
-      </c>
-      <c r="L253" s="43">
+      <c r="I255" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="J255" s="38"/>
+      <c r="K255" s="37" t="s">
+        <v>769</v>
+      </c>
+      <c r="L255" s="37">
         <v>6238</v>
       </c>
-      <c r="M253" s="45">
+      <c r="M255" s="39">
         <v>46359</v>
       </c>
     </row>
-    <row r="254" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A254" s="41">
-        <v>248</v>
-      </c>
-      <c r="B254" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C254" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="D254" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E254" s="44">
+    <row r="256" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A256" s="35">
+        <v>250</v>
+      </c>
+      <c r="B256" s="41" t="s">
+        <v>475</v>
+      </c>
+      <c r="C256" s="37" t="s">
+        <v>469</v>
+      </c>
+      <c r="D256" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E256" s="38">
         <v>1</v>
       </c>
-      <c r="F254" s="43">
-        <v>3100.5</v>
-      </c>
-      <c r="G254" s="43">
-        <v>3100.5</v>
-      </c>
-      <c r="H254" s="44">
+      <c r="F256" s="37">
+        <v>152.1</v>
+      </c>
+      <c r="G256" s="37">
+        <v>152.1</v>
+      </c>
+      <c r="H256" s="38">
         <v>83</v>
       </c>
-      <c r="I254" s="45" t="s">
-        <v>459</v>
-      </c>
-      <c r="J254" s="44"/>
-      <c r="K254" s="43" t="s">
-        <v>770</v>
-      </c>
-      <c r="L254" s="43">
+      <c r="I256" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="J256" s="38"/>
+      <c r="K256" s="37" t="s">
+        <v>769</v>
+      </c>
+      <c r="L256" s="37">
         <v>6238</v>
       </c>
-      <c r="M254" s="45">
+      <c r="M256" s="39">
         <v>46359</v>
       </c>
     </row>
-    <row r="255" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A255" s="41">
-        <v>249</v>
-      </c>
-      <c r="B255" s="42" t="s">
-        <v>475</v>
-      </c>
-      <c r="C255" s="43" t="s">
-        <v>469</v>
-      </c>
-      <c r="D255" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E255" s="44">
+    <row r="257" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A257" s="35">
+        <v>251</v>
+      </c>
+      <c r="B257" s="41" t="s">
+        <v>476</v>
+      </c>
+      <c r="C257" s="37" t="s">
+        <v>470</v>
+      </c>
+      <c r="D257" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E257" s="38">
         <v>1</v>
       </c>
-      <c r="F255" s="43">
-        <v>3393</v>
-      </c>
-      <c r="G255" s="43">
-        <v>3393</v>
-      </c>
-      <c r="H255" s="44">
+      <c r="F257" s="37">
+        <v>157.94999999999999</v>
+      </c>
+      <c r="G257" s="37">
+        <v>157.94999999999999</v>
+      </c>
+      <c r="H257" s="38">
         <v>83</v>
       </c>
-      <c r="I255" s="45" t="s">
-        <v>459</v>
-      </c>
-      <c r="J255" s="44"/>
-      <c r="K255" s="43" t="s">
-        <v>770</v>
-      </c>
-      <c r="L255" s="43">
+      <c r="I257" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="J257" s="38"/>
+      <c r="K257" s="37" t="s">
+        <v>769</v>
+      </c>
+      <c r="L257" s="37">
         <v>6238</v>
       </c>
-      <c r="M255" s="45">
-        <v>46359</v>
-      </c>
-    </row>
-    <row r="256" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A256" s="41">
-        <v>250</v>
-      </c>
-      <c r="B256" s="47" t="s">
-        <v>476</v>
-      </c>
-      <c r="C256" s="43" t="s">
-        <v>470</v>
-      </c>
-      <c r="D256" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E256" s="44">
-        <v>1</v>
-      </c>
-      <c r="F256" s="43">
-        <v>152.1</v>
-      </c>
-      <c r="G256" s="43">
-        <v>152.1</v>
-      </c>
-      <c r="H256" s="44">
-        <v>83</v>
-      </c>
-      <c r="I256" s="45" t="s">
-        <v>459</v>
-      </c>
-      <c r="J256" s="44"/>
-      <c r="K256" s="43" t="s">
-        <v>770</v>
-      </c>
-      <c r="L256" s="43">
-        <v>6238</v>
-      </c>
-      <c r="M256" s="45">
-        <v>46359</v>
-      </c>
-    </row>
-    <row r="257" spans="1:13" s="46" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A257" s="41">
-        <v>251</v>
-      </c>
-      <c r="B257" s="47" t="s">
-        <v>477</v>
-      </c>
-      <c r="C257" s="43" t="s">
-        <v>471</v>
-      </c>
-      <c r="D257" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E257" s="44">
-        <v>1</v>
-      </c>
-      <c r="F257" s="43">
-        <v>157.94999999999999</v>
-      </c>
-      <c r="G257" s="43">
-        <v>157.94999999999999</v>
-      </c>
-      <c r="H257" s="44">
-        <v>83</v>
-      </c>
-      <c r="I257" s="45" t="s">
-        <v>459</v>
-      </c>
-      <c r="J257" s="44"/>
-      <c r="K257" s="43" t="s">
-        <v>770</v>
-      </c>
-      <c r="L257" s="43">
-        <v>6238</v>
-      </c>
-      <c r="M257" s="45">
+      <c r="M257" s="39">
         <v>46359</v>
       </c>
     </row>
@@ -12868,10 +12868,10 @@
         <v>252</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D258" s="7" t="s">
         <v>17</v>
@@ -12889,11 +12889,11 @@
         <v>39</v>
       </c>
       <c r="I258" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J258" s="6"/>
       <c r="K258" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L258" s="7">
         <v>6239</v>
@@ -12907,10 +12907,10 @@
         <v>253</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D259" s="7" t="s">
         <v>17</v>
@@ -12928,11 +12928,11 @@
         <v>39</v>
       </c>
       <c r="I259" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J259" s="6"/>
       <c r="K259" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L259" s="7">
         <v>6239</v>
@@ -12949,7 +12949,7 @@
         <v>92</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D260" s="7" t="s">
         <v>17</v>
@@ -12967,11 +12967,11 @@
         <v>39</v>
       </c>
       <c r="I260" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J260" s="6"/>
       <c r="K260" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L260" s="7">
         <v>6239</v>
@@ -12985,10 +12985,10 @@
         <v>255</v>
       </c>
       <c r="B261" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="C261" s="7" t="s">
         <v>480</v>
-      </c>
-      <c r="C261" s="7" t="s">
-        <v>481</v>
       </c>
       <c r="D261" s="7" t="s">
         <v>17</v>
@@ -13006,11 +13006,11 @@
         <v>39</v>
       </c>
       <c r="I261" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J261" s="6"/>
       <c r="K261" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L261" s="7">
         <v>6239</v>
@@ -13024,10 +13024,10 @@
         <v>256</v>
       </c>
       <c r="B262" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D262" s="7" t="s">
         <v>17</v>
@@ -13045,7 +13045,7 @@
         <v>2437</v>
       </c>
       <c r="I262" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J262" s="6"/>
       <c r="K262" s="7" t="s">
@@ -13063,10 +13063,10 @@
         <v>257</v>
       </c>
       <c r="B263" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D263" s="7" t="s">
         <v>17</v>
@@ -13084,7 +13084,7 @@
         <v>2437</v>
       </c>
       <c r="I263" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J263" s="6"/>
       <c r="K263" s="7" t="s">
@@ -13102,13 +13102,13 @@
         <v>258</v>
       </c>
       <c r="B264" s="11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D264" s="7" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E264" s="6">
         <v>1</v>
@@ -13123,7 +13123,7 @@
         <v>2437</v>
       </c>
       <c r="I264" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J264" s="6"/>
       <c r="K264" s="7" t="s">
@@ -13141,10 +13141,10 @@
         <v>259</v>
       </c>
       <c r="B265" s="11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D265" s="7" t="s">
         <v>17</v>
@@ -13162,7 +13162,7 @@
         <v>2437</v>
       </c>
       <c r="I265" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J265" s="6"/>
       <c r="K265" s="7" t="s">
@@ -13180,10 +13180,10 @@
         <v>260</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D266" s="7" t="s">
         <v>17</v>
@@ -13201,7 +13201,7 @@
         <v>2437</v>
       </c>
       <c r="I266" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J266" s="6"/>
       <c r="K266" s="7" t="s">
@@ -13219,10 +13219,10 @@
         <v>261</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D267" s="7" t="s">
         <v>17</v>
@@ -13240,7 +13240,7 @@
         <v>2437</v>
       </c>
       <c r="I267" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J267" s="6"/>
       <c r="K267" s="7" t="s">
@@ -13258,10 +13258,10 @@
         <v>262</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D268" s="7" t="s">
         <v>17</v>
@@ -13279,7 +13279,7 @@
         <v>2437</v>
       </c>
       <c r="I268" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J268" s="6"/>
       <c r="K268" s="7" t="s">
@@ -13297,10 +13297,10 @@
         <v>263</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D269" s="7" t="s">
         <v>17</v>
@@ -13318,7 +13318,7 @@
         <v>2437</v>
       </c>
       <c r="I269" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J269" s="6"/>
       <c r="K269" s="7" t="s">
@@ -13336,10 +13336,10 @@
         <v>264</v>
       </c>
       <c r="B270" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D270" s="7" t="s">
         <v>17</v>
@@ -13357,7 +13357,7 @@
         <v>2437</v>
       </c>
       <c r="I270" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J270" s="6"/>
       <c r="K270" s="7" t="s">
@@ -13375,10 +13375,10 @@
         <v>265</v>
       </c>
       <c r="B271" s="11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D271" s="7" t="s">
         <v>17</v>
@@ -13396,7 +13396,7 @@
         <v>2437</v>
       </c>
       <c r="I271" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J271" s="6"/>
       <c r="K271" s="7" t="s">
@@ -13414,10 +13414,10 @@
         <v>266</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D272" s="7" t="s">
         <v>17</v>
@@ -13435,7 +13435,7 @@
         <v>2437</v>
       </c>
       <c r="I272" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J272" s="6"/>
       <c r="K272" s="7" t="s">
@@ -13453,10 +13453,10 @@
         <v>267</v>
       </c>
       <c r="B273" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D273" s="7" t="s">
         <v>17</v>
@@ -13474,7 +13474,7 @@
         <v>2437</v>
       </c>
       <c r="I273" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J273" s="6"/>
       <c r="K273" s="7" t="s">
@@ -13492,10 +13492,10 @@
         <v>268</v>
       </c>
       <c r="B274" s="11" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D274" s="7" t="s">
         <v>17</v>
@@ -13513,7 +13513,7 @@
         <v>2437</v>
       </c>
       <c r="I274" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J274" s="6"/>
       <c r="K274" s="7" t="s">
@@ -13531,10 +13531,10 @@
         <v>269</v>
       </c>
       <c r="B275" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D275" s="7" t="s">
         <v>17</v>
@@ -13552,7 +13552,7 @@
         <v>2437</v>
       </c>
       <c r="I275" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J275" s="6"/>
       <c r="K275" s="7" t="s">
@@ -13570,10 +13570,10 @@
         <v>270</v>
       </c>
       <c r="B276" s="11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D276" s="7" t="s">
         <v>17</v>
@@ -13591,7 +13591,7 @@
         <v>2437</v>
       </c>
       <c r="I276" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J276" s="6"/>
       <c r="K276" s="7" t="s">
@@ -13609,10 +13609,10 @@
         <v>271</v>
       </c>
       <c r="B277" s="12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D277" s="7" t="s">
         <v>17</v>
@@ -13630,7 +13630,7 @@
         <v>2437</v>
       </c>
       <c r="I277" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J277" s="6"/>
       <c r="K277" s="7" t="s">
@@ -13648,10 +13648,10 @@
         <v>272</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D278" s="7" t="s">
         <v>17</v>
@@ -13669,7 +13669,7 @@
         <v>2437</v>
       </c>
       <c r="I278" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J278" s="6"/>
       <c r="K278" s="7" t="s">
@@ -13687,10 +13687,10 @@
         <v>273</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D279" s="7" t="s">
         <v>17</v>
@@ -13708,7 +13708,7 @@
         <v>2437</v>
       </c>
       <c r="I279" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J279" s="6"/>
       <c r="K279" s="7" t="s">
@@ -13726,10 +13726,10 @@
         <v>274</v>
       </c>
       <c r="B280" s="15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D280" s="7" t="s">
         <v>17</v>
@@ -13747,7 +13747,7 @@
         <v>2437</v>
       </c>
       <c r="I280" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J280" s="6"/>
       <c r="K280" s="7" t="s">
@@ -13765,10 +13765,10 @@
         <v>275</v>
       </c>
       <c r="B281" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D281" s="7" t="s">
         <v>17</v>
@@ -13786,7 +13786,7 @@
         <v>2437</v>
       </c>
       <c r="I281" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J281" s="6"/>
       <c r="K281" s="7" t="s">
@@ -13804,10 +13804,10 @@
         <v>276</v>
       </c>
       <c r="B282" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D282" s="7" t="s">
         <v>17</v>
@@ -13825,7 +13825,7 @@
         <v>2437</v>
       </c>
       <c r="I282" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J282" s="6"/>
       <c r="K282" s="7" t="s">
@@ -13843,10 +13843,10 @@
         <v>277</v>
       </c>
       <c r="B283" s="11" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D283" s="7" t="s">
         <v>17</v>
@@ -13864,7 +13864,7 @@
         <v>2437</v>
       </c>
       <c r="I283" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J283" s="6"/>
       <c r="K283" s="7" t="s">
@@ -13882,10 +13882,10 @@
         <v>278</v>
       </c>
       <c r="B284" s="15" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D284" s="7" t="s">
         <v>17</v>
@@ -13903,7 +13903,7 @@
         <v>2437</v>
       </c>
       <c r="I284" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J284" s="6"/>
       <c r="K284" s="7" t="s">
@@ -13921,10 +13921,10 @@
         <v>279</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D285" s="7" t="s">
         <v>17</v>
@@ -13942,7 +13942,7 @@
         <v>2437</v>
       </c>
       <c r="I285" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J285" s="6"/>
       <c r="K285" s="7" t="s">
@@ -13960,10 +13960,10 @@
         <v>280</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D286" s="7" t="s">
         <v>17</v>
@@ -13981,7 +13981,7 @@
         <v>2437</v>
       </c>
       <c r="I286" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J286" s="6"/>
       <c r="K286" s="7" t="s">
@@ -13999,10 +13999,10 @@
         <v>281</v>
       </c>
       <c r="B287" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D287" s="7" t="s">
         <v>17</v>
@@ -14020,7 +14020,7 @@
         <v>2437</v>
       </c>
       <c r="I287" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J287" s="6"/>
       <c r="K287" s="7" t="s">
@@ -14038,10 +14038,10 @@
         <v>282</v>
       </c>
       <c r="B288" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D288" s="7" t="s">
         <v>17</v>
@@ -14059,7 +14059,7 @@
         <v>2437</v>
       </c>
       <c r="I288" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J288" s="6"/>
       <c r="K288" s="7" t="s">
@@ -14077,10 +14077,10 @@
         <v>283</v>
       </c>
       <c r="B289" s="15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D289" s="7" t="s">
         <v>17</v>
@@ -14098,7 +14098,7 @@
         <v>2437</v>
       </c>
       <c r="I289" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J289" s="6"/>
       <c r="K289" s="7" t="s">
@@ -14116,10 +14116,10 @@
         <v>284</v>
       </c>
       <c r="B290" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D290" s="7" t="s">
         <v>17</v>
@@ -14137,7 +14137,7 @@
         <v>2437</v>
       </c>
       <c r="I290" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J290" s="6"/>
       <c r="K290" s="7" t="s">
@@ -14155,10 +14155,10 @@
         <v>285</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D291" s="7" t="s">
         <v>17</v>
@@ -14176,7 +14176,7 @@
         <v>2437</v>
       </c>
       <c r="I291" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J291" s="6"/>
       <c r="K291" s="7" t="s">
@@ -14194,10 +14194,10 @@
         <v>286</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D292" s="7" t="s">
         <v>17</v>
@@ -14215,7 +14215,7 @@
         <v>2437</v>
       </c>
       <c r="I292" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J292" s="6"/>
       <c r="K292" s="7" t="s">
@@ -14233,10 +14233,10 @@
         <v>287</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D293" s="7" t="s">
         <v>17</v>
@@ -14254,7 +14254,7 @@
         <v>2437</v>
       </c>
       <c r="I293" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J293" s="6"/>
       <c r="K293" s="7" t="s">
@@ -14272,10 +14272,10 @@
         <v>288</v>
       </c>
       <c r="B294" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D294" s="7" t="s">
         <v>17</v>
@@ -14293,7 +14293,7 @@
         <v>2437</v>
       </c>
       <c r="I294" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J294" s="6"/>
       <c r="K294" s="7" t="s">
@@ -14311,10 +14311,10 @@
         <v>289</v>
       </c>
       <c r="B295" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D295" s="7" t="s">
         <v>17</v>
@@ -14332,7 +14332,7 @@
         <v>1480</v>
       </c>
       <c r="I295" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J295" s="6"/>
       <c r="K295" s="7" t="s">
@@ -14350,10 +14350,10 @@
         <v>290</v>
       </c>
       <c r="B296" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D296" s="7" t="s">
         <v>17</v>
@@ -14371,7 +14371,7 @@
         <v>1480</v>
       </c>
       <c r="I296" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J296" s="6"/>
       <c r="K296" s="7" t="s">
@@ -14389,10 +14389,10 @@
         <v>291</v>
       </c>
       <c r="B297" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D297" s="7" t="s">
         <v>75</v>
@@ -14410,11 +14410,11 @@
         <v>809</v>
       </c>
       <c r="I297" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J297" s="6"/>
       <c r="K297" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L297" s="7">
         <v>6244</v>
@@ -14428,10 +14428,10 @@
         <v>292</v>
       </c>
       <c r="B298" s="9" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D298" s="7" t="s">
         <v>75</v>
@@ -14449,11 +14449,11 @@
         <v>809</v>
       </c>
       <c r="I298" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J298" s="6"/>
       <c r="K298" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L298" s="7">
         <v>6244</v>
@@ -14467,10 +14467,10 @@
         <v>293</v>
       </c>
       <c r="B299" s="9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D299" s="7" t="s">
         <v>17</v>
@@ -14488,11 +14488,11 @@
         <v>34382</v>
       </c>
       <c r="I299" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J299" s="6"/>
       <c r="K299" s="7" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L299" s="7">
         <v>6245</v>
@@ -14506,10 +14506,10 @@
         <v>294</v>
       </c>
       <c r="B300" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D300" s="7" t="s">
         <v>17</v>
@@ -14527,11 +14527,11 @@
         <v>34382</v>
       </c>
       <c r="I300" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J300" s="6"/>
       <c r="K300" s="7" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L300" s="7">
         <v>6245</v>
@@ -14545,10 +14545,10 @@
         <v>295</v>
       </c>
       <c r="B301" s="9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D301" s="7" t="s">
         <v>17</v>
@@ -14566,11 +14566,11 @@
         <v>34382</v>
       </c>
       <c r="I301" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J301" s="6"/>
       <c r="K301" s="7" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L301" s="7">
         <v>6245</v>
@@ -14584,10 +14584,10 @@
         <v>296</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D302" s="7" t="s">
         <v>17</v>
@@ -14605,7 +14605,7 @@
         <v>394</v>
       </c>
       <c r="I302" s="8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J302" s="6"/>
       <c r="K302" s="7" t="s">
@@ -14615,7 +14615,7 @@
         <v>6246</v>
       </c>
       <c r="M302" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="303" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14623,10 +14623,10 @@
         <v>297</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D303" s="7" t="s">
         <v>17</v>
@@ -14644,7 +14644,7 @@
         <v>394</v>
       </c>
       <c r="I303" s="8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J303" s="6"/>
       <c r="K303" s="7" t="s">
@@ -14654,7 +14654,7 @@
         <v>6246</v>
       </c>
       <c r="M303" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="304" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14662,10 +14662,10 @@
         <v>298</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D304" s="7" t="s">
         <v>17</v>
@@ -14683,17 +14683,17 @@
         <v>42</v>
       </c>
       <c r="I304" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J304" s="6"/>
       <c r="K304" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L304" s="7">
         <v>6247</v>
       </c>
       <c r="M304" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="305" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14701,10 +14701,10 @@
         <v>299</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D305" s="7" t="s">
         <v>17</v>
@@ -14722,17 +14722,17 @@
         <v>42</v>
       </c>
       <c r="I305" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J305" s="6"/>
       <c r="K305" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L305" s="7">
         <v>6247</v>
       </c>
       <c r="M305" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="306" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14740,10 +14740,10 @@
         <v>300</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D306" s="7" t="s">
         <v>17</v>
@@ -14761,17 +14761,17 @@
         <v>42</v>
       </c>
       <c r="I306" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J306" s="6"/>
       <c r="K306" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L306" s="7">
         <v>6247</v>
       </c>
       <c r="M306" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="307" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14779,10 +14779,10 @@
         <v>301</v>
       </c>
       <c r="B307" s="9" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D307" s="7" t="s">
         <v>17</v>
@@ -14800,17 +14800,17 @@
         <v>42</v>
       </c>
       <c r="I307" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J307" s="6"/>
       <c r="K307" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L307" s="7">
         <v>6247</v>
       </c>
       <c r="M307" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="308" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14818,10 +14818,10 @@
         <v>302</v>
       </c>
       <c r="B308" s="9" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D308" s="7" t="s">
         <v>17</v>
@@ -14839,17 +14839,17 @@
         <v>42</v>
       </c>
       <c r="I308" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J308" s="6"/>
       <c r="K308" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L308" s="7">
         <v>6247</v>
       </c>
       <c r="M308" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="309" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14857,10 +14857,10 @@
         <v>303</v>
       </c>
       <c r="B309" s="9" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D309" s="7" t="s">
         <v>17</v>
@@ -14878,17 +14878,17 @@
         <v>42</v>
       </c>
       <c r="I309" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J309" s="6"/>
       <c r="K309" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L309" s="7">
         <v>6247</v>
       </c>
       <c r="M309" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="310" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14896,10 +14896,10 @@
         <v>304</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D310" s="7" t="s">
         <v>17</v>
@@ -14917,17 +14917,17 @@
         <v>42</v>
       </c>
       <c r="I310" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J310" s="6"/>
       <c r="K310" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L310" s="7">
         <v>6247</v>
       </c>
       <c r="M310" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="311" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14956,17 +14956,17 @@
         <v>42</v>
       </c>
       <c r="I311" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J311" s="6"/>
       <c r="K311" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L311" s="7">
         <v>6247</v>
       </c>
       <c r="M311" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14974,10 +14974,10 @@
         <v>306</v>
       </c>
       <c r="B312" s="9" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D312" s="7" t="s">
         <v>17</v>
@@ -14995,17 +14995,17 @@
         <v>42</v>
       </c>
       <c r="I312" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J312" s="6"/>
       <c r="K312" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L312" s="7">
         <v>6247</v>
       </c>
       <c r="M312" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15044,7 +15044,7 @@
         <v>6248</v>
       </c>
       <c r="M313" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="314" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15052,10 +15052,10 @@
         <v>308</v>
       </c>
       <c r="B314" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="C314" s="17" t="s">
         <v>631</v>
-      </c>
-      <c r="C314" s="17" t="s">
-        <v>632</v>
       </c>
       <c r="D314" s="6" t="s">
         <v>17</v>
@@ -15073,7 +15073,7 @@
         <v>89598</v>
       </c>
       <c r="I314" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J314" s="6"/>
       <c r="K314" s="7" t="s">
@@ -15083,7 +15083,7 @@
         <v>6250</v>
       </c>
       <c r="M314" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="315" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15091,10 +15091,10 @@
         <v>309</v>
       </c>
       <c r="B315" s="16" t="s">
+        <v>632</v>
+      </c>
+      <c r="C315" s="17" t="s">
         <v>633</v>
-      </c>
-      <c r="C315" s="17" t="s">
-        <v>634</v>
       </c>
       <c r="D315" s="6" t="s">
         <v>17</v>
@@ -15112,7 +15112,7 @@
         <v>89598</v>
       </c>
       <c r="I315" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J315" s="6"/>
       <c r="K315" s="7" t="s">
@@ -15122,7 +15122,7 @@
         <v>6250</v>
       </c>
       <c r="M315" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="316" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15130,10 +15130,10 @@
         <v>310</v>
       </c>
       <c r="B316" s="16" t="s">
+        <v>634</v>
+      </c>
+      <c r="C316" s="17" t="s">
         <v>635</v>
-      </c>
-      <c r="C316" s="17" t="s">
-        <v>636</v>
       </c>
       <c r="D316" s="6" t="s">
         <v>17</v>
@@ -15151,7 +15151,7 @@
         <v>89598</v>
       </c>
       <c r="I316" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J316" s="6"/>
       <c r="K316" s="7" t="s">
@@ -15161,7 +15161,7 @@
         <v>6250</v>
       </c>
       <c r="M316" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="317" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15169,10 +15169,10 @@
         <v>311</v>
       </c>
       <c r="B317" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="C317" s="17" t="s">
         <v>637</v>
-      </c>
-      <c r="C317" s="17" t="s">
-        <v>638</v>
       </c>
       <c r="D317" s="6" t="s">
         <v>17</v>
@@ -15190,7 +15190,7 @@
         <v>89598</v>
       </c>
       <c r="I317" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J317" s="6"/>
       <c r="K317" s="7" t="s">
@@ -15200,7 +15200,7 @@
         <v>6250</v>
       </c>
       <c r="M317" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="318" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15208,10 +15208,10 @@
         <v>312</v>
       </c>
       <c r="B318" s="16" t="s">
+        <v>638</v>
+      </c>
+      <c r="C318" s="17" t="s">
         <v>639</v>
-      </c>
-      <c r="C318" s="17" t="s">
-        <v>640</v>
       </c>
       <c r="D318" s="6" t="s">
         <v>17</v>
@@ -15229,7 +15229,7 @@
         <v>89598</v>
       </c>
       <c r="I318" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J318" s="6"/>
       <c r="K318" s="7" t="s">
@@ -15239,7 +15239,7 @@
         <v>6250</v>
       </c>
       <c r="M318" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="319" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15247,10 +15247,10 @@
         <v>313</v>
       </c>
       <c r="B319" s="16" t="s">
+        <v>640</v>
+      </c>
+      <c r="C319" s="17" t="s">
         <v>641</v>
-      </c>
-      <c r="C319" s="17" t="s">
-        <v>642</v>
       </c>
       <c r="D319" s="6" t="s">
         <v>17</v>
@@ -15268,7 +15268,7 @@
         <v>89598</v>
       </c>
       <c r="I319" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J319" s="6"/>
       <c r="K319" s="7" t="s">
@@ -15278,7 +15278,7 @@
         <v>6250</v>
       </c>
       <c r="M319" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="320" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15286,10 +15286,10 @@
         <v>314</v>
       </c>
       <c r="B320" s="16" t="s">
+        <v>642</v>
+      </c>
+      <c r="C320" s="17" t="s">
         <v>643</v>
-      </c>
-      <c r="C320" s="17" t="s">
-        <v>644</v>
       </c>
       <c r="D320" s="6" t="s">
         <v>17</v>
@@ -15307,7 +15307,7 @@
         <v>89598</v>
       </c>
       <c r="I320" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J320" s="6"/>
       <c r="K320" s="7" t="s">
@@ -15317,7 +15317,7 @@
         <v>6250</v>
       </c>
       <c r="M320" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="321" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15325,10 +15325,10 @@
         <v>315</v>
       </c>
       <c r="B321" s="16" t="s">
+        <v>644</v>
+      </c>
+      <c r="C321" s="17" t="s">
         <v>645</v>
-      </c>
-      <c r="C321" s="17" t="s">
-        <v>646</v>
       </c>
       <c r="D321" s="6" t="s">
         <v>17</v>
@@ -15346,7 +15346,7 @@
         <v>89598</v>
       </c>
       <c r="I321" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J321" s="6"/>
       <c r="K321" s="7" t="s">
@@ -15356,7 +15356,7 @@
         <v>6250</v>
       </c>
       <c r="M321" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="322" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15364,10 +15364,10 @@
         <v>316</v>
       </c>
       <c r="B322" s="11" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D322" s="6" t="s">
         <v>17</v>
@@ -15385,17 +15385,17 @@
         <v>420</v>
       </c>
       <c r="I322" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J322" s="6"/>
       <c r="K322" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L322" s="7">
         <v>6252</v>
       </c>
       <c r="M322" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="323" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15403,10 +15403,10 @@
         <v>317</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C323" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D323" s="6" t="s">
         <v>17</v>
@@ -15424,17 +15424,17 @@
         <v>420</v>
       </c>
       <c r="I323" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J323" s="6"/>
       <c r="K323" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L323" s="7">
         <v>6252</v>
       </c>
       <c r="M323" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="324" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15442,10 +15442,10 @@
         <v>318</v>
       </c>
       <c r="B324" s="11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D324" s="6" t="s">
         <v>17</v>
@@ -15463,17 +15463,17 @@
         <v>420</v>
       </c>
       <c r="I324" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J324" s="6"/>
       <c r="K324" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L324" s="7">
         <v>6252</v>
       </c>
       <c r="M324" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="325" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15481,10 +15481,10 @@
         <v>319</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C325" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D325" s="6" t="s">
         <v>17</v>
@@ -15502,17 +15502,17 @@
         <v>420</v>
       </c>
       <c r="I325" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J325" s="6"/>
       <c r="K325" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L325" s="7">
         <v>6252</v>
       </c>
       <c r="M325" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="326" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15520,10 +15520,10 @@
         <v>320</v>
       </c>
       <c r="B326" s="11" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C326" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D326" s="6" t="s">
         <v>17</v>
@@ -15541,17 +15541,17 @@
         <v>420</v>
       </c>
       <c r="I326" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J326" s="6"/>
       <c r="K326" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L326" s="7">
         <v>6252</v>
       </c>
       <c r="M326" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="327" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15559,10 +15559,10 @@
         <v>321</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C327" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D327" s="6" t="s">
         <v>17</v>
@@ -15580,17 +15580,17 @@
         <v>420</v>
       </c>
       <c r="I327" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J327" s="6"/>
       <c r="K327" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L327" s="7">
         <v>6252</v>
       </c>
       <c r="M327" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="328" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15598,10 +15598,10 @@
         <v>322</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C328" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D328" s="6" t="s">
         <v>17</v>
@@ -15619,17 +15619,17 @@
         <v>420</v>
       </c>
       <c r="I328" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J328" s="6"/>
       <c r="K328" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L328" s="7">
         <v>6252</v>
       </c>
       <c r="M328" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="329" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15637,10 +15637,10 @@
         <v>323</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C329" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D329" s="6" t="s">
         <v>17</v>
@@ -15658,17 +15658,17 @@
         <v>420</v>
       </c>
       <c r="I329" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J329" s="6"/>
       <c r="K329" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L329" s="7">
         <v>6252</v>
       </c>
       <c r="M329" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="330" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15676,10 +15676,10 @@
         <v>324</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C330" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>17</v>
@@ -15697,17 +15697,17 @@
         <v>420</v>
       </c>
       <c r="I330" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J330" s="6"/>
       <c r="K330" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L330" s="7">
         <v>6252</v>
       </c>
       <c r="M330" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="331" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15718,7 +15718,7 @@
         <v>298</v>
       </c>
       <c r="C331" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D331" s="6" t="s">
         <v>17</v>
@@ -15736,17 +15736,17 @@
         <v>420</v>
       </c>
       <c r="I331" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J331" s="6"/>
       <c r="K331" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L331" s="7">
         <v>6252</v>
       </c>
       <c r="M331" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="332" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15754,10 +15754,10 @@
         <v>326</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D332" s="6" t="s">
         <v>17</v>
@@ -15775,17 +15775,17 @@
         <v>420</v>
       </c>
       <c r="I332" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J332" s="6"/>
       <c r="K332" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L332" s="7">
         <v>6252</v>
       </c>
       <c r="M332" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="333" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15793,10 +15793,10 @@
         <v>327</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C333" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D333" s="6" t="s">
         <v>17</v>
@@ -15814,17 +15814,17 @@
         <v>420</v>
       </c>
       <c r="I333" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J333" s="6"/>
       <c r="K333" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L333" s="7">
         <v>6252</v>
       </c>
       <c r="M333" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="334" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15832,10 +15832,10 @@
         <v>328</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C334" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D334" s="6" t="s">
         <v>17</v>
@@ -15853,17 +15853,17 @@
         <v>420</v>
       </c>
       <c r="I334" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J334" s="6"/>
       <c r="K334" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L334" s="7">
         <v>6253</v>
       </c>
       <c r="M334" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="335" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15871,10 +15871,10 @@
         <v>329</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D335" s="6" t="s">
         <v>17</v>
@@ -15892,17 +15892,17 @@
         <v>420</v>
       </c>
       <c r="I335" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J335" s="6"/>
       <c r="K335" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L335" s="7">
         <v>6253</v>
       </c>
       <c r="M335" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="336" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15910,10 +15910,10 @@
         <v>330</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C336" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D336" s="6" t="s">
         <v>17</v>
@@ -15931,17 +15931,17 @@
         <v>420</v>
       </c>
       <c r="I336" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J336" s="6"/>
       <c r="K336" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L336" s="7">
         <v>6253</v>
       </c>
       <c r="M336" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="337" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15949,10 +15949,10 @@
         <v>331</v>
       </c>
       <c r="B337" s="11" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C337" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D337" s="6" t="s">
         <v>17</v>
@@ -15970,17 +15970,17 @@
         <v>420</v>
       </c>
       <c r="I337" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J337" s="6"/>
       <c r="K337" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L337" s="7">
         <v>6253</v>
       </c>
       <c r="M337" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="338" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15988,10 +15988,10 @@
         <v>332</v>
       </c>
       <c r="B338" s="11" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C338" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D338" s="6" t="s">
         <v>17</v>
@@ -16009,17 +16009,17 @@
         <v>420</v>
       </c>
       <c r="I338" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J338" s="6"/>
       <c r="K338" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L338" s="7">
         <v>6253</v>
       </c>
       <c r="M338" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="339" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16027,10 +16027,10 @@
         <v>333</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C339" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D339" s="6" t="s">
         <v>17</v>
@@ -16048,17 +16048,17 @@
         <v>420</v>
       </c>
       <c r="I339" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J339" s="6"/>
       <c r="K339" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L339" s="7">
         <v>6253</v>
       </c>
       <c r="M339" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="340" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16066,10 +16066,10 @@
         <v>334</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C340" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D340" s="6" t="s">
         <v>52</v>
@@ -16087,17 +16087,17 @@
         <v>420</v>
       </c>
       <c r="I340" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J340" s="6"/>
       <c r="K340" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L340" s="7">
         <v>6253</v>
       </c>
       <c r="M340" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="341" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16105,10 +16105,10 @@
         <v>335</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C341" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D341" s="6" t="s">
         <v>17</v>
@@ -16126,17 +16126,17 @@
         <v>420</v>
       </c>
       <c r="I341" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J341" s="6"/>
       <c r="K341" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L341" s="7">
         <v>6253</v>
       </c>
       <c r="M341" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="342" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16144,10 +16144,10 @@
         <v>336</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C342" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D342" s="6" t="s">
         <v>17</v>
@@ -16165,17 +16165,17 @@
         <v>420</v>
       </c>
       <c r="I342" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J342" s="6"/>
       <c r="K342" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L342" s="7">
         <v>6253</v>
       </c>
       <c r="M342" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="343" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16183,10 +16183,10 @@
         <v>338</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C343" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D343" s="6" t="s">
         <v>17</v>
@@ -16204,17 +16204,17 @@
         <v>420</v>
       </c>
       <c r="I343" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J343" s="6"/>
       <c r="K343" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L343" s="7">
         <v>6253</v>
       </c>
       <c r="M343" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="344" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16222,10 +16222,10 @@
         <v>339</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C344" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D344" s="6" t="s">
         <v>17</v>
@@ -16243,17 +16243,17 @@
         <v>420</v>
       </c>
       <c r="I344" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J344" s="6"/>
       <c r="K344" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L344" s="7">
         <v>6254</v>
       </c>
       <c r="M344" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="345" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16261,10 +16261,10 @@
         <v>340</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C345" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D345" s="6" t="s">
         <v>17</v>
@@ -16282,17 +16282,17 @@
         <v>420</v>
       </c>
       <c r="I345" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J345" s="6"/>
       <c r="K345" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L345" s="7">
         <v>6254</v>
       </c>
       <c r="M345" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="346" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16300,10 +16300,10 @@
         <v>341</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C346" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D346" s="6" t="s">
         <v>17</v>
@@ -16321,17 +16321,17 @@
         <v>420</v>
       </c>
       <c r="I346" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J346" s="6"/>
       <c r="K346" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L346" s="7">
         <v>6254</v>
       </c>
       <c r="M346" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="347" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16339,10 +16339,10 @@
         <v>342</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C347" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D347" s="6" t="s">
         <v>17</v>
@@ -16360,17 +16360,17 @@
         <v>420</v>
       </c>
       <c r="I347" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J347" s="6"/>
       <c r="K347" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L347" s="7">
         <v>6254</v>
       </c>
       <c r="M347" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="348" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16378,10 +16378,10 @@
         <v>343</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C348" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D348" s="6" t="s">
         <v>17</v>
@@ -16399,17 +16399,17 @@
         <v>420</v>
       </c>
       <c r="I348" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J348" s="6"/>
       <c r="K348" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L348" s="7">
         <v>6254</v>
       </c>
       <c r="M348" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="349" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16417,10 +16417,10 @@
         <v>344</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D349" s="6" t="s">
         <v>17</v>
@@ -16438,17 +16438,17 @@
         <v>420</v>
       </c>
       <c r="I349" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J349" s="6"/>
       <c r="K349" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L349" s="7">
         <v>6254</v>
       </c>
       <c r="M349" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="350" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16456,10 +16456,10 @@
         <v>346</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C350" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D350" s="6" t="s">
         <v>17</v>
@@ -16477,17 +16477,17 @@
         <v>420</v>
       </c>
       <c r="I350" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J350" s="6"/>
       <c r="K350" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L350" s="7">
         <v>6254</v>
       </c>
       <c r="M350" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="351" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16495,10 +16495,10 @@
         <v>347</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C351" s="7" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D351" s="6" t="s">
         <v>17</v>
@@ -16516,17 +16516,17 @@
         <v>420</v>
       </c>
       <c r="I351" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J351" s="6"/>
       <c r="K351" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L351" s="7">
         <v>6254</v>
       </c>
       <c r="M351" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="352" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16534,10 +16534,10 @@
         <v>348</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C352" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D352" s="6" t="s">
         <v>17</v>
@@ -16555,17 +16555,17 @@
         <v>420</v>
       </c>
       <c r="I352" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J352" s="6"/>
       <c r="K352" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L352" s="7">
         <v>6254</v>
       </c>
       <c r="M352" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="353" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16573,10 +16573,10 @@
         <v>349</v>
       </c>
       <c r="B353" s="11" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C353" s="7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D353" s="6" t="s">
         <v>17</v>
@@ -16594,17 +16594,17 @@
         <v>420</v>
       </c>
       <c r="I353" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J353" s="6"/>
       <c r="K353" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L353" s="7">
         <v>6254</v>
       </c>
       <c r="M353" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="354" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16612,10 +16612,10 @@
         <v>350</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C354" s="7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D354" s="6" t="s">
         <v>17</v>
@@ -16633,17 +16633,17 @@
         <v>420</v>
       </c>
       <c r="I354" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J354" s="6"/>
       <c r="K354" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L354" s="7">
         <v>6255</v>
       </c>
       <c r="M354" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="355" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16651,10 +16651,10 @@
         <v>351</v>
       </c>
       <c r="B355" s="11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C355" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D355" s="6" t="s">
         <v>17</v>
@@ -16672,17 +16672,17 @@
         <v>420</v>
       </c>
       <c r="I355" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J355" s="6"/>
       <c r="K355" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L355" s="7">
         <v>6255</v>
       </c>
       <c r="M355" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="356" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16690,10 +16690,10 @@
         <v>352</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C356" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D356" s="6" t="s">
         <v>17</v>
@@ -16711,17 +16711,17 @@
         <v>420</v>
       </c>
       <c r="I356" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J356" s="6"/>
       <c r="K356" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L356" s="7">
         <v>6255</v>
       </c>
       <c r="M356" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="357" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16729,13 +16729,13 @@
         <v>353</v>
       </c>
       <c r="B357" s="11" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C357" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D357" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E357" s="6">
         <v>3</v>
@@ -16750,17 +16750,17 @@
         <v>420</v>
       </c>
       <c r="I357" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J357" s="6"/>
       <c r="K357" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L357" s="7">
         <v>6255</v>
       </c>
       <c r="M357" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="358" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16768,10 +16768,10 @@
         <v>354</v>
       </c>
       <c r="B358" s="11" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C358" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D358" s="6" t="s">
         <v>17</v>
@@ -16789,17 +16789,17 @@
         <v>420</v>
       </c>
       <c r="I358" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J358" s="6"/>
       <c r="K358" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L358" s="7">
         <v>6255</v>
       </c>
       <c r="M358" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="359" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16807,10 +16807,10 @@
         <v>355</v>
       </c>
       <c r="B359" s="11" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C359" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D359" s="6" t="s">
         <v>17</v>
@@ -16828,17 +16828,17 @@
         <v>420</v>
       </c>
       <c r="I359" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J359" s="6"/>
       <c r="K359" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L359" s="7">
         <v>6255</v>
       </c>
       <c r="M359" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="360" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16846,10 +16846,10 @@
         <v>356</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C360" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D360" s="6" t="s">
         <v>17</v>
@@ -16867,17 +16867,17 @@
         <v>420</v>
       </c>
       <c r="I360" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J360" s="6"/>
       <c r="K360" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L360" s="7">
         <v>6255</v>
       </c>
       <c r="M360" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="361" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16888,7 +16888,7 @@
         <v>340</v>
       </c>
       <c r="C361" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D361" s="6" t="s">
         <v>17</v>
@@ -16906,17 +16906,17 @@
         <v>420</v>
       </c>
       <c r="I361" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J361" s="6"/>
       <c r="K361" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L361" s="7">
         <v>6255</v>
       </c>
       <c r="M361" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="362" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16924,10 +16924,10 @@
         <v>358</v>
       </c>
       <c r="B362" s="11" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C362" s="7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D362" s="6" t="s">
         <v>17</v>
@@ -16945,17 +16945,17 @@
         <v>419</v>
       </c>
       <c r="I362" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J362" s="6"/>
       <c r="K362" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L362" s="7">
         <v>6256</v>
       </c>
       <c r="M362" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="363" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16963,10 +16963,10 @@
         <v>359</v>
       </c>
       <c r="B363" s="11" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C363" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D363" s="6" t="s">
         <v>17</v>
@@ -16984,17 +16984,17 @@
         <v>419</v>
       </c>
       <c r="I363" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J363" s="6"/>
       <c r="K363" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L363" s="7">
         <v>6256</v>
       </c>
       <c r="M363" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="364" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17002,13 +17002,13 @@
         <v>360</v>
       </c>
       <c r="B364" s="11" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C364" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D364" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E364" s="6">
         <v>3</v>
@@ -17023,17 +17023,17 @@
         <v>419</v>
       </c>
       <c r="I364" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J364" s="6"/>
       <c r="K364" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L364" s="7">
         <v>6256</v>
       </c>
       <c r="M364" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="365" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17041,10 +17041,10 @@
         <v>361</v>
       </c>
       <c r="B365" s="11" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C365" s="7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D365" s="6" t="s">
         <v>17</v>
@@ -17062,17 +17062,17 @@
         <v>419</v>
       </c>
       <c r="I365" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J365" s="6"/>
       <c r="K365" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L365" s="7">
         <v>6256</v>
       </c>
       <c r="M365" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="366" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17080,10 +17080,10 @@
         <v>362</v>
       </c>
       <c r="B366" s="11" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C366" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D366" s="6" t="s">
         <v>17</v>
@@ -17101,17 +17101,17 @@
         <v>419</v>
       </c>
       <c r="I366" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J366" s="6"/>
       <c r="K366" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L366" s="7">
         <v>6256</v>
       </c>
       <c r="M366" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="367" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17119,13 +17119,13 @@
         <v>365</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C367" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D367" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E367" s="6">
         <v>25</v>
@@ -17140,17 +17140,17 @@
         <v>419</v>
       </c>
       <c r="I367" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J367" s="6"/>
       <c r="K367" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L367" s="7">
         <v>6256</v>
       </c>
       <c r="M367" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="368" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17158,10 +17158,10 @@
         <v>366</v>
       </c>
       <c r="B368" s="9" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C368" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D368" s="6" t="s">
         <v>17</v>
@@ -17179,17 +17179,17 @@
         <v>419</v>
       </c>
       <c r="I368" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J368" s="6"/>
       <c r="K368" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L368" s="7">
         <v>6256</v>
       </c>
       <c r="M368" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="369" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17197,13 +17197,13 @@
         <v>367</v>
       </c>
       <c r="B369" s="11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C369" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D369" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E369" s="6">
         <v>11</v>
@@ -17218,17 +17218,17 @@
         <v>419</v>
       </c>
       <c r="I369" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J369" s="6"/>
       <c r="K369" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L369" s="7">
         <v>6256</v>
       </c>
       <c r="M369" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="370" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17236,10 +17236,10 @@
         <v>368</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C370" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D370" s="6" t="s">
         <v>17</v>
@@ -17257,17 +17257,17 @@
         <v>419</v>
       </c>
       <c r="I370" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J370" s="6"/>
       <c r="K370" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L370" s="7">
         <v>6256</v>
       </c>
       <c r="M370" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="371" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17275,10 +17275,10 @@
         <v>369</v>
       </c>
       <c r="B371" s="11" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C371" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D371" s="6" t="s">
         <v>17</v>
@@ -17296,17 +17296,17 @@
         <v>419</v>
       </c>
       <c r="I371" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J371" s="6"/>
       <c r="K371" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L371" s="7">
         <v>6256</v>
       </c>
       <c r="M371" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="372" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17314,10 +17314,10 @@
         <v>370</v>
       </c>
       <c r="B372" s="11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C372" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D372" s="6" t="s">
         <v>17</v>
@@ -17335,17 +17335,17 @@
         <v>419</v>
       </c>
       <c r="I372" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J372" s="6"/>
       <c r="K372" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L372" s="7">
         <v>6257</v>
       </c>
       <c r="M372" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="373" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17353,10 +17353,10 @@
         <v>371</v>
       </c>
       <c r="B373" s="11" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C373" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D373" s="6" t="s">
         <v>17</v>
@@ -17374,17 +17374,17 @@
         <v>419</v>
       </c>
       <c r="I373" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J373" s="6"/>
       <c r="K373" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L373" s="7">
         <v>6257</v>
       </c>
       <c r="M373" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="374" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17392,10 +17392,10 @@
         <v>372</v>
       </c>
       <c r="B374" s="11" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C374" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D374" s="6" t="s">
         <v>17</v>
@@ -17413,17 +17413,17 @@
         <v>419</v>
       </c>
       <c r="I374" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J374" s="6"/>
       <c r="K374" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L374" s="7">
         <v>6257</v>
       </c>
       <c r="M374" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="375" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17431,10 +17431,10 @@
         <v>373</v>
       </c>
       <c r="B375" s="11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C375" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D375" s="6" t="s">
         <v>17</v>
@@ -17452,17 +17452,17 @@
         <v>419</v>
       </c>
       <c r="I375" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J375" s="6"/>
       <c r="K375" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L375" s="7">
         <v>6257</v>
       </c>
       <c r="M375" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="376" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17470,10 +17470,10 @@
         <v>374</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C376" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D376" s="6" t="s">
         <v>17</v>
@@ -17491,17 +17491,17 @@
         <v>419</v>
       </c>
       <c r="I376" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J376" s="6"/>
       <c r="K376" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L376" s="7">
         <v>6257</v>
       </c>
       <c r="M376" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="377" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17509,10 +17509,10 @@
         <v>375</v>
       </c>
       <c r="B377" s="11" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C377" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D377" s="6" t="s">
         <v>17</v>
@@ -17530,17 +17530,17 @@
         <v>419</v>
       </c>
       <c r="I377" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J377" s="6"/>
       <c r="K377" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L377" s="7">
         <v>6257</v>
       </c>
       <c r="M377" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="378" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17548,10 +17548,10 @@
         <v>376</v>
       </c>
       <c r="B378" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C378" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D378" s="6" t="s">
         <v>17</v>
@@ -17569,17 +17569,17 @@
         <v>419</v>
       </c>
       <c r="I378" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J378" s="6"/>
       <c r="K378" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L378" s="7">
         <v>6257</v>
       </c>
       <c r="M378" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="379" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17587,10 +17587,10 @@
         <v>377</v>
       </c>
       <c r="B379" s="11" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C379" s="7" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D379" s="6" t="s">
         <v>17</v>
@@ -17608,17 +17608,17 @@
         <v>419</v>
       </c>
       <c r="I379" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J379" s="6"/>
       <c r="K379" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L379" s="7">
         <v>6257</v>
       </c>
       <c r="M379" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="380" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17629,7 +17629,7 @@
         <v>340</v>
       </c>
       <c r="C380" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D380" s="6" t="s">
         <v>17</v>
@@ -17647,17 +17647,17 @@
         <v>419</v>
       </c>
       <c r="I380" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J380" s="6"/>
       <c r="K380" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L380" s="7">
         <v>6257</v>
       </c>
       <c r="M380" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="381" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17665,10 +17665,10 @@
         <v>379</v>
       </c>
       <c r="B381" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C381" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D381" s="6" t="s">
         <v>17</v>
@@ -17686,17 +17686,17 @@
         <v>419</v>
       </c>
       <c r="I381" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J381" s="6"/>
       <c r="K381" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L381" s="7">
         <v>6257</v>
       </c>
       <c r="M381" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="382" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17707,7 +17707,7 @@
         <v>299</v>
       </c>
       <c r="C382" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D382" s="6" t="s">
         <v>17</v>
@@ -17725,17 +17725,17 @@
         <v>419</v>
       </c>
       <c r="I382" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J382" s="6"/>
       <c r="K382" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L382" s="7">
         <v>6257</v>
       </c>
       <c r="M382" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="383" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17743,10 +17743,10 @@
         <v>381</v>
       </c>
       <c r="B383" s="9" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C383" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D383" s="6" t="s">
         <v>17</v>
@@ -17764,17 +17764,17 @@
         <v>419</v>
       </c>
       <c r="I383" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J383" s="6"/>
       <c r="K383" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L383" s="7">
         <v>6257</v>
       </c>
       <c r="M383" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="384" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17782,10 +17782,10 @@
         <v>382</v>
       </c>
       <c r="B384" s="9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C384" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D384" s="6" t="s">
         <v>17</v>
@@ -17803,17 +17803,17 @@
         <v>419</v>
       </c>
       <c r="I384" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J384" s="6"/>
       <c r="K384" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L384" s="7">
         <v>6257</v>
       </c>
       <c r="M384" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="385" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17821,10 +17821,10 @@
         <v>383</v>
       </c>
       <c r="B385" s="9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C385" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D385" s="6" t="s">
         <v>17</v>
@@ -17842,17 +17842,17 @@
         <v>419</v>
       </c>
       <c r="I385" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J385" s="6"/>
       <c r="K385" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L385" s="7">
         <v>6257</v>
       </c>
       <c r="M385" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="386" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17860,10 +17860,10 @@
         <v>384</v>
       </c>
       <c r="B386" s="11" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C386" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D386" s="6" t="s">
         <v>17</v>
@@ -17881,17 +17881,17 @@
         <v>419</v>
       </c>
       <c r="I386" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J386" s="6"/>
       <c r="K386" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L386" s="7">
         <v>6257</v>
       </c>
       <c r="M386" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="387" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17899,10 +17899,10 @@
         <v>385</v>
       </c>
       <c r="B387" s="11" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C387" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D387" s="6" t="s">
         <v>17</v>
@@ -17920,17 +17920,17 @@
         <v>419</v>
       </c>
       <c r="I387" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J387" s="6"/>
       <c r="K387" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L387" s="7">
         <v>6257</v>
       </c>
       <c r="M387" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="388" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17938,10 +17938,10 @@
         <v>386</v>
       </c>
       <c r="B388" s="11" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C388" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D388" s="6" t="s">
         <v>17</v>
@@ -17959,17 +17959,17 @@
         <v>419</v>
       </c>
       <c r="I388" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J388" s="6"/>
       <c r="K388" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L388" s="7">
         <v>6257</v>
       </c>
       <c r="M388" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="389" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17977,10 +17977,10 @@
         <v>387</v>
       </c>
       <c r="B389" s="9" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C389" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D389" s="6" t="s">
         <v>17</v>
@@ -17998,17 +17998,17 @@
         <v>419</v>
       </c>
       <c r="I389" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J389" s="6"/>
       <c r="K389" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L389" s="7">
         <v>6257</v>
       </c>
       <c r="M389" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="390" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18016,10 +18016,10 @@
         <v>388</v>
       </c>
       <c r="B390" s="11" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C390" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D390" s="6" t="s">
         <v>17</v>
@@ -18037,17 +18037,17 @@
         <v>419</v>
       </c>
       <c r="I390" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J390" s="6"/>
       <c r="K390" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L390" s="7">
         <v>6257</v>
       </c>
       <c r="M390" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="391" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18055,10 +18055,10 @@
         <v>389</v>
       </c>
       <c r="B391" s="9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C391" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D391" s="6" t="s">
         <v>17</v>
@@ -18076,17 +18076,17 @@
         <v>419</v>
       </c>
       <c r="I391" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J391" s="6"/>
       <c r="K391" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L391" s="7">
         <v>6257</v>
       </c>
       <c r="M391" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="392" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18094,10 +18094,10 @@
         <v>390</v>
       </c>
       <c r="B392" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C392" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D392" s="6" t="s">
         <v>17</v>
@@ -18115,17 +18115,17 @@
         <v>419</v>
       </c>
       <c r="I392" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J392" s="6"/>
       <c r="K392" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L392" s="7">
         <v>6257</v>
       </c>
       <c r="M392" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="393" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18133,10 +18133,10 @@
         <v>391</v>
       </c>
       <c r="B393" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C393" s="7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D393" s="6" t="s">
         <v>17</v>
@@ -18154,17 +18154,17 @@
         <v>419</v>
       </c>
       <c r="I393" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J393" s="6"/>
       <c r="K393" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L393" s="7">
         <v>6257</v>
       </c>
       <c r="M393" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="394" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18172,10 +18172,10 @@
         <v>392</v>
       </c>
       <c r="B394" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C394" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D394" s="6" t="s">
         <v>17</v>
@@ -18193,17 +18193,17 @@
         <v>419</v>
       </c>
       <c r="I394" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J394" s="6"/>
       <c r="K394" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L394" s="7">
         <v>6259</v>
       </c>
       <c r="M394" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="395" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18211,10 +18211,10 @@
         <v>393</v>
       </c>
       <c r="B395" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C395" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D395" s="6" t="s">
         <v>17</v>
@@ -18232,17 +18232,17 @@
         <v>419</v>
       </c>
       <c r="I395" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J395" s="6"/>
       <c r="K395" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L395" s="7">
         <v>6259</v>
       </c>
       <c r="M395" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="396" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18250,10 +18250,10 @@
         <v>394</v>
       </c>
       <c r="B396" s="9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C396" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D396" s="6" t="s">
         <v>17</v>
@@ -18271,17 +18271,17 @@
         <v>419</v>
       </c>
       <c r="I396" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J396" s="6"/>
       <c r="K396" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L396" s="7">
         <v>6259</v>
       </c>
       <c r="M396" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="397" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18289,10 +18289,10 @@
         <v>395</v>
       </c>
       <c r="B397" s="11" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C397" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D397" s="6" t="s">
         <v>17</v>
@@ -18310,17 +18310,17 @@
         <v>419</v>
       </c>
       <c r="I397" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J397" s="6"/>
       <c r="K397" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L397" s="7">
         <v>6259</v>
       </c>
       <c r="M397" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="398" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18328,10 +18328,10 @@
         <v>396</v>
       </c>
       <c r="B398" s="9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C398" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D398" s="6" t="s">
         <v>17</v>
@@ -18349,17 +18349,17 @@
         <v>419</v>
       </c>
       <c r="I398" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J398" s="6"/>
       <c r="K398" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L398" s="7">
         <v>6259</v>
       </c>
       <c r="M398" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="399" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18367,10 +18367,10 @@
         <v>397</v>
       </c>
       <c r="B399" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C399" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D399" s="6" t="s">
         <v>17</v>
@@ -18388,7 +18388,7 @@
         <v>2443</v>
       </c>
       <c r="I399" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J399" s="6"/>
       <c r="K399" s="7" t="s">
@@ -18398,7 +18398,7 @@
         <v>6260</v>
       </c>
       <c r="M399" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="400" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18406,10 +18406,10 @@
         <v>398</v>
       </c>
       <c r="B400" s="11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C400" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D400" s="6" t="s">
         <v>17</v>
@@ -18427,7 +18427,7 @@
         <v>2443</v>
       </c>
       <c r="I400" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J400" s="6"/>
       <c r="K400" s="7" t="s">
@@ -18437,7 +18437,7 @@
         <v>6260</v>
       </c>
       <c r="M400" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="401" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18466,7 +18466,7 @@
         <v>2443</v>
       </c>
       <c r="I401" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J401" s="6"/>
       <c r="K401" s="7" t="s">
@@ -18476,7 +18476,7 @@
         <v>6260</v>
       </c>
       <c r="M401" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="402" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18484,10 +18484,10 @@
         <v>400</v>
       </c>
       <c r="B402" s="11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C402" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D402" s="6" t="s">
         <v>17</v>
@@ -18505,7 +18505,7 @@
         <v>2443</v>
       </c>
       <c r="I402" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J402" s="6"/>
       <c r="K402" s="7" t="s">
@@ -18515,7 +18515,7 @@
         <v>6260</v>
       </c>
       <c r="M402" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="403" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18523,10 +18523,10 @@
         <v>401</v>
       </c>
       <c r="B403" s="11" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C403" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D403" s="6" t="s">
         <v>17</v>
@@ -18544,7 +18544,7 @@
         <v>2443</v>
       </c>
       <c r="I403" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J403" s="6"/>
       <c r="K403" s="7" t="s">
@@ -18554,7 +18554,7 @@
         <v>6260</v>
       </c>
       <c r="M403" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="404" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18562,10 +18562,10 @@
         <v>402</v>
       </c>
       <c r="B404" s="11" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C404" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D404" s="6" t="s">
         <v>17</v>
@@ -18583,7 +18583,7 @@
         <v>2443</v>
       </c>
       <c r="I404" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J404" s="6"/>
       <c r="K404" s="7" t="s">
@@ -18593,7 +18593,7 @@
         <v>6260</v>
       </c>
       <c r="M404" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="405" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18601,10 +18601,10 @@
         <v>403</v>
       </c>
       <c r="B405" s="11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C405" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D405" s="6" t="s">
         <v>17</v>
@@ -18622,7 +18622,7 @@
         <v>2443</v>
       </c>
       <c r="I405" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J405" s="6"/>
       <c r="K405" s="7" t="s">
@@ -18632,7 +18632,7 @@
         <v>6260</v>
       </c>
       <c r="M405" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="406" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18640,10 +18640,10 @@
         <v>404</v>
       </c>
       <c r="B406" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C406" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D406" s="6" t="s">
         <v>17</v>
@@ -18661,7 +18661,7 @@
         <v>2443</v>
       </c>
       <c r="I406" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J406" s="6"/>
       <c r="K406" s="7" t="s">
@@ -18671,7 +18671,7 @@
         <v>6260</v>
       </c>
       <c r="M406" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="407" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18679,10 +18679,10 @@
         <v>405</v>
       </c>
       <c r="B407" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C407" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D407" s="6" t="s">
         <v>17</v>
@@ -18700,7 +18700,7 @@
         <v>2443</v>
       </c>
       <c r="I407" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J407" s="6"/>
       <c r="K407" s="7" t="s">
@@ -18710,7 +18710,7 @@
         <v>6260</v>
       </c>
       <c r="M407" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="408" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18718,10 +18718,10 @@
         <v>406</v>
       </c>
       <c r="B408" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C408" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D408" s="6" t="s">
         <v>17</v>
@@ -18739,7 +18739,7 @@
         <v>2443</v>
       </c>
       <c r="I408" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J408" s="6"/>
       <c r="K408" s="7" t="s">
@@ -18749,7 +18749,7 @@
         <v>6260</v>
       </c>
       <c r="M408" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="409" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18757,10 +18757,10 @@
         <v>407</v>
       </c>
       <c r="B409" s="15" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C409" s="7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D409" s="6" t="s">
         <v>17</v>
@@ -18778,7 +18778,7 @@
         <v>2443</v>
       </c>
       <c r="I409" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J409" s="6"/>
       <c r="K409" s="7" t="s">
@@ -18788,7 +18788,7 @@
         <v>6260</v>
       </c>
       <c r="M409" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="410" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18796,10 +18796,10 @@
         <v>408</v>
       </c>
       <c r="B410" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C410" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D410" s="6" t="s">
         <v>17</v>
@@ -18817,7 +18817,7 @@
         <v>2443</v>
       </c>
       <c r="I410" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J410" s="6"/>
       <c r="K410" s="7" t="s">
@@ -18827,7 +18827,7 @@
         <v>6260</v>
       </c>
       <c r="M410" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="411" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18835,10 +18835,10 @@
         <v>409</v>
       </c>
       <c r="B411" s="15" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C411" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D411" s="6" t="s">
         <v>17</v>
@@ -18856,7 +18856,7 @@
         <v>2443</v>
       </c>
       <c r="I411" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J411" s="6"/>
       <c r="K411" s="7" t="s">
@@ -18866,7 +18866,7 @@
         <v>6261</v>
       </c>
       <c r="M411" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="412" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18874,10 +18874,10 @@
         <v>410</v>
       </c>
       <c r="B412" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C412" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D412" s="6" t="s">
         <v>17</v>
@@ -18895,7 +18895,7 @@
         <v>2443</v>
       </c>
       <c r="I412" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J412" s="6"/>
       <c r="K412" s="7" t="s">
@@ -18905,7 +18905,7 @@
         <v>6261</v>
       </c>
       <c r="M412" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="413" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18913,10 +18913,10 @@
         <v>411</v>
       </c>
       <c r="B413" s="15" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C413" s="7" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D413" s="6" t="s">
         <v>17</v>
@@ -18934,7 +18934,7 @@
         <v>2443</v>
       </c>
       <c r="I413" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J413" s="6"/>
       <c r="K413" s="7" t="s">
@@ -18944,7 +18944,7 @@
         <v>6261</v>
       </c>
       <c r="M413" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="414" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18952,10 +18952,10 @@
         <v>412</v>
       </c>
       <c r="B414" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C414" s="7" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D414" s="6" t="s">
         <v>17</v>
@@ -18973,7 +18973,7 @@
         <v>2443</v>
       </c>
       <c r="I414" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J414" s="6"/>
       <c r="K414" s="7" t="s">
@@ -18983,7 +18983,7 @@
         <v>6261</v>
       </c>
       <c r="M414" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="415" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18991,10 +18991,10 @@
         <v>413</v>
       </c>
       <c r="B415" s="9" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C415" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D415" s="6" t="s">
         <v>17</v>
@@ -19012,17 +19012,17 @@
         <v>26</v>
       </c>
       <c r="I415" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="J415" s="6"/>
       <c r="K415" s="7" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L415" s="7">
         <v>6263</v>
       </c>
       <c r="M415" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="416" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19030,10 +19030,10 @@
         <v>414</v>
       </c>
       <c r="B416" s="9" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C416" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D416" s="6" t="s">
         <v>17</v>
@@ -19051,17 +19051,17 @@
         <v>26</v>
       </c>
       <c r="I416" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="J416" s="6"/>
       <c r="K416" s="7" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L416" s="7">
         <v>6263</v>
       </c>
       <c r="M416" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="417" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19069,10 +19069,10 @@
         <v>416</v>
       </c>
       <c r="B417" s="11" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C417" s="7" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D417" s="6" t="s">
         <v>17</v>
@@ -19090,17 +19090,17 @@
         <v>26</v>
       </c>
       <c r="I417" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="J417" s="6"/>
       <c r="K417" s="7" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L417" s="7">
         <v>6263</v>
       </c>
       <c r="M417" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="418" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19108,10 +19108,10 @@
         <v>417</v>
       </c>
       <c r="B418" s="11" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C418" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D418" s="6" t="s">
         <v>17</v>
@@ -19129,17 +19129,17 @@
         <v>26</v>
       </c>
       <c r="I418" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="J418" s="6"/>
       <c r="K418" s="7" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L418" s="7">
         <v>6263</v>
       </c>
       <c r="M418" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="419" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19147,10 +19147,10 @@
         <v>418</v>
       </c>
       <c r="B419" s="9" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C419" s="7" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D419" s="6" t="s">
         <v>17</v>
@@ -19168,17 +19168,17 @@
         <v>26</v>
       </c>
       <c r="I419" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="J419" s="6"/>
       <c r="K419" s="7" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L419" s="7">
         <v>6263</v>
       </c>
       <c r="M419" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="420" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>

--- a/data/transactions/أذونات الإضافة لشهر 3.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2919998B-695B-424F-98C5-82759DDC1C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613BD2F1-EC05-4427-AD69-6D4D1F68C8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="775">
   <si>
     <t>بورسعيد لصناعة المعادن</t>
   </si>
@@ -2359,6 +2359,9 @@
   </si>
   <si>
     <t>متر 3</t>
+  </si>
+  <si>
+    <t>10307010</t>
   </si>
 </sst>
 </file>
@@ -4817,7 +4820,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>158</v>
+        <v>774</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>105</v>
@@ -13959,9 +13962,7 @@
       <c r="A286" s="1">
         <v>280</v>
       </c>
-      <c r="B286" s="9" t="s">
-        <v>540</v>
-      </c>
+      <c r="B286" s="9"/>
       <c r="C286" s="7" t="s">
         <v>516</v>
       </c>

--- a/data/transactions/أذونات الإضافة لشهر 3.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613BD2F1-EC05-4427-AD69-6D4D1F68C8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DAB821-49CE-40AD-B23A-B441C64DD8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="774">
   <si>
     <t>بورسعيد لصناعة المعادن</t>
   </si>
@@ -999,30 +999,9 @@
     <t>11012008</t>
   </si>
   <si>
-    <t>لوح 8. مم مط 2×1 SST</t>
-  </si>
-  <si>
-    <t>لوح 8. مم مصنفر 2×1 SST</t>
-  </si>
-  <si>
-    <t>لوح 1.2 مم مصنفر 2×1 SST</t>
-  </si>
-  <si>
-    <t>لوح 1.2 مم مط 125×250 SST</t>
-  </si>
-  <si>
     <t>لوح 1.5 لميع 1×250 SST</t>
   </si>
   <si>
-    <t>لوح 1.2مم مط 1×2 SST</t>
-  </si>
-  <si>
-    <t>لوح 8. مصنفر 125×250 SST</t>
-  </si>
-  <si>
-    <t>لوح 1.8مم مصنفر 125 ×250 SST</t>
-  </si>
-  <si>
     <t>المصريه لتشكيل المعادن</t>
   </si>
   <si>
@@ -1038,9 +1017,6 @@
     <t>11301020</t>
   </si>
   <si>
-    <t>11301021</t>
-  </si>
-  <si>
     <t>11301045</t>
   </si>
   <si>
@@ -1143,18 +1119,6 @@
     <t>10701056</t>
   </si>
   <si>
-    <t>لوح1.5 م مط 1×2 SST</t>
-  </si>
-  <si>
-    <t>لوح 1.5 مصنفر 1×2 SST</t>
-  </si>
-  <si>
-    <t>لوح  2 مصنفر  2×125 SST</t>
-  </si>
-  <si>
-    <t>لوح 1 مم مصنفر 2×1 SST</t>
-  </si>
-  <si>
     <t>11301012</t>
   </si>
   <si>
@@ -2362,6 +2326,39 @@
   </si>
   <si>
     <t>10307010</t>
+  </si>
+  <si>
+    <t>ﻟﻮح 0.8 ﻣﻢ SST ﻣﺼﻨﻔﺮ ﻣﻐﻠﻒ 1 × 2 م</t>
+  </si>
+  <si>
+    <t>لوح 0.8 ﻣﻢ SST ﻣﺼﻨﻔﺮ ﻣﻐﻠﻒ 1.25 ×2.5 م</t>
+  </si>
+  <si>
+    <t>لوح 0.8 ﻣﻢ SST ﻣﺼﻨﻔﺮ ﻣﻐﻠﻒ 1 × 2 م</t>
+  </si>
+  <si>
+    <t>لوح.1.8 ﻣﻢ SST ﻣﺼﻨﻔﺮ 125 ×2</t>
+  </si>
+  <si>
+    <t>ﻟﻮح 1.2 ﻣﻢ SST ﻣﻂ ﻣﻐﻠﻒ 1.25 × 2.5 م</t>
+  </si>
+  <si>
+    <t>ﻟﻮح 1.2 ﻣﻢ SST ﻣﻂ ﻣﻐﻠﻒ 1 × 2 م</t>
+  </si>
+  <si>
+    <t>ﻟﻮح 1.5 ﻣﻢ SST ﻣﻂ ﻣﻐﻠﻒ 1 × 2 م</t>
+  </si>
+  <si>
+    <t>ﻟﻮح 1.5 ﻣﻢ SST ﻣﺼﻨﻔﺮ ﻣﻐﻠﻒ 1 × 2 م</t>
+  </si>
+  <si>
+    <t>ﻟﻮح 2 ﻣﻢ SST ﻣﺼﻨﻔﺮ ﻣﻐﻠﻒ 1.25 × 2 م</t>
+  </si>
+  <si>
+    <t>ﻟﻮح 1 ﻣﻢ SST ﻣﺼﻨﻔﺮ ﻣﻐﻠﻒ 1 × 2 م</t>
+  </si>
+  <si>
+    <t>ﻟﻮح 0.8 ﻣﻢ SST ﻣﻂ ﻣﻐﻠﻒ 1 × 2 م</t>
   </si>
 </sst>
 </file>
@@ -2466,7 +2463,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2560,35 +2557,6 @@
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color rgb="FF002060"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF002060"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FF002060"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color rgb="FF002060"/>
-      </right>
-      <top/>
       <bottom style="double">
         <color rgb="FF002060"/>
       </bottom>
@@ -2598,7 +2566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2681,7 +2649,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2706,24 +2674,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3012,7 +2962,8 @@
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="57.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.140625" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" customWidth="1"/>
@@ -3034,7 +2985,7 @@
     </row>
     <row r="3" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4140,7 +4091,7 @@
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L33" s="7">
         <v>6194</v>
@@ -4179,7 +4130,7 @@
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L34" s="7">
         <v>6194</v>
@@ -4218,7 +4169,7 @@
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L35" s="7">
         <v>6194</v>
@@ -4257,7 +4208,7 @@
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L36" s="7">
         <v>6194</v>
@@ -4296,7 +4247,7 @@
       </c>
       <c r="J37" s="6"/>
       <c r="K37" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L37" s="7">
         <v>6194</v>
@@ -4335,7 +4286,7 @@
       </c>
       <c r="J38" s="6"/>
       <c r="K38" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L38" s="7">
         <v>6194</v>
@@ -4374,7 +4325,7 @@
       </c>
       <c r="J39" s="6"/>
       <c r="K39" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L39" s="7">
         <v>6194</v>
@@ -4413,7 +4364,7 @@
       </c>
       <c r="J40" s="6"/>
       <c r="K40" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L40" s="7">
         <v>6194</v>
@@ -4452,7 +4403,7 @@
       </c>
       <c r="J41" s="6"/>
       <c r="K41" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L41" s="7">
         <v>6194</v>
@@ -4820,7 +4771,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>105</v>
@@ -6770,7 +6721,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>215</v>
@@ -6809,7 +6760,7 @@
         <v>96</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>217</v>
@@ -6848,7 +6799,7 @@
         <v>97</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>218</v>
@@ -6887,7 +6838,7 @@
         <v>98</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>219</v>
@@ -6926,7 +6877,7 @@
         <v>99</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>220</v>
@@ -6965,7 +6916,7 @@
         <v>100</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>221</v>
@@ -7004,7 +6955,7 @@
         <v>101</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>222</v>
@@ -7043,7 +6994,7 @@
         <v>102</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>223</v>
@@ -7082,7 +7033,7 @@
         <v>103</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>224</v>
@@ -7121,7 +7072,7 @@
         <v>104</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>225</v>
@@ -7160,7 +7111,7 @@
         <v>105</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>247</v>
@@ -7199,7 +7150,7 @@
         <v>106</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>226</v>
@@ -7238,7 +7189,7 @@
         <v>107</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>227</v>
@@ -7277,7 +7228,7 @@
         <v>108</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>228</v>
@@ -7316,7 +7267,7 @@
         <v>109</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>229</v>
@@ -7355,7 +7306,7 @@
         <v>110</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>230</v>
@@ -7394,7 +7345,7 @@
         <v>111</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>231</v>
@@ -7433,7 +7384,7 @@
         <v>112</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>232</v>
@@ -7472,7 +7423,7 @@
         <v>113</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>233</v>
@@ -7511,7 +7462,7 @@
         <v>114</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>234</v>
@@ -7550,7 +7501,7 @@
         <v>115</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>235</v>
@@ -7589,7 +7540,7 @@
         <v>116</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>236</v>
@@ -7628,7 +7579,7 @@
         <v>117</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>237</v>
@@ -7667,7 +7618,7 @@
         <v>118</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>238</v>
@@ -7706,7 +7657,7 @@
         <v>119</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>239</v>
@@ -7745,7 +7696,7 @@
         <v>120</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>240</v>
@@ -7784,7 +7735,7 @@
         <v>121</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>241</v>
@@ -7823,7 +7774,7 @@
         <v>122</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>242</v>
@@ -7862,7 +7813,7 @@
         <v>123</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>243</v>
@@ -7901,7 +7852,7 @@
         <v>124</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>244</v>
@@ -7940,7 +7891,7 @@
         <v>125</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>245</v>
@@ -7979,7 +7930,7 @@
         <v>126</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>246</v>
@@ -8018,7 +7969,7 @@
         <v>127</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>248</v>
@@ -8057,7 +8008,7 @@
         <v>128</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>249</v>
@@ -8096,7 +8047,7 @@
         <v>129</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>250</v>
@@ -8135,7 +8086,7 @@
         <v>130</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>251</v>
@@ -8174,7 +8125,7 @@
         <v>131</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>252</v>
@@ -8213,7 +8164,7 @@
         <v>132</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>253</v>
@@ -8252,7 +8203,7 @@
         <v>133</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>254</v>
@@ -8291,7 +8242,7 @@
         <v>134</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>255</v>
@@ -8330,7 +8281,7 @@
         <v>135</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>256</v>
@@ -8371,7 +8322,7 @@
         <v>136</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="C142" s="7" t="s">
         <v>257</v>
@@ -8410,7 +8361,7 @@
         <v>137</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="C143" s="7" t="s">
         <v>250</v>
@@ -8708,7 +8659,7 @@
       </c>
       <c r="J150" s="6"/>
       <c r="K150" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L150" s="7">
         <v>6211</v>
@@ -8747,7 +8698,7 @@
       </c>
       <c r="J151" s="6"/>
       <c r="K151" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L151" s="7">
         <v>6211</v>
@@ -8786,7 +8737,7 @@
       </c>
       <c r="J152" s="6"/>
       <c r="K152" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L152" s="7">
         <v>6211</v>
@@ -8825,7 +8776,7 @@
       </c>
       <c r="J153" s="6"/>
       <c r="K153" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L153" s="7">
         <v>6211</v>
@@ -8864,7 +8815,7 @@
       </c>
       <c r="J154" s="6"/>
       <c r="K154" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L154" s="7">
         <v>6211</v>
@@ -8903,7 +8854,7 @@
       </c>
       <c r="J155" s="6"/>
       <c r="K155" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L155" s="7">
         <v>6211</v>
@@ -8942,7 +8893,7 @@
       </c>
       <c r="J156" s="6"/>
       <c r="K156" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L156" s="7">
         <v>6211</v>
@@ -8981,7 +8932,7 @@
       </c>
       <c r="J157" s="6"/>
       <c r="K157" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L157" s="7">
         <v>6211</v>
@@ -9020,7 +8971,7 @@
       </c>
       <c r="J158" s="6"/>
       <c r="K158" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L158" s="7">
         <v>6211</v>
@@ -9059,7 +9010,7 @@
       </c>
       <c r="J159" s="6"/>
       <c r="K159" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L159" s="7">
         <v>6211</v>
@@ -9098,7 +9049,7 @@
       </c>
       <c r="J160" s="6"/>
       <c r="K160" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L160" s="7">
         <v>6212</v>
@@ -9137,7 +9088,7 @@
       </c>
       <c r="J161" s="6"/>
       <c r="K161" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L161" s="7">
         <v>6213</v>
@@ -9176,7 +9127,7 @@
       </c>
       <c r="J162" s="6"/>
       <c r="K162" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L162" s="7">
         <v>6213</v>
@@ -9733,24 +9684,27 @@
     </row>
     <row r="177" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="18">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B177" s="19" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C177" s="20" t="s">
         <v>320</v>
       </c>
       <c r="D177" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E177" s="21">
-        <v>173</v>
-      </c>
-      <c r="F177" s="42">
-        <v>1443407.87</v>
-      </c>
-      <c r="G177" s="43"/>
+        <v>1200</v>
+      </c>
+      <c r="F177" s="33">
+        <v>87.719300000000004</v>
+      </c>
+      <c r="G177" s="34">
+        <f>F177*E177</f>
+        <v>105263.16</v>
+      </c>
       <c r="H177" s="21">
         <v>59798</v>
       </c>
@@ -9759,7 +9713,7 @@
       </c>
       <c r="J177" s="21"/>
       <c r="K177" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L177" s="20">
         <v>6217</v>
@@ -9770,22 +9724,27 @@
     </row>
     <row r="178" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="18">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B178" s="19" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C178" s="20" t="s">
-        <v>321</v>
+        <v>767</v>
       </c>
       <c r="D178" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E178" s="21">
-        <v>247</v>
-      </c>
-      <c r="F178" s="44"/>
-      <c r="G178" s="45"/>
+        <v>3600</v>
+      </c>
+      <c r="F178" s="33">
+        <v>142</v>
+      </c>
+      <c r="G178" s="34">
+        <f t="shared" ref="G177:G185" si="0">F178*E178</f>
+        <v>511200</v>
+      </c>
       <c r="H178" s="21">
         <v>59798</v>
       </c>
@@ -9794,7 +9753,7 @@
       </c>
       <c r="J178" s="21"/>
       <c r="K178" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L178" s="20">
         <v>6217</v>
@@ -9805,22 +9764,27 @@
     </row>
     <row r="179" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="18">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>43</v>
+        <v>324</v>
       </c>
       <c r="C179" s="20" t="s">
-        <v>322</v>
+        <v>768</v>
       </c>
       <c r="D179" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E179" s="21">
-        <v>82</v>
-      </c>
-      <c r="F179" s="44"/>
-      <c r="G179" s="45"/>
+        <v>2112</v>
+      </c>
+      <c r="F179" s="33">
+        <v>142</v>
+      </c>
+      <c r="G179" s="34">
+        <f t="shared" si="0"/>
+        <v>299904</v>
+      </c>
       <c r="H179" s="21">
         <v>59798</v>
       </c>
@@ -9829,7 +9793,7 @@
       </c>
       <c r="J179" s="21"/>
       <c r="K179" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L179" s="20">
         <v>6217</v>
@@ -9839,23 +9803,26 @@
       </c>
     </row>
     <row r="180" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="18">
-        <v>174</v>
-      </c>
+      <c r="A180" s="18"/>
       <c r="B180" s="19" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="C180" s="20" t="s">
-        <v>323</v>
+        <v>769</v>
       </c>
       <c r="D180" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E180" s="21">
-        <v>125</v>
-      </c>
-      <c r="F180" s="44"/>
-      <c r="G180" s="45"/>
+        <v>696</v>
+      </c>
+      <c r="F180" s="33">
+        <v>142</v>
+      </c>
+      <c r="G180" s="34">
+        <f t="shared" si="0"/>
+        <v>98832</v>
+      </c>
       <c r="H180" s="21">
         <v>59798</v>
       </c>
@@ -9864,7 +9831,7 @@
       </c>
       <c r="J180" s="21"/>
       <c r="K180" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L180" s="20">
         <v>6217</v>
@@ -9874,23 +9841,26 @@
       </c>
     </row>
     <row r="181" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="18">
-        <v>175</v>
-      </c>
+      <c r="A181" s="18"/>
       <c r="B181" s="19" t="s">
-        <v>334</v>
+        <v>42</v>
       </c>
       <c r="C181" s="20" t="s">
-        <v>324</v>
+        <v>770</v>
       </c>
       <c r="D181" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E181" s="21">
-        <v>41</v>
-      </c>
-      <c r="F181" s="44"/>
-      <c r="G181" s="45"/>
+        <v>1104</v>
+      </c>
+      <c r="F181" s="33">
+        <v>142</v>
+      </c>
+      <c r="G181" s="34">
+        <f t="shared" si="0"/>
+        <v>156768</v>
+      </c>
       <c r="H181" s="21">
         <v>59798</v>
       </c>
@@ -9899,7 +9869,7 @@
       </c>
       <c r="J181" s="21"/>
       <c r="K181" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L181" s="20">
         <v>6217</v>
@@ -9909,23 +9879,26 @@
       </c>
     </row>
     <row r="182" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="18">
-        <v>176</v>
-      </c>
+      <c r="A182" s="18"/>
       <c r="B182" s="19" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="C182" s="20" t="s">
-        <v>325</v>
+        <v>771</v>
       </c>
       <c r="D182" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E182" s="21">
-        <v>29</v>
-      </c>
-      <c r="F182" s="44"/>
-      <c r="G182" s="45"/>
+        <v>1640</v>
+      </c>
+      <c r="F182" s="33">
+        <v>142</v>
+      </c>
+      <c r="G182" s="34">
+        <f t="shared" si="0"/>
+        <v>232880</v>
+      </c>
       <c r="H182" s="21">
         <v>59798</v>
       </c>
@@ -9934,7 +9907,7 @@
       </c>
       <c r="J182" s="21"/>
       <c r="K182" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L182" s="20">
         <v>6217</v>
@@ -9944,23 +9917,26 @@
       </c>
     </row>
     <row r="183" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="18">
-        <v>177</v>
-      </c>
+      <c r="A183" s="18"/>
       <c r="B183" s="19" t="s">
-        <v>333</v>
+        <v>40</v>
       </c>
       <c r="C183" s="20" t="s">
-        <v>326</v>
+        <v>772</v>
       </c>
       <c r="D183" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E183" s="21">
-        <v>118</v>
-      </c>
-      <c r="F183" s="44"/>
-      <c r="G183" s="45"/>
+        <v>2144</v>
+      </c>
+      <c r="F183" s="33">
+        <v>142</v>
+      </c>
+      <c r="G183" s="34">
+        <f t="shared" si="0"/>
+        <v>304448</v>
+      </c>
       <c r="H183" s="21">
         <v>59798</v>
       </c>
@@ -9969,7 +9945,7 @@
       </c>
       <c r="J183" s="21"/>
       <c r="K183" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L183" s="20">
         <v>6217</v>
@@ -9979,23 +9955,26 @@
       </c>
     </row>
     <row r="184" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="18">
-        <v>178</v>
-      </c>
+      <c r="A184" s="18"/>
       <c r="B184" s="19" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="C184" s="20" t="s">
-        <v>327</v>
+        <v>773</v>
       </c>
       <c r="D184" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E184" s="21">
-        <v>44</v>
-      </c>
-      <c r="F184" s="46"/>
-      <c r="G184" s="47"/>
+        <v>2252.8000000000002</v>
+      </c>
+      <c r="F184" s="33">
+        <v>142</v>
+      </c>
+      <c r="G184" s="34">
+        <f t="shared" si="0"/>
+        <v>319897.60000000003</v>
+      </c>
       <c r="H184" s="21">
         <v>59798</v>
       </c>
@@ -10004,7 +9983,7 @@
       </c>
       <c r="J184" s="21"/>
       <c r="K184" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L184" s="20">
         <v>6217</v>
@@ -10013,66 +9992,65 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="1">
-        <v>179</v>
-      </c>
-      <c r="B185" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="C185" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="D185" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E185" s="6">
-        <v>1</v>
-      </c>
-      <c r="F185" s="7">
-        <v>3500</v>
-      </c>
-      <c r="G185" s="7">
-        <v>3500</v>
-      </c>
-      <c r="H185" s="6">
-        <v>125</v>
-      </c>
-      <c r="I185" s="8">
-        <v>46268</v>
-      </c>
-      <c r="J185" s="6"/>
-      <c r="K185" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="L185" s="7">
-        <v>6218</v>
-      </c>
-      <c r="M185" s="8">
+    <row r="185" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A185" s="18"/>
+      <c r="B185" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="C185" s="20" t="s">
+        <v>763</v>
+      </c>
+      <c r="D185" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E185" s="21">
+        <v>2086.4</v>
+      </c>
+      <c r="F185" s="33">
+        <v>142</v>
+      </c>
+      <c r="G185" s="34">
+        <f t="shared" si="0"/>
+        <v>296268.79999999999</v>
+      </c>
+      <c r="H185" s="21">
+        <v>59798</v>
+      </c>
+      <c r="I185" s="22">
+        <v>46237</v>
+      </c>
+      <c r="J185" s="21"/>
+      <c r="K185" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="L185" s="20">
+        <v>6217</v>
+      </c>
+      <c r="M185" s="22">
         <v>46329</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="1">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D186" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E186" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F186" s="7">
-        <v>30</v>
+        <v>3500</v>
       </c>
       <c r="G186" s="7">
-        <v>300</v>
+        <v>3500</v>
       </c>
       <c r="H186" s="6">
         <v>125</v>
@@ -10082,7 +10060,7 @@
       </c>
       <c r="J186" s="6"/>
       <c r="K186" s="7" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L186" s="7">
         <v>6218</v>
@@ -10093,38 +10071,38 @@
     </row>
     <row r="187" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="1">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="D187" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E187" s="6">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F187" s="7">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G187" s="7">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H187" s="6">
-        <v>5236</v>
+        <v>125</v>
       </c>
       <c r="I187" s="8">
         <v>46268</v>
       </c>
       <c r="J187" s="6"/>
       <c r="K187" s="7" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="L187" s="7">
-        <v>6219</v>
+        <v>6218</v>
       </c>
       <c r="M187" s="8">
         <v>46329</v>
@@ -10132,13 +10110,13 @@
     </row>
     <row r="188" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="1">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D188" s="7" t="s">
         <v>17</v>
@@ -10147,10 +10125,10 @@
         <v>50</v>
       </c>
       <c r="F188" s="7">
-        <v>170</v>
+        <v>3</v>
       </c>
       <c r="G188" s="7">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="H188" s="6">
         <v>5236</v>
@@ -10160,7 +10138,7 @@
       </c>
       <c r="J188" s="6"/>
       <c r="K188" s="7" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="L188" s="7">
         <v>6219</v>
@@ -10171,38 +10149,38 @@
     </row>
     <row r="189" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="1">
-        <v>183</v>
-      </c>
-      <c r="B189" s="9" t="s">
-        <v>351</v>
+        <v>182</v>
+      </c>
+      <c r="B189" s="11" t="s">
+        <v>337</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="D189" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E189" s="6">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F189" s="7">
-        <v>3300</v>
+        <v>170</v>
       </c>
       <c r="G189" s="7">
-        <v>6600</v>
+        <v>1500</v>
       </c>
       <c r="H189" s="6">
-        <v>4729</v>
+        <v>5236</v>
       </c>
       <c r="I189" s="8">
-        <v>46328</v>
+        <v>46268</v>
       </c>
       <c r="J189" s="6"/>
       <c r="K189" s="7" t="s">
-        <v>179</v>
+        <v>334</v>
       </c>
       <c r="L189" s="7">
-        <v>6220</v>
+        <v>6219</v>
       </c>
       <c r="M189" s="8">
         <v>46329</v>
@@ -10210,13 +10188,13 @@
     </row>
     <row r="190" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="1">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="D190" s="7" t="s">
         <v>17</v>
@@ -10225,10 +10203,10 @@
         <v>2</v>
       </c>
       <c r="F190" s="7">
-        <v>1600</v>
+        <v>3300</v>
       </c>
       <c r="G190" s="7">
-        <v>3200</v>
+        <v>6600</v>
       </c>
       <c r="H190" s="6">
         <v>4729</v>
@@ -10249,25 +10227,25 @@
     </row>
     <row r="191" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="1">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="D191" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E191" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F191" s="7">
-        <v>45</v>
+        <v>1600</v>
       </c>
       <c r="G191" s="7">
-        <v>270</v>
+        <v>3200</v>
       </c>
       <c r="H191" s="6">
         <v>4729</v>
@@ -10288,38 +10266,38 @@
     </row>
     <row r="192" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="1">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E192" s="6">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="F192" s="7">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="G192" s="7">
-        <v>5535</v>
+        <v>270</v>
       </c>
       <c r="H192" s="6">
-        <v>60</v>
+        <v>4729</v>
       </c>
       <c r="I192" s="8">
         <v>46328</v>
       </c>
       <c r="J192" s="6"/>
       <c r="K192" s="7" t="s">
-        <v>354</v>
+        <v>179</v>
       </c>
       <c r="L192" s="7">
-        <v>6221</v>
+        <v>6220</v>
       </c>
       <c r="M192" s="8">
         <v>46329</v>
@@ -10327,38 +10305,38 @@
     </row>
     <row r="193" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="1">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E193" s="6">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="F193" s="7">
-        <v>1500</v>
+        <v>135</v>
       </c>
       <c r="G193" s="7">
-        <v>3000</v>
+        <v>5535</v>
       </c>
       <c r="H193" s="6">
-        <v>13728</v>
+        <v>60</v>
       </c>
       <c r="I193" s="8">
         <v>46328</v>
       </c>
       <c r="J193" s="6"/>
       <c r="K193" s="7" t="s">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="L193" s="7">
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="M193" s="8">
         <v>46329</v>
@@ -10366,13 +10344,13 @@
     </row>
     <row r="194" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="1">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D194" s="7" t="s">
         <v>17</v>
@@ -10405,25 +10383,25 @@
     </row>
     <row r="195" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="1">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>28</v>
+        <v>359</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D195" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E195" s="6">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F195" s="7">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="G195" s="7">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="H195" s="6">
         <v>13728</v>
@@ -10444,25 +10422,25 @@
     </row>
     <row r="196" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="1">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>364</v>
+        <v>28</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D196" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E196" s="6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F196" s="7">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="G196" s="7">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="H196" s="6">
         <v>13728</v>
@@ -10483,25 +10461,25 @@
     </row>
     <row r="197" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="1">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D197" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E197" s="6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F197" s="7">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="G197" s="7">
-        <v>195</v>
+        <v>500</v>
       </c>
       <c r="H197" s="6">
         <v>13728</v>
@@ -10522,25 +10500,25 @@
     </row>
     <row r="198" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="1">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="D198" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E198" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F198" s="7">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="G198" s="7">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H198" s="6">
         <v>13728</v>
@@ -10561,25 +10539,25 @@
     </row>
     <row r="199" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="1">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D199" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E199" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F199" s="7">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="G199" s="7">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H199" s="6">
         <v>13728</v>
@@ -10598,68 +10576,67 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="200" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="18">
-        <v>194</v>
-      </c>
-      <c r="B200" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="C200" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="D200" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E200" s="21">
-        <v>695.99400000000003</v>
-      </c>
-      <c r="F200" s="33">
-        <v>142.98245600000001</v>
-      </c>
-      <c r="G200" s="34">
-        <f>F200*E200</f>
-        <v>99514.931481264008</v>
-      </c>
-      <c r="H200" s="21">
-        <v>59753</v>
-      </c>
-      <c r="I200" s="22">
+    <row r="200" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A200" s="1">
+        <v>193</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E200" s="6">
+        <v>2</v>
+      </c>
+      <c r="F200" s="7">
+        <v>125</v>
+      </c>
+      <c r="G200" s="7">
+        <v>250</v>
+      </c>
+      <c r="H200" s="6">
+        <v>13728</v>
+      </c>
+      <c r="I200" s="8">
         <v>46328</v>
       </c>
-      <c r="J200" s="21"/>
-      <c r="K200" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="L200" s="20">
-        <v>6223</v>
-      </c>
-      <c r="M200" s="22">
+      <c r="J200" s="6"/>
+      <c r="K200" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L200" s="7">
+        <v>6222</v>
+      </c>
+      <c r="M200" s="8">
         <v>46329</v>
       </c>
     </row>
     <row r="201" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="18">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B201" s="19" t="s">
-        <v>42</v>
+        <v>327</v>
       </c>
       <c r="C201" s="20" t="s">
-        <v>369</v>
+        <v>766</v>
       </c>
       <c r="D201" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E201" s="21">
-        <v>1175.991</v>
+        <v>1980</v>
       </c>
       <c r="F201" s="33">
         <v>142.98245600000001</v>
       </c>
       <c r="G201" s="34">
-        <f t="shared" ref="G201:G203" si="0">F201*E201</f>
-        <v>168146.08141389603</v>
+        <f>F201*E201</f>
+        <v>283105.26288000005</v>
       </c>
       <c r="H201" s="21">
         <v>59753</v>
@@ -10669,7 +10646,7 @@
       </c>
       <c r="J201" s="21"/>
       <c r="K201" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L201" s="20">
         <v>6223</v>
@@ -10680,26 +10657,26 @@
     </row>
     <row r="202" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="18">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B202" s="19" t="s">
-        <v>373</v>
+        <v>42</v>
       </c>
       <c r="C202" s="20" t="s">
-        <v>370</v>
+        <v>764</v>
       </c>
       <c r="D202" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E202" s="21">
-        <v>1800</v>
+        <v>2260</v>
       </c>
       <c r="F202" s="33">
         <v>142.98245600000001</v>
       </c>
       <c r="G202" s="34">
-        <f t="shared" si="0"/>
-        <v>257368.42080000002</v>
+        <f t="shared" ref="G202:G203" si="1">F202*E202</f>
+        <v>323140.35056000005</v>
       </c>
       <c r="H202" s="21">
         <v>59753</v>
@@ -10709,7 +10686,7 @@
       </c>
       <c r="J202" s="21"/>
       <c r="K202" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L202" s="20">
         <v>6223</v>
@@ -10720,26 +10697,26 @@
     </row>
     <row r="203" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="18">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B203" s="19" t="s">
-        <v>40</v>
+        <v>361</v>
       </c>
       <c r="C203" s="20" t="s">
-        <v>371</v>
+        <v>765</v>
       </c>
       <c r="D203" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E203" s="21">
-        <v>2000</v>
+        <v>1126</v>
       </c>
       <c r="F203" s="33">
         <v>142.98245600000001</v>
       </c>
       <c r="G203" s="34">
-        <f t="shared" si="0"/>
-        <v>285964.91200000001</v>
+        <f t="shared" si="1"/>
+        <v>160998.245456</v>
       </c>
       <c r="H203" s="21">
         <v>59753</v>
@@ -10749,7 +10726,7 @@
       </c>
       <c r="J203" s="21"/>
       <c r="K203" s="20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="L203" s="20">
         <v>6223</v>
@@ -10763,10 +10740,10 @@
         <v>198</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="D204" s="7" t="s">
         <v>17</v>
@@ -10802,10 +10779,10 @@
         <v>199</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="C205" s="14" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D205" s="7" t="s">
         <v>17</v>
@@ -10827,7 +10804,7 @@
       </c>
       <c r="J205" s="6"/>
       <c r="K205" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L205" s="7">
         <v>6226</v>
@@ -10841,10 +10818,10 @@
         <v>200</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="D206" s="7" t="s">
         <v>17</v>
@@ -10866,7 +10843,7 @@
       </c>
       <c r="J206" s="6"/>
       <c r="K206" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L206" s="7">
         <v>6226</v>
@@ -10880,10 +10857,10 @@
         <v>201</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="D207" s="7" t="s">
         <v>17</v>
@@ -10905,7 +10882,7 @@
       </c>
       <c r="J207" s="6"/>
       <c r="K207" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L207" s="7">
         <v>6226</v>
@@ -10919,10 +10896,10 @@
         <v>202</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D208" s="7" t="s">
         <v>17</v>
@@ -10944,7 +10921,7 @@
       </c>
       <c r="J208" s="6"/>
       <c r="K208" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L208" s="7">
         <v>6226</v>
@@ -10958,10 +10935,10 @@
         <v>203</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D209" s="7" t="s">
         <v>17</v>
@@ -10983,7 +10960,7 @@
       </c>
       <c r="J209" s="6"/>
       <c r="K209" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L209" s="7">
         <v>6226</v>
@@ -10997,10 +10974,10 @@
         <v>204</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="D210" s="7" t="s">
         <v>17</v>
@@ -11022,7 +10999,7 @@
       </c>
       <c r="J210" s="6"/>
       <c r="K210" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L210" s="7">
         <v>6226</v>
@@ -11036,10 +11013,10 @@
         <v>205</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D211" s="7" t="s">
         <v>17</v>
@@ -11061,7 +11038,7 @@
       </c>
       <c r="J211" s="6"/>
       <c r="K211" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L211" s="7">
         <v>6226</v>
@@ -11075,10 +11052,10 @@
         <v>206</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D212" s="7" t="s">
         <v>17</v>
@@ -11100,7 +11077,7 @@
       </c>
       <c r="J212" s="6"/>
       <c r="K212" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L212" s="7">
         <v>6226</v>
@@ -11114,10 +11091,10 @@
         <v>207</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="D213" s="7" t="s">
         <v>17</v>
@@ -11139,7 +11116,7 @@
       </c>
       <c r="J213" s="6"/>
       <c r="K213" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L213" s="7">
         <v>6226</v>
@@ -11153,10 +11130,10 @@
         <v>208</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="D214" s="7" t="s">
         <v>17</v>
@@ -11178,7 +11155,7 @@
       </c>
       <c r="J214" s="6"/>
       <c r="K214" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L214" s="7">
         <v>6226</v>
@@ -11192,10 +11169,10 @@
         <v>209</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="D215" s="7" t="s">
         <v>17</v>
@@ -11217,7 +11194,7 @@
       </c>
       <c r="J215" s="6"/>
       <c r="K215" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L215" s="7">
         <v>6226</v>
@@ -11231,10 +11208,10 @@
         <v>210</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="D216" s="7" t="s">
         <v>17</v>
@@ -11256,7 +11233,7 @@
       </c>
       <c r="J216" s="6"/>
       <c r="K216" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L216" s="7">
         <v>6226</v>
@@ -11270,10 +11247,10 @@
         <v>211</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D217" s="7" t="s">
         <v>17</v>
@@ -11295,7 +11272,7 @@
       </c>
       <c r="J217" s="6"/>
       <c r="K217" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L217" s="7">
         <v>6226</v>
@@ -11309,10 +11286,10 @@
         <v>212</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="D218" s="7" t="s">
         <v>17</v>
@@ -11334,7 +11311,7 @@
       </c>
       <c r="J218" s="6"/>
       <c r="K218" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L218" s="7">
         <v>6227</v>
@@ -11348,10 +11325,10 @@
         <v>213</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="D219" s="7" t="s">
         <v>17</v>
@@ -11373,7 +11350,7 @@
       </c>
       <c r="J219" s="6"/>
       <c r="K219" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L219" s="7">
         <v>6227</v>
@@ -11387,10 +11364,10 @@
         <v>214</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="D220" s="7" t="s">
         <v>17</v>
@@ -11412,7 +11389,7 @@
       </c>
       <c r="J220" s="6"/>
       <c r="K220" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L220" s="7">
         <v>6227</v>
@@ -11426,10 +11403,10 @@
         <v>215</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D221" s="7" t="s">
         <v>17</v>
@@ -11451,7 +11428,7 @@
       </c>
       <c r="J221" s="6"/>
       <c r="K221" s="7" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L221" s="7">
         <v>6227</v>
@@ -11468,7 +11445,7 @@
         <v>208</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="D222" s="7" t="s">
         <v>17</v>
@@ -11486,7 +11463,7 @@
         <v>1476</v>
       </c>
       <c r="I222" s="8" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="J222" s="6"/>
       <c r="K222" s="7" t="s">
@@ -11507,7 +11484,7 @@
         <v>209</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D223" s="7" t="s">
         <v>17</v>
@@ -11525,7 +11502,7 @@
         <v>1476</v>
       </c>
       <c r="I223" s="8" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="J223" s="6"/>
       <c r="K223" s="7" t="s">
@@ -11543,13 +11520,13 @@
         <v>218</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="E224" s="6">
         <v>5.5</v>
@@ -11564,11 +11541,11 @@
         <v>783</v>
       </c>
       <c r="I224" s="8" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="J224" s="6"/>
       <c r="K224" s="7" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="L224" s="7">
         <v>6229</v>
@@ -11585,7 +11562,7 @@
         <v>40</v>
       </c>
       <c r="C225" s="26" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="D225" s="26" t="s">
         <v>75</v>
@@ -11604,7 +11581,7 @@
         <v>699</v>
       </c>
       <c r="I225" s="30" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="J225" s="27"/>
       <c r="K225" s="26" t="s">
@@ -11625,7 +11602,7 @@
         <v>43</v>
       </c>
       <c r="C226" s="26" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="D226" s="26" t="s">
         <v>75</v>
@@ -11644,7 +11621,7 @@
         <v>699</v>
       </c>
       <c r="I226" s="30" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="J226" s="27"/>
       <c r="K226" s="26" t="s">
@@ -11662,10 +11639,10 @@
         <v>221</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="D227" s="7" t="s">
         <v>17</v>
@@ -11683,7 +11660,7 @@
         <v>13750</v>
       </c>
       <c r="I227" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J227" s="6"/>
       <c r="K227" s="7" t="s">
@@ -11701,10 +11678,10 @@
         <v>222</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="D228" s="7" t="s">
         <v>17</v>
@@ -11722,7 +11699,7 @@
         <v>13750</v>
       </c>
       <c r="I228" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J228" s="6"/>
       <c r="K228" s="7" t="s">
@@ -11740,10 +11717,10 @@
         <v>223</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="D229" s="7" t="s">
         <v>17</v>
@@ -11761,7 +11738,7 @@
         <v>13750</v>
       </c>
       <c r="I229" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J229" s="6"/>
       <c r="K229" s="7" t="s">
@@ -11779,10 +11756,10 @@
         <v>224</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="D230" s="7" t="s">
         <v>17</v>
@@ -11800,11 +11777,11 @@
         <v>34</v>
       </c>
       <c r="I230" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J230" s="6"/>
       <c r="K230" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L230" s="7">
         <v>6232</v>
@@ -11818,10 +11795,10 @@
         <v>225</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="D231" s="7" t="s">
         <v>75</v>
@@ -11839,11 +11816,11 @@
         <v>34</v>
       </c>
       <c r="I231" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J231" s="6"/>
       <c r="K231" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L231" s="7">
         <v>6232</v>
@@ -11857,10 +11834,10 @@
         <v>226</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="D232" s="7" t="s">
         <v>17</v>
@@ -11878,11 +11855,11 @@
         <v>34</v>
       </c>
       <c r="I232" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J232" s="6"/>
       <c r="K232" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L232" s="7">
         <v>6232</v>
@@ -11896,10 +11873,10 @@
         <v>227</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="D233" s="7" t="s">
         <v>75</v>
@@ -11917,11 +11894,11 @@
         <v>34</v>
       </c>
       <c r="I233" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J233" s="6"/>
       <c r="K233" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L233" s="7">
         <v>6232</v>
@@ -11935,10 +11912,10 @@
         <v>228</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="D234" s="7" t="s">
         <v>17</v>
@@ -11956,11 +11933,11 @@
         <v>34</v>
       </c>
       <c r="I234" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J234" s="6"/>
       <c r="K234" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L234" s="7">
         <v>6232</v>
@@ -11974,10 +11951,10 @@
         <v>229</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D235" s="7" t="s">
         <v>17</v>
@@ -11995,11 +11972,11 @@
         <v>34</v>
       </c>
       <c r="I235" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J235" s="6"/>
       <c r="K235" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L235" s="7">
         <v>6232</v>
@@ -12013,10 +11990,10 @@
         <v>230</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="D236" s="7" t="s">
         <v>17</v>
@@ -12034,11 +12011,11 @@
         <v>34</v>
       </c>
       <c r="I236" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J236" s="6"/>
       <c r="K236" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L236" s="7">
         <v>6232</v>
@@ -12052,10 +12029,10 @@
         <v>231</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D237" s="7" t="s">
         <v>17</v>
@@ -12073,11 +12050,11 @@
         <v>34</v>
       </c>
       <c r="I237" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J237" s="6"/>
       <c r="K237" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L237" s="7">
         <v>6232</v>
@@ -12091,10 +12068,10 @@
         <v>232</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D238" s="7" t="s">
         <v>17</v>
@@ -12112,11 +12089,11 @@
         <v>34</v>
       </c>
       <c r="I238" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J238" s="6"/>
       <c r="K238" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L238" s="7">
         <v>6232</v>
@@ -12130,10 +12107,10 @@
         <v>233</v>
       </c>
       <c r="B239" s="11" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="D239" s="7" t="s">
         <v>17</v>
@@ -12151,11 +12128,11 @@
         <v>34</v>
       </c>
       <c r="I239" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J239" s="6"/>
       <c r="K239" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L239" s="7">
         <v>6232</v>
@@ -12169,10 +12146,10 @@
         <v>234</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="D240" s="7" t="s">
         <v>17</v>
@@ -12190,11 +12167,11 @@
         <v>35</v>
       </c>
       <c r="I240" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J240" s="6"/>
       <c r="K240" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L240" s="7">
         <v>6233</v>
@@ -12208,10 +12185,10 @@
         <v>235</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="D241" s="7" t="s">
         <v>17</v>
@@ -12229,11 +12206,11 @@
         <v>36</v>
       </c>
       <c r="I241" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J241" s="6"/>
       <c r="K241" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L241" s="7">
         <v>6234</v>
@@ -12250,7 +12227,7 @@
         <v>92</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="D242" s="7" t="s">
         <v>17</v>
@@ -12268,11 +12245,11 @@
         <v>36</v>
       </c>
       <c r="I242" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J242" s="6"/>
       <c r="K242" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L242" s="7">
         <v>6234</v>
@@ -12286,10 +12263,10 @@
         <v>237</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="D243" s="7" t="s">
         <v>17</v>
@@ -12307,11 +12284,11 @@
         <v>36</v>
       </c>
       <c r="I243" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J243" s="6"/>
       <c r="K243" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L243" s="7">
         <v>6234</v>
@@ -12325,10 +12302,10 @@
         <v>238</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="D244" s="7" t="s">
         <v>17</v>
@@ -12346,11 +12323,11 @@
         <v>36</v>
       </c>
       <c r="I244" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J244" s="6"/>
       <c r="K244" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L244" s="7">
         <v>6234</v>
@@ -12364,10 +12341,10 @@
         <v>239</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="D245" s="7" t="s">
         <v>17</v>
@@ -12385,11 +12362,11 @@
         <v>121</v>
       </c>
       <c r="I245" s="8" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="J245" s="6"/>
       <c r="K245" s="7" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L245" s="7">
         <v>6235</v>
@@ -12406,7 +12383,7 @@
         <v>298</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="D246" s="7" t="s">
         <v>17</v>
@@ -12424,7 +12401,7 @@
         <v>339</v>
       </c>
       <c r="I246" s="8" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J246" s="6"/>
       <c r="K246" s="7" t="s">
@@ -12445,7 +12422,7 @@
         <v>299</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="D247" s="7" t="s">
         <v>17</v>
@@ -12463,7 +12440,7 @@
         <v>339</v>
       </c>
       <c r="I247" s="8" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J247" s="6"/>
       <c r="K247" s="7" t="s">
@@ -12481,10 +12458,10 @@
         <v>242</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="D248" s="7" t="s">
         <v>17</v>
@@ -12502,7 +12479,7 @@
         <v>5166</v>
       </c>
       <c r="I248" s="8" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J248" s="6"/>
       <c r="K248" s="7" t="s">
@@ -12520,10 +12497,10 @@
         <v>243</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="D249" s="7" t="s">
         <v>17</v>
@@ -12541,7 +12518,7 @@
         <v>5166</v>
       </c>
       <c r="I249" s="8" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J249" s="6"/>
       <c r="K249" s="7" t="s">
@@ -12559,10 +12536,10 @@
         <v>244</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="D250" s="7" t="s">
         <v>17</v>
@@ -12580,7 +12557,7 @@
         <v>5166</v>
       </c>
       <c r="I250" s="8" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J250" s="6"/>
       <c r="K250" s="7" t="s">
@@ -12598,10 +12575,10 @@
         <v>245</v>
       </c>
       <c r="B251" s="36" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="C251" s="37" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="D251" s="37" t="s">
         <v>17</v>
@@ -12619,11 +12596,11 @@
         <v>83</v>
       </c>
       <c r="I251" s="39" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J251" s="38"/>
       <c r="K251" s="37" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L251" s="37">
         <v>6238</v>
@@ -12637,10 +12614,10 @@
         <v>246</v>
       </c>
       <c r="B252" s="36" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="C252" s="37" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="D252" s="37" t="s">
         <v>17</v>
@@ -12658,11 +12635,11 @@
         <v>83</v>
       </c>
       <c r="I252" s="39" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J252" s="38"/>
       <c r="K252" s="37" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L252" s="37">
         <v>6238</v>
@@ -12676,10 +12653,10 @@
         <v>247</v>
       </c>
       <c r="B253" s="36" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C253" s="37" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D253" s="37" t="s">
         <v>17</v>
@@ -12697,11 +12674,11 @@
         <v>83</v>
       </c>
       <c r="I253" s="39" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J253" s="38"/>
       <c r="K253" s="37" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L253" s="37">
         <v>6238</v>
@@ -12736,11 +12713,11 @@
         <v>83</v>
       </c>
       <c r="I254" s="39" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J254" s="38"/>
       <c r="K254" s="37" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L254" s="37">
         <v>6238</v>
@@ -12754,10 +12731,10 @@
         <v>249</v>
       </c>
       <c r="B255" s="36" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="C255" s="37" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="D255" s="37" t="s">
         <v>17</v>
@@ -12775,11 +12752,11 @@
         <v>83</v>
       </c>
       <c r="I255" s="39" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J255" s="38"/>
       <c r="K255" s="37" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L255" s="37">
         <v>6238</v>
@@ -12793,10 +12770,10 @@
         <v>250</v>
       </c>
       <c r="B256" s="41" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C256" s="37" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="D256" s="37" t="s">
         <v>17</v>
@@ -12814,11 +12791,11 @@
         <v>83</v>
       </c>
       <c r="I256" s="39" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J256" s="38"/>
       <c r="K256" s="37" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L256" s="37">
         <v>6238</v>
@@ -12832,10 +12809,10 @@
         <v>251</v>
       </c>
       <c r="B257" s="41" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="C257" s="37" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D257" s="37" t="s">
         <v>17</v>
@@ -12853,11 +12830,11 @@
         <v>83</v>
       </c>
       <c r="I257" s="39" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J257" s="38"/>
       <c r="K257" s="37" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L257" s="37">
         <v>6238</v>
@@ -12871,10 +12848,10 @@
         <v>252</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="D258" s="7" t="s">
         <v>17</v>
@@ -12892,11 +12869,11 @@
         <v>39</v>
       </c>
       <c r="I258" s="8" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J258" s="6"/>
       <c r="K258" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L258" s="7">
         <v>6239</v>
@@ -12910,10 +12887,10 @@
         <v>253</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="D259" s="7" t="s">
         <v>17</v>
@@ -12931,11 +12908,11 @@
         <v>39</v>
       </c>
       <c r="I259" s="8" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J259" s="6"/>
       <c r="K259" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L259" s="7">
         <v>6239</v>
@@ -12952,7 +12929,7 @@
         <v>92</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="D260" s="7" t="s">
         <v>17</v>
@@ -12970,11 +12947,11 @@
         <v>39</v>
       </c>
       <c r="I260" s="8" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J260" s="6"/>
       <c r="K260" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L260" s="7">
         <v>6239</v>
@@ -12988,10 +12965,10 @@
         <v>255</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="D261" s="7" t="s">
         <v>17</v>
@@ -13009,11 +12986,11 @@
         <v>39</v>
       </c>
       <c r="I261" s="8" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="J261" s="6"/>
       <c r="K261" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L261" s="7">
         <v>6239</v>
@@ -13027,10 +13004,10 @@
         <v>256</v>
       </c>
       <c r="B262" s="15" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="D262" s="7" t="s">
         <v>17</v>
@@ -13048,7 +13025,7 @@
         <v>2437</v>
       </c>
       <c r="I262" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J262" s="6"/>
       <c r="K262" s="7" t="s">
@@ -13066,10 +13043,10 @@
         <v>257</v>
       </c>
       <c r="B263" s="15" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="D263" s="7" t="s">
         <v>17</v>
@@ -13087,7 +13064,7 @@
         <v>2437</v>
       </c>
       <c r="I263" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J263" s="6"/>
       <c r="K263" s="7" t="s">
@@ -13105,10 +13082,10 @@
         <v>258</v>
       </c>
       <c r="B264" s="11" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="D264" s="7" t="s">
         <v>17</v>
@@ -13126,7 +13103,7 @@
         <v>2437</v>
       </c>
       <c r="I264" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J264" s="6"/>
       <c r="K264" s="7" t="s">
@@ -13144,10 +13121,10 @@
         <v>259</v>
       </c>
       <c r="B265" s="11" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="D265" s="7" t="s">
         <v>17</v>
@@ -13165,7 +13142,7 @@
         <v>2437</v>
       </c>
       <c r="I265" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J265" s="6"/>
       <c r="K265" s="7" t="s">
@@ -13183,10 +13160,10 @@
         <v>260</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D266" s="7" t="s">
         <v>17</v>
@@ -13204,7 +13181,7 @@
         <v>2437</v>
       </c>
       <c r="I266" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J266" s="6"/>
       <c r="K266" s="7" t="s">
@@ -13222,10 +13199,10 @@
         <v>261</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="D267" s="7" t="s">
         <v>17</v>
@@ -13243,7 +13220,7 @@
         <v>2437</v>
       </c>
       <c r="I267" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J267" s="6"/>
       <c r="K267" s="7" t="s">
@@ -13261,10 +13238,10 @@
         <v>262</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D268" s="7" t="s">
         <v>17</v>
@@ -13282,7 +13259,7 @@
         <v>2437</v>
       </c>
       <c r="I268" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J268" s="6"/>
       <c r="K268" s="7" t="s">
@@ -13300,10 +13277,10 @@
         <v>263</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="D269" s="7" t="s">
         <v>17</v>
@@ -13321,7 +13298,7 @@
         <v>2437</v>
       </c>
       <c r="I269" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J269" s="6"/>
       <c r="K269" s="7" t="s">
@@ -13339,10 +13316,10 @@
         <v>264</v>
       </c>
       <c r="B270" s="11" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="D270" s="7" t="s">
         <v>17</v>
@@ -13360,7 +13337,7 @@
         <v>2437</v>
       </c>
       <c r="I270" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J270" s="6"/>
       <c r="K270" s="7" t="s">
@@ -13378,10 +13355,10 @@
         <v>265</v>
       </c>
       <c r="B271" s="11" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="D271" s="7" t="s">
         <v>17</v>
@@ -13399,7 +13376,7 @@
         <v>2437</v>
       </c>
       <c r="I271" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J271" s="6"/>
       <c r="K271" s="7" t="s">
@@ -13417,10 +13394,10 @@
         <v>266</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="D272" s="7" t="s">
         <v>17</v>
@@ -13438,7 +13415,7 @@
         <v>2437</v>
       </c>
       <c r="I272" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J272" s="6"/>
       <c r="K272" s="7" t="s">
@@ -13456,10 +13433,10 @@
         <v>267</v>
       </c>
       <c r="B273" s="11" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="D273" s="7" t="s">
         <v>17</v>
@@ -13477,7 +13454,7 @@
         <v>2437</v>
       </c>
       <c r="I273" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J273" s="6"/>
       <c r="K273" s="7" t="s">
@@ -13495,10 +13472,10 @@
         <v>268</v>
       </c>
       <c r="B274" s="11" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="D274" s="7" t="s">
         <v>17</v>
@@ -13516,7 +13493,7 @@
         <v>2437</v>
       </c>
       <c r="I274" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J274" s="6"/>
       <c r="K274" s="7" t="s">
@@ -13534,10 +13511,10 @@
         <v>269</v>
       </c>
       <c r="B275" s="15" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="D275" s="7" t="s">
         <v>17</v>
@@ -13555,7 +13532,7 @@
         <v>2437</v>
       </c>
       <c r="I275" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J275" s="6"/>
       <c r="K275" s="7" t="s">
@@ -13573,10 +13550,10 @@
         <v>270</v>
       </c>
       <c r="B276" s="11" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="D276" s="7" t="s">
         <v>17</v>
@@ -13594,7 +13571,7 @@
         <v>2437</v>
       </c>
       <c r="I276" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J276" s="6"/>
       <c r="K276" s="7" t="s">
@@ -13612,10 +13589,10 @@
         <v>271</v>
       </c>
       <c r="B277" s="12" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="D277" s="7" t="s">
         <v>17</v>
@@ -13633,7 +13610,7 @@
         <v>2437</v>
       </c>
       <c r="I277" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J277" s="6"/>
       <c r="K277" s="7" t="s">
@@ -13651,10 +13628,10 @@
         <v>272</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D278" s="7" t="s">
         <v>17</v>
@@ -13672,7 +13649,7 @@
         <v>2437</v>
       </c>
       <c r="I278" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J278" s="6"/>
       <c r="K278" s="7" t="s">
@@ -13690,10 +13667,10 @@
         <v>273</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="D279" s="7" t="s">
         <v>17</v>
@@ -13711,7 +13688,7 @@
         <v>2437</v>
       </c>
       <c r="I279" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J279" s="6"/>
       <c r="K279" s="7" t="s">
@@ -13729,10 +13706,10 @@
         <v>274</v>
       </c>
       <c r="B280" s="15" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="D280" s="7" t="s">
         <v>17</v>
@@ -13750,7 +13727,7 @@
         <v>2437</v>
       </c>
       <c r="I280" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J280" s="6"/>
       <c r="K280" s="7" t="s">
@@ -13768,10 +13745,10 @@
         <v>275</v>
       </c>
       <c r="B281" s="15" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="D281" s="7" t="s">
         <v>17</v>
@@ -13789,7 +13766,7 @@
         <v>2437</v>
       </c>
       <c r="I281" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J281" s="6"/>
       <c r="K281" s="7" t="s">
@@ -13807,10 +13784,10 @@
         <v>276</v>
       </c>
       <c r="B282" s="15" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="D282" s="7" t="s">
         <v>17</v>
@@ -13828,7 +13805,7 @@
         <v>2437</v>
       </c>
       <c r="I282" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J282" s="6"/>
       <c r="K282" s="7" t="s">
@@ -13846,10 +13823,10 @@
         <v>277</v>
       </c>
       <c r="B283" s="11" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="D283" s="7" t="s">
         <v>17</v>
@@ -13867,7 +13844,7 @@
         <v>2437</v>
       </c>
       <c r="I283" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J283" s="6"/>
       <c r="K283" s="7" t="s">
@@ -13885,10 +13862,10 @@
         <v>278</v>
       </c>
       <c r="B284" s="15" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="D284" s="7" t="s">
         <v>17</v>
@@ -13906,7 +13883,7 @@
         <v>2437</v>
       </c>
       <c r="I284" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J284" s="6"/>
       <c r="K284" s="7" t="s">
@@ -13924,10 +13901,10 @@
         <v>279</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D285" s="7" t="s">
         <v>17</v>
@@ -13945,7 +13922,7 @@
         <v>2437</v>
       </c>
       <c r="I285" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J285" s="6"/>
       <c r="K285" s="7" t="s">
@@ -13964,7 +13941,7 @@
       </c>
       <c r="B286" s="9"/>
       <c r="C286" s="7" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="D286" s="7" t="s">
         <v>17</v>
@@ -13982,7 +13959,7 @@
         <v>2437</v>
       </c>
       <c r="I286" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J286" s="6"/>
       <c r="K286" s="7" t="s">
@@ -14000,10 +13977,10 @@
         <v>281</v>
       </c>
       <c r="B287" s="15" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="D287" s="7" t="s">
         <v>17</v>
@@ -14021,7 +13998,7 @@
         <v>2437</v>
       </c>
       <c r="I287" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J287" s="6"/>
       <c r="K287" s="7" t="s">
@@ -14039,10 +14016,10 @@
         <v>282</v>
       </c>
       <c r="B288" s="15" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="D288" s="7" t="s">
         <v>17</v>
@@ -14060,7 +14037,7 @@
         <v>2437</v>
       </c>
       <c r="I288" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J288" s="6"/>
       <c r="K288" s="7" t="s">
@@ -14078,10 +14055,10 @@
         <v>283</v>
       </c>
       <c r="B289" s="15" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="D289" s="7" t="s">
         <v>17</v>
@@ -14099,7 +14076,7 @@
         <v>2437</v>
       </c>
       <c r="I289" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J289" s="6"/>
       <c r="K289" s="7" t="s">
@@ -14117,10 +14094,10 @@
         <v>284</v>
       </c>
       <c r="B290" s="15" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="D290" s="7" t="s">
         <v>17</v>
@@ -14138,7 +14115,7 @@
         <v>2437</v>
       </c>
       <c r="I290" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J290" s="6"/>
       <c r="K290" s="7" t="s">
@@ -14156,10 +14133,10 @@
         <v>285</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D291" s="7" t="s">
         <v>17</v>
@@ -14177,7 +14154,7 @@
         <v>2437</v>
       </c>
       <c r="I291" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J291" s="6"/>
       <c r="K291" s="7" t="s">
@@ -14195,10 +14172,10 @@
         <v>286</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="D292" s="7" t="s">
         <v>17</v>
@@ -14216,7 +14193,7 @@
         <v>2437</v>
       </c>
       <c r="I292" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J292" s="6"/>
       <c r="K292" s="7" t="s">
@@ -14234,10 +14211,10 @@
         <v>287</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="D293" s="7" t="s">
         <v>17</v>
@@ -14255,7 +14232,7 @@
         <v>2437</v>
       </c>
       <c r="I293" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J293" s="6"/>
       <c r="K293" s="7" t="s">
@@ -14273,10 +14250,10 @@
         <v>288</v>
       </c>
       <c r="B294" s="9" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="D294" s="7" t="s">
         <v>17</v>
@@ -14294,7 +14271,7 @@
         <v>2437</v>
       </c>
       <c r="I294" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J294" s="6"/>
       <c r="K294" s="7" t="s">
@@ -14312,10 +14289,10 @@
         <v>289</v>
       </c>
       <c r="B295" s="9" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="D295" s="7" t="s">
         <v>17</v>
@@ -14333,7 +14310,7 @@
         <v>1480</v>
       </c>
       <c r="I295" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J295" s="6"/>
       <c r="K295" s="7" t="s">
@@ -14351,10 +14328,10 @@
         <v>290</v>
       </c>
       <c r="B296" s="9" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="D296" s="7" t="s">
         <v>17</v>
@@ -14372,7 +14349,7 @@
         <v>1480</v>
       </c>
       <c r="I296" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J296" s="6"/>
       <c r="K296" s="7" t="s">
@@ -14390,10 +14367,10 @@
         <v>291</v>
       </c>
       <c r="B297" s="9" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="D297" s="7" t="s">
         <v>75</v>
@@ -14411,11 +14388,11 @@
         <v>809</v>
       </c>
       <c r="I297" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J297" s="6"/>
       <c r="K297" s="7" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="L297" s="7">
         <v>6244</v>
@@ -14429,10 +14406,10 @@
         <v>292</v>
       </c>
       <c r="B298" s="9" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="D298" s="7" t="s">
         <v>75</v>
@@ -14450,11 +14427,11 @@
         <v>809</v>
       </c>
       <c r="I298" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J298" s="6"/>
       <c r="K298" s="7" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="L298" s="7">
         <v>6244</v>
@@ -14468,10 +14445,10 @@
         <v>293</v>
       </c>
       <c r="B299" s="9" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="D299" s="7" t="s">
         <v>17</v>
@@ -14489,11 +14466,11 @@
         <v>34382</v>
       </c>
       <c r="I299" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J299" s="6"/>
       <c r="K299" s="7" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="L299" s="7">
         <v>6245</v>
@@ -14507,10 +14484,10 @@
         <v>294</v>
       </c>
       <c r="B300" s="9" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="D300" s="7" t="s">
         <v>17</v>
@@ -14528,11 +14505,11 @@
         <v>34382</v>
       </c>
       <c r="I300" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J300" s="6"/>
       <c r="K300" s="7" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="L300" s="7">
         <v>6245</v>
@@ -14546,10 +14523,10 @@
         <v>295</v>
       </c>
       <c r="B301" s="9" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="D301" s="7" t="s">
         <v>17</v>
@@ -14567,11 +14544,11 @@
         <v>34382</v>
       </c>
       <c r="I301" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J301" s="6"/>
       <c r="K301" s="7" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="L301" s="7">
         <v>6245</v>
@@ -14585,10 +14562,10 @@
         <v>296</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="D302" s="7" t="s">
         <v>17</v>
@@ -14606,7 +14583,7 @@
         <v>394</v>
       </c>
       <c r="I302" s="8" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="J302" s="6"/>
       <c r="K302" s="7" t="s">
@@ -14616,7 +14593,7 @@
         <v>6246</v>
       </c>
       <c r="M302" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="303" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14624,10 +14601,10 @@
         <v>297</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="D303" s="7" t="s">
         <v>17</v>
@@ -14645,7 +14622,7 @@
         <v>394</v>
       </c>
       <c r="I303" s="8" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="J303" s="6"/>
       <c r="K303" s="7" t="s">
@@ -14655,7 +14632,7 @@
         <v>6246</v>
       </c>
       <c r="M303" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="304" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14663,10 +14640,10 @@
         <v>298</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="D304" s="7" t="s">
         <v>17</v>
@@ -14684,17 +14661,17 @@
         <v>42</v>
       </c>
       <c r="I304" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="J304" s="6"/>
       <c r="K304" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L304" s="7">
         <v>6247</v>
       </c>
       <c r="M304" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="305" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14702,10 +14679,10 @@
         <v>299</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="D305" s="7" t="s">
         <v>17</v>
@@ -14723,17 +14700,17 @@
         <v>42</v>
       </c>
       <c r="I305" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="J305" s="6"/>
       <c r="K305" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L305" s="7">
         <v>6247</v>
       </c>
       <c r="M305" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="306" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14741,10 +14718,10 @@
         <v>300</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="D306" s="7" t="s">
         <v>17</v>
@@ -14762,17 +14739,17 @@
         <v>42</v>
       </c>
       <c r="I306" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="J306" s="6"/>
       <c r="K306" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L306" s="7">
         <v>6247</v>
       </c>
       <c r="M306" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="307" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14780,10 +14757,10 @@
         <v>301</v>
       </c>
       <c r="B307" s="9" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="D307" s="7" t="s">
         <v>17</v>
@@ -14801,17 +14778,17 @@
         <v>42</v>
       </c>
       <c r="I307" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="J307" s="6"/>
       <c r="K307" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L307" s="7">
         <v>6247</v>
       </c>
       <c r="M307" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="308" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14819,10 +14796,10 @@
         <v>302</v>
       </c>
       <c r="B308" s="9" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D308" s="7" t="s">
         <v>17</v>
@@ -14840,17 +14817,17 @@
         <v>42</v>
       </c>
       <c r="I308" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="J308" s="6"/>
       <c r="K308" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L308" s="7">
         <v>6247</v>
       </c>
       <c r="M308" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="309" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14858,10 +14835,10 @@
         <v>303</v>
       </c>
       <c r="B309" s="9" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="D309" s="7" t="s">
         <v>17</v>
@@ -14879,17 +14856,17 @@
         <v>42</v>
       </c>
       <c r="I309" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="J309" s="6"/>
       <c r="K309" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L309" s="7">
         <v>6247</v>
       </c>
       <c r="M309" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="310" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14897,10 +14874,10 @@
         <v>304</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="D310" s="7" t="s">
         <v>17</v>
@@ -14918,17 +14895,17 @@
         <v>42</v>
       </c>
       <c r="I310" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="J310" s="6"/>
       <c r="K310" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L310" s="7">
         <v>6247</v>
       </c>
       <c r="M310" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="311" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14957,17 +14934,17 @@
         <v>42</v>
       </c>
       <c r="I311" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="J311" s="6"/>
       <c r="K311" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L311" s="7">
         <v>6247</v>
       </c>
       <c r="M311" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14975,10 +14952,10 @@
         <v>306</v>
       </c>
       <c r="B312" s="9" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="D312" s="7" t="s">
         <v>17</v>
@@ -14996,17 +14973,17 @@
         <v>42</v>
       </c>
       <c r="I312" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="J312" s="6"/>
       <c r="K312" s="7" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L312" s="7">
         <v>6247</v>
       </c>
       <c r="M312" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15014,10 +14991,10 @@
         <v>307</v>
       </c>
       <c r="B313" s="9" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C313" s="7" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="D313" s="6" t="s">
         <v>17</v>
@@ -15045,7 +15022,7 @@
         <v>6248</v>
       </c>
       <c r="M313" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="314" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15053,10 +15030,10 @@
         <v>308</v>
       </c>
       <c r="B314" s="16" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="C314" s="17" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="D314" s="6" t="s">
         <v>17</v>
@@ -15074,7 +15051,7 @@
         <v>89598</v>
       </c>
       <c r="I314" s="8" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="J314" s="6"/>
       <c r="K314" s="7" t="s">
@@ -15084,7 +15061,7 @@
         <v>6250</v>
       </c>
       <c r="M314" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="315" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15092,10 +15069,10 @@
         <v>309</v>
       </c>
       <c r="B315" s="16" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="C315" s="17" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="D315" s="6" t="s">
         <v>17</v>
@@ -15113,7 +15090,7 @@
         <v>89598</v>
       </c>
       <c r="I315" s="8" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="J315" s="6"/>
       <c r="K315" s="7" t="s">
@@ -15123,7 +15100,7 @@
         <v>6250</v>
       </c>
       <c r="M315" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="316" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15131,10 +15108,10 @@
         <v>310</v>
       </c>
       <c r="B316" s="16" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="C316" s="17" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="D316" s="6" t="s">
         <v>17</v>
@@ -15152,7 +15129,7 @@
         <v>89598</v>
       </c>
       <c r="I316" s="8" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="J316" s="6"/>
       <c r="K316" s="7" t="s">
@@ -15162,7 +15139,7 @@
         <v>6250</v>
       </c>
       <c r="M316" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="317" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15170,10 +15147,10 @@
         <v>311</v>
       </c>
       <c r="B317" s="16" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="C317" s="17" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="D317" s="6" t="s">
         <v>17</v>
@@ -15191,7 +15168,7 @@
         <v>89598</v>
       </c>
       <c r="I317" s="8" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="J317" s="6"/>
       <c r="K317" s="7" t="s">
@@ -15201,7 +15178,7 @@
         <v>6250</v>
       </c>
       <c r="M317" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="318" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15209,10 +15186,10 @@
         <v>312</v>
       </c>
       <c r="B318" s="16" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="C318" s="17" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="D318" s="6" t="s">
         <v>17</v>
@@ -15230,7 +15207,7 @@
         <v>89598</v>
       </c>
       <c r="I318" s="8" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="J318" s="6"/>
       <c r="K318" s="7" t="s">
@@ -15240,7 +15217,7 @@
         <v>6250</v>
       </c>
       <c r="M318" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="319" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15248,10 +15225,10 @@
         <v>313</v>
       </c>
       <c r="B319" s="16" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="C319" s="17" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="D319" s="6" t="s">
         <v>17</v>
@@ -15269,7 +15246,7 @@
         <v>89598</v>
       </c>
       <c r="I319" s="8" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="J319" s="6"/>
       <c r="K319" s="7" t="s">
@@ -15279,7 +15256,7 @@
         <v>6250</v>
       </c>
       <c r="M319" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="320" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15287,10 +15264,10 @@
         <v>314</v>
       </c>
       <c r="B320" s="16" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="C320" s="17" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="D320" s="6" t="s">
         <v>17</v>
@@ -15308,7 +15285,7 @@
         <v>89598</v>
       </c>
       <c r="I320" s="8" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="J320" s="6"/>
       <c r="K320" s="7" t="s">
@@ -15318,7 +15295,7 @@
         <v>6250</v>
       </c>
       <c r="M320" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="321" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15326,10 +15303,10 @@
         <v>315</v>
       </c>
       <c r="B321" s="16" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C321" s="17" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D321" s="6" t="s">
         <v>17</v>
@@ -15347,7 +15324,7 @@
         <v>89598</v>
       </c>
       <c r="I321" s="8" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="J321" s="6"/>
       <c r="K321" s="7" t="s">
@@ -15357,7 +15334,7 @@
         <v>6250</v>
       </c>
       <c r="M321" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="322" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15365,10 +15342,10 @@
         <v>316</v>
       </c>
       <c r="B322" s="11" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="D322" s="6" t="s">
         <v>17</v>
@@ -15386,17 +15363,17 @@
         <v>420</v>
       </c>
       <c r="I322" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J322" s="6"/>
       <c r="K322" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L322" s="7">
         <v>6252</v>
       </c>
       <c r="M322" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="323" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15404,10 +15381,10 @@
         <v>317</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="C323" s="7" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="D323" s="6" t="s">
         <v>17</v>
@@ -15425,17 +15402,17 @@
         <v>420</v>
       </c>
       <c r="I323" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J323" s="6"/>
       <c r="K323" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L323" s="7">
         <v>6252</v>
       </c>
       <c r="M323" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="324" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15443,10 +15420,10 @@
         <v>318</v>
       </c>
       <c r="B324" s="11" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="D324" s="6" t="s">
         <v>17</v>
@@ -15464,17 +15441,17 @@
         <v>420</v>
       </c>
       <c r="I324" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J324" s="6"/>
       <c r="K324" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L324" s="7">
         <v>6252</v>
       </c>
       <c r="M324" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="325" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15482,10 +15459,10 @@
         <v>319</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="C325" s="7" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="D325" s="6" t="s">
         <v>17</v>
@@ -15503,17 +15480,17 @@
         <v>420</v>
       </c>
       <c r="I325" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J325" s="6"/>
       <c r="K325" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L325" s="7">
         <v>6252</v>
       </c>
       <c r="M325" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="326" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15521,10 +15498,10 @@
         <v>320</v>
       </c>
       <c r="B326" s="11" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="C326" s="7" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="D326" s="6" t="s">
         <v>17</v>
@@ -15542,17 +15519,17 @@
         <v>420</v>
       </c>
       <c r="I326" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J326" s="6"/>
       <c r="K326" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L326" s="7">
         <v>6252</v>
       </c>
       <c r="M326" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="327" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15560,10 +15537,10 @@
         <v>321</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="C327" s="7" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="D327" s="6" t="s">
         <v>17</v>
@@ -15581,17 +15558,17 @@
         <v>420</v>
       </c>
       <c r="I327" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J327" s="6"/>
       <c r="K327" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L327" s="7">
         <v>6252</v>
       </c>
       <c r="M327" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="328" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15599,10 +15576,10 @@
         <v>322</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="C328" s="7" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="D328" s="6" t="s">
         <v>17</v>
@@ -15620,17 +15597,17 @@
         <v>420</v>
       </c>
       <c r="I328" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J328" s="6"/>
       <c r="K328" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L328" s="7">
         <v>6252</v>
       </c>
       <c r="M328" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="329" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15638,10 +15615,10 @@
         <v>323</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="C329" s="7" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="D329" s="6" t="s">
         <v>17</v>
@@ -15659,17 +15636,17 @@
         <v>420</v>
       </c>
       <c r="I329" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J329" s="6"/>
       <c r="K329" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L329" s="7">
         <v>6252</v>
       </c>
       <c r="M329" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="330" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15677,10 +15654,10 @@
         <v>324</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="C330" s="7" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>17</v>
@@ -15698,17 +15675,17 @@
         <v>420</v>
       </c>
       <c r="I330" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J330" s="6"/>
       <c r="K330" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L330" s="7">
         <v>6252</v>
       </c>
       <c r="M330" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="331" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15719,7 +15696,7 @@
         <v>298</v>
       </c>
       <c r="C331" s="7" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="D331" s="6" t="s">
         <v>17</v>
@@ -15737,17 +15714,17 @@
         <v>420</v>
       </c>
       <c r="I331" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J331" s="6"/>
       <c r="K331" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L331" s="7">
         <v>6252</v>
       </c>
       <c r="M331" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="332" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15755,10 +15732,10 @@
         <v>326</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="D332" s="6" t="s">
         <v>17</v>
@@ -15776,17 +15753,17 @@
         <v>420</v>
       </c>
       <c r="I332" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J332" s="6"/>
       <c r="K332" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L332" s="7">
         <v>6252</v>
       </c>
       <c r="M332" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="333" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15794,10 +15771,10 @@
         <v>327</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="C333" s="7" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="D333" s="6" t="s">
         <v>17</v>
@@ -15815,17 +15792,17 @@
         <v>420</v>
       </c>
       <c r="I333" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J333" s="6"/>
       <c r="K333" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L333" s="7">
         <v>6252</v>
       </c>
       <c r="M333" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="334" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15833,10 +15810,10 @@
         <v>328</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="C334" s="7" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="D334" s="6" t="s">
         <v>17</v>
@@ -15854,17 +15831,17 @@
         <v>420</v>
       </c>
       <c r="I334" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J334" s="6"/>
       <c r="K334" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L334" s="7">
         <v>6253</v>
       </c>
       <c r="M334" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="335" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15872,10 +15849,10 @@
         <v>329</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="D335" s="6" t="s">
         <v>17</v>
@@ -15893,17 +15870,17 @@
         <v>420</v>
       </c>
       <c r="I335" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J335" s="6"/>
       <c r="K335" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L335" s="7">
         <v>6253</v>
       </c>
       <c r="M335" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="336" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15911,10 +15888,10 @@
         <v>330</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C336" s="7" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="D336" s="6" t="s">
         <v>17</v>
@@ -15932,17 +15909,17 @@
         <v>420</v>
       </c>
       <c r="I336" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J336" s="6"/>
       <c r="K336" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L336" s="7">
         <v>6253</v>
       </c>
       <c r="M336" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="337" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15950,10 +15927,10 @@
         <v>331</v>
       </c>
       <c r="B337" s="11" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="C337" s="7" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="D337" s="6" t="s">
         <v>17</v>
@@ -15971,17 +15948,17 @@
         <v>420</v>
       </c>
       <c r="I337" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J337" s="6"/>
       <c r="K337" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L337" s="7">
         <v>6253</v>
       </c>
       <c r="M337" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="338" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -15989,10 +15966,10 @@
         <v>332</v>
       </c>
       <c r="B338" s="11" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="C338" s="7" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="D338" s="6" t="s">
         <v>17</v>
@@ -16010,17 +15987,17 @@
         <v>420</v>
       </c>
       <c r="I338" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J338" s="6"/>
       <c r="K338" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L338" s="7">
         <v>6253</v>
       </c>
       <c r="M338" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="339" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16028,10 +16005,10 @@
         <v>333</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="C339" s="7" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="D339" s="6" t="s">
         <v>17</v>
@@ -16049,17 +16026,17 @@
         <v>420</v>
       </c>
       <c r="I339" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J339" s="6"/>
       <c r="K339" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L339" s="7">
         <v>6253</v>
       </c>
       <c r="M339" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="340" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16067,10 +16044,10 @@
         <v>334</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="C340" s="7" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="D340" s="6" t="s">
         <v>52</v>
@@ -16088,17 +16065,17 @@
         <v>420</v>
       </c>
       <c r="I340" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J340" s="6"/>
       <c r="K340" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L340" s="7">
         <v>6253</v>
       </c>
       <c r="M340" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="341" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16106,10 +16083,10 @@
         <v>335</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="C341" s="7" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="D341" s="6" t="s">
         <v>17</v>
@@ -16127,17 +16104,17 @@
         <v>420</v>
       </c>
       <c r="I341" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J341" s="6"/>
       <c r="K341" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L341" s="7">
         <v>6253</v>
       </c>
       <c r="M341" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="342" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16145,10 +16122,10 @@
         <v>336</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="C342" s="7" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D342" s="6" t="s">
         <v>17</v>
@@ -16166,17 +16143,17 @@
         <v>420</v>
       </c>
       <c r="I342" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J342" s="6"/>
       <c r="K342" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L342" s="7">
         <v>6253</v>
       </c>
       <c r="M342" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="343" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16184,10 +16161,10 @@
         <v>338</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="C343" s="7" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="D343" s="6" t="s">
         <v>17</v>
@@ -16205,17 +16182,17 @@
         <v>420</v>
       </c>
       <c r="I343" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J343" s="6"/>
       <c r="K343" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L343" s="7">
         <v>6253</v>
       </c>
       <c r="M343" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="344" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16223,10 +16200,10 @@
         <v>339</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="C344" s="7" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="D344" s="6" t="s">
         <v>17</v>
@@ -16244,17 +16221,17 @@
         <v>420</v>
       </c>
       <c r="I344" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J344" s="6"/>
       <c r="K344" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L344" s="7">
         <v>6254</v>
       </c>
       <c r="M344" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="345" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16262,10 +16239,10 @@
         <v>340</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C345" s="7" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="D345" s="6" t="s">
         <v>17</v>
@@ -16283,17 +16260,17 @@
         <v>420</v>
       </c>
       <c r="I345" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J345" s="6"/>
       <c r="K345" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L345" s="7">
         <v>6254</v>
       </c>
       <c r="M345" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="346" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16301,10 +16278,10 @@
         <v>341</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="C346" s="7" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="D346" s="6" t="s">
         <v>17</v>
@@ -16322,17 +16299,17 @@
         <v>420</v>
       </c>
       <c r="I346" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J346" s="6"/>
       <c r="K346" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L346" s="7">
         <v>6254</v>
       </c>
       <c r="M346" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="347" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16340,10 +16317,10 @@
         <v>342</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="C347" s="7" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="D347" s="6" t="s">
         <v>17</v>
@@ -16361,17 +16338,17 @@
         <v>420</v>
       </c>
       <c r="I347" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J347" s="6"/>
       <c r="K347" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L347" s="7">
         <v>6254</v>
       </c>
       <c r="M347" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="348" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16379,10 +16356,10 @@
         <v>343</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="C348" s="7" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="D348" s="6" t="s">
         <v>17</v>
@@ -16400,17 +16377,17 @@
         <v>420</v>
       </c>
       <c r="I348" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J348" s="6"/>
       <c r="K348" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L348" s="7">
         <v>6254</v>
       </c>
       <c r="M348" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="349" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16418,10 +16395,10 @@
         <v>344</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="D349" s="6" t="s">
         <v>17</v>
@@ -16439,17 +16416,17 @@
         <v>420</v>
       </c>
       <c r="I349" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J349" s="6"/>
       <c r="K349" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L349" s="7">
         <v>6254</v>
       </c>
       <c r="M349" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="350" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16457,10 +16434,10 @@
         <v>346</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="C350" s="7" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="D350" s="6" t="s">
         <v>17</v>
@@ -16478,17 +16455,17 @@
         <v>420</v>
       </c>
       <c r="I350" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J350" s="6"/>
       <c r="K350" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L350" s="7">
         <v>6254</v>
       </c>
       <c r="M350" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="351" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16496,10 +16473,10 @@
         <v>347</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="C351" s="7" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="D351" s="6" t="s">
         <v>17</v>
@@ -16517,17 +16494,17 @@
         <v>420</v>
       </c>
       <c r="I351" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J351" s="6"/>
       <c r="K351" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L351" s="7">
         <v>6254</v>
       </c>
       <c r="M351" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="352" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16535,10 +16512,10 @@
         <v>348</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="C352" s="7" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="D352" s="6" t="s">
         <v>17</v>
@@ -16556,17 +16533,17 @@
         <v>420</v>
       </c>
       <c r="I352" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J352" s="6"/>
       <c r="K352" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L352" s="7">
         <v>6254</v>
       </c>
       <c r="M352" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="353" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16574,10 +16551,10 @@
         <v>349</v>
       </c>
       <c r="B353" s="11" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="C353" s="7" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="D353" s="6" t="s">
         <v>17</v>
@@ -16595,17 +16572,17 @@
         <v>420</v>
       </c>
       <c r="I353" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J353" s="6"/>
       <c r="K353" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L353" s="7">
         <v>6254</v>
       </c>
       <c r="M353" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="354" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16613,10 +16590,10 @@
         <v>350</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="C354" s="7" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="D354" s="6" t="s">
         <v>17</v>
@@ -16634,17 +16611,17 @@
         <v>420</v>
       </c>
       <c r="I354" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J354" s="6"/>
       <c r="K354" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L354" s="7">
         <v>6255</v>
       </c>
       <c r="M354" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="355" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16652,10 +16629,10 @@
         <v>351</v>
       </c>
       <c r="B355" s="11" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="C355" s="7" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="D355" s="6" t="s">
         <v>17</v>
@@ -16673,17 +16650,17 @@
         <v>420</v>
       </c>
       <c r="I355" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J355" s="6"/>
       <c r="K355" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L355" s="7">
         <v>6255</v>
       </c>
       <c r="M355" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="356" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16691,10 +16668,10 @@
         <v>352</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="C356" s="7" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="D356" s="6" t="s">
         <v>17</v>
@@ -16712,17 +16689,17 @@
         <v>420</v>
       </c>
       <c r="I356" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J356" s="6"/>
       <c r="K356" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L356" s="7">
         <v>6255</v>
       </c>
       <c r="M356" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="357" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16730,13 +16707,13 @@
         <v>353</v>
       </c>
       <c r="B357" s="11" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="C357" s="7" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="D357" s="6" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="E357" s="6">
         <v>3</v>
@@ -16751,17 +16728,17 @@
         <v>420</v>
       </c>
       <c r="I357" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J357" s="6"/>
       <c r="K357" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L357" s="7">
         <v>6255</v>
       </c>
       <c r="M357" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="358" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16769,10 +16746,10 @@
         <v>354</v>
       </c>
       <c r="B358" s="11" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="C358" s="7" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="D358" s="6" t="s">
         <v>17</v>
@@ -16790,17 +16767,17 @@
         <v>420</v>
       </c>
       <c r="I358" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J358" s="6"/>
       <c r="K358" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L358" s="7">
         <v>6255</v>
       </c>
       <c r="M358" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="359" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16808,10 +16785,10 @@
         <v>355</v>
       </c>
       <c r="B359" s="11" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="C359" s="7" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="D359" s="6" t="s">
         <v>17</v>
@@ -16829,17 +16806,17 @@
         <v>420</v>
       </c>
       <c r="I359" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J359" s="6"/>
       <c r="K359" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L359" s="7">
         <v>6255</v>
       </c>
       <c r="M359" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="360" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16847,10 +16824,10 @@
         <v>356</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="C360" s="7" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="D360" s="6" t="s">
         <v>17</v>
@@ -16868,17 +16845,17 @@
         <v>420</v>
       </c>
       <c r="I360" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J360" s="6"/>
       <c r="K360" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L360" s="7">
         <v>6255</v>
       </c>
       <c r="M360" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="361" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16886,10 +16863,10 @@
         <v>357</v>
       </c>
       <c r="B361" s="11" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C361" s="7" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="D361" s="6" t="s">
         <v>17</v>
@@ -16907,17 +16884,17 @@
         <v>420</v>
       </c>
       <c r="I361" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J361" s="6"/>
       <c r="K361" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L361" s="7">
         <v>6255</v>
       </c>
       <c r="M361" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="362" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16925,10 +16902,10 @@
         <v>358</v>
       </c>
       <c r="B362" s="11" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="C362" s="7" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="D362" s="6" t="s">
         <v>17</v>
@@ -16946,17 +16923,17 @@
         <v>419</v>
       </c>
       <c r="I362" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J362" s="6"/>
       <c r="K362" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L362" s="7">
         <v>6256</v>
       </c>
       <c r="M362" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="363" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -16964,19 +16941,19 @@
         <v>359</v>
       </c>
       <c r="B363" s="11" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="C363" s="7" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="D363" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E363" s="6">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F363" s="7">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="G363" s="7">
         <v>1250</v>
@@ -16985,17 +16962,17 @@
         <v>419</v>
       </c>
       <c r="I363" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J363" s="6"/>
       <c r="K363" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L363" s="7">
         <v>6256</v>
       </c>
       <c r="M363" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="364" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17003,13 +16980,13 @@
         <v>360</v>
       </c>
       <c r="B364" s="11" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="C364" s="7" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="D364" s="6" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="E364" s="6">
         <v>3</v>
@@ -17024,17 +17001,17 @@
         <v>419</v>
       </c>
       <c r="I364" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J364" s="6"/>
       <c r="K364" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L364" s="7">
         <v>6256</v>
       </c>
       <c r="M364" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="365" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17042,10 +17019,10 @@
         <v>361</v>
       </c>
       <c r="B365" s="11" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="C365" s="7" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="D365" s="6" t="s">
         <v>17</v>
@@ -17063,17 +17040,17 @@
         <v>419</v>
       </c>
       <c r="I365" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J365" s="6"/>
       <c r="K365" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L365" s="7">
         <v>6256</v>
       </c>
       <c r="M365" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="366" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17081,10 +17058,10 @@
         <v>362</v>
       </c>
       <c r="B366" s="11" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="C366" s="7" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="D366" s="6" t="s">
         <v>17</v>
@@ -17102,17 +17079,17 @@
         <v>419</v>
       </c>
       <c r="I366" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J366" s="6"/>
       <c r="K366" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L366" s="7">
         <v>6256</v>
       </c>
       <c r="M366" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="367" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17120,13 +17097,13 @@
         <v>365</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="C367" s="7" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="D367" s="6" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="E367" s="6">
         <v>25</v>
@@ -17141,17 +17118,17 @@
         <v>419</v>
       </c>
       <c r="I367" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J367" s="6"/>
       <c r="K367" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L367" s="7">
         <v>6256</v>
       </c>
       <c r="M367" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="368" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17159,10 +17136,10 @@
         <v>366</v>
       </c>
       <c r="B368" s="9" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="C368" s="7" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="D368" s="6" t="s">
         <v>17</v>
@@ -17180,17 +17157,17 @@
         <v>419</v>
       </c>
       <c r="I368" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J368" s="6"/>
       <c r="K368" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L368" s="7">
         <v>6256</v>
       </c>
       <c r="M368" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="369" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17198,13 +17175,13 @@
         <v>367</v>
       </c>
       <c r="B369" s="11" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="C369" s="7" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D369" s="6" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="E369" s="6">
         <v>11</v>
@@ -17219,17 +17196,17 @@
         <v>419</v>
       </c>
       <c r="I369" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J369" s="6"/>
       <c r="K369" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L369" s="7">
         <v>6256</v>
       </c>
       <c r="M369" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="370" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17237,10 +17214,10 @@
         <v>368</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="C370" s="7" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="D370" s="6" t="s">
         <v>17</v>
@@ -17258,17 +17235,17 @@
         <v>419</v>
       </c>
       <c r="I370" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J370" s="6"/>
       <c r="K370" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L370" s="7">
         <v>6256</v>
       </c>
       <c r="M370" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="371" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17276,10 +17253,10 @@
         <v>369</v>
       </c>
       <c r="B371" s="11" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="C371" s="7" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D371" s="6" t="s">
         <v>17</v>
@@ -17297,17 +17274,17 @@
         <v>419</v>
       </c>
       <c r="I371" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J371" s="6"/>
       <c r="K371" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L371" s="7">
         <v>6256</v>
       </c>
       <c r="M371" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="372" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17315,10 +17292,10 @@
         <v>370</v>
       </c>
       <c r="B372" s="11" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="C372" s="7" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="D372" s="6" t="s">
         <v>17</v>
@@ -17336,17 +17313,17 @@
         <v>419</v>
       </c>
       <c r="I372" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J372" s="6"/>
       <c r="K372" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L372" s="7">
         <v>6257</v>
       </c>
       <c r="M372" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="373" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17354,10 +17331,10 @@
         <v>371</v>
       </c>
       <c r="B373" s="11" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="C373" s="7" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="D373" s="6" t="s">
         <v>17</v>
@@ -17375,17 +17352,17 @@
         <v>419</v>
       </c>
       <c r="I373" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J373" s="6"/>
       <c r="K373" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L373" s="7">
         <v>6257</v>
       </c>
       <c r="M373" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="374" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17393,10 +17370,10 @@
         <v>372</v>
       </c>
       <c r="B374" s="11" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="C374" s="7" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="D374" s="6" t="s">
         <v>17</v>
@@ -17414,17 +17391,17 @@
         <v>419</v>
       </c>
       <c r="I374" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J374" s="6"/>
       <c r="K374" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L374" s="7">
         <v>6257</v>
       </c>
       <c r="M374" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="375" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17432,10 +17409,10 @@
         <v>373</v>
       </c>
       <c r="B375" s="11" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="C375" s="7" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="D375" s="6" t="s">
         <v>17</v>
@@ -17453,17 +17430,17 @@
         <v>419</v>
       </c>
       <c r="I375" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J375" s="6"/>
       <c r="K375" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L375" s="7">
         <v>6257</v>
       </c>
       <c r="M375" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="376" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17471,10 +17448,10 @@
         <v>374</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="C376" s="7" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="D376" s="6" t="s">
         <v>17</v>
@@ -17492,17 +17469,17 @@
         <v>419</v>
       </c>
       <c r="I376" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J376" s="6"/>
       <c r="K376" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L376" s="7">
         <v>6257</v>
       </c>
       <c r="M376" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="377" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17510,10 +17487,10 @@
         <v>375</v>
       </c>
       <c r="B377" s="11" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="C377" s="7" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="D377" s="6" t="s">
         <v>17</v>
@@ -17531,17 +17508,17 @@
         <v>419</v>
       </c>
       <c r="I377" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J377" s="6"/>
       <c r="K377" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L377" s="7">
         <v>6257</v>
       </c>
       <c r="M377" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="378" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17549,10 +17526,10 @@
         <v>376</v>
       </c>
       <c r="B378" s="9" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="C378" s="7" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="D378" s="6" t="s">
         <v>17</v>
@@ -17570,17 +17547,17 @@
         <v>419</v>
       </c>
       <c r="I378" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J378" s="6"/>
       <c r="K378" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L378" s="7">
         <v>6257</v>
       </c>
       <c r="M378" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="379" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17588,10 +17565,10 @@
         <v>377</v>
       </c>
       <c r="B379" s="11" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="C379" s="7" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="D379" s="6" t="s">
         <v>17</v>
@@ -17609,17 +17586,17 @@
         <v>419</v>
       </c>
       <c r="I379" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J379" s="6"/>
       <c r="K379" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L379" s="7">
         <v>6257</v>
       </c>
       <c r="M379" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="380" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17627,10 +17604,10 @@
         <v>378</v>
       </c>
       <c r="B380" s="11" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C380" s="7" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="D380" s="6" t="s">
         <v>17</v>
@@ -17648,17 +17625,17 @@
         <v>419</v>
       </c>
       <c r="I380" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J380" s="6"/>
       <c r="K380" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L380" s="7">
         <v>6257</v>
       </c>
       <c r="M380" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="381" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17666,10 +17643,10 @@
         <v>379</v>
       </c>
       <c r="B381" s="9" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="C381" s="7" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="D381" s="6" t="s">
         <v>17</v>
@@ -17687,17 +17664,17 @@
         <v>419</v>
       </c>
       <c r="I381" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J381" s="6"/>
       <c r="K381" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L381" s="7">
         <v>6257</v>
       </c>
       <c r="M381" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="382" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17708,7 +17685,7 @@
         <v>299</v>
       </c>
       <c r="C382" s="7" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="D382" s="6" t="s">
         <v>17</v>
@@ -17726,17 +17703,17 @@
         <v>419</v>
       </c>
       <c r="I382" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J382" s="6"/>
       <c r="K382" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L382" s="7">
         <v>6257</v>
       </c>
       <c r="M382" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="383" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17744,10 +17721,10 @@
         <v>381</v>
       </c>
       <c r="B383" s="9" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="C383" s="7" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="D383" s="6" t="s">
         <v>17</v>
@@ -17765,17 +17742,17 @@
         <v>419</v>
       </c>
       <c r="I383" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J383" s="6"/>
       <c r="K383" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L383" s="7">
         <v>6257</v>
       </c>
       <c r="M383" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="384" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17783,10 +17760,10 @@
         <v>382</v>
       </c>
       <c r="B384" s="9" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="C384" s="7" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="D384" s="6" t="s">
         <v>17</v>
@@ -17804,17 +17781,17 @@
         <v>419</v>
       </c>
       <c r="I384" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J384" s="6"/>
       <c r="K384" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L384" s="7">
         <v>6257</v>
       </c>
       <c r="M384" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="385" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17822,10 +17799,10 @@
         <v>383</v>
       </c>
       <c r="B385" s="9" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C385" s="7" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="D385" s="6" t="s">
         <v>17</v>
@@ -17843,17 +17820,17 @@
         <v>419</v>
       </c>
       <c r="I385" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J385" s="6"/>
       <c r="K385" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L385" s="7">
         <v>6257</v>
       </c>
       <c r="M385" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="386" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17861,10 +17838,10 @@
         <v>384</v>
       </c>
       <c r="B386" s="11" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="C386" s="7" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="D386" s="6" t="s">
         <v>17</v>
@@ -17882,17 +17859,17 @@
         <v>419</v>
       </c>
       <c r="I386" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J386" s="6"/>
       <c r="K386" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L386" s="7">
         <v>6257</v>
       </c>
       <c r="M386" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="387" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17900,10 +17877,10 @@
         <v>385</v>
       </c>
       <c r="B387" s="11" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="C387" s="7" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="D387" s="6" t="s">
         <v>17</v>
@@ -17921,17 +17898,17 @@
         <v>419</v>
       </c>
       <c r="I387" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J387" s="6"/>
       <c r="K387" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L387" s="7">
         <v>6257</v>
       </c>
       <c r="M387" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="388" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17939,10 +17916,10 @@
         <v>386</v>
       </c>
       <c r="B388" s="11" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="C388" s="7" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="D388" s="6" t="s">
         <v>17</v>
@@ -17960,17 +17937,17 @@
         <v>419</v>
       </c>
       <c r="I388" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J388" s="6"/>
       <c r="K388" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L388" s="7">
         <v>6257</v>
       </c>
       <c r="M388" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="389" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -17978,10 +17955,10 @@
         <v>387</v>
       </c>
       <c r="B389" s="9" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="C389" s="7" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="D389" s="6" t="s">
         <v>17</v>
@@ -17999,17 +17976,17 @@
         <v>419</v>
       </c>
       <c r="I389" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J389" s="6"/>
       <c r="K389" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L389" s="7">
         <v>6257</v>
       </c>
       <c r="M389" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="390" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18017,10 +17994,10 @@
         <v>388</v>
       </c>
       <c r="B390" s="11" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="C390" s="7" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="D390" s="6" t="s">
         <v>17</v>
@@ -18038,17 +18015,17 @@
         <v>419</v>
       </c>
       <c r="I390" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J390" s="6"/>
       <c r="K390" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L390" s="7">
         <v>6257</v>
       </c>
       <c r="M390" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="391" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18056,10 +18033,10 @@
         <v>389</v>
       </c>
       <c r="B391" s="9" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="C391" s="7" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="D391" s="6" t="s">
         <v>17</v>
@@ -18077,17 +18054,17 @@
         <v>419</v>
       </c>
       <c r="I391" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J391" s="6"/>
       <c r="K391" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L391" s="7">
         <v>6257</v>
       </c>
       <c r="M391" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="392" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18095,10 +18072,10 @@
         <v>390</v>
       </c>
       <c r="B392" s="9" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="C392" s="7" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="D392" s="6" t="s">
         <v>17</v>
@@ -18116,17 +18093,17 @@
         <v>419</v>
       </c>
       <c r="I392" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J392" s="6"/>
       <c r="K392" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L392" s="7">
         <v>6257</v>
       </c>
       <c r="M392" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="393" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18134,10 +18111,10 @@
         <v>391</v>
       </c>
       <c r="B393" s="9" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="C393" s="7" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="D393" s="6" t="s">
         <v>17</v>
@@ -18155,17 +18132,17 @@
         <v>419</v>
       </c>
       <c r="I393" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J393" s="6"/>
       <c r="K393" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L393" s="7">
         <v>6257</v>
       </c>
       <c r="M393" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="394" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18173,10 +18150,10 @@
         <v>392</v>
       </c>
       <c r="B394" s="9" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="C394" s="7" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="D394" s="6" t="s">
         <v>17</v>
@@ -18194,17 +18171,17 @@
         <v>419</v>
       </c>
       <c r="I394" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J394" s="6"/>
       <c r="K394" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L394" s="7">
         <v>6259</v>
       </c>
       <c r="M394" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="395" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18212,10 +18189,10 @@
         <v>393</v>
       </c>
       <c r="B395" s="9" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="C395" s="7" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="D395" s="6" t="s">
         <v>17</v>
@@ -18233,17 +18210,17 @@
         <v>419</v>
       </c>
       <c r="I395" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J395" s="6"/>
       <c r="K395" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L395" s="7">
         <v>6259</v>
       </c>
       <c r="M395" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="396" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18251,10 +18228,10 @@
         <v>394</v>
       </c>
       <c r="B396" s="9" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="C396" s="7" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="D396" s="6" t="s">
         <v>17</v>
@@ -18272,17 +18249,17 @@
         <v>419</v>
       </c>
       <c r="I396" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J396" s="6"/>
       <c r="K396" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L396" s="7">
         <v>6259</v>
       </c>
       <c r="M396" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="397" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18290,10 +18267,10 @@
         <v>395</v>
       </c>
       <c r="B397" s="11" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="C397" s="7" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="D397" s="6" t="s">
         <v>17</v>
@@ -18311,17 +18288,17 @@
         <v>419</v>
       </c>
       <c r="I397" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J397" s="6"/>
       <c r="K397" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L397" s="7">
         <v>6259</v>
       </c>
       <c r="M397" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="398" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18329,10 +18306,10 @@
         <v>396</v>
       </c>
       <c r="B398" s="9" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="C398" s="7" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="D398" s="6" t="s">
         <v>17</v>
@@ -18350,17 +18327,17 @@
         <v>419</v>
       </c>
       <c r="I398" s="8" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="J398" s="6"/>
       <c r="K398" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="L398" s="7">
         <v>6259</v>
       </c>
       <c r="M398" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="399" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18368,10 +18345,10 @@
         <v>397</v>
       </c>
       <c r="B399" s="15" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C399" s="7" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="D399" s="6" t="s">
         <v>17</v>
@@ -18389,7 +18366,7 @@
         <v>2443</v>
       </c>
       <c r="I399" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J399" s="6"/>
       <c r="K399" s="7" t="s">
@@ -18399,7 +18376,7 @@
         <v>6260</v>
       </c>
       <c r="M399" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="400" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18407,10 +18384,10 @@
         <v>398</v>
       </c>
       <c r="B400" s="11" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C400" s="7" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="D400" s="6" t="s">
         <v>17</v>
@@ -18428,7 +18405,7 @@
         <v>2443</v>
       </c>
       <c r="I400" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J400" s="6"/>
       <c r="K400" s="7" t="s">
@@ -18438,7 +18415,7 @@
         <v>6260</v>
       </c>
       <c r="M400" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="401" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18467,7 +18444,7 @@
         <v>2443</v>
       </c>
       <c r="I401" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J401" s="6"/>
       <c r="K401" s="7" t="s">
@@ -18477,7 +18454,7 @@
         <v>6260</v>
       </c>
       <c r="M401" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="402" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18485,10 +18462,10 @@
         <v>400</v>
       </c>
       <c r="B402" s="11" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C402" s="7" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="D402" s="6" t="s">
         <v>17</v>
@@ -18506,7 +18483,7 @@
         <v>2443</v>
       </c>
       <c r="I402" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J402" s="6"/>
       <c r="K402" s="7" t="s">
@@ -18516,7 +18493,7 @@
         <v>6260</v>
       </c>
       <c r="M402" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="403" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18524,10 +18501,10 @@
         <v>401</v>
       </c>
       <c r="B403" s="11" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="C403" s="7" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D403" s="6" t="s">
         <v>17</v>
@@ -18545,7 +18522,7 @@
         <v>2443</v>
       </c>
       <c r="I403" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J403" s="6"/>
       <c r="K403" s="7" t="s">
@@ -18555,7 +18532,7 @@
         <v>6260</v>
       </c>
       <c r="M403" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="404" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18563,10 +18540,10 @@
         <v>402</v>
       </c>
       <c r="B404" s="11" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="C404" s="7" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="D404" s="6" t="s">
         <v>17</v>
@@ -18584,7 +18561,7 @@
         <v>2443</v>
       </c>
       <c r="I404" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J404" s="6"/>
       <c r="K404" s="7" t="s">
@@ -18594,7 +18571,7 @@
         <v>6260</v>
       </c>
       <c r="M404" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="405" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18602,10 +18579,10 @@
         <v>403</v>
       </c>
       <c r="B405" s="11" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="C405" s="7" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="D405" s="6" t="s">
         <v>17</v>
@@ -18623,7 +18600,7 @@
         <v>2443</v>
       </c>
       <c r="I405" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J405" s="6"/>
       <c r="K405" s="7" t="s">
@@ -18633,7 +18610,7 @@
         <v>6260</v>
       </c>
       <c r="M405" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="406" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18641,10 +18618,10 @@
         <v>404</v>
       </c>
       <c r="B406" s="15" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C406" s="7" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="D406" s="6" t="s">
         <v>17</v>
@@ -18662,7 +18639,7 @@
         <v>2443</v>
       </c>
       <c r="I406" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J406" s="6"/>
       <c r="K406" s="7" t="s">
@@ -18672,7 +18649,7 @@
         <v>6260</v>
       </c>
       <c r="M406" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="407" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18680,10 +18657,10 @@
         <v>405</v>
       </c>
       <c r="B407" s="11" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C407" s="7" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="D407" s="6" t="s">
         <v>17</v>
@@ -18701,7 +18678,7 @@
         <v>2443</v>
       </c>
       <c r="I407" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J407" s="6"/>
       <c r="K407" s="7" t="s">
@@ -18711,7 +18688,7 @@
         <v>6260</v>
       </c>
       <c r="M407" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="408" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18719,10 +18696,10 @@
         <v>406</v>
       </c>
       <c r="B408" s="9" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="C408" s="7" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D408" s="6" t="s">
         <v>17</v>
@@ -18740,7 +18717,7 @@
         <v>2443</v>
       </c>
       <c r="I408" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J408" s="6"/>
       <c r="K408" s="7" t="s">
@@ -18750,7 +18727,7 @@
         <v>6260</v>
       </c>
       <c r="M408" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="409" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18758,10 +18735,10 @@
         <v>407</v>
       </c>
       <c r="B409" s="15" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="C409" s="7" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="D409" s="6" t="s">
         <v>17</v>
@@ -18779,7 +18756,7 @@
         <v>2443</v>
       </c>
       <c r="I409" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J409" s="6"/>
       <c r="K409" s="7" t="s">
@@ -18789,7 +18766,7 @@
         <v>6260</v>
       </c>
       <c r="M409" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="410" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18797,10 +18774,10 @@
         <v>408</v>
       </c>
       <c r="B410" s="15" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C410" s="7" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="D410" s="6" t="s">
         <v>17</v>
@@ -18818,7 +18795,7 @@
         <v>2443</v>
       </c>
       <c r="I410" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J410" s="6"/>
       <c r="K410" s="7" t="s">
@@ -18828,7 +18805,7 @@
         <v>6260</v>
       </c>
       <c r="M410" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="411" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18836,10 +18813,10 @@
         <v>409</v>
       </c>
       <c r="B411" s="15" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="C411" s="7" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="D411" s="6" t="s">
         <v>17</v>
@@ -18857,7 +18834,7 @@
         <v>2443</v>
       </c>
       <c r="I411" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J411" s="6"/>
       <c r="K411" s="7" t="s">
@@ -18867,7 +18844,7 @@
         <v>6261</v>
       </c>
       <c r="M411" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="412" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18875,10 +18852,10 @@
         <v>410</v>
       </c>
       <c r="B412" s="15" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C412" s="7" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="D412" s="6" t="s">
         <v>17</v>
@@ -18896,7 +18873,7 @@
         <v>2443</v>
       </c>
       <c r="I412" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J412" s="6"/>
       <c r="K412" s="7" t="s">
@@ -18906,7 +18883,7 @@
         <v>6261</v>
       </c>
       <c r="M412" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="413" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18914,10 +18891,10 @@
         <v>411</v>
       </c>
       <c r="B413" s="15" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="C413" s="7" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="D413" s="6" t="s">
         <v>17</v>
@@ -18935,7 +18912,7 @@
         <v>2443</v>
       </c>
       <c r="I413" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J413" s="6"/>
       <c r="K413" s="7" t="s">
@@ -18945,7 +18922,7 @@
         <v>6261</v>
       </c>
       <c r="M413" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="414" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18953,10 +18930,10 @@
         <v>412</v>
       </c>
       <c r="B414" s="11" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C414" s="7" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="D414" s="6" t="s">
         <v>17</v>
@@ -18974,7 +18951,7 @@
         <v>2443</v>
       </c>
       <c r="I414" s="8" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="J414" s="6"/>
       <c r="K414" s="7" t="s">
@@ -18984,7 +18961,7 @@
         <v>6261</v>
       </c>
       <c r="M414" s="8" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="415" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -18992,10 +18969,10 @@
         <v>413</v>
       </c>
       <c r="B415" s="9" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="C415" s="7" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="D415" s="6" t="s">
         <v>17</v>
@@ -19013,17 +18990,17 @@
         <v>26</v>
       </c>
       <c r="I415" s="8" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="J415" s="6"/>
       <c r="K415" s="7" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="L415" s="7">
         <v>6263</v>
       </c>
       <c r="M415" s="8" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
     </row>
     <row r="416" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19031,10 +19008,10 @@
         <v>414</v>
       </c>
       <c r="B416" s="9" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="C416" s="7" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="D416" s="6" t="s">
         <v>17</v>
@@ -19052,17 +19029,17 @@
         <v>26</v>
       </c>
       <c r="I416" s="8" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="J416" s="6"/>
       <c r="K416" s="7" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="L416" s="7">
         <v>6263</v>
       </c>
       <c r="M416" s="8" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
     </row>
     <row r="417" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19070,10 +19047,10 @@
         <v>416</v>
       </c>
       <c r="B417" s="11" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="C417" s="7" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="D417" s="6" t="s">
         <v>17</v>
@@ -19091,17 +19068,17 @@
         <v>26</v>
       </c>
       <c r="I417" s="8" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="J417" s="6"/>
       <c r="K417" s="7" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="L417" s="7">
         <v>6263</v>
       </c>
       <c r="M417" s="8" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
     </row>
     <row r="418" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19109,10 +19086,10 @@
         <v>417</v>
       </c>
       <c r="B418" s="11" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="C418" s="7" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="D418" s="6" t="s">
         <v>17</v>
@@ -19130,17 +19107,17 @@
         <v>26</v>
       </c>
       <c r="I418" s="8" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="J418" s="6"/>
       <c r="K418" s="7" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="L418" s="7">
         <v>6263</v>
       </c>
       <c r="M418" s="8" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
     </row>
     <row r="419" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19148,10 +19125,10 @@
         <v>418</v>
       </c>
       <c r="B419" s="9" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="C419" s="7" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="D419" s="6" t="s">
         <v>17</v>
@@ -19169,24 +19146,21 @@
         <v>26</v>
       </c>
       <c r="I419" s="8" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="J419" s="6"/>
       <c r="K419" s="7" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="L419" s="7">
         <v>6263</v>
       </c>
       <c r="M419" s="8" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
     </row>
     <row r="420" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="F177:G184"/>
-  </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/transactions/أذونات الإضافة لشهر 3.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DAB821-49CE-40AD-B23A-B441C64DD8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D61B6C-4B75-4DBA-9F5B-556EDC776E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$419</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$420</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="775">
   <si>
     <t>بورسعيد لصناعة المعادن</t>
   </si>
@@ -2359,6 +2359,9 @@
   </si>
   <si>
     <t>ﻟﻮح 0.8 ﻣﻢ SST ﻣﻂ ﻣﻐﻠﻒ 1 × 2 م</t>
+  </si>
+  <si>
+    <t>ﻟﻮح 1.2 ﻣﻢ SST مصنفر ﻣﻐﻠﻒ 1 × 2 م</t>
   </si>
 </sst>
 </file>
@@ -2955,7 +2958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U420"/>
+  <dimension ref="A1:U421"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" customWidth="1"/>
@@ -9742,7 +9745,7 @@
         <v>142</v>
       </c>
       <c r="G178" s="34">
-        <f t="shared" ref="G177:G185" si="0">F178*E178</f>
+        <f t="shared" ref="G178:G186" si="0">F178*E178</f>
         <v>511200</v>
       </c>
       <c r="H178" s="21">
@@ -9763,30 +9766,28 @@
       </c>
     </row>
     <row r="179" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="18">
-        <v>177</v>
-      </c>
+      <c r="A179" s="18"/>
       <c r="B179" s="19" t="s">
-        <v>324</v>
+        <v>43</v>
       </c>
       <c r="C179" s="20" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="D179" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E179" s="21">
-        <v>2112</v>
+        <v>557</v>
       </c>
       <c r="F179" s="33">
         <v>142</v>
       </c>
       <c r="G179" s="34">
-        <f t="shared" si="0"/>
-        <v>299904</v>
+        <f t="shared" ref="G179" si="1">F179*E179</f>
+        <v>79094</v>
       </c>
       <c r="H179" s="21">
-        <v>59798</v>
+        <v>59799</v>
       </c>
       <c r="I179" s="22">
         <v>46237</v>
@@ -9803,25 +9804,27 @@
       </c>
     </row>
     <row r="180" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="18"/>
+      <c r="A180" s="18">
+        <v>177</v>
+      </c>
       <c r="B180" s="19" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="C180" s="20" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D180" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E180" s="21">
-        <v>696</v>
+        <v>1561</v>
       </c>
       <c r="F180" s="33">
         <v>142</v>
       </c>
       <c r="G180" s="34">
         <f t="shared" si="0"/>
-        <v>98832</v>
+        <v>221662</v>
       </c>
       <c r="H180" s="21">
         <v>59798</v>
@@ -9843,23 +9846,23 @@
     <row r="181" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="18"/>
       <c r="B181" s="19" t="s">
-        <v>42</v>
+        <v>360</v>
       </c>
       <c r="C181" s="20" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D181" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E181" s="21">
-        <v>1104</v>
+        <v>696</v>
       </c>
       <c r="F181" s="33">
         <v>142</v>
       </c>
       <c r="G181" s="34">
         <f t="shared" si="0"/>
-        <v>156768</v>
+        <v>98832</v>
       </c>
       <c r="H181" s="21">
         <v>59798</v>
@@ -9881,23 +9884,23 @@
     <row r="182" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="18"/>
       <c r="B182" s="19" t="s">
-        <v>361</v>
+        <v>42</v>
       </c>
       <c r="C182" s="20" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D182" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E182" s="21">
-        <v>1640</v>
+        <v>1104</v>
       </c>
       <c r="F182" s="33">
         <v>142</v>
       </c>
       <c r="G182" s="34">
         <f t="shared" si="0"/>
-        <v>232880</v>
+        <v>156768</v>
       </c>
       <c r="H182" s="21">
         <v>59798</v>
@@ -9919,23 +9922,23 @@
     <row r="183" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="18"/>
       <c r="B183" s="19" t="s">
-        <v>40</v>
+        <v>361</v>
       </c>
       <c r="C183" s="20" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D183" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E183" s="21">
-        <v>2144</v>
+        <v>1640</v>
       </c>
       <c r="F183" s="33">
         <v>142</v>
       </c>
       <c r="G183" s="34">
         <f t="shared" si="0"/>
-        <v>304448</v>
+        <v>232880</v>
       </c>
       <c r="H183" s="21">
         <v>59798</v>
@@ -9957,23 +9960,23 @@
     <row r="184" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="18"/>
       <c r="B184" s="19" t="s">
-        <v>322</v>
+        <v>40</v>
       </c>
       <c r="C184" s="20" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D184" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E184" s="21">
-        <v>2252.8000000000002</v>
+        <v>2144</v>
       </c>
       <c r="F184" s="33">
         <v>142</v>
       </c>
       <c r="G184" s="34">
         <f t="shared" si="0"/>
-        <v>319897.60000000003</v>
+        <v>304448</v>
       </c>
       <c r="H184" s="21">
         <v>59798</v>
@@ -9995,23 +9998,23 @@
     <row r="185" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="18"/>
       <c r="B185" s="19" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C185" s="20" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="D185" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E185" s="21">
-        <v>2086.4</v>
+        <v>2252.8000000000002</v>
       </c>
       <c r="F185" s="33">
         <v>142</v>
       </c>
       <c r="G185" s="34">
         <f t="shared" si="0"/>
-        <v>296268.79999999999</v>
+        <v>319897.60000000003</v>
       </c>
       <c r="H185" s="21">
         <v>59798</v>
@@ -10030,66 +10033,65 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="1">
-        <v>179</v>
-      </c>
-      <c r="B186" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="D186" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E186" s="6">
-        <v>1</v>
-      </c>
-      <c r="F186" s="7">
-        <v>3500</v>
-      </c>
-      <c r="G186" s="7">
-        <v>3500</v>
-      </c>
-      <c r="H186" s="6">
-        <v>125</v>
-      </c>
-      <c r="I186" s="8">
-        <v>46268</v>
-      </c>
-      <c r="J186" s="6"/>
-      <c r="K186" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="L186" s="7">
-        <v>6218</v>
-      </c>
-      <c r="M186" s="8">
+    <row r="186" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A186" s="18"/>
+      <c r="B186" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="C186" s="20" t="s">
+        <v>763</v>
+      </c>
+      <c r="D186" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E186" s="21">
+        <v>2086.4</v>
+      </c>
+      <c r="F186" s="33">
+        <v>142</v>
+      </c>
+      <c r="G186" s="34">
+        <f t="shared" si="0"/>
+        <v>296268.79999999999</v>
+      </c>
+      <c r="H186" s="21">
+        <v>59798</v>
+      </c>
+      <c r="I186" s="22">
+        <v>46237</v>
+      </c>
+      <c r="J186" s="21"/>
+      <c r="K186" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="L186" s="20">
+        <v>6217</v>
+      </c>
+      <c r="M186" s="22">
         <v>46329</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="1">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D187" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E187" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F187" s="7">
-        <v>30</v>
+        <v>3500</v>
       </c>
       <c r="G187" s="7">
-        <v>300</v>
+        <v>3500</v>
       </c>
       <c r="H187" s="6">
         <v>125</v>
@@ -10110,38 +10112,38 @@
     </row>
     <row r="188" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="1">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D188" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E188" s="6">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F188" s="7">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G188" s="7">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H188" s="6">
-        <v>5236</v>
+        <v>125</v>
       </c>
       <c r="I188" s="8">
         <v>46268</v>
       </c>
       <c r="J188" s="6"/>
       <c r="K188" s="7" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L188" s="7">
-        <v>6219</v>
+        <v>6218</v>
       </c>
       <c r="M188" s="8">
         <v>46329</v>
@@ -10149,13 +10151,13 @@
     </row>
     <row r="189" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="1">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D189" s="7" t="s">
         <v>17</v>
@@ -10164,10 +10166,10 @@
         <v>50</v>
       </c>
       <c r="F189" s="7">
-        <v>170</v>
+        <v>3</v>
       </c>
       <c r="G189" s="7">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="H189" s="6">
         <v>5236</v>
@@ -10188,38 +10190,38 @@
     </row>
     <row r="190" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="1">
-        <v>183</v>
-      </c>
-      <c r="B190" s="9" t="s">
-        <v>343</v>
+        <v>182</v>
+      </c>
+      <c r="B190" s="11" t="s">
+        <v>337</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D190" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E190" s="6">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F190" s="7">
-        <v>3300</v>
+        <v>170</v>
       </c>
       <c r="G190" s="7">
-        <v>6600</v>
+        <v>1500</v>
       </c>
       <c r="H190" s="6">
-        <v>4729</v>
+        <v>5236</v>
       </c>
       <c r="I190" s="8">
-        <v>46328</v>
+        <v>46268</v>
       </c>
       <c r="J190" s="6"/>
       <c r="K190" s="7" t="s">
-        <v>179</v>
+        <v>334</v>
       </c>
       <c r="L190" s="7">
-        <v>6220</v>
+        <v>6219</v>
       </c>
       <c r="M190" s="8">
         <v>46329</v>
@@ -10227,13 +10229,13 @@
     </row>
     <row r="191" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="1">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D191" s="7" t="s">
         <v>17</v>
@@ -10242,10 +10244,10 @@
         <v>2</v>
       </c>
       <c r="F191" s="7">
-        <v>1600</v>
+        <v>3300</v>
       </c>
       <c r="G191" s="7">
-        <v>3200</v>
+        <v>6600</v>
       </c>
       <c r="H191" s="6">
         <v>4729</v>
@@ -10266,25 +10268,25 @@
     </row>
     <row r="192" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="1">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D192" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E192" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F192" s="7">
-        <v>45</v>
+        <v>1600</v>
       </c>
       <c r="G192" s="7">
-        <v>270</v>
+        <v>3200</v>
       </c>
       <c r="H192" s="6">
         <v>4729</v>
@@ -10305,38 +10307,38 @@
     </row>
     <row r="193" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="1">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E193" s="6">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="F193" s="7">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="G193" s="7">
-        <v>5535</v>
+        <v>270</v>
       </c>
       <c r="H193" s="6">
-        <v>60</v>
+        <v>4729</v>
       </c>
       <c r="I193" s="8">
         <v>46328</v>
       </c>
       <c r="J193" s="6"/>
       <c r="K193" s="7" t="s">
-        <v>346</v>
+        <v>179</v>
       </c>
       <c r="L193" s="7">
-        <v>6221</v>
+        <v>6220</v>
       </c>
       <c r="M193" s="8">
         <v>46329</v>
@@ -10344,38 +10346,38 @@
     </row>
     <row r="194" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="1">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E194" s="6">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="F194" s="7">
-        <v>1500</v>
+        <v>135</v>
       </c>
       <c r="G194" s="7">
-        <v>3000</v>
+        <v>5535</v>
       </c>
       <c r="H194" s="6">
-        <v>13728</v>
+        <v>60</v>
       </c>
       <c r="I194" s="8">
         <v>46328</v>
       </c>
       <c r="J194" s="6"/>
       <c r="K194" s="7" t="s">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="L194" s="7">
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="M194" s="8">
         <v>46329</v>
@@ -10383,13 +10385,13 @@
     </row>
     <row r="195" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="1">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D195" s="7" t="s">
         <v>17</v>
@@ -10422,25 +10424,25 @@
     </row>
     <row r="196" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="1">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>28</v>
+        <v>359</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D196" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E196" s="6">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F196" s="7">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="G196" s="7">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="H196" s="6">
         <v>13728</v>
@@ -10461,25 +10463,25 @@
     </row>
     <row r="197" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="1">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>356</v>
+        <v>28</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D197" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E197" s="6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F197" s="7">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="G197" s="7">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="H197" s="6">
         <v>13728</v>
@@ -10500,25 +10502,25 @@
     </row>
     <row r="198" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="1">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D198" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E198" s="6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F198" s="7">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="G198" s="7">
-        <v>195</v>
+        <v>500</v>
       </c>
       <c r="H198" s="6">
         <v>13728</v>
@@ -10539,25 +10541,25 @@
     </row>
     <row r="199" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="1">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D199" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E199" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F199" s="7">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="G199" s="7">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H199" s="6">
         <v>13728</v>
@@ -10578,25 +10580,25 @@
     </row>
     <row r="200" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="1">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D200" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E200" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F200" s="7">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="G200" s="7">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H200" s="6">
         <v>13728</v>
@@ -10615,68 +10617,67 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="201" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="18">
-        <v>194</v>
-      </c>
-      <c r="B201" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="C201" s="20" t="s">
-        <v>766</v>
-      </c>
-      <c r="D201" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E201" s="21">
-        <v>1980</v>
-      </c>
-      <c r="F201" s="33">
-        <v>142.98245600000001</v>
-      </c>
-      <c r="G201" s="34">
-        <f>F201*E201</f>
-        <v>283105.26288000005</v>
-      </c>
-      <c r="H201" s="21">
-        <v>59753</v>
-      </c>
-      <c r="I201" s="22">
+    <row r="201" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A201" s="1">
+        <v>193</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E201" s="6">
+        <v>2</v>
+      </c>
+      <c r="F201" s="7">
+        <v>125</v>
+      </c>
+      <c r="G201" s="7">
+        <v>250</v>
+      </c>
+      <c r="H201" s="6">
+        <v>13728</v>
+      </c>
+      <c r="I201" s="8">
         <v>46328</v>
       </c>
-      <c r="J201" s="21"/>
-      <c r="K201" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="L201" s="20">
-        <v>6223</v>
-      </c>
-      <c r="M201" s="22">
+      <c r="J201" s="6"/>
+      <c r="K201" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L201" s="7">
+        <v>6222</v>
+      </c>
+      <c r="M201" s="8">
         <v>46329</v>
       </c>
     </row>
     <row r="202" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="18">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B202" s="19" t="s">
-        <v>42</v>
+        <v>327</v>
       </c>
       <c r="C202" s="20" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D202" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E202" s="21">
-        <v>2260</v>
+        <v>1980</v>
       </c>
       <c r="F202" s="33">
         <v>142.98245600000001</v>
       </c>
       <c r="G202" s="34">
-        <f t="shared" ref="G202:G203" si="1">F202*E202</f>
-        <v>323140.35056000005</v>
+        <f>F202*E202</f>
+        <v>283105.26288000005</v>
       </c>
       <c r="H202" s="21">
         <v>59753</v>
@@ -10697,26 +10698,26 @@
     </row>
     <row r="203" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="18">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B203" s="19" t="s">
-        <v>361</v>
+        <v>42</v>
       </c>
       <c r="C203" s="20" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D203" s="20" t="s">
         <v>75</v>
       </c>
       <c r="E203" s="21">
-        <v>1126</v>
+        <v>2260</v>
       </c>
       <c r="F203" s="33">
         <v>142.98245600000001</v>
       </c>
       <c r="G203" s="34">
-        <f t="shared" si="1"/>
-        <v>160998.245456</v>
+        <f t="shared" ref="G203:G204" si="2">F203*E203</f>
+        <v>323140.35056000005</v>
       </c>
       <c r="H203" s="21">
         <v>59753</v>
@@ -10735,79 +10736,80 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="1">
-        <v>198</v>
-      </c>
-      <c r="B204" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="C204" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="D204" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E204" s="6">
-        <v>15</v>
-      </c>
-      <c r="F204" s="7">
-        <v>2675</v>
-      </c>
-      <c r="G204" s="7">
-        <v>40125</v>
-      </c>
-      <c r="H204" s="6">
-        <v>698</v>
-      </c>
-      <c r="I204" s="8">
+    <row r="204" spans="1:13" s="23" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A204" s="18">
+        <v>196</v>
+      </c>
+      <c r="B204" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="C204" s="20" t="s">
+        <v>765</v>
+      </c>
+      <c r="D204" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E204" s="21">
+        <v>1126</v>
+      </c>
+      <c r="F204" s="33">
+        <v>142.98245600000001</v>
+      </c>
+      <c r="G204" s="34">
+        <f t="shared" si="2"/>
+        <v>160998.245456</v>
+      </c>
+      <c r="H204" s="21">
+        <v>59753</v>
+      </c>
+      <c r="I204" s="22">
         <v>46328</v>
       </c>
-      <c r="J204" s="6"/>
-      <c r="K204" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L204" s="7">
-        <v>6225</v>
-      </c>
-      <c r="M204" s="8">
+      <c r="J204" s="21"/>
+      <c r="K204" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="L204" s="20">
+        <v>6223</v>
+      </c>
+      <c r="M204" s="22">
         <v>46329</v>
       </c>
     </row>
     <row r="205" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="1">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="C205" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="D205" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E205" s="6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F205" s="7">
-        <v>471.95</v>
+        <v>2675</v>
       </c>
       <c r="G205" s="7">
-        <v>471.95</v>
-      </c>
-      <c r="H205" s="13">
-        <v>324329</v>
+        <v>40125</v>
+      </c>
+      <c r="H205" s="6">
+        <v>698</v>
       </c>
       <c r="I205" s="8">
         <v>46328</v>
       </c>
       <c r="J205" s="6"/>
       <c r="K205" s="7" t="s">
-        <v>759</v>
+        <v>31</v>
       </c>
       <c r="L205" s="7">
-        <v>6226</v>
+        <v>6225</v>
       </c>
       <c r="M205" s="8">
         <v>46329</v>
@@ -10815,25 +10817,25 @@
     </row>
     <row r="206" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="1">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="C206" s="7" t="s">
-        <v>365</v>
+        <v>381</v>
+      </c>
+      <c r="C206" s="14" t="s">
+        <v>364</v>
       </c>
       <c r="D206" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E206" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F206" s="7">
-        <v>170.54</v>
+        <v>471.95</v>
       </c>
       <c r="G206" s="7">
-        <v>341.5</v>
+        <v>471.95</v>
       </c>
       <c r="H206" s="13">
         <v>324329</v>
@@ -10854,13 +10856,13 @@
     </row>
     <row r="207" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="1">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D207" s="7" t="s">
         <v>17</v>
@@ -10869,10 +10871,10 @@
         <v>2</v>
       </c>
       <c r="F207" s="7">
-        <v>380.34</v>
+        <v>170.54</v>
       </c>
       <c r="G207" s="7">
-        <v>760.68</v>
+        <v>341.5</v>
       </c>
       <c r="H207" s="13">
         <v>324329</v>
@@ -10893,25 +10895,25 @@
     </row>
     <row r="208" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D208" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E208" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F208" s="7">
-        <v>695.56</v>
+        <v>380.34</v>
       </c>
       <c r="G208" s="7">
-        <v>695.56</v>
+        <v>760.68</v>
       </c>
       <c r="H208" s="13">
         <v>324329</v>
@@ -10932,13 +10934,13 @@
     </row>
     <row r="209" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D209" s="7" t="s">
         <v>17</v>
@@ -10947,10 +10949,10 @@
         <v>1</v>
       </c>
       <c r="F209" s="7">
-        <v>475.39</v>
+        <v>695.56</v>
       </c>
       <c r="G209" s="7">
-        <v>475.39</v>
+        <v>695.56</v>
       </c>
       <c r="H209" s="13">
         <v>324329</v>
@@ -10971,13 +10973,13 @@
     </row>
     <row r="210" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D210" s="7" t="s">
         <v>17</v>
@@ -10986,10 +10988,10 @@
         <v>1</v>
       </c>
       <c r="F210" s="7">
-        <v>713.56</v>
+        <v>475.39</v>
       </c>
       <c r="G210" s="7">
-        <v>713.56</v>
+        <v>475.39</v>
       </c>
       <c r="H210" s="13">
         <v>324329</v>
@@ -11010,13 +11012,13 @@
     </row>
     <row r="211" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D211" s="7" t="s">
         <v>17</v>
@@ -11025,10 +11027,10 @@
         <v>1</v>
       </c>
       <c r="F211" s="7">
-        <v>1119.9100000000001</v>
+        <v>713.56</v>
       </c>
       <c r="G211" s="7">
-        <v>1119.9100000000001</v>
+        <v>713.56</v>
       </c>
       <c r="H211" s="13">
         <v>324329</v>
@@ -11049,25 +11051,25 @@
     </row>
     <row r="212" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D212" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E212" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F212" s="7">
-        <v>273.57</v>
+        <v>1119.9100000000001</v>
       </c>
       <c r="G212" s="7">
-        <v>547.14</v>
+        <v>1119.9100000000001</v>
       </c>
       <c r="H212" s="13">
         <v>324329</v>
@@ -11088,13 +11090,13 @@
     </row>
     <row r="213" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D213" s="7" t="s">
         <v>17</v>
@@ -11103,10 +11105,10 @@
         <v>2</v>
       </c>
       <c r="F213" s="7">
-        <v>170.54</v>
+        <v>273.57</v>
       </c>
       <c r="G213" s="7">
-        <v>341.5</v>
+        <v>547.14</v>
       </c>
       <c r="H213" s="13">
         <v>324329</v>
@@ -11127,13 +11129,13 @@
     </row>
     <row r="214" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D214" s="7" t="s">
         <v>17</v>
@@ -11142,10 +11144,10 @@
         <v>2</v>
       </c>
       <c r="F214" s="7">
-        <v>360.96</v>
+        <v>170.54</v>
       </c>
       <c r="G214" s="7">
-        <v>721.9</v>
+        <v>341.5</v>
       </c>
       <c r="H214" s="13">
         <v>324329</v>
@@ -11166,13 +11168,13 @@
     </row>
     <row r="215" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D215" s="7" t="s">
         <v>17</v>
@@ -11181,10 +11183,10 @@
         <v>2</v>
       </c>
       <c r="F215" s="7">
-        <v>145.36000000000001</v>
+        <v>360.96</v>
       </c>
       <c r="G215" s="7">
-        <v>290.8</v>
+        <v>721.9</v>
       </c>
       <c r="H215" s="13">
         <v>324329</v>
@@ -11205,25 +11207,25 @@
     </row>
     <row r="216" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D216" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E216" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F216" s="7">
-        <v>744.44</v>
+        <v>145.36000000000001</v>
       </c>
       <c r="G216" s="7">
-        <v>744.44</v>
+        <v>290.8</v>
       </c>
       <c r="H216" s="13">
         <v>324329</v>
@@ -11244,13 +11246,13 @@
     </row>
     <row r="217" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D217" s="7" t="s">
         <v>17</v>
@@ -11259,10 +11261,10 @@
         <v>1</v>
       </c>
       <c r="F217" s="7">
-        <v>251.71</v>
+        <v>744.44</v>
       </c>
       <c r="G217" s="7">
-        <v>251.71</v>
+        <v>744.44</v>
       </c>
       <c r="H217" s="13">
         <v>324329</v>
@@ -11283,25 +11285,25 @@
     </row>
     <row r="218" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D218" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E218" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F218" s="7">
-        <v>134.74</v>
+        <v>251.71</v>
       </c>
       <c r="G218" s="7">
-        <v>269.48</v>
+        <v>251.71</v>
       </c>
       <c r="H218" s="13">
         <v>324329</v>
@@ -11314,7 +11316,7 @@
         <v>759</v>
       </c>
       <c r="L218" s="7">
-        <v>6227</v>
+        <v>6226</v>
       </c>
       <c r="M218" s="8">
         <v>46329</v>
@@ -11322,13 +11324,13 @@
     </row>
     <row r="219" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="1">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D219" s="7" t="s">
         <v>17</v>
@@ -11337,10 +11339,10 @@
         <v>2</v>
       </c>
       <c r="F219" s="7">
-        <v>1055.3599999999999</v>
+        <v>134.74</v>
       </c>
       <c r="G219" s="7">
-        <v>2111.2600000000002</v>
+        <v>269.48</v>
       </c>
       <c r="H219" s="13">
         <v>324329</v>
@@ -11361,13 +11363,13 @@
     </row>
     <row r="220" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D220" s="7" t="s">
         <v>17</v>
@@ -11376,10 +11378,10 @@
         <v>2</v>
       </c>
       <c r="F220" s="7">
-        <v>800.59</v>
+        <v>1055.3599999999999</v>
       </c>
       <c r="G220" s="7">
-        <v>1601</v>
+        <v>2111.2600000000002</v>
       </c>
       <c r="H220" s="13">
         <v>324329</v>
@@ -11400,13 +11402,13 @@
     </row>
     <row r="221" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="1">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D221" s="7" t="s">
         <v>17</v>
@@ -11415,10 +11417,10 @@
         <v>2</v>
       </c>
       <c r="F221" s="7">
-        <v>405.24</v>
+        <v>800.59</v>
       </c>
       <c r="G221" s="7">
-        <v>810.4</v>
+        <v>1601</v>
       </c>
       <c r="H221" s="13">
         <v>324329</v>
@@ -11439,52 +11441,52 @@
     </row>
     <row r="222" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>208</v>
+        <v>397</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="D222" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E222" s="6">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F222" s="7">
-        <v>625</v>
+        <v>405.24</v>
       </c>
       <c r="G222" s="7">
-        <v>12500</v>
-      </c>
-      <c r="H222" s="6">
-        <v>1476</v>
-      </c>
-      <c r="I222" s="8" t="s">
-        <v>400</v>
+        <v>810.4</v>
+      </c>
+      <c r="H222" s="13">
+        <v>324329</v>
+      </c>
+      <c r="I222" s="8">
+        <v>46328</v>
       </c>
       <c r="J222" s="6"/>
       <c r="K222" s="7" t="s">
-        <v>204</v>
+        <v>759</v>
       </c>
       <c r="L222" s="7">
-        <v>6228</v>
+        <v>6227</v>
       </c>
       <c r="M222" s="8">
-        <v>46359</v>
+        <v>46329</v>
       </c>
     </row>
     <row r="223" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D223" s="7" t="s">
         <v>17</v>
@@ -11493,10 +11495,10 @@
         <v>20</v>
       </c>
       <c r="F223" s="7">
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="G223" s="7">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="H223" s="6">
         <v>1476</v>
@@ -11517,105 +11519,104 @@
     </row>
     <row r="224" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>403</v>
+        <v>209</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>761</v>
+        <v>17</v>
       </c>
       <c r="E224" s="6">
-        <v>5.5</v>
-      </c>
-      <c r="F224" s="10">
-        <v>19000</v>
+        <v>20</v>
+      </c>
+      <c r="F224" s="7">
+        <v>500</v>
       </c>
       <c r="G224" s="7">
-        <v>104519</v>
+        <v>10000</v>
       </c>
       <c r="H224" s="6">
-        <v>783</v>
+        <v>1476</v>
       </c>
       <c r="I224" s="8" t="s">
         <v>400</v>
       </c>
       <c r="J224" s="6"/>
       <c r="K224" s="7" t="s">
-        <v>402</v>
+        <v>204</v>
       </c>
       <c r="L224" s="7">
-        <v>6229</v>
+        <v>6228</v>
       </c>
       <c r="M224" s="8">
         <v>46359</v>
       </c>
     </row>
-    <row r="225" spans="1:13" s="31" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A225" s="24">
-        <v>219</v>
-      </c>
-      <c r="B225" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C225" s="26" t="s">
-        <v>404</v>
-      </c>
-      <c r="D225" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E225" s="27">
+    <row r="225" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A225" s="1">
+        <v>218</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="E225" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="F225" s="10">
+        <v>19000</v>
+      </c>
+      <c r="G225" s="7">
+        <v>104519</v>
+      </c>
+      <c r="H225" s="6">
+        <v>783</v>
+      </c>
+      <c r="I225" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="F225" s="28">
-        <v>129.15163999999999</v>
-      </c>
-      <c r="G225" s="29">
-        <f>F225*E225</f>
-        <v>51660.655999999995</v>
-      </c>
-      <c r="H225" s="27">
-        <v>699</v>
-      </c>
-      <c r="I225" s="30" t="s">
-        <v>400</v>
-      </c>
-      <c r="J225" s="27"/>
-      <c r="K225" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="L225" s="26">
-        <v>6230</v>
-      </c>
-      <c r="M225" s="30">
+      <c r="J225" s="6"/>
+      <c r="K225" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="L225" s="7">
+        <v>6229</v>
+      </c>
+      <c r="M225" s="8">
         <v>46359</v>
       </c>
     </row>
     <row r="226" spans="1:13" s="31" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="24">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B226" s="25" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C226" s="26" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D226" s="26" t="s">
         <v>75</v>
       </c>
       <c r="E226" s="27">
-        <v>200</v>
-      </c>
-      <c r="F226" s="32">
+        <v>400</v>
+      </c>
+      <c r="F226" s="28">
         <v>129.15163999999999</v>
       </c>
       <c r="G226" s="29">
         <f>F226*E226</f>
-        <v>25830.327999999998</v>
+        <v>51660.655999999995</v>
       </c>
       <c r="H226" s="27">
         <v>699</v>
@@ -11634,66 +11635,67 @@
         <v>46359</v>
       </c>
     </row>
-    <row r="227" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A227" s="1">
-        <v>221</v>
-      </c>
-      <c r="B227" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="C227" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="D227" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E227" s="6">
-        <v>2</v>
-      </c>
-      <c r="F227" s="7">
-        <v>1400</v>
-      </c>
-      <c r="G227" s="7">
-        <v>2800</v>
-      </c>
-      <c r="H227" s="6">
-        <v>13750</v>
-      </c>
-      <c r="I227" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="J227" s="6"/>
-      <c r="K227" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L227" s="7">
-        <v>6231</v>
-      </c>
-      <c r="M227" s="8">
+    <row r="227" spans="1:13" s="31" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A227" s="24">
+        <v>220</v>
+      </c>
+      <c r="B227" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C227" s="26" t="s">
+        <v>405</v>
+      </c>
+      <c r="D227" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E227" s="27">
+        <v>200</v>
+      </c>
+      <c r="F227" s="32">
+        <v>129.15163999999999</v>
+      </c>
+      <c r="G227" s="29">
+        <f>F227*E227</f>
+        <v>25830.327999999998</v>
+      </c>
+      <c r="H227" s="27">
+        <v>699</v>
+      </c>
+      <c r="I227" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="J227" s="27"/>
+      <c r="K227" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L227" s="26">
+        <v>6230</v>
+      </c>
+      <c r="M227" s="30">
         <v>46359</v>
       </c>
     </row>
     <row r="228" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D228" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E228" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F228" s="7">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="G228" s="7">
-        <v>400</v>
+        <v>2800</v>
       </c>
       <c r="H228" s="6">
         <v>13750</v>
@@ -11714,25 +11716,25 @@
     </row>
     <row r="229" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="1">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D229" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E229" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F229" s="7">
-        <v>45</v>
+        <v>400</v>
       </c>
       <c r="G229" s="7">
-        <v>180</v>
+        <v>400</v>
       </c>
       <c r="H229" s="6">
         <v>13750</v>
@@ -11753,38 +11755,38 @@
     </row>
     <row r="230" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="1">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D230" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E230" s="6">
-        <v>1</v>
-      </c>
-      <c r="F230" s="10">
-        <v>11700</v>
+        <v>4</v>
+      </c>
+      <c r="F230" s="7">
+        <v>45</v>
       </c>
       <c r="G230" s="7">
-        <v>11700</v>
+        <v>180</v>
       </c>
       <c r="H230" s="6">
-        <v>34</v>
+        <v>13750</v>
       </c>
       <c r="I230" s="8" t="s">
         <v>409</v>
       </c>
       <c r="J230" s="6"/>
       <c r="K230" s="7" t="s">
-        <v>757</v>
+        <v>20</v>
       </c>
       <c r="L230" s="7">
-        <v>6232</v>
+        <v>6231</v>
       </c>
       <c r="M230" s="8">
         <v>46359</v>
@@ -11792,25 +11794,25 @@
     </row>
     <row r="231" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="1">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E231" s="6">
-        <v>14.95</v>
-      </c>
-      <c r="F231" s="7">
-        <v>444.6</v>
+        <v>1</v>
+      </c>
+      <c r="F231" s="10">
+        <v>11700</v>
       </c>
       <c r="G231" s="7">
-        <v>6646.77</v>
+        <v>11700</v>
       </c>
       <c r="H231" s="6">
         <v>34</v>
@@ -11831,25 +11833,25 @@
     </row>
     <row r="232" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D232" s="7" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E232" s="6">
-        <v>1</v>
+        <v>14.95</v>
       </c>
       <c r="F232" s="7">
-        <v>526.5</v>
+        <v>444.6</v>
       </c>
       <c r="G232" s="7">
-        <v>526.5</v>
+        <v>6646.77</v>
       </c>
       <c r="H232" s="6">
         <v>34</v>
@@ -11870,25 +11872,25 @@
     </row>
     <row r="233" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E233" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F233" s="7">
-        <v>152.1</v>
+        <v>526.5</v>
       </c>
       <c r="G233" s="7">
-        <v>760.5</v>
+        <v>526.5</v>
       </c>
       <c r="H233" s="6">
         <v>34</v>
@@ -11909,25 +11911,25 @@
     </row>
     <row r="234" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="1">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D234" s="7" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E234" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F234" s="7">
-        <v>1236.57</v>
+        <v>152.1</v>
       </c>
       <c r="G234" s="7">
-        <v>2473.14</v>
+        <v>760.5</v>
       </c>
       <c r="H234" s="6">
         <v>34</v>
@@ -11948,13 +11950,13 @@
     </row>
     <row r="235" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="1">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D235" s="7" t="s">
         <v>17</v>
@@ -11963,10 +11965,10 @@
         <v>2</v>
       </c>
       <c r="F235" s="7">
-        <v>862.4</v>
+        <v>1236.57</v>
       </c>
       <c r="G235" s="7">
-        <v>1724.8</v>
+        <v>2473.14</v>
       </c>
       <c r="H235" s="6">
         <v>34</v>
@@ -11987,25 +11989,25 @@
     </row>
     <row r="236" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="1">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D236" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E236" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F236" s="7">
-        <v>857.84</v>
+        <v>862.4</v>
       </c>
       <c r="G236" s="7">
-        <v>857.84</v>
+        <v>1724.8</v>
       </c>
       <c r="H236" s="6">
         <v>34</v>
@@ -12026,13 +12028,13 @@
     </row>
     <row r="237" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="1">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D237" s="7" t="s">
         <v>17</v>
@@ -12041,10 +12043,10 @@
         <v>1</v>
       </c>
       <c r="F237" s="7">
-        <v>866.97</v>
+        <v>857.84</v>
       </c>
       <c r="G237" s="7">
-        <v>866.97</v>
+        <v>857.84</v>
       </c>
       <c r="H237" s="6">
         <v>34</v>
@@ -12065,25 +12067,25 @@
     </row>
     <row r="238" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="1">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D238" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E238" s="6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F238" s="7">
-        <v>9.36</v>
+        <v>866.97</v>
       </c>
       <c r="G238" s="7">
-        <v>468</v>
+        <v>866.97</v>
       </c>
       <c r="H238" s="6">
         <v>34</v>
@@ -12104,25 +12106,25 @@
     </row>
     <row r="239" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="1">
-        <v>233</v>
-      </c>
-      <c r="B239" s="11" t="s">
-        <v>432</v>
+        <v>232</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>431</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D239" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E239" s="6">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F239" s="7">
-        <v>140</v>
+        <v>9.36</v>
       </c>
       <c r="G239" s="7">
-        <v>280</v>
+        <v>468</v>
       </c>
       <c r="H239" s="6">
         <v>34</v>
@@ -12143,28 +12145,28 @@
     </row>
     <row r="240" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="1">
-        <v>234</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>434</v>
+        <v>233</v>
+      </c>
+      <c r="B240" s="11" t="s">
+        <v>432</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="D240" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E240" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F240" s="7">
-        <v>3861</v>
+        <v>140</v>
       </c>
       <c r="G240" s="7">
-        <v>3861</v>
+        <v>280</v>
       </c>
       <c r="H240" s="6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I240" s="8" t="s">
         <v>409</v>
@@ -12174,7 +12176,7 @@
         <v>757</v>
       </c>
       <c r="L240" s="7">
-        <v>6233</v>
+        <v>6232</v>
       </c>
       <c r="M240" s="8">
         <v>46359</v>
@@ -12182,28 +12184,28 @@
     </row>
     <row r="241" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="1">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D241" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E241" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F241" s="7">
-        <v>150</v>
+        <v>3861</v>
       </c>
       <c r="G241" s="7">
-        <v>300</v>
+        <v>3861</v>
       </c>
       <c r="H241" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I241" s="8" t="s">
         <v>409</v>
@@ -12213,7 +12215,7 @@
         <v>757</v>
       </c>
       <c r="L241" s="7">
-        <v>6234</v>
+        <v>6233</v>
       </c>
       <c r="M241" s="8">
         <v>46359</v>
@@ -12221,25 +12223,25 @@
     </row>
     <row r="242" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="1">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>92</v>
+        <v>439</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D242" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E242" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F242" s="7">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G242" s="7">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="H242" s="6">
         <v>36</v>
@@ -12260,25 +12262,25 @@
     </row>
     <row r="243" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="1">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>440</v>
+        <v>92</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D243" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E243" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F243" s="7">
-        <v>1450</v>
+        <v>140</v>
       </c>
       <c r="G243" s="7">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="H243" s="6">
         <v>36</v>
@@ -12299,13 +12301,13 @@
     </row>
     <row r="244" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="1">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D244" s="7" t="s">
         <v>17</v>
@@ -12314,10 +12316,10 @@
         <v>1</v>
       </c>
       <c r="F244" s="7">
-        <v>275</v>
+        <v>1450</v>
       </c>
       <c r="G244" s="7">
-        <v>275</v>
+        <v>1450</v>
       </c>
       <c r="H244" s="6">
         <v>36</v>
@@ -12338,38 +12340,38 @@
     </row>
     <row r="245" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="1">
-        <v>239</v>
-      </c>
-      <c r="B245" s="11" t="s">
-        <v>443</v>
+        <v>238</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>441</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D245" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E245" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F245" s="7">
-        <v>115</v>
+        <v>275</v>
       </c>
       <c r="G245" s="7">
-        <v>2875</v>
+        <v>275</v>
       </c>
       <c r="H245" s="6">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="I245" s="8" t="s">
         <v>409</v>
       </c>
       <c r="J245" s="6"/>
       <c r="K245" s="7" t="s">
-        <v>329</v>
+        <v>757</v>
       </c>
       <c r="L245" s="7">
-        <v>6235</v>
+        <v>6234</v>
       </c>
       <c r="M245" s="8">
         <v>46359</v>
@@ -12377,52 +12379,52 @@
     </row>
     <row r="246" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="1">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B246" s="11" t="s">
-        <v>298</v>
+        <v>443</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D246" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E246" s="6">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F246" s="7">
-        <v>1637.37</v>
+        <v>115</v>
       </c>
       <c r="G246" s="7">
-        <v>16373.76</v>
+        <v>2875</v>
       </c>
       <c r="H246" s="6">
-        <v>339</v>
+        <v>121</v>
       </c>
       <c r="I246" s="8" t="s">
-        <v>446</v>
+        <v>409</v>
       </c>
       <c r="J246" s="6"/>
       <c r="K246" s="7" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="L246" s="7">
-        <v>6236</v>
+        <v>6235</v>
       </c>
       <c r="M246" s="8">
-        <v>46329</v>
+        <v>46359</v>
       </c>
     </row>
     <row r="247" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="1">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B247" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D247" s="7" t="s">
         <v>17</v>
@@ -12431,10 +12433,10 @@
         <v>10</v>
       </c>
       <c r="F247" s="7">
-        <v>2117.7600000000002</v>
+        <v>1637.37</v>
       </c>
       <c r="G247" s="7">
-        <v>21170.7</v>
+        <v>16373.76</v>
       </c>
       <c r="H247" s="6">
         <v>339</v>
@@ -12455,38 +12457,38 @@
     </row>
     <row r="248" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="1">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>451</v>
+        <v>299</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D248" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E248" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F248" s="7">
-        <v>1800</v>
+        <v>2117.7600000000002</v>
       </c>
       <c r="G248" s="7">
-        <v>10800</v>
+        <v>21170.7</v>
       </c>
       <c r="H248" s="6">
-        <v>5166</v>
+        <v>339</v>
       </c>
       <c r="I248" s="8" t="s">
         <v>446</v>
       </c>
       <c r="J248" s="6"/>
       <c r="K248" s="7" t="s">
-        <v>168</v>
+        <v>297</v>
       </c>
       <c r="L248" s="7">
-        <v>6237</v>
+        <v>6236</v>
       </c>
       <c r="M248" s="8">
         <v>46329</v>
@@ -12494,25 +12496,25 @@
     </row>
     <row r="249" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="1">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D249" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E249" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F249" s="7">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="G249" s="7">
-        <v>1800</v>
+        <v>10800</v>
       </c>
       <c r="H249" s="6">
         <v>5166</v>
@@ -12533,25 +12535,25 @@
     </row>
     <row r="250" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="1">
-        <v>244</v>
-      </c>
-      <c r="B250" s="9" t="s">
-        <v>452</v>
+        <v>243</v>
+      </c>
+      <c r="B250" s="11" t="s">
+        <v>450</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D250" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E250" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F250" s="7">
-        <v>2700</v>
+        <v>900</v>
       </c>
       <c r="G250" s="7">
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="H250" s="6">
         <v>5166</v>
@@ -12570,66 +12572,66 @@
         <v>46329</v>
       </c>
     </row>
-    <row r="251" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A251" s="35">
-        <v>245</v>
-      </c>
-      <c r="B251" s="36" t="s">
-        <v>459</v>
-      </c>
-      <c r="C251" s="37" t="s">
-        <v>453</v>
-      </c>
-      <c r="D251" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E251" s="38">
-        <v>100</v>
-      </c>
-      <c r="F251" s="37">
-        <v>204.75</v>
-      </c>
-      <c r="G251" s="37">
-        <v>20475</v>
-      </c>
-      <c r="H251" s="38">
-        <v>83</v>
-      </c>
-      <c r="I251" s="39" t="s">
+    <row r="251" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A251" s="1">
+        <v>244</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="C251" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="D251" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E251" s="6">
+        <v>1</v>
+      </c>
+      <c r="F251" s="7">
+        <v>2700</v>
+      </c>
+      <c r="G251" s="7">
+        <v>2700</v>
+      </c>
+      <c r="H251" s="6">
+        <v>5166</v>
+      </c>
+      <c r="I251" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="J251" s="38"/>
-      <c r="K251" s="37" t="s">
-        <v>757</v>
-      </c>
-      <c r="L251" s="37">
-        <v>6238</v>
-      </c>
-      <c r="M251" s="39">
-        <v>46359</v>
+      <c r="J251" s="6"/>
+      <c r="K251" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="L251" s="7">
+        <v>6237</v>
+      </c>
+      <c r="M251" s="8">
+        <v>46329</v>
       </c>
     </row>
     <row r="252" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="35">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B252" s="36" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C252" s="37" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D252" s="37" t="s">
         <v>17</v>
       </c>
       <c r="E252" s="38">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F252" s="37">
-        <v>526.5</v>
+        <v>204.75</v>
       </c>
       <c r="G252" s="37">
-        <v>1053</v>
+        <v>20475</v>
       </c>
       <c r="H252" s="38">
         <v>83</v>
@@ -12650,25 +12652,25 @@
     </row>
     <row r="253" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="35">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B253" s="36" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C253" s="37" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D253" s="37" t="s">
         <v>17</v>
       </c>
       <c r="E253" s="38">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F253" s="37">
-        <v>58.5</v>
+        <v>526.5</v>
       </c>
       <c r="G253" s="37">
-        <v>1462.5</v>
+        <v>1053</v>
       </c>
       <c r="H253" s="38">
         <v>83</v>
@@ -12689,25 +12691,25 @@
     </row>
     <row r="254" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="35">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B254" s="36" t="s">
-        <v>91</v>
+        <v>461</v>
       </c>
       <c r="C254" s="37" t="s">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="D254" s="37" t="s">
         <v>17</v>
       </c>
       <c r="E254" s="38">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F254" s="37">
-        <v>3100.5</v>
+        <v>58.5</v>
       </c>
       <c r="G254" s="37">
-        <v>3100.5</v>
+        <v>1462.5</v>
       </c>
       <c r="H254" s="38">
         <v>83</v>
@@ -12728,13 +12730,13 @@
     </row>
     <row r="255" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="35">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B255" s="36" t="s">
-        <v>462</v>
+        <v>91</v>
       </c>
       <c r="C255" s="37" t="s">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="D255" s="37" t="s">
         <v>17</v>
@@ -12743,10 +12745,10 @@
         <v>1</v>
       </c>
       <c r="F255" s="37">
-        <v>3393</v>
+        <v>3100.5</v>
       </c>
       <c r="G255" s="37">
-        <v>3393</v>
+        <v>3100.5</v>
       </c>
       <c r="H255" s="38">
         <v>83</v>
@@ -12767,13 +12769,13 @@
     </row>
     <row r="256" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="35">
-        <v>250</v>
-      </c>
-      <c r="B256" s="41" t="s">
-        <v>463</v>
+        <v>249</v>
+      </c>
+      <c r="B256" s="36" t="s">
+        <v>462</v>
       </c>
       <c r="C256" s="37" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D256" s="37" t="s">
         <v>17</v>
@@ -12782,10 +12784,10 @@
         <v>1</v>
       </c>
       <c r="F256" s="37">
-        <v>152.1</v>
+        <v>3393</v>
       </c>
       <c r="G256" s="37">
-        <v>152.1</v>
+        <v>3393</v>
       </c>
       <c r="H256" s="38">
         <v>83</v>
@@ -12806,13 +12808,13 @@
     </row>
     <row r="257" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="35">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B257" s="41" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C257" s="37" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D257" s="37" t="s">
         <v>17</v>
@@ -12821,10 +12823,10 @@
         <v>1</v>
       </c>
       <c r="F257" s="37">
-        <v>157.94999999999999</v>
+        <v>152.1</v>
       </c>
       <c r="G257" s="37">
-        <v>157.94999999999999</v>
+        <v>152.1</v>
       </c>
       <c r="H257" s="38">
         <v>83</v>
@@ -12843,54 +12845,54 @@
         <v>46359</v>
       </c>
     </row>
-    <row r="258" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A258" s="1">
-        <v>252</v>
-      </c>
-      <c r="B258" s="11" t="s">
-        <v>469</v>
-      </c>
-      <c r="C258" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="D258" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E258" s="6">
+    <row r="258" spans="1:13" s="40" customFormat="1" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A258" s="35">
+        <v>251</v>
+      </c>
+      <c r="B258" s="41" t="s">
+        <v>464</v>
+      </c>
+      <c r="C258" s="37" t="s">
+        <v>458</v>
+      </c>
+      <c r="D258" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E258" s="38">
         <v>1</v>
       </c>
-      <c r="F258" s="7">
-        <v>1755</v>
-      </c>
-      <c r="G258" s="7">
-        <v>1755</v>
-      </c>
-      <c r="H258" s="6">
-        <v>39</v>
-      </c>
-      <c r="I258" s="8" t="s">
+      <c r="F258" s="37">
+        <v>157.94999999999999</v>
+      </c>
+      <c r="G258" s="37">
+        <v>157.94999999999999</v>
+      </c>
+      <c r="H258" s="38">
+        <v>83</v>
+      </c>
+      <c r="I258" s="39" t="s">
         <v>446</v>
       </c>
-      <c r="J258" s="6"/>
-      <c r="K258" s="7" t="s">
+      <c r="J258" s="38"/>
+      <c r="K258" s="37" t="s">
         <v>757</v>
       </c>
-      <c r="L258" s="7">
-        <v>6239</v>
-      </c>
-      <c r="M258" s="8">
+      <c r="L258" s="37">
+        <v>6238</v>
+      </c>
+      <c r="M258" s="39">
         <v>46359</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="1">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B259" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D259" s="7" t="s">
         <v>17</v>
@@ -12899,10 +12901,10 @@
         <v>1</v>
       </c>
       <c r="F259" s="7">
-        <v>292.5</v>
+        <v>1755</v>
       </c>
       <c r="G259" s="7">
-        <v>1872</v>
+        <v>1755</v>
       </c>
       <c r="H259" s="6">
         <v>39</v>
@@ -12923,25 +12925,25 @@
     </row>
     <row r="260" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="1">
-        <v>254</v>
-      </c>
-      <c r="B260" s="9" t="s">
-        <v>92</v>
+        <v>253</v>
+      </c>
+      <c r="B260" s="11" t="s">
+        <v>470</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="D260" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E260" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F260" s="7">
-        <v>140</v>
+        <v>292.5</v>
       </c>
       <c r="G260" s="7">
-        <v>280</v>
+        <v>1872</v>
       </c>
       <c r="H260" s="6">
         <v>39</v>
@@ -12962,25 +12964,25 @@
     </row>
     <row r="261" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="1">
-        <v>255</v>
-      </c>
-      <c r="B261" s="11" t="s">
-        <v>467</v>
+        <v>254</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>468</v>
+        <v>436</v>
       </c>
       <c r="D261" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E261" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F261" s="7">
-        <v>292.5</v>
+        <v>140</v>
       </c>
       <c r="G261" s="7">
-        <v>292.5</v>
+        <v>280</v>
       </c>
       <c r="H261" s="6">
         <v>39</v>
@@ -13001,38 +13003,38 @@
     </row>
     <row r="262" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="1">
-        <v>256</v>
-      </c>
-      <c r="B262" s="15" t="s">
-        <v>505</v>
+        <v>255</v>
+      </c>
+      <c r="B262" s="11" t="s">
+        <v>467</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D262" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E262" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F262" s="7">
-        <v>6930</v>
+        <v>292.5</v>
       </c>
       <c r="G262" s="7">
-        <v>13890</v>
+        <v>292.5</v>
       </c>
       <c r="H262" s="6">
-        <v>2437</v>
+        <v>39</v>
       </c>
       <c r="I262" s="8" t="s">
-        <v>484</v>
+        <v>446</v>
       </c>
       <c r="J262" s="6"/>
       <c r="K262" s="7" t="s">
-        <v>204</v>
+        <v>757</v>
       </c>
       <c r="L262" s="7">
-        <v>6240</v>
+        <v>6239</v>
       </c>
       <c r="M262" s="8">
         <v>46359</v>
@@ -13040,25 +13042,25 @@
     </row>
     <row r="263" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="1">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B263" s="15" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D263" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E263" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F263" s="7">
-        <v>440</v>
+        <v>6930</v>
       </c>
       <c r="G263" s="7">
-        <v>440</v>
+        <v>13890</v>
       </c>
       <c r="H263" s="6">
         <v>2437</v>
@@ -13079,13 +13081,13 @@
     </row>
     <row r="264" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="1">
-        <v>258</v>
-      </c>
-      <c r="B264" s="11" t="s">
-        <v>508</v>
+        <v>257</v>
+      </c>
+      <c r="B264" s="15" t="s">
+        <v>507</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D264" s="7" t="s">
         <v>17</v>
@@ -13094,10 +13096,10 @@
         <v>1</v>
       </c>
       <c r="F264" s="7">
-        <v>690</v>
+        <v>440</v>
       </c>
       <c r="G264" s="7">
-        <v>690</v>
+        <v>440</v>
       </c>
       <c r="H264" s="6">
         <v>2437</v>
@@ -13118,25 +13120,25 @@
     </row>
     <row r="265" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="1">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B265" s="11" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D265" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E265" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F265" s="7">
-        <v>288.5</v>
+        <v>690</v>
       </c>
       <c r="G265" s="7">
-        <v>577</v>
+        <v>690</v>
       </c>
       <c r="H265" s="6">
         <v>2437</v>
@@ -13157,25 +13159,25 @@
     </row>
     <row r="266" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="1">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D266" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E266" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F266" s="7">
-        <v>3190</v>
+        <v>288.5</v>
       </c>
       <c r="G266" s="7">
-        <v>3190</v>
+        <v>577</v>
       </c>
       <c r="H266" s="6">
         <v>2437</v>
@@ -13196,13 +13198,13 @@
     </row>
     <row r="267" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="1">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D267" s="7" t="s">
         <v>17</v>
@@ -13211,10 +13213,10 @@
         <v>1</v>
       </c>
       <c r="F267" s="7">
-        <v>940</v>
+        <v>3190</v>
       </c>
       <c r="G267" s="7">
-        <v>940</v>
+        <v>3190</v>
       </c>
       <c r="H267" s="6">
         <v>2437</v>
@@ -13235,13 +13237,13 @@
     </row>
     <row r="268" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="1">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D268" s="7" t="s">
         <v>17</v>
@@ -13250,10 +13252,10 @@
         <v>1</v>
       </c>
       <c r="F268" s="7">
-        <v>600</v>
+        <v>940</v>
       </c>
       <c r="G268" s="7">
-        <v>600</v>
+        <v>940</v>
       </c>
       <c r="H268" s="6">
         <v>2437</v>
@@ -13274,13 +13276,13 @@
     </row>
     <row r="269" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="1">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D269" s="7" t="s">
         <v>17</v>
@@ -13289,10 +13291,10 @@
         <v>1</v>
       </c>
       <c r="F269" s="7">
-        <v>439</v>
+        <v>600</v>
       </c>
       <c r="G269" s="7">
-        <v>439</v>
+        <v>600</v>
       </c>
       <c r="H269" s="6">
         <v>2437</v>
@@ -13313,13 +13315,13 @@
     </row>
     <row r="270" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="1">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B270" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D270" s="7" t="s">
         <v>17</v>
@@ -13328,10 +13330,10 @@
         <v>1</v>
       </c>
       <c r="F270" s="7">
-        <v>1918.5</v>
+        <v>439</v>
       </c>
       <c r="G270" s="7">
-        <v>1918.5</v>
+        <v>439</v>
       </c>
       <c r="H270" s="6">
         <v>2437</v>
@@ -13352,25 +13354,25 @@
     </row>
     <row r="271" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="1">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B271" s="11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D271" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E271" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F271" s="7">
-        <v>1097.25</v>
+        <v>1918.5</v>
       </c>
       <c r="G271" s="7">
-        <v>2194.5</v>
+        <v>1918.5</v>
       </c>
       <c r="H271" s="6">
         <v>2437</v>
@@ -13391,25 +13393,25 @@
     </row>
     <row r="272" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="1">
-        <v>266</v>
-      </c>
-      <c r="B272" s="9" t="s">
-        <v>516</v>
+        <v>265</v>
+      </c>
+      <c r="B272" s="11" t="s">
+        <v>515</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D272" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E272" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F272" s="7">
-        <v>75.25</v>
+        <v>1097.25</v>
       </c>
       <c r="G272" s="7">
-        <v>75.25</v>
+        <v>2194.5</v>
       </c>
       <c r="H272" s="6">
         <v>2437</v>
@@ -13430,13 +13432,13 @@
     </row>
     <row r="273" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="1">
-        <v>267</v>
-      </c>
-      <c r="B273" s="11" t="s">
-        <v>469</v>
+        <v>266</v>
+      </c>
+      <c r="B273" s="9" t="s">
+        <v>516</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D273" s="7" t="s">
         <v>17</v>
@@ -13445,10 +13447,10 @@
         <v>1</v>
       </c>
       <c r="F273" s="7">
-        <v>4345</v>
+        <v>75.25</v>
       </c>
       <c r="G273" s="7">
-        <v>4345</v>
+        <v>75.25</v>
       </c>
       <c r="H273" s="6">
         <v>2437</v>
@@ -13469,13 +13471,13 @@
     </row>
     <row r="274" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="1">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B274" s="11" t="s">
-        <v>517</v>
+        <v>469</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D274" s="7" t="s">
         <v>17</v>
@@ -13484,10 +13486,10 @@
         <v>1</v>
       </c>
       <c r="F274" s="7">
-        <v>1925</v>
+        <v>4345</v>
       </c>
       <c r="G274" s="7">
-        <v>1925</v>
+        <v>4345</v>
       </c>
       <c r="H274" s="6">
         <v>2437</v>
@@ -13500,7 +13502,7 @@
         <v>204</v>
       </c>
       <c r="L274" s="7">
-        <v>6241</v>
+        <v>6240</v>
       </c>
       <c r="M274" s="8">
         <v>46359</v>
@@ -13508,13 +13510,13 @@
     </row>
     <row r="275" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="1">
-        <v>269</v>
-      </c>
-      <c r="B275" s="15" t="s">
-        <v>518</v>
+        <v>268</v>
+      </c>
+      <c r="B275" s="11" t="s">
+        <v>517</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="D275" s="7" t="s">
         <v>17</v>
@@ -13523,10 +13525,10 @@
         <v>1</v>
       </c>
       <c r="F275" s="7">
-        <v>689.7</v>
+        <v>1925</v>
       </c>
       <c r="G275" s="7">
-        <v>689.7</v>
+        <v>1925</v>
       </c>
       <c r="H275" s="6">
         <v>2437</v>
@@ -13547,13 +13549,13 @@
     </row>
     <row r="276" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="1">
-        <v>270</v>
-      </c>
-      <c r="B276" s="11" t="s">
-        <v>519</v>
+        <v>269</v>
+      </c>
+      <c r="B276" s="15" t="s">
+        <v>518</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D276" s="7" t="s">
         <v>17</v>
@@ -13562,10 +13564,10 @@
         <v>1</v>
       </c>
       <c r="F276" s="7">
-        <v>501.6</v>
+        <v>689.7</v>
       </c>
       <c r="G276" s="7">
-        <v>501.6</v>
+        <v>689.7</v>
       </c>
       <c r="H276" s="6">
         <v>2437</v>
@@ -13586,25 +13588,25 @@
     </row>
     <row r="277" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="1">
-        <v>271</v>
-      </c>
-      <c r="B277" s="12" t="s">
-        <v>520</v>
+        <v>270</v>
+      </c>
+      <c r="B277" s="11" t="s">
+        <v>519</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D277" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E277" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F277" s="7">
-        <v>21.5</v>
+        <v>501.6</v>
       </c>
       <c r="G277" s="7">
-        <v>215</v>
+        <v>501.6</v>
       </c>
       <c r="H277" s="6">
         <v>2437</v>
@@ -13625,25 +13627,25 @@
     </row>
     <row r="278" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="1">
-        <v>272</v>
-      </c>
-      <c r="B278" s="11" t="s">
-        <v>521</v>
+        <v>271</v>
+      </c>
+      <c r="B278" s="12" t="s">
+        <v>520</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D278" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E278" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F278" s="7">
-        <v>250</v>
+        <v>21.5</v>
       </c>
       <c r="G278" s="7">
-        <v>501.6</v>
+        <v>215</v>
       </c>
       <c r="H278" s="6">
         <v>2437</v>
@@ -13664,13 +13666,13 @@
     </row>
     <row r="279" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="1">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D279" s="7" t="s">
         <v>17</v>
@@ -13679,10 +13681,10 @@
         <v>2</v>
       </c>
       <c r="F279" s="7">
-        <v>3720</v>
+        <v>250</v>
       </c>
       <c r="G279" s="7">
-        <v>7440</v>
+        <v>501.6</v>
       </c>
       <c r="H279" s="6">
         <v>2437</v>
@@ -13703,22 +13705,22 @@
     </row>
     <row r="280" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="1">
-        <v>274</v>
-      </c>
-      <c r="B280" s="15" t="s">
-        <v>506</v>
+        <v>273</v>
+      </c>
+      <c r="B280" s="11" t="s">
+        <v>522</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D280" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E280" s="6">
-        <v>1</v>
-      </c>
-      <c r="F280" s="10">
-        <v>71500</v>
+        <v>2</v>
+      </c>
+      <c r="F280" s="7">
+        <v>3720</v>
       </c>
       <c r="G280" s="7">
         <v>7440</v>
@@ -13742,13 +13744,13 @@
     </row>
     <row r="281" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="1">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B281" s="15" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D281" s="7" t="s">
         <v>17</v>
@@ -13756,11 +13758,11 @@
       <c r="E281" s="6">
         <v>1</v>
       </c>
-      <c r="F281" s="7">
-        <v>8910</v>
+      <c r="F281" s="10">
+        <v>71500</v>
       </c>
       <c r="G281" s="7">
-        <v>8910</v>
+        <v>7440</v>
       </c>
       <c r="H281" s="6">
         <v>2437</v>
@@ -13781,25 +13783,25 @@
     </row>
     <row r="282" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="1">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B282" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D282" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E282" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F282" s="7">
-        <v>1812</v>
+        <v>8910</v>
       </c>
       <c r="G282" s="7">
-        <v>3624</v>
+        <v>8910</v>
       </c>
       <c r="H282" s="6">
         <v>2437</v>
@@ -13820,25 +13822,25 @@
     </row>
     <row r="283" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="1">
-        <v>277</v>
-      </c>
-      <c r="B283" s="11" t="s">
-        <v>525</v>
+        <v>276</v>
+      </c>
+      <c r="B283" s="15" t="s">
+        <v>524</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D283" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E283" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F283" s="7">
-        <v>1568.5</v>
+        <v>1812</v>
       </c>
       <c r="G283" s="7">
-        <v>1567.5</v>
+        <v>3624</v>
       </c>
       <c r="H283" s="6">
         <v>2437</v>
@@ -13859,13 +13861,13 @@
     </row>
     <row r="284" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="1">
-        <v>278</v>
-      </c>
-      <c r="B284" s="15" t="s">
-        <v>526</v>
+        <v>277</v>
+      </c>
+      <c r="B284" s="11" t="s">
+        <v>525</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D284" s="7" t="s">
         <v>17</v>
@@ -13874,10 +13876,10 @@
         <v>1</v>
       </c>
       <c r="F284" s="7">
-        <v>3135</v>
+        <v>1568.5</v>
       </c>
       <c r="G284" s="7">
-        <v>3135</v>
+        <v>1567.5</v>
       </c>
       <c r="H284" s="6">
         <v>2437</v>
@@ -13898,25 +13900,25 @@
     </row>
     <row r="285" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="1">
-        <v>279</v>
-      </c>
-      <c r="B285" s="9" t="s">
-        <v>527</v>
+        <v>278</v>
+      </c>
+      <c r="B285" s="15" t="s">
+        <v>526</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D285" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E285" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F285" s="7">
-        <v>250</v>
+        <v>3135</v>
       </c>
       <c r="G285" s="7">
-        <v>500</v>
+        <v>3135</v>
       </c>
       <c r="H285" s="6">
         <v>2437</v>
@@ -13929,7 +13931,7 @@
         <v>204</v>
       </c>
       <c r="L285" s="7">
-        <v>6242</v>
+        <v>6241</v>
       </c>
       <c r="M285" s="8">
         <v>46359</v>
@@ -13937,23 +13939,25 @@
     </row>
     <row r="286" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="1">
-        <v>280</v>
-      </c>
-      <c r="B286" s="9"/>
+        <v>279</v>
+      </c>
+      <c r="B286" s="9" t="s">
+        <v>527</v>
+      </c>
       <c r="C286" s="7" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="D286" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E286" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F286" s="7">
-        <v>415</v>
+        <v>250</v>
       </c>
       <c r="G286" s="7">
-        <v>415</v>
+        <v>500</v>
       </c>
       <c r="H286" s="6">
         <v>2437</v>
@@ -13974,25 +13978,23 @@
     </row>
     <row r="287" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="1">
-        <v>281</v>
-      </c>
-      <c r="B287" s="15" t="s">
-        <v>529</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="B287" s="9"/>
       <c r="C287" s="7" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="D287" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E287" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F287" s="7">
-        <v>495.33</v>
+        <v>415</v>
       </c>
       <c r="G287" s="7">
-        <v>1485.99</v>
+        <v>415</v>
       </c>
       <c r="H287" s="6">
         <v>2437</v>
@@ -14013,25 +14015,25 @@
     </row>
     <row r="288" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="1">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B288" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D288" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E288" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F288" s="7">
-        <v>8213.7000000000007</v>
+        <v>495.33</v>
       </c>
       <c r="G288" s="7">
-        <v>16427.400000000001</v>
+        <v>1485.99</v>
       </c>
       <c r="H288" s="6">
         <v>2437</v>
@@ -14052,25 +14054,25 @@
     </row>
     <row r="289" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="1">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B289" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D289" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E289" s="6">
-        <v>1</v>
-      </c>
-      <c r="F289" s="10">
-        <v>57200</v>
+        <v>2</v>
+      </c>
+      <c r="F289" s="7">
+        <v>8213.7000000000007</v>
       </c>
       <c r="G289" s="7">
-        <v>57200</v>
+        <v>16427.400000000001</v>
       </c>
       <c r="H289" s="6">
         <v>2437</v>
@@ -14091,13 +14093,13 @@
     </row>
     <row r="290" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="1">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B290" s="15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D290" s="7" t="s">
         <v>17</v>
@@ -14105,11 +14107,11 @@
       <c r="E290" s="6">
         <v>1</v>
       </c>
-      <c r="F290" s="7">
-        <v>565</v>
+      <c r="F290" s="10">
+        <v>57200</v>
       </c>
       <c r="G290" s="7">
-        <v>565</v>
+        <v>57200</v>
       </c>
       <c r="H290" s="6">
         <v>2437</v>
@@ -14130,13 +14132,13 @@
     </row>
     <row r="291" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="1">
-        <v>285</v>
-      </c>
-      <c r="B291" s="11" t="s">
-        <v>533</v>
+        <v>284</v>
+      </c>
+      <c r="B291" s="15" t="s">
+        <v>532</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D291" s="7" t="s">
         <v>17</v>
@@ -14145,10 +14147,10 @@
         <v>1</v>
       </c>
       <c r="F291" s="7">
-        <v>62</v>
+        <v>565</v>
       </c>
       <c r="G291" s="7">
-        <v>62</v>
+        <v>565</v>
       </c>
       <c r="H291" s="6">
         <v>2437</v>
@@ -14169,25 +14171,25 @@
     </row>
     <row r="292" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="1">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D292" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E292" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F292" s="7">
-        <v>2320</v>
+        <v>62</v>
       </c>
       <c r="G292" s="7">
-        <v>9280</v>
+        <v>62</v>
       </c>
       <c r="H292" s="6">
         <v>2437</v>
@@ -14208,25 +14210,25 @@
     </row>
     <row r="293" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D293" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E293" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F293" s="7">
-        <v>4445</v>
+        <v>2320</v>
       </c>
       <c r="G293" s="7">
-        <v>4445</v>
+        <v>9280</v>
       </c>
       <c r="H293" s="6">
         <v>2437</v>
@@ -14247,13 +14249,13 @@
     </row>
     <row r="294" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="1">
-        <v>288</v>
-      </c>
-      <c r="B294" s="9" t="s">
-        <v>528</v>
+        <v>287</v>
+      </c>
+      <c r="B294" s="11" t="s">
+        <v>535</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="D294" s="7" t="s">
         <v>17</v>
@@ -14262,10 +14264,10 @@
         <v>1</v>
       </c>
       <c r="F294" s="7">
-        <v>364</v>
+        <v>4445</v>
       </c>
       <c r="G294" s="7">
-        <v>364</v>
+        <v>4445</v>
       </c>
       <c r="H294" s="6">
         <v>2437</v>
@@ -14286,28 +14288,28 @@
     </row>
     <row r="295" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="1">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B295" s="9" t="s">
-        <v>581</v>
+        <v>528</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>579</v>
+        <v>496</v>
       </c>
       <c r="D295" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E295" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F295" s="7">
-        <v>650</v>
+        <v>364</v>
       </c>
       <c r="G295" s="7">
-        <v>2600</v>
+        <v>364</v>
       </c>
       <c r="H295" s="6">
-        <v>1480</v>
+        <v>2437</v>
       </c>
       <c r="I295" s="8" t="s">
         <v>484</v>
@@ -14317,7 +14319,7 @@
         <v>204</v>
       </c>
       <c r="L295" s="7">
-        <v>6243</v>
+        <v>6242</v>
       </c>
       <c r="M295" s="8">
         <v>46359</v>
@@ -14325,13 +14327,13 @@
     </row>
     <row r="296" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="1">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B296" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D296" s="7" t="s">
         <v>17</v>
@@ -14340,10 +14342,10 @@
         <v>4</v>
       </c>
       <c r="F296" s="7">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="G296" s="7">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="H296" s="6">
         <v>1480</v>
@@ -14364,38 +14366,38 @@
     </row>
     <row r="297" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="1">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B297" s="9" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D297" s="7" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E297" s="6">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="F297" s="7">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="G297" s="7">
-        <v>37500</v>
+        <v>2400</v>
       </c>
       <c r="H297" s="6">
-        <v>809</v>
+        <v>1480</v>
       </c>
       <c r="I297" s="8" t="s">
         <v>484</v>
       </c>
       <c r="J297" s="6"/>
       <c r="K297" s="7" t="s">
-        <v>584</v>
+        <v>204</v>
       </c>
       <c r="L297" s="7">
-        <v>6244</v>
+        <v>6243</v>
       </c>
       <c r="M297" s="8">
         <v>46359</v>
@@ -14403,25 +14405,25 @@
     </row>
     <row r="298" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="1">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B298" s="9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D298" s="7" t="s">
         <v>75</v>
       </c>
       <c r="E298" s="6">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="F298" s="7">
         <v>150</v>
       </c>
       <c r="G298" s="7">
-        <v>33000</v>
+        <v>37500</v>
       </c>
       <c r="H298" s="6">
         <v>809</v>
@@ -14442,38 +14444,38 @@
     </row>
     <row r="299" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="1">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B299" s="9" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D299" s="7" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E299" s="6">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="F299" s="7">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="G299" s="7">
-        <v>1500</v>
+        <v>33000</v>
       </c>
       <c r="H299" s="6">
-        <v>34382</v>
+        <v>809</v>
       </c>
       <c r="I299" s="8" t="s">
         <v>484</v>
       </c>
       <c r="J299" s="6"/>
       <c r="K299" s="7" t="s">
-        <v>760</v>
+        <v>584</v>
       </c>
       <c r="L299" s="7">
-        <v>6245</v>
+        <v>6244</v>
       </c>
       <c r="M299" s="8">
         <v>46359</v>
@@ -14481,13 +14483,13 @@
     </row>
     <row r="300" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="1">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B300" s="9" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D300" s="7" t="s">
         <v>17</v>
@@ -14496,10 +14498,10 @@
         <v>2</v>
       </c>
       <c r="F300" s="7">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="G300" s="7">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="H300" s="6">
         <v>34382</v>
@@ -14520,13 +14522,13 @@
     </row>
     <row r="301" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="1">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B301" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D301" s="7" t="s">
         <v>17</v>
@@ -14559,64 +14561,64 @@
     </row>
     <row r="302" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="1">
-        <v>296</v>
-      </c>
-      <c r="B302" s="11" t="s">
-        <v>597</v>
+        <v>295</v>
+      </c>
+      <c r="B302" s="9" t="s">
+        <v>593</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D302" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E302" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F302" s="7">
-        <v>2630</v>
+        <v>150</v>
       </c>
       <c r="G302" s="7">
-        <v>13150</v>
+        <v>300</v>
       </c>
       <c r="H302" s="6">
-        <v>394</v>
+        <v>34382</v>
       </c>
       <c r="I302" s="8" t="s">
-        <v>596</v>
+        <v>484</v>
       </c>
       <c r="J302" s="6"/>
       <c r="K302" s="7" t="s">
-        <v>297</v>
+        <v>760</v>
       </c>
       <c r="L302" s="7">
-        <v>6246</v>
-      </c>
-      <c r="M302" s="8" t="s">
-        <v>601</v>
+        <v>6245</v>
+      </c>
+      <c r="M302" s="8">
+        <v>46359</v>
       </c>
     </row>
     <row r="303" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="1">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D303" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E303" s="6">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F303" s="7">
-        <v>100</v>
+        <v>2630</v>
       </c>
       <c r="G303" s="7">
-        <v>5029.75</v>
+        <v>13150</v>
       </c>
       <c r="H303" s="6">
         <v>394</v>
@@ -14637,38 +14639,38 @@
     </row>
     <row r="304" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="1">
-        <v>298</v>
-      </c>
-      <c r="B304" s="9" t="s">
-        <v>613</v>
+        <v>297</v>
+      </c>
+      <c r="B304" s="11" t="s">
+        <v>598</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D304" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E304" s="6">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F304" s="7">
-        <v>995</v>
+        <v>100</v>
       </c>
       <c r="G304" s="7">
-        <v>1990</v>
+        <v>5029.75</v>
       </c>
       <c r="H304" s="6">
-        <v>42</v>
+        <v>394</v>
       </c>
       <c r="I304" s="8" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="J304" s="6"/>
       <c r="K304" s="7" t="s">
-        <v>757</v>
+        <v>297</v>
       </c>
       <c r="L304" s="7">
-        <v>6247</v>
+        <v>6246</v>
       </c>
       <c r="M304" s="8" t="s">
         <v>601</v>
@@ -14676,25 +14678,25 @@
     </row>
     <row r="305" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="1">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D305" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E305" s="6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F305" s="7">
-        <v>52.65</v>
+        <v>995</v>
       </c>
       <c r="G305" s="7">
-        <v>789</v>
+        <v>1990</v>
       </c>
       <c r="H305" s="6">
         <v>42</v>
@@ -14715,13 +14717,13 @@
     </row>
     <row r="306" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="1">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D306" s="7" t="s">
         <v>17</v>
@@ -14730,10 +14732,10 @@
         <v>15</v>
       </c>
       <c r="F306" s="7">
-        <v>35.1</v>
+        <v>52.65</v>
       </c>
       <c r="G306" s="7">
-        <v>526</v>
+        <v>789</v>
       </c>
       <c r="H306" s="6">
         <v>42</v>
@@ -14754,13 +14756,13 @@
     </row>
     <row r="307" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="1">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B307" s="9" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D307" s="7" t="s">
         <v>17</v>
@@ -14769,10 +14771,10 @@
         <v>15</v>
       </c>
       <c r="F307" s="7">
-        <v>409.5</v>
+        <v>35.1</v>
       </c>
       <c r="G307" s="7">
-        <v>6142</v>
+        <v>526</v>
       </c>
       <c r="H307" s="6">
         <v>42</v>
@@ -14793,25 +14795,25 @@
     </row>
     <row r="308" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="1">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B308" s="9" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D308" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E308" s="6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F308" s="7">
-        <v>99.54</v>
+        <v>409.5</v>
       </c>
       <c r="G308" s="7">
-        <v>99.54</v>
+        <v>6142</v>
       </c>
       <c r="H308" s="6">
         <v>42</v>
@@ -14832,25 +14834,25 @@
     </row>
     <row r="309" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="1">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B309" s="9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D309" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E309" s="6">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="F309" s="7">
         <v>99.54</v>
       </c>
       <c r="G309" s="7">
-        <v>10740</v>
+        <v>99.54</v>
       </c>
       <c r="H309" s="6">
         <v>42</v>
@@ -14871,25 +14873,25 @@
     </row>
     <row r="310" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="1">
-        <v>304</v>
-      </c>
-      <c r="B310" s="11" t="s">
-        <v>610</v>
+        <v>303</v>
+      </c>
+      <c r="B310" s="9" t="s">
+        <v>611</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D310" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E310" s="6">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="F310" s="7">
-        <v>468</v>
+        <v>99.54</v>
       </c>
       <c r="G310" s="7">
-        <v>2340</v>
+        <v>10740</v>
       </c>
       <c r="H310" s="6">
         <v>42</v>
@@ -14910,25 +14912,25 @@
     </row>
     <row r="311" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="1">
-        <v>305</v>
-      </c>
-      <c r="B311" s="9" t="s">
-        <v>278</v>
+        <v>304</v>
+      </c>
+      <c r="B311" s="11" t="s">
+        <v>610</v>
       </c>
       <c r="C311" s="7" t="s">
-        <v>271</v>
+        <v>607</v>
       </c>
       <c r="D311" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E311" s="6">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F311" s="7">
-        <v>3.51</v>
+        <v>468</v>
       </c>
       <c r="G311" s="7">
-        <v>351</v>
+        <v>2340</v>
       </c>
       <c r="H311" s="6">
         <v>42</v>
@@ -14949,25 +14951,25 @@
     </row>
     <row r="312" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A312" s="1">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B312" s="9" t="s">
-        <v>609</v>
+        <v>278</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>608</v>
+        <v>271</v>
       </c>
       <c r="D312" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E312" s="6">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F312" s="7">
-        <v>1145.31</v>
+        <v>3.51</v>
       </c>
       <c r="G312" s="7">
-        <v>2290.62</v>
+        <v>351</v>
       </c>
       <c r="H312" s="6">
         <v>42</v>
@@ -14988,38 +14990,38 @@
     </row>
     <row r="313" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="1">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B313" s="9" t="s">
-        <v>363</v>
+        <v>609</v>
       </c>
       <c r="C313" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="D313" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="D313" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E313" s="6">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F313" s="7">
-        <v>2675</v>
+        <v>1145.31</v>
       </c>
       <c r="G313" s="7">
-        <v>53500</v>
+        <v>2290.62</v>
       </c>
       <c r="H313" s="6">
-        <v>704</v>
-      </c>
-      <c r="I313" s="8">
-        <v>46237</v>
+        <v>42</v>
+      </c>
+      <c r="I313" s="8" t="s">
+        <v>600</v>
       </c>
       <c r="J313" s="6"/>
       <c r="K313" s="7" t="s">
-        <v>31</v>
+        <v>757</v>
       </c>
       <c r="L313" s="7">
-        <v>6248</v>
+        <v>6247</v>
       </c>
       <c r="M313" s="8" t="s">
         <v>601</v>
@@ -15027,38 +15029,38 @@
     </row>
     <row r="314" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A314" s="1">
-        <v>308</v>
-      </c>
-      <c r="B314" s="16" t="s">
-        <v>618</v>
-      </c>
-      <c r="C314" s="17" t="s">
-        <v>619</v>
+        <v>307</v>
+      </c>
+      <c r="B314" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="D314" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E314" s="6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F314" s="7">
-        <v>3215</v>
+        <v>2675</v>
       </c>
       <c r="G314" s="7">
-        <v>3215</v>
+        <v>53500</v>
       </c>
       <c r="H314" s="6">
-        <v>89598</v>
-      </c>
-      <c r="I314" s="8" t="s">
-        <v>634</v>
+        <v>704</v>
+      </c>
+      <c r="I314" s="8">
+        <v>46237</v>
       </c>
       <c r="J314" s="6"/>
       <c r="K314" s="7" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L314" s="7">
-        <v>6250</v>
+        <v>6248</v>
       </c>
       <c r="M314" s="8" t="s">
         <v>601</v>
@@ -15066,13 +15068,13 @@
     </row>
     <row r="315" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A315" s="1">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B315" s="16" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C315" s="17" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D315" s="6" t="s">
         <v>17</v>
@@ -15081,10 +15083,10 @@
         <v>1</v>
       </c>
       <c r="F315" s="7">
-        <v>346</v>
+        <v>3215</v>
       </c>
       <c r="G315" s="7">
-        <v>346</v>
+        <v>3215</v>
       </c>
       <c r="H315" s="6">
         <v>89598</v>
@@ -15105,13 +15107,13 @@
     </row>
     <row r="316" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="1">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B316" s="16" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C316" s="17" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D316" s="6" t="s">
         <v>17</v>
@@ -15120,10 +15122,10 @@
         <v>1</v>
       </c>
       <c r="F316" s="7">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="G316" s="7">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H316" s="6">
         <v>89598</v>
@@ -15144,25 +15146,25 @@
     </row>
     <row r="317" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="1">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B317" s="16" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C317" s="17" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D317" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E317" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F317" s="7">
-        <v>609</v>
+        <v>354</v>
       </c>
       <c r="G317" s="7">
-        <v>1219</v>
+        <v>354</v>
       </c>
       <c r="H317" s="6">
         <v>89598</v>
@@ -15183,25 +15185,25 @@
     </row>
     <row r="318" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A318" s="1">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B318" s="16" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C318" s="17" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D318" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E318" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F318" s="7">
-        <v>346</v>
+        <v>609</v>
       </c>
       <c r="G318" s="7">
-        <v>346</v>
+        <v>1219</v>
       </c>
       <c r="H318" s="6">
         <v>89598</v>
@@ -15222,13 +15224,13 @@
     </row>
     <row r="319" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A319" s="1">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B319" s="16" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C319" s="17" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D319" s="6" t="s">
         <v>17</v>
@@ -15237,10 +15239,10 @@
         <v>1</v>
       </c>
       <c r="F319" s="7">
-        <v>1105</v>
+        <v>346</v>
       </c>
       <c r="G319" s="7">
-        <v>1105</v>
+        <v>346</v>
       </c>
       <c r="H319" s="6">
         <v>89598</v>
@@ -15261,13 +15263,13 @@
     </row>
     <row r="320" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A320" s="1">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B320" s="16" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C320" s="17" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D320" s="6" t="s">
         <v>17</v>
@@ -15276,10 +15278,10 @@
         <v>1</v>
       </c>
       <c r="F320" s="7">
-        <v>1057</v>
+        <v>1105</v>
       </c>
       <c r="G320" s="7">
-        <v>1057</v>
+        <v>1105</v>
       </c>
       <c r="H320" s="6">
         <v>89598</v>
@@ -15300,13 +15302,13 @@
     </row>
     <row r="321" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A321" s="1">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B321" s="16" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C321" s="17" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D321" s="6" t="s">
         <v>17</v>
@@ -15315,10 +15317,10 @@
         <v>1</v>
       </c>
       <c r="F321" s="7">
-        <v>362</v>
+        <v>1057</v>
       </c>
       <c r="G321" s="7">
-        <v>362</v>
+        <v>1057</v>
       </c>
       <c r="H321" s="6">
         <v>89598</v>
@@ -15339,13 +15341,13 @@
     </row>
     <row r="322" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A322" s="1">
-        <v>316</v>
-      </c>
-      <c r="B322" s="11" t="s">
-        <v>704</v>
-      </c>
-      <c r="C322" s="7" t="s">
-        <v>445</v>
+        <v>315</v>
+      </c>
+      <c r="B322" s="16" t="s">
+        <v>632</v>
+      </c>
+      <c r="C322" s="17" t="s">
+        <v>633</v>
       </c>
       <c r="D322" s="6" t="s">
         <v>17</v>
@@ -15354,23 +15356,23 @@
         <v>1</v>
       </c>
       <c r="F322" s="7">
-        <v>2150</v>
+        <v>362</v>
       </c>
       <c r="G322" s="7">
-        <v>2150</v>
+        <v>362</v>
       </c>
       <c r="H322" s="6">
-        <v>420</v>
+        <v>89598</v>
       </c>
       <c r="I322" s="8" t="s">
-        <v>484</v>
+        <v>634</v>
       </c>
       <c r="J322" s="6"/>
       <c r="K322" s="7" t="s">
-        <v>645</v>
+        <v>20</v>
       </c>
       <c r="L322" s="7">
-        <v>6252</v>
+        <v>6250</v>
       </c>
       <c r="M322" s="8" t="s">
         <v>601</v>
@@ -15378,25 +15380,25 @@
     </row>
     <row r="323" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A323" s="1">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C323" s="7" t="s">
-        <v>635</v>
+        <v>445</v>
       </c>
       <c r="D323" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E323" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F323" s="7">
-        <v>12</v>
+        <v>2150</v>
       </c>
       <c r="G323" s="7">
-        <v>300</v>
+        <v>2150</v>
       </c>
       <c r="H323" s="6">
         <v>420</v>
@@ -15417,25 +15419,25 @@
     </row>
     <row r="324" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A324" s="1">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B324" s="11" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D324" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E324" s="6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F324" s="7">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G324" s="7">
-        <v>1750</v>
+        <v>300</v>
       </c>
       <c r="H324" s="6">
         <v>420</v>
@@ -15456,25 +15458,25 @@
     </row>
     <row r="325" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A325" s="1">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C325" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D325" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E325" s="6">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F325" s="7">
-        <v>1000</v>
+        <v>35</v>
       </c>
       <c r="G325" s="7">
-        <v>5000</v>
+        <v>1750</v>
       </c>
       <c r="H325" s="6">
         <v>420</v>
@@ -15495,25 +15497,25 @@
     </row>
     <row r="326" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A326" s="1">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B326" s="11" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C326" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D326" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E326" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F326" s="7">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="G326" s="7">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="H326" s="6">
         <v>420</v>
@@ -15534,13 +15536,13 @@
     </row>
     <row r="327" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A327" s="1">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C327" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D327" s="6" t="s">
         <v>17</v>
@@ -15549,10 +15551,10 @@
         <v>1</v>
       </c>
       <c r="F327" s="7">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="G327" s="7">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="H327" s="6">
         <v>420</v>
@@ -15573,13 +15575,13 @@
     </row>
     <row r="328" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="1">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C328" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D328" s="6" t="s">
         <v>17</v>
@@ -15588,10 +15590,10 @@
         <v>1</v>
       </c>
       <c r="F328" s="7">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="G328" s="7">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="H328" s="6">
         <v>420</v>
@@ -15612,25 +15614,25 @@
     </row>
     <row r="329" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A329" s="1">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C329" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D329" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E329" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F329" s="7">
-        <v>25</v>
+        <v>1500</v>
       </c>
       <c r="G329" s="7">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="H329" s="6">
         <v>420</v>
@@ -15651,25 +15653,25 @@
     </row>
     <row r="330" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A330" s="1">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C330" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E330" s="6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F330" s="7">
-        <v>2850</v>
+        <v>25</v>
       </c>
       <c r="G330" s="7">
-        <v>2850</v>
+        <v>625</v>
       </c>
       <c r="H330" s="6">
         <v>420</v>
@@ -15690,13 +15692,13 @@
     </row>
     <row r="331" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A331" s="1">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B331" s="11" t="s">
-        <v>298</v>
+        <v>712</v>
       </c>
       <c r="C331" s="7" t="s">
-        <v>444</v>
+        <v>642</v>
       </c>
       <c r="D331" s="6" t="s">
         <v>17</v>
@@ -15705,10 +15707,10 @@
         <v>1</v>
       </c>
       <c r="F331" s="7">
-        <v>1650</v>
+        <v>2850</v>
       </c>
       <c r="G331" s="7">
-        <v>1650</v>
+        <v>2850</v>
       </c>
       <c r="H331" s="6">
         <v>420</v>
@@ -15729,13 +15731,13 @@
     </row>
     <row r="332" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A332" s="1">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>713</v>
+        <v>298</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>643</v>
+        <v>444</v>
       </c>
       <c r="D332" s="6" t="s">
         <v>17</v>
@@ -15744,10 +15746,10 @@
         <v>1</v>
       </c>
       <c r="F332" s="7">
-        <v>1000</v>
+        <v>1650</v>
       </c>
       <c r="G332" s="7">
-        <v>1000</v>
+        <v>1650</v>
       </c>
       <c r="H332" s="6">
         <v>420</v>
@@ -15768,13 +15770,13 @@
     </row>
     <row r="333" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A333" s="1">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C333" s="7" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D333" s="6" t="s">
         <v>17</v>
@@ -15783,10 +15785,10 @@
         <v>1</v>
       </c>
       <c r="F333" s="7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G333" s="7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H333" s="6">
         <v>420</v>
@@ -15807,13 +15809,13 @@
     </row>
     <row r="334" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A334" s="1">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C334" s="7" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D334" s="6" t="s">
         <v>17</v>
@@ -15822,10 +15824,10 @@
         <v>1</v>
       </c>
       <c r="F334" s="7">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="G334" s="7">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="H334" s="6">
         <v>420</v>
@@ -15838,7 +15840,7 @@
         <v>645</v>
       </c>
       <c r="L334" s="7">
-        <v>6253</v>
+        <v>6252</v>
       </c>
       <c r="M334" s="8" t="s">
         <v>601</v>
@@ -15846,13 +15848,13 @@
     </row>
     <row r="335" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A335" s="1">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D335" s="6" t="s">
         <v>17</v>
@@ -15861,10 +15863,10 @@
         <v>1</v>
       </c>
       <c r="F335" s="7">
-        <v>40</v>
+        <v>450</v>
       </c>
       <c r="G335" s="7">
-        <v>40</v>
+        <v>450</v>
       </c>
       <c r="H335" s="6">
         <v>420</v>
@@ -15885,13 +15887,13 @@
     </row>
     <row r="336" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A336" s="1">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>443</v>
+        <v>716</v>
       </c>
       <c r="C336" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D336" s="6" t="s">
         <v>17</v>
@@ -15900,10 +15902,10 @@
         <v>1</v>
       </c>
       <c r="F336" s="7">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="G336" s="7">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="H336" s="6">
         <v>420</v>
@@ -15924,13 +15926,13 @@
     </row>
     <row r="337" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A337" s="1">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B337" s="11" t="s">
-        <v>718</v>
+        <v>443</v>
       </c>
       <c r="C337" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D337" s="6" t="s">
         <v>17</v>
@@ -15939,10 +15941,10 @@
         <v>1</v>
       </c>
       <c r="F337" s="7">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G337" s="7">
-        <v>30000</v>
+        <v>200</v>
       </c>
       <c r="H337" s="6">
         <v>420</v>
@@ -15963,25 +15965,25 @@
     </row>
     <row r="338" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A338" s="1">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B338" s="11" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C338" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D338" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E338" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F338" s="7">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="G338" s="7">
-        <v>30</v>
+        <v>30000</v>
       </c>
       <c r="H338" s="6">
         <v>420</v>
@@ -16002,13 +16004,13 @@
     </row>
     <row r="339" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A339" s="1">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C339" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D339" s="6" t="s">
         <v>17</v>
@@ -16017,10 +16019,10 @@
         <v>2</v>
       </c>
       <c r="F339" s="7">
-        <v>250</v>
+        <v>15</v>
       </c>
       <c r="G339" s="7">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="H339" s="6">
         <v>420</v>
@@ -16041,25 +16043,25 @@
     </row>
     <row r="340" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A340" s="1">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C340" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D340" s="6" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E340" s="6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F340" s="7">
-        <v>385</v>
+        <v>250</v>
       </c>
       <c r="G340" s="7">
-        <v>4235</v>
+        <v>500</v>
       </c>
       <c r="H340" s="6">
         <v>420</v>
@@ -16080,25 +16082,25 @@
     </row>
     <row r="341" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A341" s="1">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C341" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D341" s="6" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E341" s="6">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F341" s="7">
-        <v>30</v>
+        <v>385</v>
       </c>
       <c r="G341" s="7">
-        <v>750</v>
+        <v>4235</v>
       </c>
       <c r="H341" s="6">
         <v>420</v>
@@ -16119,25 +16121,25 @@
     </row>
     <row r="342" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A342" s="1">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C342" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D342" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E342" s="6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F342" s="7">
-        <v>1400</v>
+        <v>30</v>
       </c>
       <c r="G342" s="7">
-        <v>1400</v>
+        <v>750</v>
       </c>
       <c r="H342" s="6">
         <v>420</v>
@@ -16158,13 +16160,13 @@
     </row>
     <row r="343" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A343" s="1">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C343" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D343" s="6" t="s">
         <v>17</v>
@@ -16173,10 +16175,10 @@
         <v>1</v>
       </c>
       <c r="F343" s="7">
-        <v>50</v>
+        <v>1400</v>
       </c>
       <c r="G343" s="7">
-        <v>50</v>
+        <v>1400</v>
       </c>
       <c r="H343" s="6">
         <v>420</v>
@@ -16197,25 +16199,25 @@
     </row>
     <row r="344" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A344" s="1">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C344" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D344" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E344" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F344" s="7">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G344" s="7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H344" s="6">
         <v>420</v>
@@ -16228,7 +16230,7 @@
         <v>645</v>
       </c>
       <c r="L344" s="7">
-        <v>6254</v>
+        <v>6253</v>
       </c>
       <c r="M344" s="8" t="s">
         <v>601</v>
@@ -16236,25 +16238,25 @@
     </row>
     <row r="345" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A345" s="1">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>598</v>
+        <v>724</v>
       </c>
       <c r="C345" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D345" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E345" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F345" s="7">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="G345" s="7">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="H345" s="6">
         <v>420</v>
@@ -16275,25 +16277,25 @@
     </row>
     <row r="346" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A346" s="1">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>725</v>
+        <v>598</v>
       </c>
       <c r="C346" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D346" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E346" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F346" s="7">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="G346" s="7">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="H346" s="6">
         <v>420</v>
@@ -16314,25 +16316,25 @@
     </row>
     <row r="347" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A347" s="1">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C347" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D347" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E347" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F347" s="7">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G347" s="7">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H347" s="6">
         <v>420</v>
@@ -16353,25 +16355,25 @@
     </row>
     <row r="348" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A348" s="1">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C348" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D348" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E348" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F348" s="7">
         <v>15</v>
       </c>
       <c r="G348" s="7">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="H348" s="6">
         <v>420</v>
@@ -16392,25 +16394,25 @@
     </row>
     <row r="349" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A349" s="1">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D349" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E349" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F349" s="7">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G349" s="7">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H349" s="6">
         <v>420</v>
@@ -16431,25 +16433,25 @@
     </row>
     <row r="350" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="1">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C350" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D350" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E350" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F350" s="7">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="G350" s="7">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="H350" s="6">
         <v>420</v>
@@ -16470,13 +16472,13 @@
     </row>
     <row r="351" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A351" s="1">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="C351" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D351" s="6" t="s">
         <v>17</v>
@@ -16485,10 +16487,10 @@
         <v>2</v>
       </c>
       <c r="F351" s="7">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G351" s="7">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H351" s="6">
         <v>420</v>
@@ -16509,25 +16511,25 @@
     </row>
     <row r="352" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="1">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="C352" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D352" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E352" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F352" s="7">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G352" s="7">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="H352" s="6">
         <v>420</v>
@@ -16548,25 +16550,25 @@
     </row>
     <row r="353" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A353" s="1">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B353" s="11" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="C353" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D353" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E353" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F353" s="7">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="G353" s="7">
-        <v>600</v>
+        <v>75</v>
       </c>
       <c r="H353" s="6">
         <v>420</v>
@@ -16587,25 +16589,25 @@
     </row>
     <row r="354" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A354" s="1">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="C354" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D354" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E354" s="6">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F354" s="7">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="G354" s="7">
-        <v>1250</v>
+        <v>600</v>
       </c>
       <c r="H354" s="6">
         <v>420</v>
@@ -16618,7 +16620,7 @@
         <v>645</v>
       </c>
       <c r="L354" s="7">
-        <v>6255</v>
+        <v>6254</v>
       </c>
       <c r="M354" s="8" t="s">
         <v>601</v>
@@ -16626,25 +16628,25 @@
     </row>
     <row r="355" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="1">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B355" s="11" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="C355" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D355" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E355" s="6">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F355" s="7">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G355" s="7">
-        <v>200</v>
+        <v>1250</v>
       </c>
       <c r="H355" s="6">
         <v>420</v>
@@ -16665,25 +16667,25 @@
     </row>
     <row r="356" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="1">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="C356" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D356" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E356" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F356" s="7">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G356" s="7">
-        <v>1250</v>
+        <v>200</v>
       </c>
       <c r="H356" s="6">
         <v>420</v>
@@ -16704,25 +16706,25 @@
     </row>
     <row r="357" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A357" s="1">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B357" s="11" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C357" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D357" s="6" t="s">
-        <v>673</v>
+        <v>17</v>
       </c>
       <c r="E357" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F357" s="7">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="G357" s="7">
-        <v>1800</v>
+        <v>1250</v>
       </c>
       <c r="H357" s="6">
         <v>420</v>
@@ -16743,25 +16745,25 @@
     </row>
     <row r="358" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A358" s="1">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B358" s="11" t="s">
-        <v>705</v>
+        <v>738</v>
       </c>
       <c r="C358" s="7" t="s">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="D358" s="6" t="s">
-        <v>17</v>
+        <v>673</v>
       </c>
       <c r="E358" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F358" s="7">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="G358" s="7">
-        <v>6000</v>
+        <v>1800</v>
       </c>
       <c r="H358" s="6">
         <v>420</v>
@@ -16782,25 +16784,25 @@
     </row>
     <row r="359" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A359" s="1">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B359" s="11" t="s">
-        <v>729</v>
+        <v>705</v>
       </c>
       <c r="C359" s="7" t="s">
-        <v>670</v>
+        <v>637</v>
       </c>
       <c r="D359" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E359" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F359" s="7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G359" s="7">
-        <v>200</v>
+        <v>6000</v>
       </c>
       <c r="H359" s="6">
         <v>420</v>
@@ -16821,25 +16823,25 @@
     </row>
     <row r="360" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A360" s="1">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C360" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D360" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E360" s="6">
+        <v>2</v>
+      </c>
+      <c r="F360" s="7">
         <v>100</v>
       </c>
-      <c r="F360" s="7">
-        <v>10</v>
-      </c>
       <c r="G360" s="7">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="H360" s="6">
         <v>420</v>
@@ -16860,25 +16862,25 @@
     </row>
     <row r="361" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A361" s="1">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B361" s="11" t="s">
-        <v>332</v>
+        <v>731</v>
       </c>
       <c r="C361" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D361" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E361" s="6">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F361" s="7">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G361" s="7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="H361" s="6">
         <v>420</v>
@@ -16899,13 +16901,13 @@
     </row>
     <row r="362" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A362" s="1">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B362" s="11" t="s">
-        <v>739</v>
+        <v>332</v>
       </c>
       <c r="C362" s="7" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D362" s="6" t="s">
         <v>17</v>
@@ -16914,13 +16916,13 @@
         <v>2</v>
       </c>
       <c r="F362" s="7">
-        <v>7200</v>
+        <v>30</v>
       </c>
       <c r="G362" s="7">
-        <v>14400</v>
+        <v>60</v>
       </c>
       <c r="H362" s="6">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I362" s="8" t="s">
         <v>484</v>
@@ -16930,7 +16932,7 @@
         <v>645</v>
       </c>
       <c r="L362" s="7">
-        <v>6256</v>
+        <v>6255</v>
       </c>
       <c r="M362" s="8" t="s">
         <v>601</v>
@@ -16938,25 +16940,25 @@
     </row>
     <row r="363" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="1">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B363" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C363" s="7" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D363" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E363" s="6">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F363" s="7">
-        <v>25</v>
+        <v>7200</v>
       </c>
       <c r="G363" s="7">
-        <v>1250</v>
+        <v>14400</v>
       </c>
       <c r="H363" s="6">
         <v>419</v>
@@ -16977,25 +16979,25 @@
     </row>
     <row r="364" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="1">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B364" s="11" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C364" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D364" s="6" t="s">
-        <v>673</v>
+        <v>17</v>
       </c>
       <c r="E364" s="6">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F364" s="7">
-        <v>600</v>
+        <v>25</v>
       </c>
       <c r="G364" s="7">
-        <v>1800</v>
+        <v>1250</v>
       </c>
       <c r="H364" s="6">
         <v>419</v>
@@ -17016,25 +17018,25 @@
     </row>
     <row r="365" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A365" s="1">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B365" s="11" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C365" s="7" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D365" s="6" t="s">
-        <v>17</v>
+        <v>673</v>
       </c>
       <c r="E365" s="6">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F365" s="7">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="G365" s="7">
-        <v>1250</v>
+        <v>1800</v>
       </c>
       <c r="H365" s="6">
         <v>419</v>
@@ -17055,25 +17057,25 @@
     </row>
     <row r="366" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A366" s="1">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B366" s="11" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C366" s="7" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="D366" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E366" s="6">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F366" s="7">
-        <v>2750</v>
+        <v>25</v>
       </c>
       <c r="G366" s="7">
-        <v>2750</v>
+        <v>1250</v>
       </c>
       <c r="H366" s="6">
         <v>419</v>
@@ -17094,25 +17096,25 @@
     </row>
     <row r="367" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A367" s="1">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>721</v>
+        <v>740</v>
       </c>
       <c r="C367" s="7" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="D367" s="6" t="s">
-        <v>673</v>
+        <v>17</v>
       </c>
       <c r="E367" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F367" s="7">
-        <v>30</v>
+        <v>2750</v>
       </c>
       <c r="G367" s="7">
-        <v>750</v>
+        <v>2750</v>
       </c>
       <c r="H367" s="6">
         <v>419</v>
@@ -17133,25 +17135,25 @@
     </row>
     <row r="368" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A368" s="1">
-        <v>366</v>
-      </c>
-      <c r="B368" s="9" t="s">
-        <v>741</v>
+        <v>365</v>
+      </c>
+      <c r="B368" s="11" t="s">
+        <v>721</v>
       </c>
       <c r="C368" s="7" t="s">
-        <v>676</v>
+        <v>653</v>
       </c>
       <c r="D368" s="6" t="s">
-        <v>17</v>
+        <v>673</v>
       </c>
       <c r="E368" s="6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F368" s="7">
-        <v>2900</v>
+        <v>30</v>
       </c>
       <c r="G368" s="7">
-        <v>2900</v>
+        <v>750</v>
       </c>
       <c r="H368" s="6">
         <v>419</v>
@@ -17172,25 +17174,25 @@
     </row>
     <row r="369" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A369" s="1">
-        <v>367</v>
-      </c>
-      <c r="B369" s="11" t="s">
-        <v>742</v>
+        <v>366</v>
+      </c>
+      <c r="B369" s="9" t="s">
+        <v>741</v>
       </c>
       <c r="C369" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D369" s="6" t="s">
-        <v>673</v>
+        <v>17</v>
       </c>
       <c r="E369" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F369" s="7">
-        <v>385</v>
+        <v>2900</v>
       </c>
       <c r="G369" s="7">
-        <v>4235</v>
+        <v>2900</v>
       </c>
       <c r="H369" s="6">
         <v>419</v>
@@ -17211,25 +17213,25 @@
     </row>
     <row r="370" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A370" s="1">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>706</v>
+        <v>742</v>
       </c>
       <c r="C370" s="7" t="s">
-        <v>635</v>
+        <v>677</v>
       </c>
       <c r="D370" s="6" t="s">
-        <v>17</v>
+        <v>673</v>
       </c>
       <c r="E370" s="6">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F370" s="7">
-        <v>12</v>
+        <v>385</v>
       </c>
       <c r="G370" s="7">
-        <v>300</v>
+        <v>4235</v>
       </c>
       <c r="H370" s="6">
         <v>419</v>
@@ -17250,25 +17252,25 @@
     </row>
     <row r="371" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A371" s="1">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B371" s="11" t="s">
-        <v>722</v>
+        <v>706</v>
       </c>
       <c r="C371" s="7" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
       <c r="D371" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E371" s="6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F371" s="7">
-        <v>1400</v>
+        <v>12</v>
       </c>
       <c r="G371" s="7">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="H371" s="6">
         <v>419</v>
@@ -17289,25 +17291,25 @@
     </row>
     <row r="372" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A372" s="1">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B372" s="11" t="s">
-        <v>707</v>
+        <v>722</v>
       </c>
       <c r="C372" s="7" t="s">
-        <v>678</v>
+        <v>654</v>
       </c>
       <c r="D372" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E372" s="6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F372" s="7">
-        <v>35</v>
+        <v>1400</v>
       </c>
       <c r="G372" s="7">
-        <v>1750</v>
+        <v>1400</v>
       </c>
       <c r="H372" s="6">
         <v>419</v>
@@ -17320,7 +17322,7 @@
         <v>645</v>
       </c>
       <c r="L372" s="7">
-        <v>6257</v>
+        <v>6256</v>
       </c>
       <c r="M372" s="8" t="s">
         <v>601</v>
@@ -17328,25 +17330,25 @@
     </row>
     <row r="373" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A373" s="1">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B373" s="11" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C373" s="7" t="s">
-        <v>637</v>
+        <v>678</v>
       </c>
       <c r="D373" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E373" s="6">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F373" s="7">
-        <v>1000</v>
+        <v>35</v>
       </c>
       <c r="G373" s="7">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="H373" s="6">
         <v>419</v>
@@ -17367,25 +17369,25 @@
     </row>
     <row r="374" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A374" s="1">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B374" s="11" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C374" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D374" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E374" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F374" s="7">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="G374" s="7">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="H374" s="6">
         <v>419</v>
@@ -17406,13 +17408,13 @@
     </row>
     <row r="375" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A375" s="1">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B375" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C375" s="7" t="s">
-        <v>679</v>
+        <v>638</v>
       </c>
       <c r="D375" s="6" t="s">
         <v>17</v>
@@ -17421,10 +17423,10 @@
         <v>1</v>
       </c>
       <c r="F375" s="7">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="G375" s="7">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="H375" s="6">
         <v>419</v>
@@ -17445,13 +17447,13 @@
     </row>
     <row r="376" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A376" s="1">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C376" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D376" s="6" t="s">
         <v>17</v>
@@ -17460,10 +17462,10 @@
         <v>1</v>
       </c>
       <c r="F376" s="7">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="G376" s="7">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="H376" s="6">
         <v>419</v>
@@ -17484,25 +17486,25 @@
     </row>
     <row r="377" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A377" s="1">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B377" s="11" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C377" s="7" t="s">
-        <v>641</v>
+        <v>680</v>
       </c>
       <c r="D377" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E377" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F377" s="7">
-        <v>25</v>
+        <v>1500</v>
       </c>
       <c r="G377" s="7">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="H377" s="6">
         <v>419</v>
@@ -17523,25 +17525,25 @@
     </row>
     <row r="378" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A378" s="1">
-        <v>376</v>
-      </c>
-      <c r="B378" s="9" t="s">
-        <v>740</v>
+        <v>375</v>
+      </c>
+      <c r="B378" s="11" t="s">
+        <v>711</v>
       </c>
       <c r="C378" s="7" t="s">
-        <v>681</v>
+        <v>641</v>
       </c>
       <c r="D378" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E378" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F378" s="7">
-        <v>2750</v>
+        <v>25</v>
       </c>
       <c r="G378" s="7">
-        <v>5500</v>
+        <v>625</v>
       </c>
       <c r="H378" s="6">
         <v>419</v>
@@ -17562,13 +17564,13 @@
     </row>
     <row r="379" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A379" s="1">
-        <v>377</v>
-      </c>
-      <c r="B379" s="11" t="s">
-        <v>743</v>
+        <v>376</v>
+      </c>
+      <c r="B379" s="9" t="s">
+        <v>740</v>
       </c>
       <c r="C379" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D379" s="6" t="s">
         <v>17</v>
@@ -17577,10 +17579,10 @@
         <v>2</v>
       </c>
       <c r="F379" s="7">
-        <v>3750</v>
+        <v>2750</v>
       </c>
       <c r="G379" s="7">
-        <v>7500</v>
+        <v>5500</v>
       </c>
       <c r="H379" s="6">
         <v>419</v>
@@ -17601,25 +17603,25 @@
     </row>
     <row r="380" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A380" s="1">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B380" s="11" t="s">
-        <v>332</v>
+        <v>743</v>
       </c>
       <c r="C380" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D380" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E380" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F380" s="7">
-        <v>30</v>
+        <v>3750</v>
       </c>
       <c r="G380" s="7">
-        <v>90</v>
+        <v>7500</v>
       </c>
       <c r="H380" s="6">
         <v>419</v>
@@ -17640,13 +17642,13 @@
     </row>
     <row r="381" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="1">
-        <v>379</v>
-      </c>
-      <c r="B381" s="9" t="s">
-        <v>728</v>
+        <v>378</v>
+      </c>
+      <c r="B381" s="11" t="s">
+        <v>332</v>
       </c>
       <c r="C381" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D381" s="6" t="s">
         <v>17</v>
@@ -17655,10 +17657,10 @@
         <v>3</v>
       </c>
       <c r="F381" s="7">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G381" s="7">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="H381" s="6">
         <v>419</v>
@@ -17679,25 +17681,25 @@
     </row>
     <row r="382" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A382" s="1">
-        <v>380</v>
-      </c>
-      <c r="B382" s="11" t="s">
-        <v>299</v>
+        <v>379</v>
+      </c>
+      <c r="B382" s="9" t="s">
+        <v>728</v>
       </c>
       <c r="C382" s="7" t="s">
-        <v>445</v>
+        <v>684</v>
       </c>
       <c r="D382" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E382" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F382" s="7">
-        <v>2150</v>
+        <v>100</v>
       </c>
       <c r="G382" s="7">
-        <v>2150</v>
+        <v>300</v>
       </c>
       <c r="H382" s="6">
         <v>419</v>
@@ -17718,25 +17720,25 @@
     </row>
     <row r="383" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A383" s="1">
-        <v>381</v>
-      </c>
-      <c r="B383" s="9" t="s">
-        <v>723</v>
+        <v>380</v>
+      </c>
+      <c r="B383" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="C383" s="7" t="s">
-        <v>655</v>
+        <v>445</v>
       </c>
       <c r="D383" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E383" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F383" s="7">
-        <v>50</v>
+        <v>2150</v>
       </c>
       <c r="G383" s="7">
-        <v>100</v>
+        <v>2150</v>
       </c>
       <c r="H383" s="6">
         <v>419</v>
@@ -17757,25 +17759,25 @@
     </row>
     <row r="384" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A384" s="1">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B384" s="9" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C384" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D384" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E384" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F384" s="7">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G384" s="7">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="H384" s="6">
         <v>419</v>
@@ -17796,25 +17798,25 @@
     </row>
     <row r="385" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="1">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B385" s="9" t="s">
-        <v>598</v>
+        <v>724</v>
       </c>
       <c r="C385" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D385" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E385" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F385" s="7">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="G385" s="7">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="H385" s="6">
         <v>419</v>
@@ -17835,13 +17837,13 @@
     </row>
     <row r="386" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A386" s="1">
-        <v>384</v>
-      </c>
-      <c r="B386" s="11" t="s">
-        <v>744</v>
+        <v>383</v>
+      </c>
+      <c r="B386" s="9" t="s">
+        <v>598</v>
       </c>
       <c r="C386" s="7" t="s">
-        <v>685</v>
+        <v>657</v>
       </c>
       <c r="D386" s="6" t="s">
         <v>17</v>
@@ -17850,10 +17852,10 @@
         <v>1</v>
       </c>
       <c r="F386" s="7">
-        <v>1600</v>
+        <v>150</v>
       </c>
       <c r="G386" s="7">
-        <v>1600</v>
+        <v>150</v>
       </c>
       <c r="H386" s="6">
         <v>419</v>
@@ -17874,13 +17876,13 @@
     </row>
     <row r="387" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A387" s="1">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B387" s="11" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C387" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D387" s="6" t="s">
         <v>17</v>
@@ -17889,10 +17891,10 @@
         <v>1</v>
       </c>
       <c r="F387" s="7">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="G387" s="7">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="H387" s="6">
         <v>419</v>
@@ -17913,13 +17915,13 @@
     </row>
     <row r="388" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A388" s="1">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B388" s="11" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C388" s="7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D388" s="6" t="s">
         <v>17</v>
@@ -17928,10 +17930,10 @@
         <v>1</v>
       </c>
       <c r="F388" s="7">
-        <v>2750</v>
+        <v>1300</v>
       </c>
       <c r="G388" s="7">
-        <v>2750</v>
+        <v>1300</v>
       </c>
       <c r="H388" s="6">
         <v>419</v>
@@ -17952,25 +17954,25 @@
     </row>
     <row r="389" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A389" s="1">
-        <v>387</v>
-      </c>
-      <c r="B389" s="9" t="s">
-        <v>725</v>
+        <v>386</v>
+      </c>
+      <c r="B389" s="11" t="s">
+        <v>746</v>
       </c>
       <c r="C389" s="7" t="s">
-        <v>658</v>
+        <v>687</v>
       </c>
       <c r="D389" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E389" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F389" s="7">
-        <v>45</v>
+        <v>2750</v>
       </c>
       <c r="G389" s="7">
-        <v>90</v>
+        <v>2750</v>
       </c>
       <c r="H389" s="6">
         <v>419</v>
@@ -17991,25 +17993,25 @@
     </row>
     <row r="390" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A390" s="1">
-        <v>388</v>
-      </c>
-      <c r="B390" s="11" t="s">
-        <v>747</v>
+        <v>387</v>
+      </c>
+      <c r="B390" s="9" t="s">
+        <v>725</v>
       </c>
       <c r="C390" s="7" t="s">
-        <v>688</v>
+        <v>658</v>
       </c>
       <c r="D390" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E390" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F390" s="7">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="G390" s="7">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="H390" s="6">
         <v>419</v>
@@ -18030,25 +18032,25 @@
     </row>
     <row r="391" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A391" s="1">
-        <v>389</v>
-      </c>
-      <c r="B391" s="9" t="s">
-        <v>732</v>
+        <v>388</v>
+      </c>
+      <c r="B391" s="11" t="s">
+        <v>747</v>
       </c>
       <c r="C391" s="7" t="s">
-        <v>660</v>
+        <v>688</v>
       </c>
       <c r="D391" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E391" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F391" s="7">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="G391" s="7">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="H391" s="6">
         <v>419</v>
@@ -18069,19 +18071,19 @@
     </row>
     <row r="392" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A392" s="1">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B392" s="9" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="C392" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D392" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E392" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F392" s="7">
         <v>15</v>
@@ -18108,25 +18110,25 @@
     </row>
     <row r="393" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A393" s="1">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B393" s="9" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C393" s="7" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="D393" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E393" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F393" s="7">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="G393" s="7">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="H393" s="6">
         <v>419</v>
@@ -18147,13 +18149,13 @@
     </row>
     <row r="394" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A394" s="1">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B394" s="9" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C394" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D394" s="6" t="s">
         <v>17</v>
@@ -18162,7 +18164,7 @@
         <v>3</v>
       </c>
       <c r="F394" s="7">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G394" s="7">
         <v>300</v>
@@ -18178,7 +18180,7 @@
         <v>645</v>
       </c>
       <c r="L394" s="7">
-        <v>6259</v>
+        <v>6257</v>
       </c>
       <c r="M394" s="8" t="s">
         <v>601</v>
@@ -18186,25 +18188,25 @@
     </row>
     <row r="395" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A395" s="1">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B395" s="9" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C395" s="7" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D395" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E395" s="6">
+        <v>3</v>
+      </c>
+      <c r="F395" s="7">
         <v>100</v>
       </c>
-      <c r="F395" s="7">
-        <v>10</v>
-      </c>
       <c r="G395" s="7">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="H395" s="6">
         <v>419</v>
@@ -18225,25 +18227,25 @@
     </row>
     <row r="396" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A396" s="1">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B396" s="9" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C396" s="7" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="D396" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E396" s="6">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F396" s="7">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G396" s="7">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H396" s="6">
         <v>419</v>
@@ -18264,25 +18266,25 @@
     </row>
     <row r="397" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A397" s="1">
-        <v>395</v>
-      </c>
-      <c r="B397" s="11" t="s">
-        <v>735</v>
+        <v>394</v>
+      </c>
+      <c r="B397" s="9" t="s">
+        <v>734</v>
       </c>
       <c r="C397" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D397" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E397" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F397" s="7">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G397" s="7">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="H397" s="6">
         <v>419</v>
@@ -18303,13 +18305,13 @@
     </row>
     <row r="398" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A398" s="1">
-        <v>396</v>
-      </c>
-      <c r="B398" s="9" t="s">
-        <v>733</v>
+        <v>395</v>
+      </c>
+      <c r="B398" s="11" t="s">
+        <v>735</v>
       </c>
       <c r="C398" s="7" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="D398" s="6" t="s">
         <v>17</v>
@@ -18318,10 +18320,10 @@
         <v>1</v>
       </c>
       <c r="F398" s="7">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G398" s="7">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="H398" s="6">
         <v>419</v>
@@ -18342,38 +18344,38 @@
     </row>
     <row r="399" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A399" s="1">
-        <v>397</v>
-      </c>
-      <c r="B399" s="15" t="s">
-        <v>505</v>
+        <v>396</v>
+      </c>
+      <c r="B399" s="9" t="s">
+        <v>733</v>
       </c>
       <c r="C399" s="7" t="s">
-        <v>471</v>
+        <v>661</v>
       </c>
       <c r="D399" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E399" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F399" s="7">
-        <v>7116</v>
+        <v>40</v>
       </c>
       <c r="G399" s="7">
-        <v>21349</v>
+        <v>40</v>
       </c>
       <c r="H399" s="6">
-        <v>2443</v>
+        <v>419</v>
       </c>
       <c r="I399" s="8" t="s">
-        <v>694</v>
+        <v>484</v>
       </c>
       <c r="J399" s="6"/>
       <c r="K399" s="7" t="s">
-        <v>204</v>
+        <v>645</v>
       </c>
       <c r="L399" s="7">
-        <v>6260</v>
+        <v>6259</v>
       </c>
       <c r="M399" s="8" t="s">
         <v>601</v>
@@ -18381,25 +18383,25 @@
     </row>
     <row r="400" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A400" s="1">
-        <v>398</v>
-      </c>
-      <c r="B400" s="11" t="s">
-        <v>509</v>
+        <v>397</v>
+      </c>
+      <c r="B400" s="15" t="s">
+        <v>505</v>
       </c>
       <c r="C400" s="7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D400" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E400" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F400" s="7">
-        <v>288</v>
+        <v>7116</v>
       </c>
       <c r="G400" s="7">
-        <v>576</v>
+        <v>21349</v>
       </c>
       <c r="H400" s="6">
         <v>2443</v>
@@ -18420,25 +18422,25 @@
     </row>
     <row r="401" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A401" s="1">
-        <v>399</v>
-      </c>
-      <c r="B401" s="9" t="s">
-        <v>280</v>
+        <v>398</v>
+      </c>
+      <c r="B401" s="11" t="s">
+        <v>509</v>
       </c>
       <c r="C401" s="7" t="s">
-        <v>279</v>
+        <v>474</v>
       </c>
       <c r="D401" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E401" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F401" s="7">
-        <v>352</v>
+        <v>288</v>
       </c>
       <c r="G401" s="7">
-        <v>3168</v>
+        <v>576</v>
       </c>
       <c r="H401" s="6">
         <v>2443</v>
@@ -18459,25 +18461,25 @@
     </row>
     <row r="402" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A402" s="1">
-        <v>400</v>
-      </c>
-      <c r="B402" s="11" t="s">
-        <v>515</v>
+        <v>399</v>
+      </c>
+      <c r="B402" s="9" t="s">
+        <v>280</v>
       </c>
       <c r="C402" s="7" t="s">
-        <v>689</v>
+        <v>279</v>
       </c>
       <c r="D402" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E402" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F402" s="7">
-        <v>225</v>
+        <v>352</v>
       </c>
       <c r="G402" s="7">
-        <v>6710</v>
+        <v>3168</v>
       </c>
       <c r="H402" s="6">
         <v>2443</v>
@@ -18498,25 +18500,25 @@
     </row>
     <row r="403" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A403" s="1">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B403" s="11" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C403" s="7" t="s">
-        <v>486</v>
+        <v>689</v>
       </c>
       <c r="D403" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E403" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F403" s="7">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="G403" s="7">
-        <v>489</v>
+        <v>6710</v>
       </c>
       <c r="H403" s="6">
         <v>2443</v>
@@ -18537,25 +18539,25 @@
     </row>
     <row r="404" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A404" s="1">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B404" s="11" t="s">
-        <v>748</v>
+        <v>521</v>
       </c>
       <c r="C404" s="7" t="s">
-        <v>690</v>
+        <v>486</v>
       </c>
       <c r="D404" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E404" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F404" s="7">
-        <v>1793</v>
+        <v>244</v>
       </c>
       <c r="G404" s="7">
-        <v>1793</v>
+        <v>489</v>
       </c>
       <c r="H404" s="6">
         <v>2443</v>
@@ -18576,13 +18578,13 @@
     </row>
     <row r="405" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A405" s="1">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B405" s="11" t="s">
-        <v>533</v>
+        <v>748</v>
       </c>
       <c r="C405" s="7" t="s">
-        <v>501</v>
+        <v>690</v>
       </c>
       <c r="D405" s="6" t="s">
         <v>17</v>
@@ -18591,10 +18593,10 @@
         <v>1</v>
       </c>
       <c r="F405" s="7">
-        <v>1692</v>
+        <v>1793</v>
       </c>
       <c r="G405" s="7">
-        <v>1692</v>
+        <v>1793</v>
       </c>
       <c r="H405" s="6">
         <v>2443</v>
@@ -18615,25 +18617,25 @@
     </row>
     <row r="406" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A406" s="1">
-        <v>404</v>
-      </c>
-      <c r="B406" s="15" t="s">
-        <v>530</v>
+        <v>403</v>
+      </c>
+      <c r="B406" s="11" t="s">
+        <v>533</v>
       </c>
       <c r="C406" s="7" t="s">
-        <v>691</v>
+        <v>501</v>
       </c>
       <c r="D406" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E406" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F406" s="7">
-        <v>9350</v>
+        <v>1692</v>
       </c>
       <c r="G406" s="7">
-        <v>102850</v>
+        <v>1692</v>
       </c>
       <c r="H406" s="6">
         <v>2443</v>
@@ -18654,25 +18656,25 @@
     </row>
     <row r="407" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A407" s="1">
-        <v>405</v>
-      </c>
-      <c r="B407" s="11" t="s">
-        <v>469</v>
+        <v>404</v>
+      </c>
+      <c r="B407" s="15" t="s">
+        <v>530</v>
       </c>
       <c r="C407" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D407" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E407" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F407" s="7">
-        <v>4293</v>
+        <v>9350</v>
       </c>
       <c r="G407" s="7">
-        <v>4293</v>
+        <v>102850</v>
       </c>
       <c r="H407" s="6">
         <v>2443</v>
@@ -18693,25 +18695,25 @@
     </row>
     <row r="408" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="1">
-        <v>406</v>
-      </c>
-      <c r="B408" s="9" t="s">
-        <v>527</v>
+        <v>405</v>
+      </c>
+      <c r="B408" s="11" t="s">
+        <v>469</v>
       </c>
       <c r="C408" s="7" t="s">
-        <v>495</v>
+        <v>692</v>
       </c>
       <c r="D408" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E408" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F408" s="7">
-        <v>250</v>
+        <v>4293</v>
       </c>
       <c r="G408" s="7">
-        <v>3009</v>
+        <v>4293</v>
       </c>
       <c r="H408" s="6">
         <v>2443</v>
@@ -18732,25 +18734,25 @@
     </row>
     <row r="409" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A409" s="1">
-        <v>407</v>
-      </c>
-      <c r="B409" s="15" t="s">
-        <v>749</v>
+        <v>406</v>
+      </c>
+      <c r="B409" s="9" t="s">
+        <v>527</v>
       </c>
       <c r="C409" s="7" t="s">
-        <v>693</v>
+        <v>495</v>
       </c>
       <c r="D409" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E409" s="6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F409" s="7">
-        <v>5956</v>
+        <v>250</v>
       </c>
       <c r="G409" s="7">
-        <v>5956</v>
+        <v>3009</v>
       </c>
       <c r="H409" s="6">
         <v>2443</v>
@@ -18771,25 +18773,25 @@
     </row>
     <row r="410" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A410" s="1">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B410" s="15" t="s">
-        <v>529</v>
+        <v>749</v>
       </c>
       <c r="C410" s="7" t="s">
-        <v>497</v>
+        <v>693</v>
       </c>
       <c r="D410" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E410" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F410" s="7">
-        <v>495</v>
+        <v>5956</v>
       </c>
       <c r="G410" s="7">
-        <v>5943</v>
+        <v>5956</v>
       </c>
       <c r="H410" s="6">
         <v>2443</v>
@@ -18810,25 +18812,25 @@
     </row>
     <row r="411" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A411" s="1">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B411" s="15" t="s">
-        <v>751</v>
+        <v>529</v>
       </c>
       <c r="C411" s="7" t="s">
-        <v>695</v>
+        <v>497</v>
       </c>
       <c r="D411" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E411" s="6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F411" s="7">
-        <v>1366</v>
+        <v>495</v>
       </c>
       <c r="G411" s="7">
-        <v>10934</v>
+        <v>5943</v>
       </c>
       <c r="H411" s="6">
         <v>2443</v>
@@ -18841,7 +18843,7 @@
         <v>204</v>
       </c>
       <c r="L411" s="7">
-        <v>6261</v>
+        <v>6260</v>
       </c>
       <c r="M411" s="8" t="s">
         <v>601</v>
@@ -18849,25 +18851,25 @@
     </row>
     <row r="412" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A412" s="1">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B412" s="15" t="s">
-        <v>524</v>
+        <v>751</v>
       </c>
       <c r="C412" s="7" t="s">
-        <v>492</v>
+        <v>695</v>
       </c>
       <c r="D412" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E412" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F412" s="7">
-        <v>1775</v>
+        <v>1366</v>
       </c>
       <c r="G412" s="7">
-        <v>5325</v>
+        <v>10934</v>
       </c>
       <c r="H412" s="6">
         <v>2443</v>
@@ -18888,25 +18890,25 @@
     </row>
     <row r="413" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A413" s="1">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B413" s="15" t="s">
-        <v>750</v>
+        <v>524</v>
       </c>
       <c r="C413" s="7" t="s">
-        <v>696</v>
+        <v>492</v>
       </c>
       <c r="D413" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E413" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F413" s="7">
-        <v>5956</v>
+        <v>1775</v>
       </c>
       <c r="G413" s="7">
-        <v>47652</v>
+        <v>5325</v>
       </c>
       <c r="H413" s="6">
         <v>2443</v>
@@ -18927,25 +18929,25 @@
     </row>
     <row r="414" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A414" s="1">
-        <v>412</v>
-      </c>
-      <c r="B414" s="11" t="s">
-        <v>470</v>
+        <v>411</v>
+      </c>
+      <c r="B414" s="15" t="s">
+        <v>750</v>
       </c>
       <c r="C414" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D414" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E414" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F414" s="7">
-        <v>7210</v>
+        <v>5956</v>
       </c>
       <c r="G414" s="7">
-        <v>7210</v>
+        <v>47652</v>
       </c>
       <c r="H414" s="6">
         <v>2443</v>
@@ -18966,64 +18968,64 @@
     </row>
     <row r="415" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A415" s="1">
-        <v>413</v>
-      </c>
-      <c r="B415" s="9" t="s">
-        <v>756</v>
+        <v>412</v>
+      </c>
+      <c r="B415" s="11" t="s">
+        <v>470</v>
       </c>
       <c r="C415" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D415" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E415" s="6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F415" s="7">
-        <v>833</v>
+        <v>7210</v>
       </c>
       <c r="G415" s="7">
-        <v>41666</v>
+        <v>7210</v>
       </c>
       <c r="H415" s="6">
-        <v>26</v>
+        <v>2443</v>
       </c>
       <c r="I415" s="8" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="J415" s="6"/>
       <c r="K415" s="7" t="s">
-        <v>758</v>
+        <v>204</v>
       </c>
       <c r="L415" s="7">
-        <v>6263</v>
+        <v>6261</v>
       </c>
       <c r="M415" s="8" t="s">
-        <v>703</v>
+        <v>601</v>
       </c>
     </row>
     <row r="416" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A416" s="1">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B416" s="9" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C416" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D416" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E416" s="6">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F416" s="7">
-        <v>96</v>
+        <v>833</v>
       </c>
       <c r="G416" s="7">
-        <v>963</v>
+        <v>41666</v>
       </c>
       <c r="H416" s="6">
         <v>26</v>
@@ -19044,25 +19046,25 @@
     </row>
     <row r="417" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A417" s="1">
-        <v>416</v>
-      </c>
-      <c r="B417" s="11" t="s">
-        <v>752</v>
+        <v>414</v>
+      </c>
+      <c r="B417" s="9" t="s">
+        <v>755</v>
       </c>
       <c r="C417" s="7" t="s">
-        <v>480</v>
+        <v>699</v>
       </c>
       <c r="D417" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E417" s="6">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F417" s="7">
-        <v>8333</v>
+        <v>96</v>
       </c>
       <c r="G417" s="7">
-        <v>49999</v>
+        <v>963</v>
       </c>
       <c r="H417" s="6">
         <v>26</v>
@@ -19083,25 +19085,25 @@
     </row>
     <row r="418" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A418" s="1">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B418" s="11" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C418" s="7" t="s">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="D418" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E418" s="6">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F418" s="7">
-        <v>2324</v>
+        <v>8333</v>
       </c>
       <c r="G418" s="7">
-        <v>58114</v>
+        <v>49999</v>
       </c>
       <c r="H418" s="6">
         <v>26</v>
@@ -19122,25 +19124,25 @@
     </row>
     <row r="419" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A419" s="1">
-        <v>418</v>
-      </c>
-      <c r="B419" s="9" t="s">
-        <v>754</v>
+        <v>417</v>
+      </c>
+      <c r="B419" s="11" t="s">
+        <v>753</v>
       </c>
       <c r="C419" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D419" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E419" s="6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F419" s="7">
-        <v>289</v>
+        <v>2324</v>
       </c>
       <c r="G419" s="7">
-        <v>14473</v>
+        <v>58114</v>
       </c>
       <c r="H419" s="6">
         <v>26</v>
@@ -19159,7 +19161,46 @@
         <v>703</v>
       </c>
     </row>
-    <row r="420" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A420" s="1">
+        <v>418</v>
+      </c>
+      <c r="B420" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="C420" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="D420" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E420" s="6">
+        <v>50</v>
+      </c>
+      <c r="F420" s="7">
+        <v>289</v>
+      </c>
+      <c r="G420" s="7">
+        <v>14473</v>
+      </c>
+      <c r="H420" s="6">
+        <v>26</v>
+      </c>
+      <c r="I420" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="J420" s="6"/>
+      <c r="K420" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="L420" s="7">
+        <v>6263</v>
+      </c>
+      <c r="M420" s="8" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="421" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -19167,8 +19208,8 @@
   <pageSetup paperSize="9" scale="25" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="72" max="12" man="1"/>
-    <brk id="249" max="12" man="1"/>
-    <brk id="373" max="12" man="1"/>
+    <brk id="250" max="12" man="1"/>
+    <brk id="374" max="12" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>